--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -521,7 +521,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 28 Jul 2026 03:03</t>
+          <t>Generated 28 Jul 2026 03:11</t>
         </is>
       </c>
     </row>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Daily picks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Price history" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Price history" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Coverage" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +522,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 28 Jul 2026 03:11</t>
+          <t>Generated 28 Jul 2026 03:38</t>
         </is>
       </c>
     </row>
@@ -758,13 +759,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>obs_date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -774,34 +775,69 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>entry_close</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>ret_1d_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ret_5d_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ret_10d_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ret_15d_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ret_20d_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>max_gain_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>sessions_tracked</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -810,802 +846,112 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1188.4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1207.9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1158</v>
+        <v>100</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>1201.8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3482939</v>
+        <v>1214.9</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1225</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1318.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1225</v>
+        <v>96</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>1296.4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17106822</v>
+        <v>192.54</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1325</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1345</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1251.5</v>
+        <v>92</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>1267.1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10436460</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1270</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1285</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1246.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1282.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4135957</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1282.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1296.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5275779</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1302.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1315.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1257.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1288.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3844546</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1290</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1312</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1262</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1268.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2691508</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1268.2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1233.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2619436</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1224.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1224.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1188.1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1208.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3613338</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1214.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1233.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1196.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1214.9</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1911132</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>211.95</v>
-      </c>
-      <c r="D12" t="n">
-        <v>214.55</v>
-      </c>
-      <c r="E12" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>212.78</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12863408</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>214.3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>223.41</v>
-      </c>
-      <c r="E13" t="n">
-        <v>214.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>223.08</v>
-      </c>
-      <c r="G13" t="n">
-        <v>32151413</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>226</v>
-      </c>
-      <c r="D14" t="n">
-        <v>229.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>221.18</v>
-      </c>
-      <c r="F14" t="n">
-        <v>224.38</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14379534</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>217.24</v>
-      </c>
-      <c r="D15" t="n">
-        <v>219.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>213.17</v>
-      </c>
-      <c r="F15" t="n">
-        <v>213.17</v>
-      </c>
-      <c r="G15" t="n">
-        <v>14642282</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>208.25</v>
-      </c>
-      <c r="D16" t="n">
-        <v>213.7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>203.16</v>
-      </c>
-      <c r="F16" t="n">
-        <v>208.03</v>
-      </c>
-      <c r="G16" t="n">
-        <v>18348510</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>209</v>
-      </c>
-      <c r="D17" t="n">
-        <v>218.43</v>
-      </c>
-      <c r="E17" t="n">
-        <v>209</v>
-      </c>
-      <c r="F17" t="n">
-        <v>217.97</v>
-      </c>
-      <c r="G17" t="n">
-        <v>20144780</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>222</v>
-      </c>
-      <c r="D18" t="n">
-        <v>228</v>
-      </c>
-      <c r="E18" t="n">
-        <v>214.11</v>
-      </c>
-      <c r="F18" t="n">
-        <v>217.9</v>
-      </c>
-      <c r="G18" t="n">
-        <v>55935312</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>221.96</v>
-      </c>
-      <c r="D19" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>207.01</v>
-      </c>
-      <c r="F19" t="n">
-        <v>207.01</v>
-      </c>
-      <c r="G19" t="n">
-        <v>29190459</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>202</v>
-      </c>
-      <c r="D20" t="n">
-        <v>204.78</v>
-      </c>
-      <c r="E20" t="n">
-        <v>196.66</v>
-      </c>
-      <c r="F20" t="n">
-        <v>196.85</v>
-      </c>
-      <c r="G20" t="n">
-        <v>31552378</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>200</v>
-      </c>
-      <c r="D21" t="n">
-        <v>200.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>191.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>192.54</v>
-      </c>
-      <c r="G21" t="n">
-        <v>26152896</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4389.8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4485</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4361.9</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4398.1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1347378</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4422</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4495</v>
-      </c>
-      <c r="E23" t="n">
-        <v>4358</v>
-      </c>
-      <c r="F23" t="n">
-        <v>4371.4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>902264</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4387.7</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4404</v>
-      </c>
-      <c r="E24" t="n">
-        <v>4281.9</v>
-      </c>
-      <c r="F24" t="n">
-        <v>4304.2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>463349</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4285</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4317</v>
-      </c>
-      <c r="E25" t="n">
-        <v>4220</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4244.3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>398348</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4211</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4220</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4129.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4178.1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>470046</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4190</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4324.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4190</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4257.3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>633457</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4290</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4383</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4266</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4288.7</v>
-      </c>
-      <c r="G28" t="n">
-        <v>835107</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4299</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4340</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4216</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4243.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>422024</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4201.9</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4222</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4115</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4156</v>
-      </c>
-      <c r="G30" t="n">
-        <v>378694</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4181.8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4385</v>
-      </c>
-      <c r="E31" t="n">
-        <v>4129.4</v>
-      </c>
-      <c r="F31" t="n">
         <v>4362.2</v>
       </c>
-      <c r="G31" t="n">
-        <v>992864</v>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1619,6 +965,948 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1188.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1207.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1201.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3482939</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1225</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1318.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1225</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1296.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17106822</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1345</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1251.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1267.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10436460</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1282.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4135957</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1282.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1333.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1272.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5275779</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1302.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1315.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1257.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3844546</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1268.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2691508</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1268.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1271.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1221.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1233.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2619436</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1224.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1224.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1188.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1208.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3613338</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1233.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1196.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1911132</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1213</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1911152</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>211.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>214.55</v>
+      </c>
+      <c r="E13" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>212.78</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12863408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>223.41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>223.08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>32151413</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>226</v>
+      </c>
+      <c r="D15" t="n">
+        <v>229.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>221.18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>224.38</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14379534</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>217.24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>219.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>213.17</v>
+      </c>
+      <c r="F16" t="n">
+        <v>213.17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14642282</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>208.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>203.16</v>
+      </c>
+      <c r="F17" t="n">
+        <v>208.03</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18348510</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>209</v>
+      </c>
+      <c r="D18" t="n">
+        <v>218.43</v>
+      </c>
+      <c r="E18" t="n">
+        <v>209</v>
+      </c>
+      <c r="F18" t="n">
+        <v>217.97</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20144780</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>222</v>
+      </c>
+      <c r="D19" t="n">
+        <v>228</v>
+      </c>
+      <c r="E19" t="n">
+        <v>214.11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55935312</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>221.96</v>
+      </c>
+      <c r="D20" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>207.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>207.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29190459</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>202</v>
+      </c>
+      <c r="D21" t="n">
+        <v>204.78</v>
+      </c>
+      <c r="E21" t="n">
+        <v>196.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>196.85</v>
+      </c>
+      <c r="G21" t="n">
+        <v>31552378</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>200</v>
+      </c>
+      <c r="D22" t="n">
+        <v>200.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>192.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>26152896</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>187</v>
+      </c>
+      <c r="D23" t="n">
+        <v>187</v>
+      </c>
+      <c r="E23" t="n">
+        <v>187</v>
+      </c>
+      <c r="F23" t="n">
+        <v>192.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>26152899</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4389.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4485</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4361.9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4398.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1347378</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4422</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4495</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4358</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4371.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>902264</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4387.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4404</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4281.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4304.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>463349</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4285</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4317</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4220</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4244.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>398348</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4211</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4220</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4129.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4178.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>470046</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4324.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4257.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>633457</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4290</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4383</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4266</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4288.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>835107</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4299</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4340</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4216</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4243.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>422024</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4201.9</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4222</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4115</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4156</v>
+      </c>
+      <c r="G32" t="n">
+        <v>378694</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4181.8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4385</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4129.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4362.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>992864</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4380</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4380</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4380</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4362.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>992865</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 30 Jul 2026 06:07</t>
+          <t>Generated 01 Aug 2026 05:34</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="F2" t="n">
         <v>3.67</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.65</v>
+        <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,6 +1211,192 @@
         <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>142.98</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4524</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4135.84</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4912.16</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5300.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>388.16</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1645.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1536.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1754</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1862.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>98</v>
+      </c>
+      <c r="F13" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1251.99</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1481.61</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1596.42</v>
+      </c>
+      <c r="M13" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -1227,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,6 +1698,105 @@
       </c>
       <c r="I10" t="n">
         <v>1966.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4524</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4135.84</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>388.16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4912.16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5300.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1645.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1536.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1754</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1862.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1251.99</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1481.61</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1596.42</v>
       </c>
     </row>
   </sheetData>
@@ -1643,21 +1928,23 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1437.7</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>1377.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.8</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.16</v>
+        <v>6.55</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.12</v>
+        <v>-1.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>1318.08</v>
@@ -1695,21 +1982,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1663.3</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>1659</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.28</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>-1.82</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>1555.52</v>
@@ -1747,21 +2036,23 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1786.9</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>1781.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.96</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>2.54</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1697.2</v>
@@ -1802,7 +2093,7 @@
         <v>193.56</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.65</v>
+        <v>-4.58</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -1848,20 +2139,20 @@
         <v>4364.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.75</v>
+        <v>-3.87</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>4.12</v>
+        <v>5.36</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8</v>
+        <v>-4.32</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1894,20 +2185,20 @@
         <v>1781.3</v>
       </c>
       <c r="G7" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.99</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
         <v>-1.52</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1947,13 +2238,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>5.32</v>
+        <v>6.04</v>
       </c>
       <c r="M8" t="n">
         <v>-0.91</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2039,13 +2330,13 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5</v>
+        <v>-5.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -2063,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,49 +2652,49 @@
         <v>1667.8</v>
       </c>
       <c r="D11" t="n">
-        <v>1667.9</v>
+        <v>1674.7</v>
       </c>
       <c r="E11" t="n">
         <v>1633</v>
       </c>
       <c r="F11" t="n">
-        <v>1663.3</v>
+        <v>1659</v>
       </c>
       <c r="G11" t="n">
-        <v>610887</v>
+        <v>1361733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1188.4</v>
+        <v>1666</v>
       </c>
       <c r="D12" t="n">
-        <v>1207.9</v>
+        <v>1682</v>
       </c>
       <c r="E12" t="n">
-        <v>1158</v>
+        <v>1628.8</v>
       </c>
       <c r="F12" t="n">
-        <v>1201.8</v>
+        <v>1645.4</v>
       </c>
       <c r="G12" t="n">
-        <v>3482939</v>
+        <v>1779312</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2412,25 +2703,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F13" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G13" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2439,25 +2730,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D14" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F14" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G14" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2466,25 +2757,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D15" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E15" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2493,25 +2784,25 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F16" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D16" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G16" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2520,25 +2811,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E17" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F17" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G17" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2547,25 +2838,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D18" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E18" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2574,25 +2865,25 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F19" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D19" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G19" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2601,25 +2892,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2628,25 +2919,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D21" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E21" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F21" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G21" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2655,25 +2946,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D22" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F22" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G22" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2682,25 +2973,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D23" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E23" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F23" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G23" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2709,79 +3000,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E24" t="n">
-        <v>1240.6</v>
+        <v>1191.1</v>
       </c>
       <c r="F24" t="n">
-        <v>1254.5</v>
+        <v>1246.1</v>
       </c>
       <c r="G24" t="n">
-        <v>1474348</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>211.95</v>
+        <v>1253</v>
       </c>
       <c r="D25" t="n">
-        <v>214.55</v>
+        <v>1265.9</v>
       </c>
       <c r="E25" t="n">
-        <v>206.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F25" t="n">
-        <v>212.78</v>
+        <v>1240.9</v>
       </c>
       <c r="G25" t="n">
-        <v>12863408</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>214.3</v>
+        <v>1247</v>
       </c>
       <c r="D26" t="n">
-        <v>223.41</v>
+        <v>1274.6</v>
       </c>
       <c r="E26" t="n">
-        <v>214.3</v>
+        <v>1232.1</v>
       </c>
       <c r="F26" t="n">
-        <v>223.08</v>
+        <v>1260.3</v>
       </c>
       <c r="G26" t="n">
-        <v>32151413</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2790,25 +3081,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D27" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E27" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F27" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G27" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2817,25 +3108,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D28" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E28" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F28" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G28" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2844,25 +3135,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D29" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E29" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F29" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G29" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2871,25 +3162,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D30" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E30" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F30" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G30" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2898,25 +3189,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D31" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E31" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F31" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G31" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2925,25 +3216,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D32" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E32" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F32" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G32" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2952,25 +3243,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D33" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E33" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F33" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G33" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2979,25 +3270,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D34" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E34" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F34" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G34" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3006,25 +3297,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D35" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E35" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F35" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G35" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3033,25 +3324,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D36" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E36" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F36" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G36" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3060,79 +3351,79 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D37" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E37" t="n">
-        <v>184.98</v>
+        <v>182.92</v>
       </c>
       <c r="F37" t="n">
-        <v>186.5</v>
+        <v>188.39</v>
       </c>
       <c r="G37" t="n">
-        <v>11153694</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1554.3</v>
+        <v>189</v>
       </c>
       <c r="D38" t="n">
-        <v>1569</v>
+        <v>195.5</v>
       </c>
       <c r="E38" t="n">
-        <v>1551.3</v>
+        <v>181.05</v>
       </c>
       <c r="F38" t="n">
-        <v>1557.6</v>
+        <v>193.56</v>
       </c>
       <c r="G38" t="n">
-        <v>1001677</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1560.4</v>
+        <v>193</v>
       </c>
       <c r="D39" t="n">
-        <v>1561</v>
+        <v>195.53</v>
       </c>
       <c r="E39" t="n">
-        <v>1520.4</v>
+        <v>183.9</v>
       </c>
       <c r="F39" t="n">
-        <v>1529.8</v>
+        <v>184.69</v>
       </c>
       <c r="G39" t="n">
-        <v>1011017</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3141,25 +3432,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1534.9</v>
+        <v>1554.3</v>
       </c>
       <c r="D40" t="n">
-        <v>1572.2</v>
+        <v>1569</v>
       </c>
       <c r="E40" t="n">
-        <v>1527.2</v>
+        <v>1551.3</v>
       </c>
       <c r="F40" t="n">
-        <v>1558.9</v>
+        <v>1557.6</v>
       </c>
       <c r="G40" t="n">
-        <v>1235837</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3168,25 +3459,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1559.7</v>
+        <v>1560.4</v>
       </c>
       <c r="D41" t="n">
-        <v>1600.1</v>
+        <v>1561</v>
       </c>
       <c r="E41" t="n">
-        <v>1557</v>
+        <v>1520.4</v>
       </c>
       <c r="F41" t="n">
-        <v>1593.2</v>
+        <v>1529.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1871739</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3195,25 +3486,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1591</v>
+        <v>1534.9</v>
       </c>
       <c r="D42" t="n">
-        <v>1593.2</v>
+        <v>1572.2</v>
       </c>
       <c r="E42" t="n">
-        <v>1566</v>
+        <v>1527.2</v>
       </c>
       <c r="F42" t="n">
-        <v>1577.8</v>
+        <v>1558.9</v>
       </c>
       <c r="G42" t="n">
-        <v>1183077</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3222,25 +3513,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1577.7</v>
+        <v>1559.7</v>
       </c>
       <c r="D43" t="n">
-        <v>1586.1</v>
+        <v>1600.1</v>
       </c>
       <c r="E43" t="n">
-        <v>1561.1</v>
+        <v>1557</v>
       </c>
       <c r="F43" t="n">
-        <v>1568.3</v>
+        <v>1593.2</v>
       </c>
       <c r="G43" t="n">
-        <v>1098268</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3249,25 +3540,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1560</v>
+        <v>1591</v>
       </c>
       <c r="D44" t="n">
-        <v>1610</v>
+        <v>1593.2</v>
       </c>
       <c r="E44" t="n">
-        <v>1554.9</v>
+        <v>1566</v>
       </c>
       <c r="F44" t="n">
-        <v>1601.2</v>
+        <v>1577.8</v>
       </c>
       <c r="G44" t="n">
-        <v>2647403</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3276,25 +3567,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1624.8</v>
+        <v>1577.7</v>
       </c>
       <c r="D45" t="n">
-        <v>1734.5</v>
+        <v>1586.1</v>
       </c>
       <c r="E45" t="n">
-        <v>1617.1</v>
+        <v>1561.1</v>
       </c>
       <c r="F45" t="n">
-        <v>1713.4</v>
+        <v>1568.3</v>
       </c>
       <c r="G45" t="n">
-        <v>7989771</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3303,25 +3594,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1713</v>
+        <v>1560</v>
       </c>
       <c r="D46" t="n">
-        <v>1762</v>
+        <v>1610</v>
       </c>
       <c r="E46" t="n">
-        <v>1707.7</v>
+        <v>1554.9</v>
       </c>
       <c r="F46" t="n">
-        <v>1758.9</v>
+        <v>1601.2</v>
       </c>
       <c r="G46" t="n">
-        <v>4407907</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3330,25 +3621,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1762</v>
+        <v>1624.8</v>
       </c>
       <c r="D47" t="n">
-        <v>1797.9</v>
+        <v>1734.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1754.3</v>
+        <v>1617.1</v>
       </c>
       <c r="F47" t="n">
-        <v>1781.3</v>
+        <v>1713.4</v>
       </c>
       <c r="G47" t="n">
-        <v>3000811</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3357,106 +3648,106 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1785</v>
+        <v>1713</v>
       </c>
       <c r="D48" t="n">
-        <v>1798.9</v>
+        <v>1762</v>
       </c>
       <c r="E48" t="n">
-        <v>1774.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F48" t="n">
-        <v>1786.9</v>
+        <v>1758.9</v>
       </c>
       <c r="G48" t="n">
-        <v>1383949</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4389.8</v>
+        <v>1762</v>
       </c>
       <c r="D49" t="n">
-        <v>4485</v>
+        <v>1797.9</v>
       </c>
       <c r="E49" t="n">
-        <v>4361.9</v>
+        <v>1754.3</v>
       </c>
       <c r="F49" t="n">
-        <v>4398.1</v>
+        <v>1781.3</v>
       </c>
       <c r="G49" t="n">
-        <v>1347378</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4422</v>
+        <v>1785</v>
       </c>
       <c r="D50" t="n">
-        <v>4495</v>
+        <v>1798.9</v>
       </c>
       <c r="E50" t="n">
-        <v>4358</v>
+        <v>1773.3</v>
       </c>
       <c r="F50" t="n">
-        <v>4371.4</v>
+        <v>1781.3</v>
       </c>
       <c r="G50" t="n">
-        <v>902264</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4387.7</v>
+        <v>1785</v>
       </c>
       <c r="D51" t="n">
-        <v>4404</v>
+        <v>1826.6</v>
       </c>
       <c r="E51" t="n">
-        <v>4281.9</v>
+        <v>1785</v>
       </c>
       <c r="F51" t="n">
-        <v>4304.2</v>
+        <v>1816.2</v>
       </c>
       <c r="G51" t="n">
-        <v>463349</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3465,25 +3756,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4285</v>
+        <v>4389.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4317</v>
+        <v>4485</v>
       </c>
       <c r="E52" t="n">
-        <v>4220</v>
+        <v>4361.9</v>
       </c>
       <c r="F52" t="n">
-        <v>4244.3</v>
+        <v>4398.1</v>
       </c>
       <c r="G52" t="n">
-        <v>398348</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3492,25 +3783,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4211</v>
+        <v>4422</v>
       </c>
       <c r="D53" t="n">
-        <v>4220</v>
+        <v>4495</v>
       </c>
       <c r="E53" t="n">
-        <v>4129.3</v>
+        <v>4358</v>
       </c>
       <c r="F53" t="n">
-        <v>4178.1</v>
+        <v>4371.4</v>
       </c>
       <c r="G53" t="n">
-        <v>470046</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3519,25 +3810,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4190</v>
+        <v>4387.7</v>
       </c>
       <c r="D54" t="n">
-        <v>4324.4</v>
+        <v>4404</v>
       </c>
       <c r="E54" t="n">
-        <v>4190</v>
+        <v>4281.9</v>
       </c>
       <c r="F54" t="n">
-        <v>4257.3</v>
+        <v>4304.2</v>
       </c>
       <c r="G54" t="n">
-        <v>633457</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3546,25 +3837,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="D55" t="n">
-        <v>4383</v>
+        <v>4317</v>
       </c>
       <c r="E55" t="n">
-        <v>4266</v>
+        <v>4220</v>
       </c>
       <c r="F55" t="n">
-        <v>4288.7</v>
+        <v>4244.3</v>
       </c>
       <c r="G55" t="n">
-        <v>835107</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3573,25 +3864,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4299</v>
+        <v>4211</v>
       </c>
       <c r="D56" t="n">
-        <v>4340</v>
+        <v>4220</v>
       </c>
       <c r="E56" t="n">
-        <v>4216</v>
+        <v>4129.3</v>
       </c>
       <c r="F56" t="n">
-        <v>4243.8</v>
+        <v>4178.1</v>
       </c>
       <c r="G56" t="n">
-        <v>422024</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3600,25 +3891,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4201.9</v>
+        <v>4190</v>
       </c>
       <c r="D57" t="n">
-        <v>4222</v>
+        <v>4324.4</v>
       </c>
       <c r="E57" t="n">
-        <v>4115</v>
+        <v>4190</v>
       </c>
       <c r="F57" t="n">
-        <v>4156</v>
+        <v>4257.3</v>
       </c>
       <c r="G57" t="n">
-        <v>378694</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3627,25 +3918,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4181.8</v>
+        <v>4290</v>
       </c>
       <c r="D58" t="n">
-        <v>4385</v>
+        <v>4383</v>
       </c>
       <c r="E58" t="n">
-        <v>4129.4</v>
+        <v>4266</v>
       </c>
       <c r="F58" t="n">
-        <v>4362.2</v>
+        <v>4288.7</v>
       </c>
       <c r="G58" t="n">
-        <v>992864</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3654,25 +3945,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4380</v>
+        <v>4299</v>
       </c>
       <c r="D59" t="n">
-        <v>4478.3</v>
+        <v>4340</v>
       </c>
       <c r="E59" t="n">
-        <v>4280.1</v>
+        <v>4216</v>
       </c>
       <c r="F59" t="n">
-        <v>4395.7</v>
+        <v>4243.8</v>
       </c>
       <c r="G59" t="n">
-        <v>960643</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3681,25 +3972,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4500</v>
+        <v>4201.9</v>
       </c>
       <c r="D60" t="n">
-        <v>4544</v>
+        <v>4222</v>
       </c>
       <c r="E60" t="n">
-        <v>4322</v>
+        <v>4115</v>
       </c>
       <c r="F60" t="n">
-        <v>4364.1</v>
+        <v>4156</v>
       </c>
       <c r="G60" t="n">
-        <v>1616021</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3708,133 +3999,133 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4340.7</v>
+        <v>4181.8</v>
       </c>
       <c r="D61" t="n">
-        <v>4341.8</v>
+        <v>4385</v>
       </c>
       <c r="E61" t="n">
-        <v>4242</v>
+        <v>4129.4</v>
       </c>
       <c r="F61" t="n">
-        <v>4244</v>
+        <v>4362.2</v>
       </c>
       <c r="G61" t="n">
-        <v>319425</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1417</v>
+        <v>4380</v>
       </c>
       <c r="D62" t="n">
-        <v>1436</v>
+        <v>4478.3</v>
       </c>
       <c r="E62" t="n">
-        <v>1410.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F62" t="n">
-        <v>1423.9</v>
+        <v>4395.7</v>
       </c>
       <c r="G62" t="n">
-        <v>623969</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1428</v>
+        <v>4500</v>
       </c>
       <c r="D63" t="n">
-        <v>1428</v>
+        <v>4544</v>
       </c>
       <c r="E63" t="n">
-        <v>1351.5</v>
+        <v>4322</v>
       </c>
       <c r="F63" t="n">
-        <v>1359.1</v>
+        <v>4364.1</v>
       </c>
       <c r="G63" t="n">
-        <v>808190</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1349.8</v>
+        <v>4340.7</v>
       </c>
       <c r="D64" t="n">
-        <v>1357.8</v>
+        <v>4341.8</v>
       </c>
       <c r="E64" t="n">
-        <v>1330.1</v>
+        <v>4175.5</v>
       </c>
       <c r="F64" t="n">
-        <v>1340.8</v>
+        <v>4195.2</v>
       </c>
       <c r="G64" t="n">
-        <v>345535</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1340.8</v>
+        <v>4300</v>
       </c>
       <c r="D65" t="n">
-        <v>1387.7</v>
+        <v>4598</v>
       </c>
       <c r="E65" t="n">
-        <v>1316</v>
+        <v>4252</v>
       </c>
       <c r="F65" t="n">
-        <v>1374.4</v>
+        <v>4524</v>
       </c>
       <c r="G65" t="n">
-        <v>974660</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3843,25 +4134,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1372.9</v>
+        <v>1417</v>
       </c>
       <c r="D66" t="n">
-        <v>1390</v>
+        <v>1436</v>
       </c>
       <c r="E66" t="n">
-        <v>1355.1</v>
+        <v>1410.1</v>
       </c>
       <c r="F66" t="n">
-        <v>1363.5</v>
+        <v>1423.9</v>
       </c>
       <c r="G66" t="n">
-        <v>479123</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3870,25 +4161,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1363</v>
+        <v>1428</v>
       </c>
       <c r="D67" t="n">
-        <v>1392</v>
+        <v>1428</v>
       </c>
       <c r="E67" t="n">
-        <v>1355.1</v>
+        <v>1351.5</v>
       </c>
       <c r="F67" t="n">
-        <v>1380</v>
+        <v>1359.1</v>
       </c>
       <c r="G67" t="n">
-        <v>616767</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3897,25 +4188,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1360</v>
+        <v>1349.8</v>
       </c>
       <c r="D68" t="n">
-        <v>1368</v>
+        <v>1357.8</v>
       </c>
       <c r="E68" t="n">
-        <v>1272.1</v>
+        <v>1330.1</v>
       </c>
       <c r="F68" t="n">
-        <v>1288.3</v>
+        <v>1340.8</v>
       </c>
       <c r="G68" t="n">
-        <v>1098492</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3924,25 +4215,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1300</v>
+        <v>1340.8</v>
       </c>
       <c r="D69" t="n">
-        <v>1318.5</v>
+        <v>1387.7</v>
       </c>
       <c r="E69" t="n">
-        <v>1257</v>
+        <v>1316</v>
       </c>
       <c r="F69" t="n">
-        <v>1316.2</v>
+        <v>1374.4</v>
       </c>
       <c r="G69" t="n">
-        <v>1172726</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3951,46 +4242,208 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1317.7</v>
+        <v>1372.9</v>
       </c>
       <c r="D70" t="n">
-        <v>1319.8</v>
+        <v>1390</v>
       </c>
       <c r="E70" t="n">
-        <v>1270.5</v>
+        <v>1355.1</v>
       </c>
       <c r="F70" t="n">
-        <v>1306</v>
+        <v>1363.5</v>
       </c>
       <c r="G70" t="n">
-        <v>832973</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G71" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G74" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C76" t="n">
         <v>1379</v>
       </c>
-      <c r="D71" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1364.1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1437.7</v>
-      </c>
-      <c r="G71" t="n">
-        <v>4810248</v>
+      <c r="D76" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G76" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1567542</v>
       </c>
     </row>
   </sheetData>
@@ -4004,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4069,6 +4522,21 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 01 Aug 2026 05:34</t>
+          <t>Generated 04 Aug 2026 06:11</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,6 +1397,192 @@
         <v>1</v>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>168.24</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>201.72</v>
+      </c>
+      <c r="I14" t="n">
+        <v>178.12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>225.32</v>
+      </c>
+      <c r="L14" t="n">
+        <v>248.92</v>
+      </c>
+      <c r="M14" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F15" t="n">
+        <v>124.69</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>4694</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4301.58</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5086.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5478.84</v>
+      </c>
+      <c r="M15" t="n">
+        <v>392.42</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>97</v>
+      </c>
+      <c r="F16" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="K16" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="L16" t="n">
+        <v>422.56</v>
+      </c>
+      <c r="M16" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -1413,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1983,105 @@
       </c>
       <c r="I13" t="n">
         <v>1596.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>201.72</v>
+      </c>
+      <c r="E14" t="n">
+        <v>178.12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>225.32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>248.92</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4694</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4301.58</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>392.42</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5086.42</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5478.84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="H16" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>422.56</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,19 +2193,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1928,26 +2213,24 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1377.8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.8</v>
-      </c>
+        <v>201.72</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>6.55</v>
+        <v>2.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.22</v>
+        <v>-0.74</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1318.08</v>
+        <v>178.12</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -1962,19 +2245,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1982,26 +2265,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1659</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>4694</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.82</v>
+        <v>-2.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1555.52</v>
+        <v>4301.58</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -2016,12 +2297,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2036,26 +2317,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1781.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.96</v>
-      </c>
+        <v>375.4</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.45</v>
+        <v>-2.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1697.2</v>
+        <v>351.82</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -2070,12 +2349,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2090,45 +2369,51 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>193.56</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-4.58</v>
-      </c>
+        <v>4694</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>-6.46</v>
+        <v>-2.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4135.84</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2136,45 +2421,51 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4364.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.87</v>
-      </c>
+        <v>1653</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>5.36</v>
+        <v>0.68</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.32</v>
+        <v>-0.6</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1536.8</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2182,45 +2473,51 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1781.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
+        <v>1403.5</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.52</v>
+        <v>-3.49</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1251.99</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2228,45 +2525,53 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1202</v>
+        <v>1377.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.67</v>
+        <v>-0.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.04</v>
+        <v>6.55</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.91</v>
+        <v>-1.69</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2274,45 +2579,53 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>188.39</v>
+        <v>1659</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>-0.82</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>4.52</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.9</v>
+        <v>-1.82</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2320,28 +2633,312 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.72</v>
+        <v>1.96</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="M10" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>97</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4364.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>96</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1781.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>96</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M16" t="n">
         <v>-5.01</v>
       </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2354,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,34 +3291,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1188.4</v>
+        <v>1650</v>
       </c>
       <c r="D13" t="n">
-        <v>1207.9</v>
+        <v>1664.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1158</v>
+        <v>1643</v>
       </c>
       <c r="F13" t="n">
-        <v>1201.8</v>
+        <v>1653</v>
       </c>
       <c r="G13" t="n">
-        <v>3482939</v>
+        <v>422859</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2730,25 +3327,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F14" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G14" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2757,25 +3354,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D15" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E15" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F15" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2784,25 +3381,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D16" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E16" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F16" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G16" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2811,25 +3408,25 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F17" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D17" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G17" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2838,25 +3435,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F18" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G18" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2865,25 +3462,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D19" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E19" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F19" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G19" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2892,25 +3489,25 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F20" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D20" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G20" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2919,25 +3516,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F21" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G21" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2946,25 +3543,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D22" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E22" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2973,25 +3570,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D23" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F23" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G23" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3000,25 +3597,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D24" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E24" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F24" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G24" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3027,25 +3624,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E25" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F25" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3054,79 +3651,79 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D26" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G26" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>211.95</v>
+        <v>1247</v>
       </c>
       <c r="D27" t="n">
-        <v>214.55</v>
+        <v>1274.6</v>
       </c>
       <c r="E27" t="n">
-        <v>206.1</v>
+        <v>1232.1</v>
       </c>
       <c r="F27" t="n">
-        <v>212.78</v>
+        <v>1260.3</v>
       </c>
       <c r="G27" t="n">
-        <v>12863408</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>214.3</v>
+        <v>1341.2</v>
       </c>
       <c r="D28" t="n">
-        <v>223.41</v>
+        <v>1500</v>
       </c>
       <c r="E28" t="n">
-        <v>214.3</v>
+        <v>1336.5</v>
       </c>
       <c r="F28" t="n">
-        <v>223.08</v>
+        <v>1458.5</v>
       </c>
       <c r="G28" t="n">
-        <v>32151413</v>
+        <v>16793214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3135,25 +3732,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D29" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E29" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F29" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G29" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3162,25 +3759,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D30" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E30" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F30" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G30" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3189,25 +3786,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D31" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E31" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F31" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G31" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3216,25 +3813,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D32" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E32" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F32" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G32" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3243,25 +3840,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D33" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E33" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F33" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G33" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3270,25 +3867,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D34" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E34" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F34" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G34" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3297,25 +3894,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D35" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E35" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F35" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G35" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3324,25 +3921,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D36" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E36" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F36" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G36" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3351,25 +3948,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D37" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E37" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F37" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G37" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3378,25 +3975,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D38" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E38" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F38" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G38" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3405,106 +4002,106 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D39" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E39" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F39" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G39" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1554.3</v>
+        <v>189</v>
       </c>
       <c r="D40" t="n">
-        <v>1569</v>
+        <v>195.5</v>
       </c>
       <c r="E40" t="n">
-        <v>1551.3</v>
+        <v>181.05</v>
       </c>
       <c r="F40" t="n">
-        <v>1557.6</v>
+        <v>193.56</v>
       </c>
       <c r="G40" t="n">
-        <v>1001677</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1560.4</v>
+        <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>1561</v>
+        <v>195.53</v>
       </c>
       <c r="E41" t="n">
-        <v>1520.4</v>
+        <v>183.9</v>
       </c>
       <c r="F41" t="n">
-        <v>1529.8</v>
+        <v>184.69</v>
       </c>
       <c r="G41" t="n">
-        <v>1011017</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1534.9</v>
+        <v>202.4</v>
       </c>
       <c r="D42" t="n">
-        <v>1572.2</v>
+        <v>206.3</v>
       </c>
       <c r="E42" t="n">
-        <v>1527.2</v>
+        <v>200.22</v>
       </c>
       <c r="F42" t="n">
-        <v>1558.9</v>
+        <v>201.72</v>
       </c>
       <c r="G42" t="n">
-        <v>1235837</v>
+        <v>10525451</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3513,25 +4110,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1559.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D43" t="n">
-        <v>1600.1</v>
+        <v>1569</v>
       </c>
       <c r="E43" t="n">
-        <v>1557</v>
+        <v>1551.3</v>
       </c>
       <c r="F43" t="n">
-        <v>1593.2</v>
+        <v>1557.6</v>
       </c>
       <c r="G43" t="n">
-        <v>1871739</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3540,25 +4137,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1591</v>
+        <v>1560.4</v>
       </c>
       <c r="D44" t="n">
-        <v>1593.2</v>
+        <v>1561</v>
       </c>
       <c r="E44" t="n">
-        <v>1566</v>
+        <v>1520.4</v>
       </c>
       <c r="F44" t="n">
-        <v>1577.8</v>
+        <v>1529.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1183077</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3567,25 +4164,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1577.7</v>
+        <v>1534.9</v>
       </c>
       <c r="D45" t="n">
-        <v>1586.1</v>
+        <v>1572.2</v>
       </c>
       <c r="E45" t="n">
-        <v>1561.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F45" t="n">
-        <v>1568.3</v>
+        <v>1558.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1098268</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3594,25 +4191,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1560</v>
+        <v>1559.7</v>
       </c>
       <c r="D46" t="n">
-        <v>1610</v>
+        <v>1600.1</v>
       </c>
       <c r="E46" t="n">
-        <v>1554.9</v>
+        <v>1557</v>
       </c>
       <c r="F46" t="n">
-        <v>1601.2</v>
+        <v>1593.2</v>
       </c>
       <c r="G46" t="n">
-        <v>2647403</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3621,25 +4218,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1624.8</v>
+        <v>1591</v>
       </c>
       <c r="D47" t="n">
-        <v>1734.5</v>
+        <v>1593.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1617.1</v>
+        <v>1566</v>
       </c>
       <c r="F47" t="n">
-        <v>1713.4</v>
+        <v>1577.8</v>
       </c>
       <c r="G47" t="n">
-        <v>7989771</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3648,25 +4245,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1713</v>
+        <v>1577.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1762</v>
+        <v>1586.1</v>
       </c>
       <c r="E48" t="n">
-        <v>1707.7</v>
+        <v>1561.1</v>
       </c>
       <c r="F48" t="n">
-        <v>1758.9</v>
+        <v>1568.3</v>
       </c>
       <c r="G48" t="n">
-        <v>4407907</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3675,25 +4272,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1762</v>
+        <v>1560</v>
       </c>
       <c r="D49" t="n">
-        <v>1797.9</v>
+        <v>1610</v>
       </c>
       <c r="E49" t="n">
-        <v>1754.3</v>
+        <v>1554.9</v>
       </c>
       <c r="F49" t="n">
-        <v>1781.3</v>
+        <v>1601.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3000811</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3702,25 +4299,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1785</v>
+        <v>1624.8</v>
       </c>
       <c r="D50" t="n">
-        <v>1798.9</v>
+        <v>1734.5</v>
       </c>
       <c r="E50" t="n">
-        <v>1773.3</v>
+        <v>1617.1</v>
       </c>
       <c r="F50" t="n">
-        <v>1781.3</v>
+        <v>1713.4</v>
       </c>
       <c r="G50" t="n">
-        <v>2402202</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3729,721 +4326,1153 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1785</v>
+        <v>1713</v>
       </c>
       <c r="D51" t="n">
-        <v>1826.6</v>
+        <v>1762</v>
       </c>
       <c r="E51" t="n">
-        <v>1785</v>
+        <v>1707.7</v>
       </c>
       <c r="F51" t="n">
-        <v>1816.2</v>
+        <v>1758.9</v>
       </c>
       <c r="G51" t="n">
-        <v>2502579</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4389.8</v>
+        <v>1762</v>
       </c>
       <c r="D52" t="n">
-        <v>4485</v>
+        <v>1797.9</v>
       </c>
       <c r="E52" t="n">
-        <v>4361.9</v>
+        <v>1754.3</v>
       </c>
       <c r="F52" t="n">
-        <v>4398.1</v>
+        <v>1781.3</v>
       </c>
       <c r="G52" t="n">
-        <v>1347378</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4422</v>
+        <v>1785</v>
       </c>
       <c r="D53" t="n">
-        <v>4495</v>
+        <v>1798.9</v>
       </c>
       <c r="E53" t="n">
-        <v>4358</v>
+        <v>1773.3</v>
       </c>
       <c r="F53" t="n">
-        <v>4371.4</v>
+        <v>1781.3</v>
       </c>
       <c r="G53" t="n">
-        <v>902264</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4387.7</v>
+        <v>1785</v>
       </c>
       <c r="D54" t="n">
-        <v>4404</v>
+        <v>1826.6</v>
       </c>
       <c r="E54" t="n">
-        <v>4281.9</v>
+        <v>1785</v>
       </c>
       <c r="F54" t="n">
-        <v>4304.2</v>
+        <v>1816.2</v>
       </c>
       <c r="G54" t="n">
-        <v>463349</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4285</v>
+        <v>1811</v>
       </c>
       <c r="D55" t="n">
-        <v>4317</v>
+        <v>1832.5</v>
       </c>
       <c r="E55" t="n">
-        <v>4220</v>
+        <v>1806.1</v>
       </c>
       <c r="F55" t="n">
-        <v>4244.3</v>
+        <v>1826.8</v>
       </c>
       <c r="G55" t="n">
-        <v>398348</v>
+        <v>668925</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4211</v>
+        <v>344</v>
       </c>
       <c r="D56" t="n">
-        <v>4220</v>
+        <v>346.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4129.3</v>
+        <v>341.25</v>
       </c>
       <c r="F56" t="n">
-        <v>4178.1</v>
+        <v>342.9</v>
       </c>
       <c r="G56" t="n">
-        <v>470046</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4190</v>
+        <v>344.2</v>
       </c>
       <c r="D57" t="n">
-        <v>4324.4</v>
+        <v>347.75</v>
       </c>
       <c r="E57" t="n">
-        <v>4190</v>
+        <v>339.95</v>
       </c>
       <c r="F57" t="n">
-        <v>4257.3</v>
+        <v>342.4</v>
       </c>
       <c r="G57" t="n">
-        <v>633457</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4290</v>
+        <v>346</v>
       </c>
       <c r="D58" t="n">
-        <v>4383</v>
+        <v>351</v>
       </c>
       <c r="E58" t="n">
-        <v>4266</v>
+        <v>343.65</v>
       </c>
       <c r="F58" t="n">
-        <v>4288.7</v>
+        <v>346</v>
       </c>
       <c r="G58" t="n">
-        <v>835107</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4299</v>
+        <v>341.8</v>
       </c>
       <c r="D59" t="n">
-        <v>4340</v>
+        <v>344.9</v>
       </c>
       <c r="E59" t="n">
-        <v>4216</v>
+        <v>339.65</v>
       </c>
       <c r="F59" t="n">
-        <v>4243.8</v>
+        <v>343.9</v>
       </c>
       <c r="G59" t="n">
-        <v>422024</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4201.9</v>
+        <v>345.1</v>
       </c>
       <c r="D60" t="n">
-        <v>4222</v>
+        <v>346.05</v>
       </c>
       <c r="E60" t="n">
-        <v>4115</v>
+        <v>338.35</v>
       </c>
       <c r="F60" t="n">
-        <v>4156</v>
+        <v>339.35</v>
       </c>
       <c r="G60" t="n">
-        <v>378694</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4181.8</v>
+        <v>339.4</v>
       </c>
       <c r="D61" t="n">
-        <v>4385</v>
+        <v>340.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4129.4</v>
+        <v>333</v>
       </c>
       <c r="F61" t="n">
-        <v>4362.2</v>
+        <v>334.55</v>
       </c>
       <c r="G61" t="n">
-        <v>992864</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4380</v>
+        <v>335</v>
       </c>
       <c r="D62" t="n">
-        <v>4478.3</v>
+        <v>346.1</v>
       </c>
       <c r="E62" t="n">
-        <v>4280.1</v>
+        <v>332</v>
       </c>
       <c r="F62" t="n">
-        <v>4395.7</v>
+        <v>344.7</v>
       </c>
       <c r="G62" t="n">
-        <v>960643</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4500</v>
+        <v>345.5</v>
       </c>
       <c r="D63" t="n">
-        <v>4544</v>
+        <v>349.65</v>
       </c>
       <c r="E63" t="n">
-        <v>4322</v>
+        <v>342.6</v>
       </c>
       <c r="F63" t="n">
-        <v>4364.1</v>
+        <v>347.65</v>
       </c>
       <c r="G63" t="n">
-        <v>1616021</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4340.7</v>
+        <v>352</v>
       </c>
       <c r="D64" t="n">
-        <v>4341.8</v>
+        <v>355.75</v>
       </c>
       <c r="E64" t="n">
-        <v>4175.5</v>
+        <v>347.65</v>
       </c>
       <c r="F64" t="n">
-        <v>4195.2</v>
+        <v>350.05</v>
       </c>
       <c r="G64" t="n">
-        <v>648341</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4300</v>
+        <v>373</v>
       </c>
       <c r="D65" t="n">
-        <v>4598</v>
+        <v>382.45</v>
       </c>
       <c r="E65" t="n">
-        <v>4252</v>
+        <v>367.15</v>
       </c>
       <c r="F65" t="n">
-        <v>4524</v>
+        <v>375.4</v>
       </c>
       <c r="G65" t="n">
-        <v>4510774</v>
+        <v>9573922</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1417</v>
+        <v>4389.8</v>
       </c>
       <c r="D66" t="n">
-        <v>1436</v>
+        <v>4485</v>
       </c>
       <c r="E66" t="n">
-        <v>1410.1</v>
+        <v>4361.9</v>
       </c>
       <c r="F66" t="n">
-        <v>1423.9</v>
+        <v>4398.1</v>
       </c>
       <c r="G66" t="n">
-        <v>623969</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1428</v>
+        <v>4422</v>
       </c>
       <c r="D67" t="n">
-        <v>1428</v>
+        <v>4495</v>
       </c>
       <c r="E67" t="n">
-        <v>1351.5</v>
+        <v>4358</v>
       </c>
       <c r="F67" t="n">
-        <v>1359.1</v>
+        <v>4371.4</v>
       </c>
       <c r="G67" t="n">
-        <v>808190</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1349.8</v>
+        <v>4387.7</v>
       </c>
       <c r="D68" t="n">
-        <v>1357.8</v>
+        <v>4404</v>
       </c>
       <c r="E68" t="n">
-        <v>1330.1</v>
+        <v>4281.9</v>
       </c>
       <c r="F68" t="n">
-        <v>1340.8</v>
+        <v>4304.2</v>
       </c>
       <c r="G68" t="n">
-        <v>345535</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1340.8</v>
+        <v>4285</v>
       </c>
       <c r="D69" t="n">
-        <v>1387.7</v>
+        <v>4317</v>
       </c>
       <c r="E69" t="n">
-        <v>1316</v>
+        <v>4220</v>
       </c>
       <c r="F69" t="n">
-        <v>1374.4</v>
+        <v>4244.3</v>
       </c>
       <c r="G69" t="n">
-        <v>974660</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1372.9</v>
+        <v>4211</v>
       </c>
       <c r="D70" t="n">
-        <v>1390</v>
+        <v>4220</v>
       </c>
       <c r="E70" t="n">
-        <v>1355.1</v>
+        <v>4129.3</v>
       </c>
       <c r="F70" t="n">
-        <v>1363.5</v>
+        <v>4178.1</v>
       </c>
       <c r="G70" t="n">
-        <v>479123</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1363</v>
+        <v>4190</v>
       </c>
       <c r="D71" t="n">
-        <v>1392</v>
+        <v>4324.4</v>
       </c>
       <c r="E71" t="n">
-        <v>1355.1</v>
+        <v>4190</v>
       </c>
       <c r="F71" t="n">
-        <v>1380</v>
+        <v>4257.3</v>
       </c>
       <c r="G71" t="n">
-        <v>616767</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1360</v>
+        <v>4290</v>
       </c>
       <c r="D72" t="n">
-        <v>1368</v>
+        <v>4383</v>
       </c>
       <c r="E72" t="n">
-        <v>1272.1</v>
+        <v>4266</v>
       </c>
       <c r="F72" t="n">
-        <v>1288.3</v>
+        <v>4288.7</v>
       </c>
       <c r="G72" t="n">
-        <v>1098492</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1300</v>
+        <v>4299</v>
       </c>
       <c r="D73" t="n">
-        <v>1318.5</v>
+        <v>4340</v>
       </c>
       <c r="E73" t="n">
-        <v>1257</v>
+        <v>4216</v>
       </c>
       <c r="F73" t="n">
-        <v>1316.2</v>
+        <v>4243.8</v>
       </c>
       <c r="G73" t="n">
-        <v>1172726</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1317.7</v>
+        <v>4201.9</v>
       </c>
       <c r="D74" t="n">
-        <v>1319.8</v>
+        <v>4222</v>
       </c>
       <c r="E74" t="n">
-        <v>1270.5</v>
+        <v>4115</v>
       </c>
       <c r="F74" t="n">
-        <v>1306</v>
+        <v>4156</v>
       </c>
       <c r="G74" t="n">
-        <v>832973</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1319.9</v>
+        <v>4181.8</v>
       </c>
       <c r="D75" t="n">
-        <v>1355.4</v>
+        <v>4385</v>
       </c>
       <c r="E75" t="n">
-        <v>1308</v>
+        <v>4129.4</v>
       </c>
       <c r="F75" t="n">
-        <v>1343.4</v>
+        <v>4362.2</v>
       </c>
       <c r="G75" t="n">
-        <v>1287698</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1379</v>
+        <v>4380</v>
       </c>
       <c r="D76" t="n">
-        <v>1468</v>
+        <v>4478.3</v>
       </c>
       <c r="E76" t="n">
-        <v>1361</v>
+        <v>4280.1</v>
       </c>
       <c r="F76" t="n">
-        <v>1377.8</v>
+        <v>4395.7</v>
       </c>
       <c r="G76" t="n">
-        <v>9950655</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4544</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4322</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4364.1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1616021</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4340.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4341.8</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4175.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4195.2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>648341</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4300</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4598</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4252</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4524</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4510774</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4609</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4749.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4593.1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4694</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1025923</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C81" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1436</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1410.1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1423.9</v>
+      </c>
+      <c r="G81" t="n">
+        <v>623969</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1428</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1359.1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>808190</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1349.8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1357.8</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="G83" t="n">
+        <v>345535</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1387.7</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1374.4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>974660</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1372.9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>479123</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G86" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G89" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G91" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
         <v>1380.5</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D92" t="n">
         <v>1403.3</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E92" t="n">
         <v>1363</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F92" t="n">
         <v>1366.8</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G92" t="n">
         <v>1567542</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1409.6</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1403.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>867735</v>
       </c>
     </row>
   </sheetData>
@@ -4457,7 +5486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4537,6 +5566,21 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 04 Aug 2026 06:11</t>
+          <t>Generated 05 Aug 2026 06:07</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,25 +601,53 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.27</v>
+        <v>0.79</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.67</v>
+        <v>4.48</v>
       </c>
       <c r="G2" t="n">
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.79</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,6 +1611,192 @@
         <v>1</v>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>199.54</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>210.97</v>
+      </c>
+      <c r="I17" t="n">
+        <v>190.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>231.86</v>
+      </c>
+      <c r="L17" t="n">
+        <v>252.75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F18" t="n">
+        <v>108.51</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>4871.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4486.28</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5255.92</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5640.74</v>
+      </c>
+      <c r="M18" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>97</v>
+      </c>
+      <c r="F19" t="n">
+        <v>104.23</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1634.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1534.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1734.21</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1834.22</v>
+      </c>
+      <c r="M19" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -1599,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2082,6 +2296,105 @@
       </c>
       <c r="I16" t="n">
         <v>422.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>210.97</v>
+      </c>
+      <c r="E17" t="n">
+        <v>190.08</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="H17" t="n">
+        <v>231.86</v>
+      </c>
+      <c r="I17" t="n">
+        <v>252.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4871.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4486.28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5255.92</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5640.74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1634.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1534.19</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1734.21</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1834.22</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2193,7 +2506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2213,7 +2526,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201.72</v>
+        <v>210.97</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2221,16 +2534,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.27</v>
+        <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.74</v>
+        <v>-2.82</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -2245,7 +2558,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2257,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2265,7 +2578,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4694</v>
+        <v>4871.1</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2273,16 +2586,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.15</v>
+        <v>-3</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -2297,12 +2610,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2317,7 +2630,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>375.4</v>
+        <v>1634.2</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2325,16 +2638,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2</v>
+        <v>-0.18</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -2349,19 +2662,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2369,24 +2682,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4694</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>202.78</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.04</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>4.54</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.15</v>
+        <v>-1.26</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -2401,19 +2716,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2421,24 +2736,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1653</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>4762.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.29</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.68</v>
+        <v>2.47</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6</v>
+        <v>-3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -2453,19 +2770,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2473,24 +2790,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1403.5</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>377</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.38</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.49</v>
+        <v>-2.61</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -2505,12 +2824,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2525,26 +2844,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1377.8</v>
+        <v>4586</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.55</v>
+        <v>6.41</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.69</v>
+        <v>-1</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -2559,7 +2878,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2579,26 +2898,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.82</v>
+        <v>-0.96</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -2613,19 +2932,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2633,26 +2952,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2.87</v>
+        <v>6.79</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -2667,12 +2986,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2687,45 +3006,53 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2733,33 +3060,41 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4364.1</v>
+        <v>1659</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>8.83</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.32</v>
+        <v>-1.82</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2771,7 +3106,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2782,42 +3117,50 @@
         <v>1781.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>4.23</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2825,23 +3168,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G14" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>-4.58</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.99</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>24.79</v>
+        <v>9.52</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2851,19 +3196,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2871,23 +3216,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>188.39</v>
+        <v>4364.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>-3.87</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.62</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>9.51</v>
+        <v>11.82</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2897,19 +3244,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2917,28 +3264,174 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.52</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>8.050000000000001</v>
+        <v>4.23</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.01</v>
+        <v>-1.52</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>96</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>92</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2951,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3291,7 +3784,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3300,79 +3793,79 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1650</v>
+        <v>1654.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1664.3</v>
+        <v>1676</v>
       </c>
       <c r="E13" t="n">
-        <v>1643</v>
+        <v>1635.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="G13" t="n">
-        <v>422859</v>
+        <v>1135101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1188.4</v>
+        <v>1650</v>
       </c>
       <c r="D14" t="n">
-        <v>1207.9</v>
+        <v>1664.3</v>
       </c>
       <c r="E14" t="n">
-        <v>1158</v>
+        <v>1638</v>
       </c>
       <c r="F14" t="n">
-        <v>1201.8</v>
+        <v>1646</v>
       </c>
       <c r="G14" t="n">
-        <v>3482939</v>
+        <v>845598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1225</v>
+        <v>1663.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1318.9</v>
+        <v>1663.8</v>
       </c>
       <c r="E15" t="n">
-        <v>1225</v>
+        <v>1631.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1296.4</v>
+        <v>1634.2</v>
       </c>
       <c r="G15" t="n">
-        <v>17106822</v>
+        <v>460474</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3381,25 +3874,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1325</v>
+        <v>1188.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1345</v>
+        <v>1207.9</v>
       </c>
       <c r="E16" t="n">
-        <v>1251.5</v>
+        <v>1158</v>
       </c>
       <c r="F16" t="n">
-        <v>1267.1</v>
+        <v>1201.8</v>
       </c>
       <c r="G16" t="n">
-        <v>10436460</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3408,25 +3901,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1270</v>
+        <v>1225</v>
       </c>
       <c r="D17" t="n">
-        <v>1285</v>
+        <v>1318.9</v>
       </c>
       <c r="E17" t="n">
-        <v>1246.1</v>
+        <v>1225</v>
       </c>
       <c r="F17" t="n">
-        <v>1282.2</v>
+        <v>1296.4</v>
       </c>
       <c r="G17" t="n">
-        <v>4135957</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3435,25 +3928,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1282.2</v>
+        <v>1325</v>
       </c>
       <c r="D18" t="n">
-        <v>1333.9</v>
+        <v>1345</v>
       </c>
       <c r="E18" t="n">
-        <v>1272.6</v>
+        <v>1251.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1296.7</v>
+        <v>1267.1</v>
       </c>
       <c r="G18" t="n">
-        <v>5275779</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3462,25 +3955,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1302.7</v>
+        <v>1270</v>
       </c>
       <c r="D19" t="n">
-        <v>1315.8</v>
+        <v>1285</v>
       </c>
       <c r="E19" t="n">
-        <v>1257.1</v>
+        <v>1246.1</v>
       </c>
       <c r="F19" t="n">
-        <v>1288.4</v>
+        <v>1282.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3844546</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3489,25 +3982,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1290</v>
+        <v>1282.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1312</v>
+        <v>1333.9</v>
       </c>
       <c r="E20" t="n">
-        <v>1262</v>
+        <v>1272.6</v>
       </c>
       <c r="F20" t="n">
-        <v>1268.2</v>
+        <v>1296.7</v>
       </c>
       <c r="G20" t="n">
-        <v>2691508</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3516,25 +4009,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1268.2</v>
+        <v>1302.7</v>
       </c>
       <c r="D21" t="n">
-        <v>1271.5</v>
+        <v>1315.8</v>
       </c>
       <c r="E21" t="n">
-        <v>1221.2</v>
+        <v>1257.1</v>
       </c>
       <c r="F21" t="n">
-        <v>1233.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2619436</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3543,25 +4036,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1224.1</v>
+        <v>1290</v>
       </c>
       <c r="D22" t="n">
-        <v>1224.7</v>
+        <v>1312</v>
       </c>
       <c r="E22" t="n">
-        <v>1188.1</v>
+        <v>1262</v>
       </c>
       <c r="F22" t="n">
-        <v>1208.7</v>
+        <v>1268.2</v>
       </c>
       <c r="G22" t="n">
-        <v>3613338</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3570,25 +4063,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1214.9</v>
+        <v>1268.2</v>
       </c>
       <c r="D23" t="n">
-        <v>1233.9</v>
+        <v>1271.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1196.5</v>
+        <v>1221.2</v>
       </c>
       <c r="F23" t="n">
-        <v>1214.9</v>
+        <v>1233.2</v>
       </c>
       <c r="G23" t="n">
-        <v>1911132</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3597,25 +4090,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1213</v>
+        <v>1224.1</v>
       </c>
       <c r="D24" t="n">
-        <v>1229</v>
+        <v>1224.7</v>
       </c>
       <c r="E24" t="n">
-        <v>1196.1</v>
+        <v>1188.1</v>
       </c>
       <c r="F24" t="n">
-        <v>1202</v>
+        <v>1208.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2067763</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3624,25 +4117,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1207.2</v>
+        <v>1214.9</v>
       </c>
       <c r="D25" t="n">
-        <v>1252</v>
+        <v>1233.9</v>
       </c>
       <c r="E25" t="n">
-        <v>1191.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F25" t="n">
-        <v>1246.1</v>
+        <v>1214.9</v>
       </c>
       <c r="G25" t="n">
-        <v>3306087</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3651,25 +4144,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1253</v>
+        <v>1213</v>
       </c>
       <c r="D26" t="n">
-        <v>1265.9</v>
+        <v>1229</v>
       </c>
       <c r="E26" t="n">
-        <v>1232.5</v>
+        <v>1196.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1240.9</v>
+        <v>1202</v>
       </c>
       <c r="G26" t="n">
-        <v>2463994</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3678,25 +4171,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1247</v>
+        <v>1207.2</v>
       </c>
       <c r="D27" t="n">
-        <v>1274.6</v>
+        <v>1252</v>
       </c>
       <c r="E27" t="n">
-        <v>1232.1</v>
+        <v>1191.1</v>
       </c>
       <c r="F27" t="n">
-        <v>1260.3</v>
+        <v>1246.1</v>
       </c>
       <c r="G27" t="n">
-        <v>3182495</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3705,133 +4198,133 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1341.2</v>
+        <v>1253</v>
       </c>
       <c r="D28" t="n">
-        <v>1500</v>
+        <v>1265.9</v>
       </c>
       <c r="E28" t="n">
-        <v>1336.5</v>
+        <v>1232.5</v>
       </c>
       <c r="F28" t="n">
-        <v>1458.5</v>
+        <v>1240.9</v>
       </c>
       <c r="G28" t="n">
-        <v>16793214</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>211.95</v>
+        <v>1247</v>
       </c>
       <c r="D29" t="n">
-        <v>214.55</v>
+        <v>1274.6</v>
       </c>
       <c r="E29" t="n">
-        <v>206.1</v>
+        <v>1232.1</v>
       </c>
       <c r="F29" t="n">
-        <v>212.78</v>
+        <v>1260.3</v>
       </c>
       <c r="G29" t="n">
-        <v>12863408</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>214.3</v>
+        <v>1269</v>
       </c>
       <c r="D30" t="n">
-        <v>223.41</v>
+        <v>1289.9</v>
       </c>
       <c r="E30" t="n">
-        <v>214.3</v>
+        <v>1242</v>
       </c>
       <c r="F30" t="n">
-        <v>223.08</v>
+        <v>1272.7</v>
       </c>
       <c r="G30" t="n">
-        <v>32151413</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>226</v>
+        <v>1341.2</v>
       </c>
       <c r="D31" t="n">
-        <v>229.4</v>
+        <v>1500</v>
       </c>
       <c r="E31" t="n">
-        <v>221.18</v>
+        <v>1336.5</v>
       </c>
       <c r="F31" t="n">
-        <v>224.38</v>
+        <v>1450.4</v>
       </c>
       <c r="G31" t="n">
-        <v>14379534</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>217.24</v>
+        <v>1465</v>
       </c>
       <c r="D32" t="n">
-        <v>219.7</v>
+        <v>1468.4</v>
       </c>
       <c r="E32" t="n">
-        <v>213.17</v>
+        <v>1405</v>
       </c>
       <c r="F32" t="n">
-        <v>213.17</v>
+        <v>1460.6</v>
       </c>
       <c r="G32" t="n">
-        <v>14642282</v>
+        <v>3479464</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3840,25 +4333,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>208.25</v>
+        <v>211.95</v>
       </c>
       <c r="D33" t="n">
-        <v>213.7</v>
+        <v>214.55</v>
       </c>
       <c r="E33" t="n">
-        <v>203.16</v>
+        <v>206.1</v>
       </c>
       <c r="F33" t="n">
-        <v>208.03</v>
+        <v>212.78</v>
       </c>
       <c r="G33" t="n">
-        <v>18348510</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3867,25 +4360,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="D34" t="n">
-        <v>218.43</v>
+        <v>223.41</v>
       </c>
       <c r="E34" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="F34" t="n">
-        <v>217.97</v>
+        <v>223.08</v>
       </c>
       <c r="G34" t="n">
-        <v>20144780</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3894,25 +4387,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D35" t="n">
-        <v>228</v>
+        <v>229.4</v>
       </c>
       <c r="E35" t="n">
-        <v>214.11</v>
+        <v>221.18</v>
       </c>
       <c r="F35" t="n">
-        <v>217.9</v>
+        <v>224.38</v>
       </c>
       <c r="G35" t="n">
-        <v>55935312</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3921,25 +4414,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>221.96</v>
+        <v>217.24</v>
       </c>
       <c r="D36" t="n">
-        <v>222.4</v>
+        <v>219.7</v>
       </c>
       <c r="E36" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="F36" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="G36" t="n">
-        <v>29190459</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3948,25 +4441,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>202</v>
+        <v>208.25</v>
       </c>
       <c r="D37" t="n">
-        <v>204.78</v>
+        <v>213.7</v>
       </c>
       <c r="E37" t="n">
-        <v>196.66</v>
+        <v>203.16</v>
       </c>
       <c r="F37" t="n">
-        <v>196.85</v>
+        <v>208.03</v>
       </c>
       <c r="G37" t="n">
-        <v>31552378</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3975,25 +4468,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D38" t="n">
-        <v>200.9</v>
+        <v>218.43</v>
       </c>
       <c r="E38" t="n">
-        <v>191.1</v>
+        <v>209</v>
       </c>
       <c r="F38" t="n">
-        <v>192.54</v>
+        <v>217.97</v>
       </c>
       <c r="G38" t="n">
-        <v>26152896</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4002,25 +4495,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D39" t="n">
-        <v>196.9</v>
+        <v>228</v>
       </c>
       <c r="E39" t="n">
-        <v>182.92</v>
+        <v>214.11</v>
       </c>
       <c r="F39" t="n">
-        <v>188.39</v>
+        <v>217.9</v>
       </c>
       <c r="G39" t="n">
-        <v>42541118</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4029,25 +4522,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>189</v>
+        <v>221.96</v>
       </c>
       <c r="D40" t="n">
-        <v>195.5</v>
+        <v>222.4</v>
       </c>
       <c r="E40" t="n">
-        <v>181.05</v>
+        <v>207.01</v>
       </c>
       <c r="F40" t="n">
-        <v>193.56</v>
+        <v>207.01</v>
       </c>
       <c r="G40" t="n">
-        <v>40104195</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4056,25 +4549,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D41" t="n">
-        <v>195.53</v>
+        <v>204.78</v>
       </c>
       <c r="E41" t="n">
-        <v>183.9</v>
+        <v>196.66</v>
       </c>
       <c r="F41" t="n">
-        <v>184.69</v>
+        <v>196.85</v>
       </c>
       <c r="G41" t="n">
-        <v>21043194</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4083,214 +4576,214 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>202.4</v>
+        <v>200</v>
       </c>
       <c r="D42" t="n">
-        <v>206.3</v>
+        <v>200.9</v>
       </c>
       <c r="E42" t="n">
-        <v>200.22</v>
+        <v>191.1</v>
       </c>
       <c r="F42" t="n">
-        <v>201.72</v>
+        <v>192.54</v>
       </c>
       <c r="G42" t="n">
-        <v>10525451</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1554.3</v>
+        <v>187</v>
       </c>
       <c r="D43" t="n">
-        <v>1569</v>
+        <v>196.9</v>
       </c>
       <c r="E43" t="n">
-        <v>1551.3</v>
+        <v>182.92</v>
       </c>
       <c r="F43" t="n">
-        <v>1557.6</v>
+        <v>188.39</v>
       </c>
       <c r="G43" t="n">
-        <v>1001677</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1560.4</v>
+        <v>189</v>
       </c>
       <c r="D44" t="n">
-        <v>1561</v>
+        <v>195.5</v>
       </c>
       <c r="E44" t="n">
-        <v>1520.4</v>
+        <v>181.05</v>
       </c>
       <c r="F44" t="n">
-        <v>1529.8</v>
+        <v>193.56</v>
       </c>
       <c r="G44" t="n">
-        <v>1011017</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1534.9</v>
+        <v>193</v>
       </c>
       <c r="D45" t="n">
-        <v>1572.2</v>
+        <v>195.53</v>
       </c>
       <c r="E45" t="n">
-        <v>1527.2</v>
+        <v>183.9</v>
       </c>
       <c r="F45" t="n">
-        <v>1558.9</v>
+        <v>184.69</v>
       </c>
       <c r="G45" t="n">
-        <v>1235837</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1559.7</v>
+        <v>193.92</v>
       </c>
       <c r="D46" t="n">
-        <v>1600.1</v>
+        <v>193.92</v>
       </c>
       <c r="E46" t="n">
-        <v>1557</v>
+        <v>191.01</v>
       </c>
       <c r="F46" t="n">
-        <v>1593.2</v>
+        <v>193.92</v>
       </c>
       <c r="G46" t="n">
-        <v>1871739</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1591</v>
+        <v>196.95</v>
       </c>
       <c r="D47" t="n">
-        <v>1593.2</v>
+        <v>203.61</v>
       </c>
       <c r="E47" t="n">
-        <v>1566</v>
+        <v>195.7</v>
       </c>
       <c r="F47" t="n">
-        <v>1577.8</v>
+        <v>202.52</v>
       </c>
       <c r="G47" t="n">
-        <v>1183077</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1577.7</v>
+        <v>202.4</v>
       </c>
       <c r="D48" t="n">
-        <v>1586.1</v>
+        <v>207</v>
       </c>
       <c r="E48" t="n">
-        <v>1561.1</v>
+        <v>200.22</v>
       </c>
       <c r="F48" t="n">
-        <v>1568.3</v>
+        <v>202.78</v>
       </c>
       <c r="G48" t="n">
-        <v>1098268</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1560</v>
+        <v>205.8</v>
       </c>
       <c r="D49" t="n">
-        <v>1610</v>
+        <v>211.99</v>
       </c>
       <c r="E49" t="n">
-        <v>1554.9</v>
+        <v>205.03</v>
       </c>
       <c r="F49" t="n">
-        <v>1601.2</v>
+        <v>210.97</v>
       </c>
       <c r="G49" t="n">
-        <v>2647403</v>
+        <v>13947707</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,25 +4792,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1624.8</v>
+        <v>1554.3</v>
       </c>
       <c r="D50" t="n">
-        <v>1734.5</v>
+        <v>1569</v>
       </c>
       <c r="E50" t="n">
-        <v>1617.1</v>
+        <v>1551.3</v>
       </c>
       <c r="F50" t="n">
-        <v>1713.4</v>
+        <v>1557.6</v>
       </c>
       <c r="G50" t="n">
-        <v>7989771</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4326,25 +4819,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1713</v>
+        <v>1560.4</v>
       </c>
       <c r="D51" t="n">
-        <v>1762</v>
+        <v>1561</v>
       </c>
       <c r="E51" t="n">
-        <v>1707.7</v>
+        <v>1520.4</v>
       </c>
       <c r="F51" t="n">
-        <v>1758.9</v>
+        <v>1529.8</v>
       </c>
       <c r="G51" t="n">
-        <v>4407907</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4353,25 +4846,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1762</v>
+        <v>1534.9</v>
       </c>
       <c r="D52" t="n">
-        <v>1797.9</v>
+        <v>1572.2</v>
       </c>
       <c r="E52" t="n">
-        <v>1754.3</v>
+        <v>1527.2</v>
       </c>
       <c r="F52" t="n">
-        <v>1781.3</v>
+        <v>1558.9</v>
       </c>
       <c r="G52" t="n">
-        <v>3000811</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4380,25 +4873,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1785</v>
+        <v>1559.7</v>
       </c>
       <c r="D53" t="n">
-        <v>1798.9</v>
+        <v>1600.1</v>
       </c>
       <c r="E53" t="n">
-        <v>1773.3</v>
+        <v>1557</v>
       </c>
       <c r="F53" t="n">
-        <v>1781.3</v>
+        <v>1593.2</v>
       </c>
       <c r="G53" t="n">
-        <v>2402202</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4407,25 +4900,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1785</v>
+        <v>1591</v>
       </c>
       <c r="D54" t="n">
-        <v>1826.6</v>
+        <v>1593.2</v>
       </c>
       <c r="E54" t="n">
-        <v>1785</v>
+        <v>1566</v>
       </c>
       <c r="F54" t="n">
-        <v>1816.2</v>
+        <v>1577.8</v>
       </c>
       <c r="G54" t="n">
-        <v>2502579</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4434,268 +4927,268 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1811</v>
+        <v>1577.7</v>
       </c>
       <c r="D55" t="n">
-        <v>1832.5</v>
+        <v>1586.1</v>
       </c>
       <c r="E55" t="n">
-        <v>1806.1</v>
+        <v>1561.1</v>
       </c>
       <c r="F55" t="n">
-        <v>1826.8</v>
+        <v>1568.3</v>
       </c>
       <c r="G55" t="n">
-        <v>668925</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>344</v>
+        <v>1560</v>
       </c>
       <c r="D56" t="n">
-        <v>346.3</v>
+        <v>1610</v>
       </c>
       <c r="E56" t="n">
-        <v>341.25</v>
+        <v>1554.9</v>
       </c>
       <c r="F56" t="n">
-        <v>342.9</v>
+        <v>1601.2</v>
       </c>
       <c r="G56" t="n">
-        <v>4465145</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>344.2</v>
+        <v>1624.8</v>
       </c>
       <c r="D57" t="n">
-        <v>347.75</v>
+        <v>1734.5</v>
       </c>
       <c r="E57" t="n">
-        <v>339.95</v>
+        <v>1617.1</v>
       </c>
       <c r="F57" t="n">
-        <v>342.4</v>
+        <v>1713.4</v>
       </c>
       <c r="G57" t="n">
-        <v>3803051</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>346</v>
+        <v>1713</v>
       </c>
       <c r="D58" t="n">
-        <v>351</v>
+        <v>1762</v>
       </c>
       <c r="E58" t="n">
-        <v>343.65</v>
+        <v>1707.7</v>
       </c>
       <c r="F58" t="n">
-        <v>346</v>
+        <v>1758.9</v>
       </c>
       <c r="G58" t="n">
-        <v>5175178</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>341.8</v>
+        <v>1762</v>
       </c>
       <c r="D59" t="n">
-        <v>344.9</v>
+        <v>1797.9</v>
       </c>
       <c r="E59" t="n">
-        <v>339.65</v>
+        <v>1754.3</v>
       </c>
       <c r="F59" t="n">
-        <v>343.9</v>
+        <v>1781.3</v>
       </c>
       <c r="G59" t="n">
-        <v>2253982</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>345.1</v>
+        <v>1785</v>
       </c>
       <c r="D60" t="n">
-        <v>346.05</v>
+        <v>1798.9</v>
       </c>
       <c r="E60" t="n">
-        <v>338.35</v>
+        <v>1773.3</v>
       </c>
       <c r="F60" t="n">
-        <v>339.35</v>
+        <v>1781.3</v>
       </c>
       <c r="G60" t="n">
-        <v>3868006</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>339.4</v>
+        <v>1785</v>
       </c>
       <c r="D61" t="n">
-        <v>340.2</v>
+        <v>1826.6</v>
       </c>
       <c r="E61" t="n">
-        <v>333</v>
+        <v>1785</v>
       </c>
       <c r="F61" t="n">
-        <v>334.55</v>
+        <v>1816.2</v>
       </c>
       <c r="G61" t="n">
-        <v>3721274</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>335</v>
+        <v>1821</v>
       </c>
       <c r="D62" t="n">
-        <v>346.1</v>
+        <v>1838.3</v>
       </c>
       <c r="E62" t="n">
-        <v>332</v>
+        <v>1789.1</v>
       </c>
       <c r="F62" t="n">
-        <v>344.7</v>
+        <v>1811.4</v>
       </c>
       <c r="G62" t="n">
-        <v>5431501</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>345.5</v>
+        <v>1811</v>
       </c>
       <c r="D63" t="n">
-        <v>349.65</v>
+        <v>1850</v>
       </c>
       <c r="E63" t="n">
-        <v>342.6</v>
+        <v>1806.1</v>
       </c>
       <c r="F63" t="n">
-        <v>347.65</v>
+        <v>1850</v>
       </c>
       <c r="G63" t="n">
-        <v>6318472</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>352</v>
+        <v>1854</v>
       </c>
       <c r="D64" t="n">
-        <v>355.75</v>
+        <v>1856.6</v>
       </c>
       <c r="E64" t="n">
-        <v>347.65</v>
+        <v>1834.5</v>
       </c>
       <c r="F64" t="n">
-        <v>350.05</v>
+        <v>1844</v>
       </c>
       <c r="G64" t="n">
-        <v>7186013</v>
+        <v>1215174</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4704,322 +5197,322 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="D65" t="n">
-        <v>382.45</v>
+        <v>346.3</v>
       </c>
       <c r="E65" t="n">
-        <v>367.15</v>
+        <v>341.25</v>
       </c>
       <c r="F65" t="n">
-        <v>375.4</v>
+        <v>342.9</v>
       </c>
       <c r="G65" t="n">
-        <v>9573922</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4389.8</v>
+        <v>344.2</v>
       </c>
       <c r="D66" t="n">
-        <v>4485</v>
+        <v>347.75</v>
       </c>
       <c r="E66" t="n">
-        <v>4361.9</v>
+        <v>339.95</v>
       </c>
       <c r="F66" t="n">
-        <v>4398.1</v>
+        <v>342.4</v>
       </c>
       <c r="G66" t="n">
-        <v>1347378</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4422</v>
+        <v>346</v>
       </c>
       <c r="D67" t="n">
-        <v>4495</v>
+        <v>351</v>
       </c>
       <c r="E67" t="n">
-        <v>4358</v>
+        <v>343.65</v>
       </c>
       <c r="F67" t="n">
-        <v>4371.4</v>
+        <v>346</v>
       </c>
       <c r="G67" t="n">
-        <v>902264</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4387.7</v>
+        <v>341.8</v>
       </c>
       <c r="D68" t="n">
-        <v>4404</v>
+        <v>344.9</v>
       </c>
       <c r="E68" t="n">
-        <v>4281.9</v>
+        <v>339.65</v>
       </c>
       <c r="F68" t="n">
-        <v>4304.2</v>
+        <v>343.9</v>
       </c>
       <c r="G68" t="n">
-        <v>463349</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4285</v>
+        <v>345.1</v>
       </c>
       <c r="D69" t="n">
-        <v>4317</v>
+        <v>346.05</v>
       </c>
       <c r="E69" t="n">
-        <v>4220</v>
+        <v>338.35</v>
       </c>
       <c r="F69" t="n">
-        <v>4244.3</v>
+        <v>339.35</v>
       </c>
       <c r="G69" t="n">
-        <v>398348</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4211</v>
+        <v>339.4</v>
       </c>
       <c r="D70" t="n">
-        <v>4220</v>
+        <v>340.2</v>
       </c>
       <c r="E70" t="n">
-        <v>4129.3</v>
+        <v>333</v>
       </c>
       <c r="F70" t="n">
-        <v>4178.1</v>
+        <v>334.55</v>
       </c>
       <c r="G70" t="n">
-        <v>470046</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4190</v>
+        <v>335</v>
       </c>
       <c r="D71" t="n">
-        <v>4324.4</v>
+        <v>346.1</v>
       </c>
       <c r="E71" t="n">
-        <v>4190</v>
+        <v>332</v>
       </c>
       <c r="F71" t="n">
-        <v>4257.3</v>
+        <v>344.7</v>
       </c>
       <c r="G71" t="n">
-        <v>633457</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4290</v>
+        <v>345.5</v>
       </c>
       <c r="D72" t="n">
-        <v>4383</v>
+        <v>349.65</v>
       </c>
       <c r="E72" t="n">
-        <v>4266</v>
+        <v>342.6</v>
       </c>
       <c r="F72" t="n">
-        <v>4288.7</v>
+        <v>347.65</v>
       </c>
       <c r="G72" t="n">
-        <v>835107</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4299</v>
+        <v>352</v>
       </c>
       <c r="D73" t="n">
-        <v>4340</v>
+        <v>355.75</v>
       </c>
       <c r="E73" t="n">
-        <v>4216</v>
+        <v>347.65</v>
       </c>
       <c r="F73" t="n">
-        <v>4243.8</v>
+        <v>350.05</v>
       </c>
       <c r="G73" t="n">
-        <v>422024</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4201.9</v>
+        <v>357.95</v>
       </c>
       <c r="D74" t="n">
-        <v>4222</v>
+        <v>369</v>
       </c>
       <c r="E74" t="n">
-        <v>4115</v>
+        <v>353.5</v>
       </c>
       <c r="F74" t="n">
-        <v>4156</v>
+        <v>369</v>
       </c>
       <c r="G74" t="n">
-        <v>378694</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4181.8</v>
+        <v>373</v>
       </c>
       <c r="D75" t="n">
-        <v>4385</v>
+        <v>382.45</v>
       </c>
       <c r="E75" t="n">
-        <v>4129.4</v>
+        <v>367.15</v>
       </c>
       <c r="F75" t="n">
-        <v>4362.2</v>
+        <v>377</v>
       </c>
       <c r="G75" t="n">
-        <v>992864</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4380</v>
+        <v>381</v>
       </c>
       <c r="D76" t="n">
-        <v>4478.3</v>
+        <v>383.9</v>
       </c>
       <c r="E76" t="n">
-        <v>4280.1</v>
+        <v>375.3</v>
       </c>
       <c r="F76" t="n">
-        <v>4395.7</v>
+        <v>375.55</v>
       </c>
       <c r="G76" t="n">
-        <v>960643</v>
+        <v>4168465</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5028,25 +5521,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4500</v>
+        <v>4389.8</v>
       </c>
       <c r="D77" t="n">
-        <v>4544</v>
+        <v>4485</v>
       </c>
       <c r="E77" t="n">
-        <v>4322</v>
+        <v>4361.9</v>
       </c>
       <c r="F77" t="n">
-        <v>4364.1</v>
+        <v>4398.1</v>
       </c>
       <c r="G77" t="n">
-        <v>1616021</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5055,25 +5548,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4340.7</v>
+        <v>4422</v>
       </c>
       <c r="D78" t="n">
-        <v>4341.8</v>
+        <v>4495</v>
       </c>
       <c r="E78" t="n">
-        <v>4175.5</v>
+        <v>4358</v>
       </c>
       <c r="F78" t="n">
-        <v>4195.2</v>
+        <v>4371.4</v>
       </c>
       <c r="G78" t="n">
-        <v>648341</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5082,25 +5575,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4300</v>
+        <v>4387.7</v>
       </c>
       <c r="D79" t="n">
-        <v>4598</v>
+        <v>4404</v>
       </c>
       <c r="E79" t="n">
-        <v>4252</v>
+        <v>4281.9</v>
       </c>
       <c r="F79" t="n">
-        <v>4524</v>
+        <v>4304.2</v>
       </c>
       <c r="G79" t="n">
-        <v>4510774</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5109,370 +5602,775 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4609</v>
+        <v>4285</v>
       </c>
       <c r="D80" t="n">
-        <v>4749.5</v>
+        <v>4317</v>
       </c>
       <c r="E80" t="n">
-        <v>4593.1</v>
+        <v>4220</v>
       </c>
       <c r="F80" t="n">
-        <v>4694</v>
+        <v>4244.3</v>
       </c>
       <c r="G80" t="n">
-        <v>1025923</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1417</v>
+        <v>4211</v>
       </c>
       <c r="D81" t="n">
-        <v>1436</v>
+        <v>4220</v>
       </c>
       <c r="E81" t="n">
-        <v>1410.1</v>
+        <v>4129.3</v>
       </c>
       <c r="F81" t="n">
-        <v>1423.9</v>
+        <v>4178.1</v>
       </c>
       <c r="G81" t="n">
-        <v>623969</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1428</v>
+        <v>4190</v>
       </c>
       <c r="D82" t="n">
-        <v>1428</v>
+        <v>4324.4</v>
       </c>
       <c r="E82" t="n">
-        <v>1351.5</v>
+        <v>4190</v>
       </c>
       <c r="F82" t="n">
-        <v>1359.1</v>
+        <v>4257.3</v>
       </c>
       <c r="G82" t="n">
-        <v>808190</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1349.8</v>
+        <v>4290</v>
       </c>
       <c r="D83" t="n">
-        <v>1357.8</v>
+        <v>4383</v>
       </c>
       <c r="E83" t="n">
-        <v>1330.1</v>
+        <v>4266</v>
       </c>
       <c r="F83" t="n">
-        <v>1340.8</v>
+        <v>4288.7</v>
       </c>
       <c r="G83" t="n">
-        <v>345535</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1340.8</v>
+        <v>4299</v>
       </c>
       <c r="D84" t="n">
-        <v>1387.7</v>
+        <v>4340</v>
       </c>
       <c r="E84" t="n">
-        <v>1316</v>
+        <v>4216</v>
       </c>
       <c r="F84" t="n">
-        <v>1374.4</v>
+        <v>4243.8</v>
       </c>
       <c r="G84" t="n">
-        <v>974660</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1372.9</v>
+        <v>4201.9</v>
       </c>
       <c r="D85" t="n">
-        <v>1390</v>
+        <v>4222</v>
       </c>
       <c r="E85" t="n">
-        <v>1355.1</v>
+        <v>4115</v>
       </c>
       <c r="F85" t="n">
-        <v>1363.5</v>
+        <v>4156</v>
       </c>
       <c r="G85" t="n">
-        <v>479123</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1363</v>
+        <v>4181.8</v>
       </c>
       <c r="D86" t="n">
-        <v>1392</v>
+        <v>4385</v>
       </c>
       <c r="E86" t="n">
-        <v>1355.1</v>
+        <v>4129.4</v>
       </c>
       <c r="F86" t="n">
-        <v>1380</v>
+        <v>4362.2</v>
       </c>
       <c r="G86" t="n">
-        <v>616767</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1360</v>
+        <v>4380</v>
       </c>
       <c r="D87" t="n">
-        <v>1368</v>
+        <v>4478.3</v>
       </c>
       <c r="E87" t="n">
-        <v>1272.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F87" t="n">
-        <v>1288.3</v>
+        <v>4395.7</v>
       </c>
       <c r="G87" t="n">
-        <v>1098492</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1300</v>
+        <v>4500</v>
       </c>
       <c r="D88" t="n">
-        <v>1318.5</v>
+        <v>4544</v>
       </c>
       <c r="E88" t="n">
-        <v>1257</v>
+        <v>4322</v>
       </c>
       <c r="F88" t="n">
-        <v>1316.2</v>
+        <v>4364.1</v>
       </c>
       <c r="G88" t="n">
-        <v>1172726</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1317.7</v>
+        <v>4340.7</v>
       </c>
       <c r="D89" t="n">
-        <v>1319.8</v>
+        <v>4341.8</v>
       </c>
       <c r="E89" t="n">
-        <v>1270.5</v>
+        <v>4175.5</v>
       </c>
       <c r="F89" t="n">
-        <v>1306</v>
+        <v>4195.2</v>
       </c>
       <c r="G89" t="n">
-        <v>832973</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1319.9</v>
+        <v>4300</v>
       </c>
       <c r="D90" t="n">
-        <v>1355.4</v>
+        <v>4598</v>
       </c>
       <c r="E90" t="n">
-        <v>1308</v>
+        <v>4252</v>
       </c>
       <c r="F90" t="n">
-        <v>1343.4</v>
+        <v>4524</v>
       </c>
       <c r="G90" t="n">
-        <v>1287698</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1379</v>
+        <v>4560.4</v>
       </c>
       <c r="D91" t="n">
-        <v>1468</v>
+        <v>4740</v>
       </c>
       <c r="E91" t="n">
-        <v>1361</v>
+        <v>4540</v>
       </c>
       <c r="F91" t="n">
-        <v>1377.8</v>
+        <v>4586</v>
       </c>
       <c r="G91" t="n">
-        <v>9950655</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1380.5</v>
+        <v>4609</v>
       </c>
       <c r="D92" t="n">
-        <v>1403.3</v>
+        <v>4780</v>
       </c>
       <c r="E92" t="n">
-        <v>1363</v>
+        <v>4593.1</v>
       </c>
       <c r="F92" t="n">
-        <v>1366.8</v>
+        <v>4762.2</v>
       </c>
       <c r="G92" t="n">
-        <v>1567542</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4820.7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4880</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4725</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4871.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>880334</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1436</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1410.1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1423.9</v>
+      </c>
+      <c r="G94" t="n">
+        <v>623969</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1428</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1359.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>808190</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1349.8</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1357.8</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="G96" t="n">
+        <v>345535</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1387.7</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1374.4</v>
+      </c>
+      <c r="G97" t="n">
+        <v>974660</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1372.9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>479123</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G99" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G102" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C107" t="n">
         <v>1360.6</v>
       </c>
-      <c r="D93" t="n">
-        <v>1409.6</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="D107" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E107" t="n">
         <v>1354.5</v>
       </c>
-      <c r="F93" t="n">
-        <v>1403.5</v>
-      </c>
-      <c r="G93" t="n">
-        <v>867735</v>
+      <c r="F107" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1422</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1438.3</v>
+      </c>
+      <c r="G108" t="n">
+        <v>766501</v>
       </c>
     </row>
   </sheetData>
@@ -5486,7 +6384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5581,6 +6479,21 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 05 Aug 2026 06:07</t>
+          <t>Generated 06 Aug 2026 06:11</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="E2" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>4.48</v>
+        <v>4.66</v>
       </c>
       <c r="G2" t="n">
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="3">
@@ -629,25 +629,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>10.13</v>
+        <v>7.52</v>
       </c>
       <c r="D3" t="n">
-        <v>8.66</v>
+        <v>7.64</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
       </c>
       <c r="G3" t="n">
-        <v>3.52</v>
+        <v>-1.53</v>
       </c>
       <c r="H3" t="n">
-        <v>5.79</v>
+        <v>6.41</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1797,192 @@
         <v>1</v>
       </c>
       <c r="P19" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" t="n">
+        <v>193.54</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>209.85</v>
+      </c>
+      <c r="I20" t="n">
+        <v>189.62</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="K20" t="n">
+        <v>230.08</v>
+      </c>
+      <c r="L20" t="n">
+        <v>250.31</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>98</v>
+      </c>
+      <c r="F21" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1633.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1537.22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1729.98</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1826.36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>357.53</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>400.27</v>
+      </c>
+      <c r="L22" t="n">
+        <v>421.64</v>
+      </c>
+      <c r="M22" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -1813,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2395,6 +2581,105 @@
       </c>
       <c r="I19" t="n">
         <v>1834.22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>209.85</v>
+      </c>
+      <c r="E20" t="n">
+        <v>189.62</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="H20" t="n">
+        <v>230.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>250.31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1633.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1537.22</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1729.98</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1826.36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>357.53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="H22" t="n">
+        <v>400.27</v>
+      </c>
+      <c r="I22" t="n">
+        <v>421.64</v>
       </c>
     </row>
   </sheetData>
@@ -2408,7 +2693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2506,7 +2791,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2526,7 +2811,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>210.97</v>
+        <v>209.85</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2534,16 +2819,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.48</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.82</v>
+        <v>-0.76</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -2558,12 +2843,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2578,7 +2863,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4871.1</v>
+        <v>1633.6</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2586,16 +2871,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.18</v>
+        <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>-3</v>
+        <v>-0.95</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -2610,12 +2895,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2630,7 +2915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1634.2</v>
+        <v>378.9</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2638,16 +2923,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -2662,7 +2947,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2682,26 +2967,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G5" t="n">
-        <v>4.04</v>
+        <v>-1.12</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.54</v>
+        <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.26</v>
+        <v>-3.39</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -2716,7 +3001,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2728,7 +3013,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2736,26 +3021,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4762.2</v>
+        <v>4893.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>0.48</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.47</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -2770,12 +3055,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2790,26 +3075,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.38</v>
+        <v>-0.51</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.61</v>
+        <v>-1.46</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -2824,19 +3109,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2844,26 +3129,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4586</v>
+        <v>202.78</v>
       </c>
       <c r="G8" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.41</v>
+        <v>5.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -2878,19 +3163,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2898,26 +3183,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1647</v>
+        <v>4762.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>4.57</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.96</v>
+        <v>-3.55</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -2932,19 +3217,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2952,26 +3237,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G10" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>6.79</v>
+        <v>2.14</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -2986,12 +3271,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3006,32 +3291,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1377.8</v>
+        <v>4586</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>6.55</v>
+        <v>8.59</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -3040,7 +3325,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3060,26 +3345,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.82</v>
+        <v>-1.75</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -3094,19 +3379,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3114,26 +3399,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>4.23</v>
+        <v>7.31</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -3148,12 +3433,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3168,47 +3453,55 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H14" t="n">
-        <v>8.99</v>
+        <v>4.27</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>9.52</v>
+        <v>6.55</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3216,35 +3509,43 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4364.1</v>
+        <v>1659</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H15" t="n">
-        <v>11.62</v>
+        <v>-1.53</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>11.82</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.32</v>
+        <v>-2.47</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3256,7 +3557,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3267,10 +3568,10 @@
         <v>1781.3</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -3279,32 +3580,40 @@
         <v>4.23</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3312,22 +3621,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G17" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H17" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>24.79</v>
+        <v>10.28</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
@@ -3340,19 +3649,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3360,22 +3669,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>188.39</v>
+        <v>4364.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H18" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>12.53</v>
+        <v>14.11</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
@@ -3388,19 +3697,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3408,22 +3717,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.34</v>
+        <v>3.01</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>11.02</v>
+        <v>4.23</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.01</v>
+        <v>-1.52</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
@@ -3432,6 +3741,150 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>96</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>92</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3444,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3853,46 +4306,46 @@
         <v>1663.8</v>
       </c>
       <c r="E15" t="n">
-        <v>1631.2</v>
+        <v>1630.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1634.2</v>
+        <v>1642</v>
       </c>
       <c r="G15" t="n">
-        <v>460474</v>
+        <v>886130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1188.4</v>
+        <v>1641.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1207.9</v>
+        <v>1641.9</v>
       </c>
       <c r="E16" t="n">
-        <v>1158</v>
+        <v>1618.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1201.8</v>
+        <v>1633.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3482939</v>
+        <v>362903</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3901,25 +4354,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D17" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E17" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F17" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G17" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3928,25 +4381,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D18" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F18" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G18" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3955,25 +4408,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D19" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E19" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G19" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3982,25 +4435,25 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F20" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D20" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G20" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4009,25 +4462,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E21" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F21" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G21" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4036,25 +4489,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D22" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E22" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4063,25 +4516,25 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F23" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D23" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G23" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4090,25 +4543,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G24" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4117,25 +4570,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E25" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F25" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4144,25 +4597,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D26" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F26" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G26" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4171,25 +4624,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D27" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E27" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F27" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G27" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4198,25 +4651,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D28" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E28" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G28" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4225,25 +4678,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D29" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G29" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4252,25 +4705,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D30" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F30" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G30" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4279,25 +4732,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D31" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E31" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F31" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G31" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4306,79 +4759,79 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D32" t="n">
-        <v>1468.4</v>
+        <v>1500</v>
       </c>
       <c r="E32" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1460.6</v>
+        <v>1450.4</v>
       </c>
       <c r="G32" t="n">
-        <v>3479464</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>211.95</v>
+        <v>1465</v>
       </c>
       <c r="D33" t="n">
-        <v>214.55</v>
+        <v>1479.5</v>
       </c>
       <c r="E33" t="n">
-        <v>206.1</v>
+        <v>1405</v>
       </c>
       <c r="F33" t="n">
-        <v>212.78</v>
+        <v>1470.8</v>
       </c>
       <c r="G33" t="n">
-        <v>12863408</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>214.3</v>
+        <v>1470.8</v>
       </c>
       <c r="D34" t="n">
-        <v>223.41</v>
+        <v>1505</v>
       </c>
       <c r="E34" t="n">
-        <v>214.3</v>
+        <v>1454.5</v>
       </c>
       <c r="F34" t="n">
-        <v>223.08</v>
+        <v>1458.3</v>
       </c>
       <c r="G34" t="n">
-        <v>32151413</v>
+        <v>3132810</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4387,25 +4840,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D35" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E35" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F35" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G35" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4414,25 +4867,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D36" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E36" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F36" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G36" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4441,25 +4894,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D37" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E37" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F37" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G37" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4468,25 +4921,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D38" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E38" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F38" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G38" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4495,25 +4948,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D39" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E39" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F39" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G39" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4522,25 +4975,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D40" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E40" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F40" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G40" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4549,25 +5002,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D41" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E41" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F41" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G41" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4576,25 +5029,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D42" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E42" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F42" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G42" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4603,25 +5056,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E43" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F43" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G43" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4630,25 +5083,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D44" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E44" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F44" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G44" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4657,25 +5110,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D45" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E45" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F45" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G45" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4684,25 +5137,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D46" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E46" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F46" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G46" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4711,25 +5164,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D47" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E47" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F47" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G47" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4738,25 +5191,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D48" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E48" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F48" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G48" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4765,106 +5218,106 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D49" t="n">
-        <v>211.99</v>
+        <v>203.61</v>
       </c>
       <c r="E49" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F49" t="n">
-        <v>210.97</v>
+        <v>202.52</v>
       </c>
       <c r="G49" t="n">
-        <v>13947707</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1554.3</v>
+        <v>202.4</v>
       </c>
       <c r="D50" t="n">
-        <v>1569</v>
+        <v>207</v>
       </c>
       <c r="E50" t="n">
-        <v>1551.3</v>
+        <v>200.22</v>
       </c>
       <c r="F50" t="n">
-        <v>1557.6</v>
+        <v>202.78</v>
       </c>
       <c r="G50" t="n">
-        <v>1001677</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1560.4</v>
+        <v>205.8</v>
       </c>
       <c r="D51" t="n">
-        <v>1561</v>
+        <v>212.91</v>
       </c>
       <c r="E51" t="n">
-        <v>1520.4</v>
+        <v>205.03</v>
       </c>
       <c r="F51" t="n">
-        <v>1529.8</v>
+        <v>212.23</v>
       </c>
       <c r="G51" t="n">
-        <v>1011017</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1534.9</v>
+        <v>212.4</v>
       </c>
       <c r="D52" t="n">
-        <v>1572.2</v>
+        <v>213.45</v>
       </c>
       <c r="E52" t="n">
-        <v>1527.2</v>
+        <v>208.25</v>
       </c>
       <c r="F52" t="n">
-        <v>1558.9</v>
+        <v>209.85</v>
       </c>
       <c r="G52" t="n">
-        <v>1235837</v>
+        <v>9791415</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4873,25 +5326,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1559.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D53" t="n">
-        <v>1600.1</v>
+        <v>1569</v>
       </c>
       <c r="E53" t="n">
-        <v>1557</v>
+        <v>1551.3</v>
       </c>
       <c r="F53" t="n">
-        <v>1593.2</v>
+        <v>1557.6</v>
       </c>
       <c r="G53" t="n">
-        <v>1871739</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4900,25 +5353,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1591</v>
+        <v>1560.4</v>
       </c>
       <c r="D54" t="n">
-        <v>1593.2</v>
+        <v>1561</v>
       </c>
       <c r="E54" t="n">
-        <v>1566</v>
+        <v>1520.4</v>
       </c>
       <c r="F54" t="n">
-        <v>1577.8</v>
+        <v>1529.8</v>
       </c>
       <c r="G54" t="n">
-        <v>1183077</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4927,25 +5380,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1577.7</v>
+        <v>1534.9</v>
       </c>
       <c r="D55" t="n">
-        <v>1586.1</v>
+        <v>1572.2</v>
       </c>
       <c r="E55" t="n">
-        <v>1561.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F55" t="n">
-        <v>1568.3</v>
+        <v>1558.9</v>
       </c>
       <c r="G55" t="n">
-        <v>1098268</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,25 +5407,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1560</v>
+        <v>1559.7</v>
       </c>
       <c r="D56" t="n">
-        <v>1610</v>
+        <v>1600.1</v>
       </c>
       <c r="E56" t="n">
-        <v>1554.9</v>
+        <v>1557</v>
       </c>
       <c r="F56" t="n">
-        <v>1601.2</v>
+        <v>1593.2</v>
       </c>
       <c r="G56" t="n">
-        <v>2647403</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,25 +5434,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1624.8</v>
+        <v>1591</v>
       </c>
       <c r="D57" t="n">
-        <v>1734.5</v>
+        <v>1593.2</v>
       </c>
       <c r="E57" t="n">
-        <v>1617.1</v>
+        <v>1566</v>
       </c>
       <c r="F57" t="n">
-        <v>1713.4</v>
+        <v>1577.8</v>
       </c>
       <c r="G57" t="n">
-        <v>7989771</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5008,25 +5461,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1713</v>
+        <v>1577.7</v>
       </c>
       <c r="D58" t="n">
-        <v>1762</v>
+        <v>1586.1</v>
       </c>
       <c r="E58" t="n">
-        <v>1707.7</v>
+        <v>1561.1</v>
       </c>
       <c r="F58" t="n">
-        <v>1758.9</v>
+        <v>1568.3</v>
       </c>
       <c r="G58" t="n">
-        <v>4407907</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5035,25 +5488,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1762</v>
+        <v>1560</v>
       </c>
       <c r="D59" t="n">
-        <v>1797.9</v>
+        <v>1610</v>
       </c>
       <c r="E59" t="n">
-        <v>1754.3</v>
+        <v>1554.9</v>
       </c>
       <c r="F59" t="n">
-        <v>1781.3</v>
+        <v>1601.2</v>
       </c>
       <c r="G59" t="n">
-        <v>3000811</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5062,25 +5515,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1785</v>
+        <v>1624.8</v>
       </c>
       <c r="D60" t="n">
-        <v>1798.9</v>
+        <v>1734.5</v>
       </c>
       <c r="E60" t="n">
-        <v>1773.3</v>
+        <v>1617.1</v>
       </c>
       <c r="F60" t="n">
-        <v>1781.3</v>
+        <v>1713.4</v>
       </c>
       <c r="G60" t="n">
-        <v>2402202</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5089,25 +5542,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1785</v>
+        <v>1713</v>
       </c>
       <c r="D61" t="n">
-        <v>1826.6</v>
+        <v>1762</v>
       </c>
       <c r="E61" t="n">
-        <v>1785</v>
+        <v>1707.7</v>
       </c>
       <c r="F61" t="n">
-        <v>1816.2</v>
+        <v>1758.9</v>
       </c>
       <c r="G61" t="n">
-        <v>2502579</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5116,25 +5569,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1821</v>
+        <v>1762</v>
       </c>
       <c r="D62" t="n">
-        <v>1838.3</v>
+        <v>1797.9</v>
       </c>
       <c r="E62" t="n">
-        <v>1789.1</v>
+        <v>1754.3</v>
       </c>
       <c r="F62" t="n">
-        <v>1811.4</v>
+        <v>1781.3</v>
       </c>
       <c r="G62" t="n">
-        <v>1919384</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5143,25 +5596,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1811</v>
+        <v>1785</v>
       </c>
       <c r="D63" t="n">
-        <v>1850</v>
+        <v>1798.9</v>
       </c>
       <c r="E63" t="n">
-        <v>1806.1</v>
+        <v>1773.3</v>
       </c>
       <c r="F63" t="n">
-        <v>1850</v>
+        <v>1781.3</v>
       </c>
       <c r="G63" t="n">
-        <v>1405192</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5170,133 +5623,133 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1854</v>
+        <v>1785</v>
       </c>
       <c r="D64" t="n">
-        <v>1856.6</v>
+        <v>1826.6</v>
       </c>
       <c r="E64" t="n">
-        <v>1834.5</v>
+        <v>1785</v>
       </c>
       <c r="F64" t="n">
-        <v>1844</v>
+        <v>1816.2</v>
       </c>
       <c r="G64" t="n">
-        <v>1215174</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>344</v>
+        <v>1821</v>
       </c>
       <c r="D65" t="n">
-        <v>346.3</v>
+        <v>1838.3</v>
       </c>
       <c r="E65" t="n">
-        <v>341.25</v>
+        <v>1789.1</v>
       </c>
       <c r="F65" t="n">
-        <v>342.9</v>
+        <v>1811.4</v>
       </c>
       <c r="G65" t="n">
-        <v>4465145</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>344.2</v>
+        <v>1811</v>
       </c>
       <c r="D66" t="n">
-        <v>347.75</v>
+        <v>1850</v>
       </c>
       <c r="E66" t="n">
-        <v>339.95</v>
+        <v>1806.1</v>
       </c>
       <c r="F66" t="n">
-        <v>342.4</v>
+        <v>1850</v>
       </c>
       <c r="G66" t="n">
-        <v>3803051</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>346</v>
+        <v>1854</v>
       </c>
       <c r="D67" t="n">
-        <v>351</v>
+        <v>1856.6</v>
       </c>
       <c r="E67" t="n">
-        <v>343.65</v>
+        <v>1834.5</v>
       </c>
       <c r="F67" t="n">
-        <v>346</v>
+        <v>1835</v>
       </c>
       <c r="G67" t="n">
-        <v>5175178</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>341.8</v>
+        <v>1843</v>
       </c>
       <c r="D68" t="n">
-        <v>344.9</v>
+        <v>1854.9</v>
       </c>
       <c r="E68" t="n">
-        <v>339.65</v>
+        <v>1837</v>
       </c>
       <c r="F68" t="n">
-        <v>343.9</v>
+        <v>1843.2</v>
       </c>
       <c r="G68" t="n">
-        <v>2253982</v>
+        <v>1228707</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5305,25 +5758,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>345.1</v>
+        <v>344</v>
       </c>
       <c r="D69" t="n">
-        <v>346.05</v>
+        <v>346.3</v>
       </c>
       <c r="E69" t="n">
-        <v>338.35</v>
+        <v>341.25</v>
       </c>
       <c r="F69" t="n">
-        <v>339.35</v>
+        <v>342.9</v>
       </c>
       <c r="G69" t="n">
-        <v>3868006</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5332,25 +5785,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>339.4</v>
+        <v>344.2</v>
       </c>
       <c r="D70" t="n">
-        <v>340.2</v>
+        <v>347.75</v>
       </c>
       <c r="E70" t="n">
-        <v>333</v>
+        <v>339.95</v>
       </c>
       <c r="F70" t="n">
-        <v>334.55</v>
+        <v>342.4</v>
       </c>
       <c r="G70" t="n">
-        <v>3721274</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5359,25 +5812,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D71" t="n">
-        <v>346.1</v>
+        <v>351</v>
       </c>
       <c r="E71" t="n">
-        <v>332</v>
+        <v>343.65</v>
       </c>
       <c r="F71" t="n">
-        <v>344.7</v>
+        <v>346</v>
       </c>
       <c r="G71" t="n">
-        <v>5431501</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5386,25 +5839,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>345.5</v>
+        <v>341.8</v>
       </c>
       <c r="D72" t="n">
-        <v>349.65</v>
+        <v>344.9</v>
       </c>
       <c r="E72" t="n">
-        <v>342.6</v>
+        <v>339.65</v>
       </c>
       <c r="F72" t="n">
-        <v>347.65</v>
+        <v>343.9</v>
       </c>
       <c r="G72" t="n">
-        <v>6318472</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5413,25 +5866,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>352</v>
+        <v>345.1</v>
       </c>
       <c r="D73" t="n">
-        <v>355.75</v>
+        <v>346.05</v>
       </c>
       <c r="E73" t="n">
-        <v>347.65</v>
+        <v>338.35</v>
       </c>
       <c r="F73" t="n">
-        <v>350.05</v>
+        <v>339.35</v>
       </c>
       <c r="G73" t="n">
-        <v>7186013</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5440,25 +5893,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>357.95</v>
+        <v>339.4</v>
       </c>
       <c r="D74" t="n">
-        <v>369</v>
+        <v>340.2</v>
       </c>
       <c r="E74" t="n">
-        <v>353.5</v>
+        <v>333</v>
       </c>
       <c r="F74" t="n">
-        <v>369</v>
+        <v>334.55</v>
       </c>
       <c r="G74" t="n">
-        <v>12541474</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5467,25 +5920,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="D75" t="n">
-        <v>382.45</v>
+        <v>346.1</v>
       </c>
       <c r="E75" t="n">
-        <v>367.15</v>
+        <v>332</v>
       </c>
       <c r="F75" t="n">
-        <v>377</v>
+        <v>344.7</v>
       </c>
       <c r="G75" t="n">
-        <v>15775994</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5494,160 +5947,160 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>381</v>
+        <v>345.5</v>
       </c>
       <c r="D76" t="n">
-        <v>383.9</v>
+        <v>349.65</v>
       </c>
       <c r="E76" t="n">
-        <v>375.3</v>
+        <v>342.6</v>
       </c>
       <c r="F76" t="n">
-        <v>375.55</v>
+        <v>347.65</v>
       </c>
       <c r="G76" t="n">
-        <v>4168465</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4389.8</v>
+        <v>352</v>
       </c>
       <c r="D77" t="n">
-        <v>4485</v>
+        <v>355.75</v>
       </c>
       <c r="E77" t="n">
-        <v>4361.9</v>
+        <v>347.65</v>
       </c>
       <c r="F77" t="n">
-        <v>4398.1</v>
+        <v>350.05</v>
       </c>
       <c r="G77" t="n">
-        <v>1347378</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4422</v>
+        <v>357.95</v>
       </c>
       <c r="D78" t="n">
-        <v>4495</v>
+        <v>369</v>
       </c>
       <c r="E78" t="n">
-        <v>4358</v>
+        <v>353.5</v>
       </c>
       <c r="F78" t="n">
-        <v>4371.4</v>
+        <v>369</v>
       </c>
       <c r="G78" t="n">
-        <v>902264</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4387.7</v>
+        <v>373</v>
       </c>
       <c r="D79" t="n">
-        <v>4404</v>
+        <v>382.45</v>
       </c>
       <c r="E79" t="n">
-        <v>4281.9</v>
+        <v>367.15</v>
       </c>
       <c r="F79" t="n">
-        <v>4304.2</v>
+        <v>377</v>
       </c>
       <c r="G79" t="n">
-        <v>463349</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4285</v>
+        <v>381</v>
       </c>
       <c r="D80" t="n">
-        <v>4317</v>
+        <v>383.9</v>
       </c>
       <c r="E80" t="n">
-        <v>4220</v>
+        <v>375.15</v>
       </c>
       <c r="F80" t="n">
-        <v>4244.3</v>
+        <v>381</v>
       </c>
       <c r="G80" t="n">
-        <v>398348</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4211</v>
+        <v>385</v>
       </c>
       <c r="D81" t="n">
-        <v>4220</v>
+        <v>385.05</v>
       </c>
       <c r="E81" t="n">
-        <v>4129.3</v>
+        <v>378.1</v>
       </c>
       <c r="F81" t="n">
-        <v>4178.1</v>
+        <v>378.9</v>
       </c>
       <c r="G81" t="n">
-        <v>470046</v>
+        <v>3486554</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5656,25 +6109,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4190</v>
+        <v>4389.8</v>
       </c>
       <c r="D82" t="n">
-        <v>4324.4</v>
+        <v>4485</v>
       </c>
       <c r="E82" t="n">
-        <v>4190</v>
+        <v>4361.9</v>
       </c>
       <c r="F82" t="n">
-        <v>4257.3</v>
+        <v>4398.1</v>
       </c>
       <c r="G82" t="n">
-        <v>633457</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5683,25 +6136,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4290</v>
+        <v>4422</v>
       </c>
       <c r="D83" t="n">
-        <v>4383</v>
+        <v>4495</v>
       </c>
       <c r="E83" t="n">
-        <v>4266</v>
+        <v>4358</v>
       </c>
       <c r="F83" t="n">
-        <v>4288.7</v>
+        <v>4371.4</v>
       </c>
       <c r="G83" t="n">
-        <v>835107</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5710,25 +6163,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4299</v>
+        <v>4387.7</v>
       </c>
       <c r="D84" t="n">
-        <v>4340</v>
+        <v>4404</v>
       </c>
       <c r="E84" t="n">
-        <v>4216</v>
+        <v>4281.9</v>
       </c>
       <c r="F84" t="n">
-        <v>4243.8</v>
+        <v>4304.2</v>
       </c>
       <c r="G84" t="n">
-        <v>422024</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5737,25 +6190,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4201.9</v>
+        <v>4285</v>
       </c>
       <c r="D85" t="n">
-        <v>4222</v>
+        <v>4317</v>
       </c>
       <c r="E85" t="n">
-        <v>4115</v>
+        <v>4220</v>
       </c>
       <c r="F85" t="n">
-        <v>4156</v>
+        <v>4244.3</v>
       </c>
       <c r="G85" t="n">
-        <v>378694</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5764,25 +6217,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4181.8</v>
+        <v>4211</v>
       </c>
       <c r="D86" t="n">
-        <v>4385</v>
+        <v>4220</v>
       </c>
       <c r="E86" t="n">
-        <v>4129.4</v>
+        <v>4129.3</v>
       </c>
       <c r="F86" t="n">
-        <v>4362.2</v>
+        <v>4178.1</v>
       </c>
       <c r="G86" t="n">
-        <v>992864</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5791,25 +6244,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4380</v>
+        <v>4190</v>
       </c>
       <c r="D87" t="n">
-        <v>4478.3</v>
+        <v>4324.4</v>
       </c>
       <c r="E87" t="n">
-        <v>4280.1</v>
+        <v>4190</v>
       </c>
       <c r="F87" t="n">
-        <v>4395.7</v>
+        <v>4257.3</v>
       </c>
       <c r="G87" t="n">
-        <v>960643</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5818,25 +6271,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4500</v>
+        <v>4290</v>
       </c>
       <c r="D88" t="n">
-        <v>4544</v>
+        <v>4383</v>
       </c>
       <c r="E88" t="n">
-        <v>4322</v>
+        <v>4266</v>
       </c>
       <c r="F88" t="n">
-        <v>4364.1</v>
+        <v>4288.7</v>
       </c>
       <c r="G88" t="n">
-        <v>1616021</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5845,25 +6298,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4340.7</v>
+        <v>4299</v>
       </c>
       <c r="D89" t="n">
-        <v>4341.8</v>
+        <v>4340</v>
       </c>
       <c r="E89" t="n">
-        <v>4175.5</v>
+        <v>4216</v>
       </c>
       <c r="F89" t="n">
-        <v>4195.2</v>
+        <v>4243.8</v>
       </c>
       <c r="G89" t="n">
-        <v>648341</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5872,25 +6325,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4300</v>
+        <v>4201.9</v>
       </c>
       <c r="D90" t="n">
-        <v>4598</v>
+        <v>4222</v>
       </c>
       <c r="E90" t="n">
-        <v>4252</v>
+        <v>4115</v>
       </c>
       <c r="F90" t="n">
-        <v>4524</v>
+        <v>4156</v>
       </c>
       <c r="G90" t="n">
-        <v>4510774</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5899,25 +6352,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4560.4</v>
+        <v>4181.8</v>
       </c>
       <c r="D91" t="n">
-        <v>4740</v>
+        <v>4385</v>
       </c>
       <c r="E91" t="n">
-        <v>4540</v>
+        <v>4129.4</v>
       </c>
       <c r="F91" t="n">
-        <v>4586</v>
+        <v>4362.2</v>
       </c>
       <c r="G91" t="n">
-        <v>2334958</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5926,25 +6379,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4609</v>
+        <v>4380</v>
       </c>
       <c r="D92" t="n">
-        <v>4780</v>
+        <v>4478.3</v>
       </c>
       <c r="E92" t="n">
-        <v>4593.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F92" t="n">
-        <v>4762.2</v>
+        <v>4395.7</v>
       </c>
       <c r="G92" t="n">
-        <v>1899271</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5953,187 +6406,187 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4820.7</v>
+        <v>4500</v>
       </c>
       <c r="D93" t="n">
-        <v>4880</v>
+        <v>4544</v>
       </c>
       <c r="E93" t="n">
-        <v>4725</v>
+        <v>4322</v>
       </c>
       <c r="F93" t="n">
-        <v>4871.1</v>
+        <v>4364.1</v>
       </c>
       <c r="G93" t="n">
-        <v>880334</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1417</v>
+        <v>4340.7</v>
       </c>
       <c r="D94" t="n">
-        <v>1436</v>
+        <v>4341.8</v>
       </c>
       <c r="E94" t="n">
-        <v>1410.1</v>
+        <v>4175.5</v>
       </c>
       <c r="F94" t="n">
-        <v>1423.9</v>
+        <v>4195.2</v>
       </c>
       <c r="G94" t="n">
-        <v>623969</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1428</v>
+        <v>4300</v>
       </c>
       <c r="D95" t="n">
-        <v>1428</v>
+        <v>4598</v>
       </c>
       <c r="E95" t="n">
-        <v>1351.5</v>
+        <v>4252</v>
       </c>
       <c r="F95" t="n">
-        <v>1359.1</v>
+        <v>4524</v>
       </c>
       <c r="G95" t="n">
-        <v>808190</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1349.8</v>
+        <v>4560.4</v>
       </c>
       <c r="D96" t="n">
-        <v>1357.8</v>
+        <v>4740</v>
       </c>
       <c r="E96" t="n">
-        <v>1330.1</v>
+        <v>4540</v>
       </c>
       <c r="F96" t="n">
-        <v>1340.8</v>
+        <v>4586</v>
       </c>
       <c r="G96" t="n">
-        <v>345535</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1340.8</v>
+        <v>4609</v>
       </c>
       <c r="D97" t="n">
-        <v>1387.7</v>
+        <v>4780</v>
       </c>
       <c r="E97" t="n">
-        <v>1316</v>
+        <v>4593.1</v>
       </c>
       <c r="F97" t="n">
-        <v>1374.4</v>
+        <v>4762.2</v>
       </c>
       <c r="G97" t="n">
-        <v>974660</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1372.9</v>
+        <v>4820.7</v>
       </c>
       <c r="D98" t="n">
-        <v>1390</v>
+        <v>4933</v>
       </c>
       <c r="E98" t="n">
-        <v>1355.1</v>
+        <v>4725</v>
       </c>
       <c r="F98" t="n">
-        <v>1363.5</v>
+        <v>4893.8</v>
       </c>
       <c r="G98" t="n">
-        <v>479123</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1363</v>
+        <v>4900</v>
       </c>
       <c r="D99" t="n">
-        <v>1392</v>
+        <v>4980</v>
       </c>
       <c r="E99" t="n">
-        <v>1355.1</v>
+        <v>4860</v>
       </c>
       <c r="F99" t="n">
-        <v>1380</v>
+        <v>4917.1</v>
       </c>
       <c r="G99" t="n">
-        <v>616767</v>
+        <v>658285</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6142,25 +6595,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1360</v>
+        <v>1417</v>
       </c>
       <c r="D100" t="n">
-        <v>1368</v>
+        <v>1436</v>
       </c>
       <c r="E100" t="n">
-        <v>1272.1</v>
+        <v>1410.1</v>
       </c>
       <c r="F100" t="n">
-        <v>1288.3</v>
+        <v>1423.9</v>
       </c>
       <c r="G100" t="n">
-        <v>1098492</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6169,25 +6622,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1300</v>
+        <v>1428</v>
       </c>
       <c r="D101" t="n">
-        <v>1318.5</v>
+        <v>1428</v>
       </c>
       <c r="E101" t="n">
-        <v>1257</v>
+        <v>1351.5</v>
       </c>
       <c r="F101" t="n">
-        <v>1316.2</v>
+        <v>1359.1</v>
       </c>
       <c r="G101" t="n">
-        <v>1172726</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6196,25 +6649,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1317.7</v>
+        <v>1349.8</v>
       </c>
       <c r="D102" t="n">
-        <v>1319.8</v>
+        <v>1357.8</v>
       </c>
       <c r="E102" t="n">
-        <v>1270.5</v>
+        <v>1330.1</v>
       </c>
       <c r="F102" t="n">
-        <v>1306</v>
+        <v>1340.8</v>
       </c>
       <c r="G102" t="n">
-        <v>832973</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6223,25 +6676,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1319.9</v>
+        <v>1340.8</v>
       </c>
       <c r="D103" t="n">
-        <v>1355.4</v>
+        <v>1387.7</v>
       </c>
       <c r="E103" t="n">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="F103" t="n">
-        <v>1343.4</v>
+        <v>1374.4</v>
       </c>
       <c r="G103" t="n">
-        <v>1287698</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6250,25 +6703,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1379</v>
+        <v>1372.9</v>
       </c>
       <c r="D104" t="n">
-        <v>1468</v>
+        <v>1390</v>
       </c>
       <c r="E104" t="n">
-        <v>1361</v>
+        <v>1355.1</v>
       </c>
       <c r="F104" t="n">
-        <v>1377.8</v>
+        <v>1363.5</v>
       </c>
       <c r="G104" t="n">
-        <v>9950655</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6277,25 +6730,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1380.5</v>
+        <v>1363</v>
       </c>
       <c r="D105" t="n">
-        <v>1403.3</v>
+        <v>1392</v>
       </c>
       <c r="E105" t="n">
-        <v>1363</v>
+        <v>1355.1</v>
       </c>
       <c r="F105" t="n">
-        <v>1366.8</v>
+        <v>1380</v>
       </c>
       <c r="G105" t="n">
-        <v>1567542</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6304,25 +6757,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="D106" t="n">
-        <v>1397.5</v>
+        <v>1368</v>
       </c>
       <c r="E106" t="n">
-        <v>1351.6</v>
+        <v>1272.1</v>
       </c>
       <c r="F106" t="n">
-        <v>1360.6</v>
+        <v>1288.3</v>
       </c>
       <c r="G106" t="n">
-        <v>1098353</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6331,46 +6784,235 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1360.6</v>
+        <v>1300</v>
       </c>
       <c r="D107" t="n">
-        <v>1428</v>
+        <v>1318.5</v>
       </c>
       <c r="E107" t="n">
-        <v>1354.5</v>
+        <v>1257</v>
       </c>
       <c r="F107" t="n">
-        <v>1421.6</v>
+        <v>1316.2</v>
       </c>
       <c r="G107" t="n">
-        <v>2055261</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G108" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G110" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="C114" t="n">
         <v>1429.6</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D114" t="n">
         <v>1453</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E114" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E115" t="n">
         <v>1422</v>
       </c>
-      <c r="F108" t="n">
-        <v>1438.3</v>
-      </c>
-      <c r="G108" t="n">
-        <v>766501</v>
+      <c r="F115" t="n">
+        <v>1436.7</v>
+      </c>
+      <c r="G115" t="n">
+        <v>651685</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +7026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6494,6 +7136,21 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 06 Aug 2026 06:11</t>
+          <t>Generated 07 Aug 2026 05:14</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -632,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>7.52</v>
+        <v>7.28</v>
       </c>
       <c r="D3" t="n">
         <v>7.64</v>
@@ -644,10 +644,10 @@
         <v>20.67</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.53</v>
+        <v>-2.35</v>
       </c>
       <c r="H3" t="n">
-        <v>6.41</v>
+        <v>6.65</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1983,6 +1983,192 @@
         <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>193.54</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>205.32</v>
+      </c>
+      <c r="I23" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="K23" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>248.28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>102.43</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1638.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1541.87</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1734.53</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1830.86</v>
+      </c>
+      <c r="M24" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>97</v>
+      </c>
+      <c r="F25" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="K25" t="n">
+        <v>401.37</v>
+      </c>
+      <c r="L25" t="n">
+        <v>422.44</v>
+      </c>
+      <c r="M25" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -1999,7 +2185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2680,6 +2866,105 @@
       </c>
       <c r="I22" t="n">
         <v>421.64</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>205.32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-10.46</v>
+      </c>
+      <c r="G23" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="H23" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>248.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1638.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1541.87</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="G24" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1734.53</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1830.86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="H25" t="n">
+        <v>401.37</v>
+      </c>
+      <c r="I25" t="n">
+        <v>422.44</v>
       </c>
     </row>
   </sheetData>
@@ -2693,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2791,7 +3076,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2811,7 +3096,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209.85</v>
+        <v>205.32</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2819,16 +3104,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.76</v>
+        <v>-2.1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -2843,7 +3128,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2863,7 +3148,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1633.6</v>
+        <v>1638.2</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2871,16 +3156,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.95</v>
+        <v>-1.97</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -2895,7 +3180,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2915,7 +3200,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>378.9</v>
+        <v>380.3</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2923,16 +3208,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -2947,7 +3232,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2967,26 +3252,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>4.8</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.39</v>
+        <v>-1.31</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -3001,12 +3286,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3021,26 +3306,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4893.8</v>
+        <v>1620</v>
       </c>
       <c r="G6" t="n">
-        <v>0.48</v>
+        <v>1.12</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.45</v>
+        <v>-0.99</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -3055,12 +3340,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3075,26 +3360,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1642</v>
+        <v>378.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.46</v>
+        <v>-0.24</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -3109,7 +3394,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3129,26 +3414,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G8" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>5.26</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -3163,7 +3448,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3175,7 +3460,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3183,26 +3468,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4762.2</v>
+        <v>4893.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.76</v>
+        <v>0.48</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>4.57</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -3217,12 +3502,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3237,26 +3522,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G10" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.61</v>
+        <v>-2.32</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -3271,19 +3556,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3291,32 +3576,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4586</v>
+        <v>202.78</v>
       </c>
       <c r="G11" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>8.59</v>
+        <v>5.26</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -3325,19 +3610,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3345,26 +3630,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1647</v>
+        <v>4762.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>4.57</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.75</v>
+        <v>-3.55</v>
       </c>
       <c r="N12" t="n">
         <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -3379,19 +3664,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3399,26 +3684,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G13" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>7.31</v>
+        <v>2.14</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -3433,12 +3718,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3453,34 +3738,32 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1377.8</v>
+        <v>4586</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.27</v>
-      </c>
+        <v>3.84</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>6.55</v>
+        <v>8.59</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -3489,7 +3772,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3509,28 +3792,26 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-1.53</v>
-      </c>
+        <v>-0.06</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.47</v>
+        <v>-2.62</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -3545,19 +3826,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3565,28 +3846,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.47</v>
-      </c>
+        <v>4.48</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>4.23</v>
+        <v>7.31</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -3601,12 +3880,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3621,47 +3900,55 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H17" t="n">
-        <v>9.65</v>
+        <v>2.92</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>10.28</v>
+        <v>6.55</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3669,35 +3956,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4364.1</v>
+        <v>1659</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>14.11</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.32</v>
+        <v>-3.32</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3709,7 +4004,7 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3720,10 +4015,10 @@
         <v>1781.3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H19" t="n">
-        <v>3.01</v>
+        <v>3.47</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -3732,32 +4027,40 @@
         <v>4.23</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3765,22 +4068,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G20" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H20" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>25.21</v>
+        <v>10.28</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N20" t="n">
         <v>8</v>
@@ -3793,19 +4096,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3813,22 +4116,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>188.39</v>
+        <v>4364.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H21" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>13.3</v>
+        <v>14.11</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N21" t="n">
         <v>8</v>
@@ -3841,19 +4144,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3861,22 +4164,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>8.34</v>
+        <v>3.01</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>13.29</v>
+        <v>4.23</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.01</v>
+        <v>-1.52</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
@@ -3885,6 +4188,150 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H23" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>96</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>92</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3897,7 +4344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4333,46 +4780,46 @@
         <v>1641.9</v>
       </c>
       <c r="E16" t="n">
-        <v>1618.1</v>
+        <v>1603.9</v>
       </c>
       <c r="F16" t="n">
-        <v>1633.6</v>
+        <v>1620</v>
       </c>
       <c r="G16" t="n">
-        <v>362903</v>
+        <v>938596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1188.4</v>
+        <v>1620</v>
       </c>
       <c r="D17" t="n">
-        <v>1207.9</v>
+        <v>1640.8</v>
       </c>
       <c r="E17" t="n">
-        <v>1158</v>
+        <v>1606</v>
       </c>
       <c r="F17" t="n">
-        <v>1201.8</v>
+        <v>1638.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3482939</v>
+        <v>420083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4381,25 +4828,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F18" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G18" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4408,25 +4855,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D19" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E19" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F19" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G19" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4435,25 +4882,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D20" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E20" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F20" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G20" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4462,25 +4909,25 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F21" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D21" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G21" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4489,25 +4936,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F22" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4516,25 +4963,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D23" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E23" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F23" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4543,25 +4990,25 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F24" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D24" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G24" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4570,25 +5017,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F25" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G25" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4597,25 +5044,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D26" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E26" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4624,25 +5071,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D27" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F27" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G27" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4651,25 +5098,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D28" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E28" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G28" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4678,25 +5125,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D29" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E29" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F29" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G29" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4705,25 +5152,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D30" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E30" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G30" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4732,25 +5179,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D31" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E31" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G31" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4759,25 +5206,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D32" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F32" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G32" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4786,25 +5233,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D33" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E33" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F33" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G33" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4813,79 +5260,79 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F34" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D34" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1454.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1458.3</v>
-      </c>
       <c r="G34" t="n">
-        <v>3132810</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>211.95</v>
+        <v>1470.8</v>
       </c>
       <c r="D35" t="n">
-        <v>214.55</v>
+        <v>1505</v>
       </c>
       <c r="E35" t="n">
-        <v>206.1</v>
+        <v>1440</v>
       </c>
       <c r="F35" t="n">
-        <v>212.78</v>
+        <v>1453.2</v>
       </c>
       <c r="G35" t="n">
-        <v>12863408</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>214.3</v>
+        <v>1450</v>
       </c>
       <c r="D36" t="n">
-        <v>223.41</v>
+        <v>1494.4</v>
       </c>
       <c r="E36" t="n">
-        <v>214.3</v>
+        <v>1446</v>
       </c>
       <c r="F36" t="n">
-        <v>223.08</v>
+        <v>1493.2</v>
       </c>
       <c r="G36" t="n">
-        <v>32151413</v>
+        <v>1551670</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4894,25 +5341,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D37" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E37" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F37" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G37" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4921,25 +5368,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D38" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E38" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F38" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G38" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4948,25 +5395,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D39" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E39" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F39" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G39" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4975,25 +5422,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D40" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E40" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F40" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G40" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5002,25 +5449,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D41" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E41" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F41" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G41" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5029,25 +5476,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D42" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E42" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F42" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G42" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5056,25 +5503,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D43" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E43" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F43" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G43" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5083,25 +5530,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D44" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E44" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F44" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G44" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5110,25 +5557,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D45" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E45" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F45" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G45" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5137,25 +5584,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D46" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E46" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F46" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G46" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5164,25 +5611,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D47" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E47" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F47" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G47" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5191,25 +5638,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D48" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E48" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F48" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G48" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5218,25 +5665,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D49" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E49" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F49" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G49" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5245,25 +5692,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D50" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E50" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F50" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G50" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5272,25 +5719,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D51" t="n">
-        <v>212.91</v>
+        <v>203.61</v>
       </c>
       <c r="E51" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F51" t="n">
-        <v>212.23</v>
+        <v>202.52</v>
       </c>
       <c r="G51" t="n">
-        <v>37479685</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5299,106 +5746,106 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>212.4</v>
+        <v>202.4</v>
       </c>
       <c r="D52" t="n">
-        <v>213.45</v>
+        <v>207</v>
       </c>
       <c r="E52" t="n">
-        <v>208.25</v>
+        <v>200.22</v>
       </c>
       <c r="F52" t="n">
-        <v>209.85</v>
+        <v>202.78</v>
       </c>
       <c r="G52" t="n">
-        <v>9791415</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1554.3</v>
+        <v>205.8</v>
       </c>
       <c r="D53" t="n">
-        <v>1569</v>
+        <v>212.91</v>
       </c>
       <c r="E53" t="n">
-        <v>1551.3</v>
+        <v>205.03</v>
       </c>
       <c r="F53" t="n">
-        <v>1557.6</v>
+        <v>212.23</v>
       </c>
       <c r="G53" t="n">
-        <v>1001677</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1560.4</v>
+        <v>212.4</v>
       </c>
       <c r="D54" t="n">
-        <v>1561</v>
+        <v>213.45</v>
       </c>
       <c r="E54" t="n">
-        <v>1520.4</v>
+        <v>203</v>
       </c>
       <c r="F54" t="n">
-        <v>1529.8</v>
+        <v>203.67</v>
       </c>
       <c r="G54" t="n">
-        <v>1011017</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1534.9</v>
+        <v>203.98</v>
       </c>
       <c r="D55" t="n">
-        <v>1572.2</v>
+        <v>206.7</v>
       </c>
       <c r="E55" t="n">
-        <v>1527.2</v>
+        <v>201</v>
       </c>
       <c r="F55" t="n">
-        <v>1558.9</v>
+        <v>205.32</v>
       </c>
       <c r="G55" t="n">
-        <v>1235837</v>
+        <v>6445459</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,25 +5854,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1559.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D56" t="n">
-        <v>1600.1</v>
+        <v>1569</v>
       </c>
       <c r="E56" t="n">
-        <v>1557</v>
+        <v>1551.3</v>
       </c>
       <c r="F56" t="n">
-        <v>1593.2</v>
+        <v>1557.6</v>
       </c>
       <c r="G56" t="n">
-        <v>1871739</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5434,25 +5881,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1591</v>
+        <v>1560.4</v>
       </c>
       <c r="D57" t="n">
-        <v>1593.2</v>
+        <v>1561</v>
       </c>
       <c r="E57" t="n">
-        <v>1566</v>
+        <v>1520.4</v>
       </c>
       <c r="F57" t="n">
-        <v>1577.8</v>
+        <v>1529.8</v>
       </c>
       <c r="G57" t="n">
-        <v>1183077</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,25 +5908,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1577.7</v>
+        <v>1534.9</v>
       </c>
       <c r="D58" t="n">
-        <v>1586.1</v>
+        <v>1572.2</v>
       </c>
       <c r="E58" t="n">
-        <v>1561.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F58" t="n">
-        <v>1568.3</v>
+        <v>1558.9</v>
       </c>
       <c r="G58" t="n">
-        <v>1098268</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5488,25 +5935,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1560</v>
+        <v>1559.7</v>
       </c>
       <c r="D59" t="n">
-        <v>1610</v>
+        <v>1600.1</v>
       </c>
       <c r="E59" t="n">
-        <v>1554.9</v>
+        <v>1557</v>
       </c>
       <c r="F59" t="n">
-        <v>1601.2</v>
+        <v>1593.2</v>
       </c>
       <c r="G59" t="n">
-        <v>2647403</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5515,25 +5962,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1624.8</v>
+        <v>1591</v>
       </c>
       <c r="D60" t="n">
-        <v>1734.5</v>
+        <v>1593.2</v>
       </c>
       <c r="E60" t="n">
-        <v>1617.1</v>
+        <v>1566</v>
       </c>
       <c r="F60" t="n">
-        <v>1713.4</v>
+        <v>1577.8</v>
       </c>
       <c r="G60" t="n">
-        <v>7989771</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5542,25 +5989,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1713</v>
+        <v>1577.7</v>
       </c>
       <c r="D61" t="n">
-        <v>1762</v>
+        <v>1586.1</v>
       </c>
       <c r="E61" t="n">
-        <v>1707.7</v>
+        <v>1561.1</v>
       </c>
       <c r="F61" t="n">
-        <v>1758.9</v>
+        <v>1568.3</v>
       </c>
       <c r="G61" t="n">
-        <v>4407907</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5569,25 +6016,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1762</v>
+        <v>1560</v>
       </c>
       <c r="D62" t="n">
-        <v>1797.9</v>
+        <v>1610</v>
       </c>
       <c r="E62" t="n">
-        <v>1754.3</v>
+        <v>1554.9</v>
       </c>
       <c r="F62" t="n">
-        <v>1781.3</v>
+        <v>1601.2</v>
       </c>
       <c r="G62" t="n">
-        <v>3000811</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5596,25 +6043,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1785</v>
+        <v>1624.8</v>
       </c>
       <c r="D63" t="n">
-        <v>1798.9</v>
+        <v>1734.5</v>
       </c>
       <c r="E63" t="n">
-        <v>1773.3</v>
+        <v>1617.1</v>
       </c>
       <c r="F63" t="n">
-        <v>1781.3</v>
+        <v>1713.4</v>
       </c>
       <c r="G63" t="n">
-        <v>2402202</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5623,25 +6070,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1785</v>
+        <v>1713</v>
       </c>
       <c r="D64" t="n">
-        <v>1826.6</v>
+        <v>1762</v>
       </c>
       <c r="E64" t="n">
-        <v>1785</v>
+        <v>1707.7</v>
       </c>
       <c r="F64" t="n">
-        <v>1816.2</v>
+        <v>1758.9</v>
       </c>
       <c r="G64" t="n">
-        <v>2502579</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5650,25 +6097,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1821</v>
+        <v>1762</v>
       </c>
       <c r="D65" t="n">
-        <v>1838.3</v>
+        <v>1797.9</v>
       </c>
       <c r="E65" t="n">
-        <v>1789.1</v>
+        <v>1754.3</v>
       </c>
       <c r="F65" t="n">
-        <v>1811.4</v>
+        <v>1781.3</v>
       </c>
       <c r="G65" t="n">
-        <v>1919384</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5677,25 +6124,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1811</v>
+        <v>1785</v>
       </c>
       <c r="D66" t="n">
-        <v>1850</v>
+        <v>1798.9</v>
       </c>
       <c r="E66" t="n">
-        <v>1806.1</v>
+        <v>1773.3</v>
       </c>
       <c r="F66" t="n">
-        <v>1850</v>
+        <v>1781.3</v>
       </c>
       <c r="G66" t="n">
-        <v>1405192</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5704,25 +6151,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1854</v>
+        <v>1785</v>
       </c>
       <c r="D67" t="n">
-        <v>1856.6</v>
+        <v>1826.6</v>
       </c>
       <c r="E67" t="n">
-        <v>1834.5</v>
+        <v>1785</v>
       </c>
       <c r="F67" t="n">
-        <v>1835</v>
+        <v>1816.2</v>
       </c>
       <c r="G67" t="n">
-        <v>2090998</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5731,133 +6178,133 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1843</v>
+        <v>1821</v>
       </c>
       <c r="D68" t="n">
-        <v>1854.9</v>
+        <v>1838.3</v>
       </c>
       <c r="E68" t="n">
-        <v>1837</v>
+        <v>1789.1</v>
       </c>
       <c r="F68" t="n">
-        <v>1843.2</v>
+        <v>1811.4</v>
       </c>
       <c r="G68" t="n">
-        <v>1228707</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>344</v>
+        <v>1811</v>
       </c>
       <c r="D69" t="n">
-        <v>346.3</v>
+        <v>1850</v>
       </c>
       <c r="E69" t="n">
-        <v>341.25</v>
+        <v>1806.1</v>
       </c>
       <c r="F69" t="n">
-        <v>342.9</v>
+        <v>1850</v>
       </c>
       <c r="G69" t="n">
-        <v>4465145</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>344.2</v>
+        <v>1854</v>
       </c>
       <c r="D70" t="n">
-        <v>347.75</v>
+        <v>1856.6</v>
       </c>
       <c r="E70" t="n">
-        <v>339.95</v>
+        <v>1834.5</v>
       </c>
       <c r="F70" t="n">
-        <v>342.4</v>
+        <v>1835</v>
       </c>
       <c r="G70" t="n">
-        <v>3803051</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>346</v>
+        <v>1843</v>
       </c>
       <c r="D71" t="n">
-        <v>351</v>
+        <v>1854.9</v>
       </c>
       <c r="E71" t="n">
-        <v>343.65</v>
+        <v>1837</v>
       </c>
       <c r="F71" t="n">
-        <v>346</v>
+        <v>1843.2</v>
       </c>
       <c r="G71" t="n">
-        <v>5175178</v>
+        <v>1228707</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>341.8</v>
+        <v>1838</v>
       </c>
       <c r="D72" t="n">
-        <v>344.9</v>
+        <v>1850</v>
       </c>
       <c r="E72" t="n">
-        <v>339.65</v>
+        <v>1833.2</v>
       </c>
       <c r="F72" t="n">
-        <v>343.9</v>
+        <v>1848.5</v>
       </c>
       <c r="G72" t="n">
-        <v>2253982</v>
+        <v>587992</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5866,25 +6313,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>345.1</v>
+        <v>344</v>
       </c>
       <c r="D73" t="n">
-        <v>346.05</v>
+        <v>346.3</v>
       </c>
       <c r="E73" t="n">
-        <v>338.35</v>
+        <v>341.25</v>
       </c>
       <c r="F73" t="n">
-        <v>339.35</v>
+        <v>342.9</v>
       </c>
       <c r="G73" t="n">
-        <v>3868006</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5893,25 +6340,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>339.4</v>
+        <v>344.2</v>
       </c>
       <c r="D74" t="n">
-        <v>340.2</v>
+        <v>347.75</v>
       </c>
       <c r="E74" t="n">
-        <v>333</v>
+        <v>339.95</v>
       </c>
       <c r="F74" t="n">
-        <v>334.55</v>
+        <v>342.4</v>
       </c>
       <c r="G74" t="n">
-        <v>3721274</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5920,25 +6367,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D75" t="n">
-        <v>346.1</v>
+        <v>351</v>
       </c>
       <c r="E75" t="n">
-        <v>332</v>
+        <v>343.65</v>
       </c>
       <c r="F75" t="n">
-        <v>344.7</v>
+        <v>346</v>
       </c>
       <c r="G75" t="n">
-        <v>5431501</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5947,25 +6394,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>345.5</v>
+        <v>341.8</v>
       </c>
       <c r="D76" t="n">
-        <v>349.65</v>
+        <v>344.9</v>
       </c>
       <c r="E76" t="n">
-        <v>342.6</v>
+        <v>339.65</v>
       </c>
       <c r="F76" t="n">
-        <v>347.65</v>
+        <v>343.9</v>
       </c>
       <c r="G76" t="n">
-        <v>6318472</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5974,25 +6421,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>352</v>
+        <v>345.1</v>
       </c>
       <c r="D77" t="n">
-        <v>355.75</v>
+        <v>346.05</v>
       </c>
       <c r="E77" t="n">
-        <v>347.65</v>
+        <v>338.35</v>
       </c>
       <c r="F77" t="n">
-        <v>350.05</v>
+        <v>339.35</v>
       </c>
       <c r="G77" t="n">
-        <v>7186013</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6001,25 +6448,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>357.95</v>
+        <v>339.4</v>
       </c>
       <c r="D78" t="n">
-        <v>369</v>
+        <v>340.2</v>
       </c>
       <c r="E78" t="n">
-        <v>353.5</v>
+        <v>333</v>
       </c>
       <c r="F78" t="n">
-        <v>369</v>
+        <v>334.55</v>
       </c>
       <c r="G78" t="n">
-        <v>12541474</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6028,25 +6475,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="D79" t="n">
-        <v>382.45</v>
+        <v>346.1</v>
       </c>
       <c r="E79" t="n">
-        <v>367.15</v>
+        <v>332</v>
       </c>
       <c r="F79" t="n">
-        <v>377</v>
+        <v>344.7</v>
       </c>
       <c r="G79" t="n">
-        <v>15775994</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6055,25 +6502,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>381</v>
+        <v>345.5</v>
       </c>
       <c r="D80" t="n">
-        <v>383.9</v>
+        <v>349.65</v>
       </c>
       <c r="E80" t="n">
-        <v>375.15</v>
+        <v>342.6</v>
       </c>
       <c r="F80" t="n">
-        <v>381</v>
+        <v>347.65</v>
       </c>
       <c r="G80" t="n">
-        <v>8940938</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6082,160 +6529,160 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="D81" t="n">
-        <v>385.05</v>
+        <v>355.75</v>
       </c>
       <c r="E81" t="n">
-        <v>378.1</v>
+        <v>347.65</v>
       </c>
       <c r="F81" t="n">
-        <v>378.9</v>
+        <v>350.05</v>
       </c>
       <c r="G81" t="n">
-        <v>3486554</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4389.8</v>
+        <v>357.95</v>
       </c>
       <c r="D82" t="n">
-        <v>4485</v>
+        <v>369</v>
       </c>
       <c r="E82" t="n">
-        <v>4361.9</v>
+        <v>353.5</v>
       </c>
       <c r="F82" t="n">
-        <v>4398.1</v>
+        <v>369</v>
       </c>
       <c r="G82" t="n">
-        <v>1347378</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4422</v>
+        <v>373</v>
       </c>
       <c r="D83" t="n">
-        <v>4495</v>
+        <v>382.45</v>
       </c>
       <c r="E83" t="n">
-        <v>4358</v>
+        <v>367.15</v>
       </c>
       <c r="F83" t="n">
-        <v>4371.4</v>
+        <v>377</v>
       </c>
       <c r="G83" t="n">
-        <v>902264</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4387.7</v>
+        <v>381</v>
       </c>
       <c r="D84" t="n">
-        <v>4404</v>
+        <v>383.9</v>
       </c>
       <c r="E84" t="n">
-        <v>4281.9</v>
+        <v>375.15</v>
       </c>
       <c r="F84" t="n">
-        <v>4304.2</v>
+        <v>381</v>
       </c>
       <c r="G84" t="n">
-        <v>463349</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4285</v>
+        <v>385</v>
       </c>
       <c r="D85" t="n">
-        <v>4317</v>
+        <v>385.05</v>
       </c>
       <c r="E85" t="n">
-        <v>4220</v>
+        <v>378.1</v>
       </c>
       <c r="F85" t="n">
-        <v>4244.3</v>
+        <v>378.9</v>
       </c>
       <c r="G85" t="n">
-        <v>398348</v>
+        <v>3486554</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4211</v>
+        <v>382.5</v>
       </c>
       <c r="D86" t="n">
-        <v>4220</v>
+        <v>382.85</v>
       </c>
       <c r="E86" t="n">
-        <v>4129.3</v>
+        <v>378</v>
       </c>
       <c r="F86" t="n">
-        <v>4178.1</v>
+        <v>380.3</v>
       </c>
       <c r="G86" t="n">
-        <v>470046</v>
+        <v>1643582</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6244,25 +6691,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4190</v>
+        <v>4389.8</v>
       </c>
       <c r="D87" t="n">
-        <v>4324.4</v>
+        <v>4485</v>
       </c>
       <c r="E87" t="n">
-        <v>4190</v>
+        <v>4361.9</v>
       </c>
       <c r="F87" t="n">
-        <v>4257.3</v>
+        <v>4398.1</v>
       </c>
       <c r="G87" t="n">
-        <v>633457</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6271,25 +6718,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4290</v>
+        <v>4422</v>
       </c>
       <c r="D88" t="n">
-        <v>4383</v>
+        <v>4495</v>
       </c>
       <c r="E88" t="n">
-        <v>4266</v>
+        <v>4358</v>
       </c>
       <c r="F88" t="n">
-        <v>4288.7</v>
+        <v>4371.4</v>
       </c>
       <c r="G88" t="n">
-        <v>835107</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6298,25 +6745,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4299</v>
+        <v>4387.7</v>
       </c>
       <c r="D89" t="n">
-        <v>4340</v>
+        <v>4404</v>
       </c>
       <c r="E89" t="n">
-        <v>4216</v>
+        <v>4281.9</v>
       </c>
       <c r="F89" t="n">
-        <v>4243.8</v>
+        <v>4304.2</v>
       </c>
       <c r="G89" t="n">
-        <v>422024</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6325,25 +6772,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4201.9</v>
+        <v>4285</v>
       </c>
       <c r="D90" t="n">
-        <v>4222</v>
+        <v>4317</v>
       </c>
       <c r="E90" t="n">
-        <v>4115</v>
+        <v>4220</v>
       </c>
       <c r="F90" t="n">
-        <v>4156</v>
+        <v>4244.3</v>
       </c>
       <c r="G90" t="n">
-        <v>378694</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6352,25 +6799,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4181.8</v>
+        <v>4211</v>
       </c>
       <c r="D91" t="n">
-        <v>4385</v>
+        <v>4220</v>
       </c>
       <c r="E91" t="n">
-        <v>4129.4</v>
+        <v>4129.3</v>
       </c>
       <c r="F91" t="n">
-        <v>4362.2</v>
+        <v>4178.1</v>
       </c>
       <c r="G91" t="n">
-        <v>992864</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6379,25 +6826,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4380</v>
+        <v>4190</v>
       </c>
       <c r="D92" t="n">
-        <v>4478.3</v>
+        <v>4324.4</v>
       </c>
       <c r="E92" t="n">
-        <v>4280.1</v>
+        <v>4190</v>
       </c>
       <c r="F92" t="n">
-        <v>4395.7</v>
+        <v>4257.3</v>
       </c>
       <c r="G92" t="n">
-        <v>960643</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6406,25 +6853,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4500</v>
+        <v>4290</v>
       </c>
       <c r="D93" t="n">
-        <v>4544</v>
+        <v>4383</v>
       </c>
       <c r="E93" t="n">
-        <v>4322</v>
+        <v>4266</v>
       </c>
       <c r="F93" t="n">
-        <v>4364.1</v>
+        <v>4288.7</v>
       </c>
       <c r="G93" t="n">
-        <v>1616021</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6433,25 +6880,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4340.7</v>
+        <v>4299</v>
       </c>
       <c r="D94" t="n">
-        <v>4341.8</v>
+        <v>4340</v>
       </c>
       <c r="E94" t="n">
-        <v>4175.5</v>
+        <v>4216</v>
       </c>
       <c r="F94" t="n">
-        <v>4195.2</v>
+        <v>4243.8</v>
       </c>
       <c r="G94" t="n">
-        <v>648341</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6460,25 +6907,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4300</v>
+        <v>4201.9</v>
       </c>
       <c r="D95" t="n">
-        <v>4598</v>
+        <v>4222</v>
       </c>
       <c r="E95" t="n">
-        <v>4252</v>
+        <v>4115</v>
       </c>
       <c r="F95" t="n">
-        <v>4524</v>
+        <v>4156</v>
       </c>
       <c r="G95" t="n">
-        <v>4510774</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6487,25 +6934,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4560.4</v>
+        <v>4181.8</v>
       </c>
       <c r="D96" t="n">
-        <v>4740</v>
+        <v>4385</v>
       </c>
       <c r="E96" t="n">
-        <v>4540</v>
+        <v>4129.4</v>
       </c>
       <c r="F96" t="n">
-        <v>4586</v>
+        <v>4362.2</v>
       </c>
       <c r="G96" t="n">
-        <v>2334958</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6514,25 +6961,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4609</v>
+        <v>4380</v>
       </c>
       <c r="D97" t="n">
-        <v>4780</v>
+        <v>4478.3</v>
       </c>
       <c r="E97" t="n">
-        <v>4593.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F97" t="n">
-        <v>4762.2</v>
+        <v>4395.7</v>
       </c>
       <c r="G97" t="n">
-        <v>1899271</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6541,25 +6988,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4820.7</v>
+        <v>4500</v>
       </c>
       <c r="D98" t="n">
-        <v>4933</v>
+        <v>4544</v>
       </c>
       <c r="E98" t="n">
-        <v>4725</v>
+        <v>4322</v>
       </c>
       <c r="F98" t="n">
-        <v>4893.8</v>
+        <v>4364.1</v>
       </c>
       <c r="G98" t="n">
-        <v>1924204</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6568,187 +7015,187 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4900</v>
+        <v>4340.7</v>
       </c>
       <c r="D99" t="n">
-        <v>4980</v>
+        <v>4341.8</v>
       </c>
       <c r="E99" t="n">
-        <v>4860</v>
+        <v>4175.5</v>
       </c>
       <c r="F99" t="n">
-        <v>4917.1</v>
+        <v>4195.2</v>
       </c>
       <c r="G99" t="n">
-        <v>658285</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1417</v>
+        <v>4300</v>
       </c>
       <c r="D100" t="n">
-        <v>1436</v>
+        <v>4598</v>
       </c>
       <c r="E100" t="n">
-        <v>1410.1</v>
+        <v>4252</v>
       </c>
       <c r="F100" t="n">
-        <v>1423.9</v>
+        <v>4524</v>
       </c>
       <c r="G100" t="n">
-        <v>623969</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1428</v>
+        <v>4560.4</v>
       </c>
       <c r="D101" t="n">
-        <v>1428</v>
+        <v>4740</v>
       </c>
       <c r="E101" t="n">
-        <v>1351.5</v>
+        <v>4540</v>
       </c>
       <c r="F101" t="n">
-        <v>1359.1</v>
+        <v>4586</v>
       </c>
       <c r="G101" t="n">
-        <v>808190</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1349.8</v>
+        <v>4609</v>
       </c>
       <c r="D102" t="n">
-        <v>1357.8</v>
+        <v>4780</v>
       </c>
       <c r="E102" t="n">
-        <v>1330.1</v>
+        <v>4593.1</v>
       </c>
       <c r="F102" t="n">
-        <v>1340.8</v>
+        <v>4762.2</v>
       </c>
       <c r="G102" t="n">
-        <v>345535</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1340.8</v>
+        <v>4820.7</v>
       </c>
       <c r="D103" t="n">
-        <v>1387.7</v>
+        <v>4933</v>
       </c>
       <c r="E103" t="n">
-        <v>1316</v>
+        <v>4725</v>
       </c>
       <c r="F103" t="n">
-        <v>1374.4</v>
+        <v>4893.8</v>
       </c>
       <c r="G103" t="n">
-        <v>974660</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1372.9</v>
+        <v>4900</v>
       </c>
       <c r="D104" t="n">
-        <v>1390</v>
+        <v>4980</v>
       </c>
       <c r="E104" t="n">
-        <v>1355.1</v>
+        <v>4860</v>
       </c>
       <c r="F104" t="n">
-        <v>1363.5</v>
+        <v>4917.1</v>
       </c>
       <c r="G104" t="n">
-        <v>479123</v>
+        <v>658285</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1363</v>
+        <v>4790</v>
       </c>
       <c r="D105" t="n">
-        <v>1392</v>
+        <v>4899</v>
       </c>
       <c r="E105" t="n">
-        <v>1355.1</v>
+        <v>4780</v>
       </c>
       <c r="F105" t="n">
-        <v>1380</v>
+        <v>4845</v>
       </c>
       <c r="G105" t="n">
-        <v>616767</v>
+        <v>377192</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6757,25 +7204,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1360</v>
+        <v>1417</v>
       </c>
       <c r="D106" t="n">
-        <v>1368</v>
+        <v>1436</v>
       </c>
       <c r="E106" t="n">
-        <v>1272.1</v>
+        <v>1410.1</v>
       </c>
       <c r="F106" t="n">
-        <v>1288.3</v>
+        <v>1423.9</v>
       </c>
       <c r="G106" t="n">
-        <v>1098492</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6784,25 +7231,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1300</v>
+        <v>1428</v>
       </c>
       <c r="D107" t="n">
-        <v>1318.5</v>
+        <v>1428</v>
       </c>
       <c r="E107" t="n">
-        <v>1257</v>
+        <v>1351.5</v>
       </c>
       <c r="F107" t="n">
-        <v>1316.2</v>
+        <v>1359.1</v>
       </c>
       <c r="G107" t="n">
-        <v>1172726</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6811,25 +7258,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1317.7</v>
+        <v>1349.8</v>
       </c>
       <c r="D108" t="n">
-        <v>1319.8</v>
+        <v>1357.8</v>
       </c>
       <c r="E108" t="n">
-        <v>1270.5</v>
+        <v>1330.1</v>
       </c>
       <c r="F108" t="n">
-        <v>1306</v>
+        <v>1340.8</v>
       </c>
       <c r="G108" t="n">
-        <v>832973</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6838,25 +7285,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1319.9</v>
+        <v>1340.8</v>
       </c>
       <c r="D109" t="n">
-        <v>1355.4</v>
+        <v>1387.7</v>
       </c>
       <c r="E109" t="n">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="F109" t="n">
-        <v>1343.4</v>
+        <v>1374.4</v>
       </c>
       <c r="G109" t="n">
-        <v>1287698</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6865,25 +7312,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1379</v>
+        <v>1372.9</v>
       </c>
       <c r="D110" t="n">
-        <v>1468</v>
+        <v>1390</v>
       </c>
       <c r="E110" t="n">
-        <v>1361</v>
+        <v>1355.1</v>
       </c>
       <c r="F110" t="n">
-        <v>1377.8</v>
+        <v>1363.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9950655</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6892,25 +7339,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1380.5</v>
+        <v>1363</v>
       </c>
       <c r="D111" t="n">
-        <v>1403.3</v>
+        <v>1392</v>
       </c>
       <c r="E111" t="n">
-        <v>1363</v>
+        <v>1355.1</v>
       </c>
       <c r="F111" t="n">
-        <v>1366.8</v>
+        <v>1380</v>
       </c>
       <c r="G111" t="n">
-        <v>1567542</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6919,25 +7366,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="D112" t="n">
-        <v>1397.5</v>
+        <v>1368</v>
       </c>
       <c r="E112" t="n">
-        <v>1351.6</v>
+        <v>1272.1</v>
       </c>
       <c r="F112" t="n">
-        <v>1360.6</v>
+        <v>1288.3</v>
       </c>
       <c r="G112" t="n">
-        <v>1098353</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6946,25 +7393,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1360.6</v>
+        <v>1300</v>
       </c>
       <c r="D113" t="n">
-        <v>1428</v>
+        <v>1318.5</v>
       </c>
       <c r="E113" t="n">
-        <v>1354.5</v>
+        <v>1257</v>
       </c>
       <c r="F113" t="n">
-        <v>1421.6</v>
+        <v>1316.2</v>
       </c>
       <c r="G113" t="n">
-        <v>2055261</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6973,46 +7420,235 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1429.6</v>
+        <v>1317.7</v>
       </c>
       <c r="D114" t="n">
-        <v>1453</v>
+        <v>1319.8</v>
       </c>
       <c r="E114" t="n">
-        <v>1419</v>
+        <v>1270.5</v>
       </c>
       <c r="F114" t="n">
-        <v>1434.1</v>
+        <v>1306</v>
       </c>
       <c r="G114" t="n">
-        <v>1243415</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G116" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="C121" t="n">
         <v>1434</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D121" t="n">
         <v>1460</v>
       </c>
-      <c r="E115" t="n">
-        <v>1422</v>
-      </c>
-      <c r="F115" t="n">
-        <v>1436.7</v>
-      </c>
-      <c r="G115" t="n">
-        <v>651685</v>
+      <c r="E121" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1413.9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1433.7</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1407.5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1427.3</v>
+      </c>
+      <c r="G122" t="n">
+        <v>146478</v>
       </c>
     </row>
   </sheetData>
@@ -7026,7 +7662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7151,6 +7787,21 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 07 Aug 2026 05:14</t>
+          <t>Generated 11 Aug 2026 04:50</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="D2" t="n">
-        <v>0.48</v>
+        <v>0.29</v>
       </c>
       <c r="E2" t="n">
-        <v>57.1</v>
+        <v>54.2</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="3">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>7.28</v>
+        <v>6.11</v>
       </c>
       <c r="D3" t="n">
-        <v>7.64</v>
+        <v>4.16</v>
       </c>
       <c r="E3" t="n">
-        <v>88.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
@@ -647,7 +647,35 @@
         <v>-2.35</v>
       </c>
       <c r="H3" t="n">
-        <v>6.65</v>
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10d</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2169,6 +2197,192 @@
         <v>1</v>
       </c>
       <c r="P25" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="n">
+        <v>195</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>211.22</v>
+      </c>
+      <c r="I26" t="n">
+        <v>191.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>231.29</v>
+      </c>
+      <c r="L26" t="n">
+        <v>251.36</v>
+      </c>
+      <c r="M26" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>4838.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4459.44</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5218.16</v>
+      </c>
+      <c r="L27" t="n">
+        <v>5597.52</v>
+      </c>
+      <c r="M27" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>99</v>
+      </c>
+      <c r="F28" t="n">
+        <v>107.89</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1652.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1559.39</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1745.81</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1839.02</v>
+      </c>
+      <c r="M28" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -2185,7 +2399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2965,6 +3179,105 @@
       </c>
       <c r="I25" t="n">
         <v>422.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>211.22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>191.15</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="H26" t="n">
+        <v>231.29</v>
+      </c>
+      <c r="I26" t="n">
+        <v>251.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4838.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4459.44</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="G27" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5218.16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5597.52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1652.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1559.39</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1745.81</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1839.02</v>
       </c>
     </row>
   </sheetData>
@@ -2978,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3076,7 +3389,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3096,7 +3409,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>205.32</v>
+        <v>211.22</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3104,16 +3417,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.67</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1</v>
+        <v>-0.77</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -3128,19 +3441,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3148,7 +3461,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1638.2</v>
+        <v>4838.8</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3156,16 +3469,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.16</v>
+        <v>2.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.97</v>
+        <v>-0.18</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -3180,19 +3493,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3200,7 +3513,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>380.3</v>
+        <v>1652.6</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3208,16 +3521,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6</v>
+        <v>-1.33</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -3232,7 +3545,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3252,26 +3565,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.8</v>
+        <v>4.14</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -3286,7 +3599,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3306,26 +3619,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.12</v>
+        <v>0.12</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>2.57</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.99</v>
+        <v>-1.48</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -3340,7 +3653,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3360,26 +3673,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>378.9</v>
+        <v>381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>3.07</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.24</v>
+        <v>-1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -3394,7 +3707,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3414,26 +3727,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>6.35</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -3448,12 +3761,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3468,26 +3781,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4893.8</v>
+        <v>1620</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>3.21</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.45</v>
+        <v>-0.99</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -3502,12 +3815,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3522,26 +3835,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>3.07</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.32</v>
+        <v>-1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -3556,7 +3869,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3576,26 +3889,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>5.26</v>
+        <v>2.06</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -3610,7 +3923,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3622,7 +3935,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3630,26 +3943,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4762.2</v>
+        <v>4890.75</v>
       </c>
       <c r="G12" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>4.57</v>
+        <v>3.97</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -3664,12 +3977,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3684,26 +3997,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G13" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.61</v>
+        <v>-2.32</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -3718,19 +4031,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3738,32 +4051,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4586</v>
+        <v>202.78</v>
       </c>
       <c r="G14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>4.66</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.16</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>8.59</v>
+        <v>6.82</v>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -3772,19 +4087,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3792,26 +4107,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>2.76</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.67</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1.76</v>
+        <v>6.85</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.62</v>
+        <v>-3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -3826,19 +4143,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3846,26 +4163,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G16" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.66</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>7.31</v>
+        <v>4.16</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -3880,12 +4199,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3900,34 +4219,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H17" t="n">
-        <v>2.92</v>
+        <v>6.98</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>6.55</v>
+        <v>10.95</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -3936,7 +4255,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3956,28 +4275,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.32</v>
+        <v>-2.62</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -3992,19 +4311,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4012,34 +4331,34 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H19" t="n">
-        <v>3.47</v>
+        <v>11.45</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>4.23</v>
+        <v>13.41</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -4048,12 +4367,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4068,47 +4387,55 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H20" t="n">
-        <v>9.65</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>10.28</v>
+        <v>11.99</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4116,35 +4443,43 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4364.1</v>
+        <v>1659</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H21" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>14.11</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.32</v>
+        <v>-3.32</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4156,7 +4491,7 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4167,44 +4502,52 @@
         <v>1781.3</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H22" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>4.23</v>
+        <v>5.02</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4212,25 +4555,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G23" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H23" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>25.21</v>
+        <v>11.9</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -4240,19 +4583,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4260,25 +4603,25 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G24" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H24" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>13.3</v>
+        <v>16.59</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -4288,19 +4631,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4308,30 +4651,180 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.34</v>
+        <v>3.01</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>13.29</v>
+        <v>5.02</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.01</v>
+        <v>-1.52</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H26" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I26" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N26" t="n">
+        <v>11</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>96</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>92</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4344,7 +4837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4804,76 +5297,76 @@
         <v>1620</v>
       </c>
       <c r="D17" t="n">
-        <v>1640.8</v>
+        <v>1647</v>
       </c>
       <c r="E17" t="n">
         <v>1606</v>
       </c>
       <c r="F17" t="n">
-        <v>1638.2</v>
+        <v>1630.1</v>
       </c>
       <c r="G17" t="n">
-        <v>420083</v>
+        <v>1391604</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1188.4</v>
+        <v>1630.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1207.9</v>
+        <v>1635.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1158</v>
+        <v>1610.8</v>
       </c>
       <c r="F18" t="n">
-        <v>1201.8</v>
+        <v>1632</v>
       </c>
       <c r="G18" t="n">
-        <v>3482939</v>
+        <v>929603</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1225</v>
+        <v>1660</v>
       </c>
       <c r="D19" t="n">
-        <v>1318.9</v>
+        <v>1672</v>
       </c>
       <c r="E19" t="n">
-        <v>1225</v>
+        <v>1630.7</v>
       </c>
       <c r="F19" t="n">
-        <v>1296.4</v>
+        <v>1652.6</v>
       </c>
       <c r="G19" t="n">
-        <v>17106822</v>
+        <v>1107616</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4882,25 +5375,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1325</v>
+        <v>1188.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1345</v>
+        <v>1207.9</v>
       </c>
       <c r="E20" t="n">
-        <v>1251.5</v>
+        <v>1158</v>
       </c>
       <c r="F20" t="n">
-        <v>1267.1</v>
+        <v>1201.8</v>
       </c>
       <c r="G20" t="n">
-        <v>10436460</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4909,25 +5402,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1270</v>
+        <v>1225</v>
       </c>
       <c r="D21" t="n">
-        <v>1285</v>
+        <v>1318.9</v>
       </c>
       <c r="E21" t="n">
-        <v>1246.1</v>
+        <v>1225</v>
       </c>
       <c r="F21" t="n">
-        <v>1282.2</v>
+        <v>1296.4</v>
       </c>
       <c r="G21" t="n">
-        <v>4135957</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4936,25 +5429,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1282.2</v>
+        <v>1325</v>
       </c>
       <c r="D22" t="n">
-        <v>1333.9</v>
+        <v>1345</v>
       </c>
       <c r="E22" t="n">
-        <v>1272.6</v>
+        <v>1251.5</v>
       </c>
       <c r="F22" t="n">
-        <v>1296.7</v>
+        <v>1267.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5275779</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4963,25 +5456,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1302.7</v>
+        <v>1270</v>
       </c>
       <c r="D23" t="n">
-        <v>1315.8</v>
+        <v>1285</v>
       </c>
       <c r="E23" t="n">
-        <v>1257.1</v>
+        <v>1246.1</v>
       </c>
       <c r="F23" t="n">
-        <v>1288.4</v>
+        <v>1282.2</v>
       </c>
       <c r="G23" t="n">
-        <v>3844546</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4990,25 +5483,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1290</v>
+        <v>1282.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1312</v>
+        <v>1333.9</v>
       </c>
       <c r="E24" t="n">
-        <v>1262</v>
+        <v>1272.6</v>
       </c>
       <c r="F24" t="n">
-        <v>1268.2</v>
+        <v>1296.7</v>
       </c>
       <c r="G24" t="n">
-        <v>2691508</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5017,25 +5510,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1268.2</v>
+        <v>1302.7</v>
       </c>
       <c r="D25" t="n">
-        <v>1271.5</v>
+        <v>1315.8</v>
       </c>
       <c r="E25" t="n">
-        <v>1221.2</v>
+        <v>1257.1</v>
       </c>
       <c r="F25" t="n">
-        <v>1233.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2619436</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5044,25 +5537,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1224.1</v>
+        <v>1290</v>
       </c>
       <c r="D26" t="n">
-        <v>1224.7</v>
+        <v>1312</v>
       </c>
       <c r="E26" t="n">
-        <v>1188.1</v>
+        <v>1262</v>
       </c>
       <c r="F26" t="n">
-        <v>1208.7</v>
+        <v>1268.2</v>
       </c>
       <c r="G26" t="n">
-        <v>3613338</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5071,25 +5564,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1214.9</v>
+        <v>1268.2</v>
       </c>
       <c r="D27" t="n">
-        <v>1233.9</v>
+        <v>1271.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1196.5</v>
+        <v>1221.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1214.9</v>
+        <v>1233.2</v>
       </c>
       <c r="G27" t="n">
-        <v>1911132</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5098,25 +5591,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1213</v>
+        <v>1224.1</v>
       </c>
       <c r="D28" t="n">
-        <v>1229</v>
+        <v>1224.7</v>
       </c>
       <c r="E28" t="n">
-        <v>1196.1</v>
+        <v>1188.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1202</v>
+        <v>1208.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2067763</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5125,25 +5618,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1207.2</v>
+        <v>1214.9</v>
       </c>
       <c r="D29" t="n">
-        <v>1252</v>
+        <v>1233.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1191.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1246.1</v>
+        <v>1214.9</v>
       </c>
       <c r="G29" t="n">
-        <v>3306087</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5152,25 +5645,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1253</v>
+        <v>1213</v>
       </c>
       <c r="D30" t="n">
-        <v>1265.9</v>
+        <v>1229</v>
       </c>
       <c r="E30" t="n">
-        <v>1232.5</v>
+        <v>1196.1</v>
       </c>
       <c r="F30" t="n">
-        <v>1240.9</v>
+        <v>1202</v>
       </c>
       <c r="G30" t="n">
-        <v>2463994</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5179,25 +5672,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1247</v>
+        <v>1207.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1274.6</v>
+        <v>1252</v>
       </c>
       <c r="E31" t="n">
-        <v>1232.1</v>
+        <v>1191.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1260.3</v>
+        <v>1246.1</v>
       </c>
       <c r="G31" t="n">
-        <v>3182495</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5206,25 +5699,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1269</v>
+        <v>1253</v>
       </c>
       <c r="D32" t="n">
-        <v>1289.9</v>
+        <v>1265.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1242</v>
+        <v>1232.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1272.7</v>
+        <v>1240.9</v>
       </c>
       <c r="G32" t="n">
-        <v>3918512</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5233,25 +5726,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1341.2</v>
+        <v>1247</v>
       </c>
       <c r="D33" t="n">
-        <v>1500</v>
+        <v>1274.6</v>
       </c>
       <c r="E33" t="n">
-        <v>1336.5</v>
+        <v>1232.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1450.4</v>
+        <v>1260.3</v>
       </c>
       <c r="G33" t="n">
-        <v>23853424</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5260,25 +5753,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1465</v>
+        <v>1269</v>
       </c>
       <c r="D34" t="n">
-        <v>1479.5</v>
+        <v>1289.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1405</v>
+        <v>1242</v>
       </c>
       <c r="F34" t="n">
-        <v>1470.8</v>
+        <v>1272.7</v>
       </c>
       <c r="G34" t="n">
-        <v>6958528</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5287,25 +5780,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1470.8</v>
+        <v>1341.2</v>
       </c>
       <c r="D35" t="n">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="E35" t="n">
-        <v>1440</v>
+        <v>1336.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1453.2</v>
+        <v>1450.4</v>
       </c>
       <c r="G35" t="n">
-        <v>4844393</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5314,133 +5807,133 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1450</v>
+        <v>1465</v>
       </c>
       <c r="D36" t="n">
-        <v>1494.4</v>
+        <v>1479.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1446</v>
+        <v>1405</v>
       </c>
       <c r="F36" t="n">
-        <v>1493.2</v>
+        <v>1470.8</v>
       </c>
       <c r="G36" t="n">
-        <v>1551670</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>211.95</v>
+        <v>1470.8</v>
       </c>
       <c r="D37" t="n">
-        <v>214.55</v>
+        <v>1505</v>
       </c>
       <c r="E37" t="n">
-        <v>206.1</v>
+        <v>1440</v>
       </c>
       <c r="F37" t="n">
-        <v>212.78</v>
+        <v>1453.2</v>
       </c>
       <c r="G37" t="n">
-        <v>12863408</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>214.3</v>
+        <v>1450</v>
       </c>
       <c r="D38" t="n">
-        <v>223.41</v>
+        <v>1508</v>
       </c>
       <c r="E38" t="n">
-        <v>214.3</v>
+        <v>1446</v>
       </c>
       <c r="F38" t="n">
-        <v>223.08</v>
+        <v>1481.5</v>
       </c>
       <c r="G38" t="n">
-        <v>32151413</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>226</v>
+        <v>1488</v>
       </c>
       <c r="D39" t="n">
-        <v>229.4</v>
+        <v>1520</v>
       </c>
       <c r="E39" t="n">
-        <v>221.18</v>
+        <v>1457</v>
       </c>
       <c r="F39" t="n">
-        <v>224.38</v>
+        <v>1466.2</v>
       </c>
       <c r="G39" t="n">
-        <v>14379534</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>217.24</v>
+        <v>1472.4</v>
       </c>
       <c r="D40" t="n">
-        <v>219.7</v>
+        <v>1512.5</v>
       </c>
       <c r="E40" t="n">
-        <v>213.17</v>
+        <v>1472</v>
       </c>
       <c r="F40" t="n">
-        <v>213.17</v>
+        <v>1501</v>
       </c>
       <c r="G40" t="n">
-        <v>14642282</v>
+        <v>1599028</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5449,25 +5942,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>208.25</v>
+        <v>211.95</v>
       </c>
       <c r="D41" t="n">
-        <v>213.7</v>
+        <v>214.55</v>
       </c>
       <c r="E41" t="n">
-        <v>203.16</v>
+        <v>206.1</v>
       </c>
       <c r="F41" t="n">
-        <v>208.03</v>
+        <v>212.78</v>
       </c>
       <c r="G41" t="n">
-        <v>18348510</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5476,25 +5969,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="D42" t="n">
-        <v>218.43</v>
+        <v>223.41</v>
       </c>
       <c r="E42" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="F42" t="n">
-        <v>217.97</v>
+        <v>223.08</v>
       </c>
       <c r="G42" t="n">
-        <v>20144780</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5503,25 +5996,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D43" t="n">
-        <v>228</v>
+        <v>229.4</v>
       </c>
       <c r="E43" t="n">
-        <v>214.11</v>
+        <v>221.18</v>
       </c>
       <c r="F43" t="n">
-        <v>217.9</v>
+        <v>224.38</v>
       </c>
       <c r="G43" t="n">
-        <v>55935312</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5530,25 +6023,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>221.96</v>
+        <v>217.24</v>
       </c>
       <c r="D44" t="n">
-        <v>222.4</v>
+        <v>219.7</v>
       </c>
       <c r="E44" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="F44" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="G44" t="n">
-        <v>29190459</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5557,25 +6050,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>202</v>
+        <v>208.25</v>
       </c>
       <c r="D45" t="n">
-        <v>204.78</v>
+        <v>213.7</v>
       </c>
       <c r="E45" t="n">
-        <v>196.66</v>
+        <v>203.16</v>
       </c>
       <c r="F45" t="n">
-        <v>196.85</v>
+        <v>208.03</v>
       </c>
       <c r="G45" t="n">
-        <v>31552378</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5584,25 +6077,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D46" t="n">
-        <v>200.9</v>
+        <v>218.43</v>
       </c>
       <c r="E46" t="n">
-        <v>191.1</v>
+        <v>209</v>
       </c>
       <c r="F46" t="n">
-        <v>192.54</v>
+        <v>217.97</v>
       </c>
       <c r="G46" t="n">
-        <v>26152896</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5611,25 +6104,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D47" t="n">
-        <v>196.9</v>
+        <v>228</v>
       </c>
       <c r="E47" t="n">
-        <v>182.92</v>
+        <v>214.11</v>
       </c>
       <c r="F47" t="n">
-        <v>188.39</v>
+        <v>217.9</v>
       </c>
       <c r="G47" t="n">
-        <v>42541118</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5638,25 +6131,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>189</v>
+        <v>221.96</v>
       </c>
       <c r="D48" t="n">
-        <v>195.5</v>
+        <v>222.4</v>
       </c>
       <c r="E48" t="n">
-        <v>181.05</v>
+        <v>207.01</v>
       </c>
       <c r="F48" t="n">
-        <v>193.56</v>
+        <v>207.01</v>
       </c>
       <c r="G48" t="n">
-        <v>40104195</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5665,25 +6158,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D49" t="n">
-        <v>195.53</v>
+        <v>204.78</v>
       </c>
       <c r="E49" t="n">
-        <v>183.9</v>
+        <v>196.66</v>
       </c>
       <c r="F49" t="n">
-        <v>184.69</v>
+        <v>196.85</v>
       </c>
       <c r="G49" t="n">
-        <v>21043194</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5692,25 +6185,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>193.92</v>
+        <v>200</v>
       </c>
       <c r="D50" t="n">
-        <v>193.92</v>
+        <v>200.9</v>
       </c>
       <c r="E50" t="n">
-        <v>191.01</v>
+        <v>191.1</v>
       </c>
       <c r="F50" t="n">
-        <v>193.92</v>
+        <v>192.54</v>
       </c>
       <c r="G50" t="n">
-        <v>33053426</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5719,25 +6212,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>196.95</v>
+        <v>187</v>
       </c>
       <c r="D51" t="n">
-        <v>203.61</v>
+        <v>196.9</v>
       </c>
       <c r="E51" t="n">
-        <v>195.7</v>
+        <v>182.92</v>
       </c>
       <c r="F51" t="n">
-        <v>202.52</v>
+        <v>188.39</v>
       </c>
       <c r="G51" t="n">
-        <v>39140552</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5746,25 +6239,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>202.4</v>
+        <v>189</v>
       </c>
       <c r="D52" t="n">
-        <v>207</v>
+        <v>195.5</v>
       </c>
       <c r="E52" t="n">
-        <v>200.22</v>
+        <v>181.05</v>
       </c>
       <c r="F52" t="n">
-        <v>202.78</v>
+        <v>193.56</v>
       </c>
       <c r="G52" t="n">
-        <v>19636718</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5773,25 +6266,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>205.8</v>
+        <v>193</v>
       </c>
       <c r="D53" t="n">
-        <v>212.91</v>
+        <v>195.53</v>
       </c>
       <c r="E53" t="n">
-        <v>205.03</v>
+        <v>183.9</v>
       </c>
       <c r="F53" t="n">
-        <v>212.23</v>
+        <v>184.69</v>
       </c>
       <c r="G53" t="n">
-        <v>37479685</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5800,25 +6293,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>212.4</v>
+        <v>193.92</v>
       </c>
       <c r="D54" t="n">
-        <v>213.45</v>
+        <v>193.92</v>
       </c>
       <c r="E54" t="n">
-        <v>203</v>
+        <v>191.01</v>
       </c>
       <c r="F54" t="n">
-        <v>203.67</v>
+        <v>193.92</v>
       </c>
       <c r="G54" t="n">
-        <v>19195935</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5827,187 +6320,187 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>203.98</v>
+        <v>196.95</v>
       </c>
       <c r="D55" t="n">
-        <v>206.7</v>
+        <v>203.61</v>
       </c>
       <c r="E55" t="n">
-        <v>201</v>
+        <v>195.7</v>
       </c>
       <c r="F55" t="n">
-        <v>205.32</v>
+        <v>202.52</v>
       </c>
       <c r="G55" t="n">
-        <v>6445459</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1554.3</v>
+        <v>202.4</v>
       </c>
       <c r="D56" t="n">
-        <v>1569</v>
+        <v>207</v>
       </c>
       <c r="E56" t="n">
-        <v>1551.3</v>
+        <v>200.22</v>
       </c>
       <c r="F56" t="n">
-        <v>1557.6</v>
+        <v>202.78</v>
       </c>
       <c r="G56" t="n">
-        <v>1001677</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1560.4</v>
+        <v>205.8</v>
       </c>
       <c r="D57" t="n">
-        <v>1561</v>
+        <v>212.91</v>
       </c>
       <c r="E57" t="n">
-        <v>1520.4</v>
+        <v>205.03</v>
       </c>
       <c r="F57" t="n">
-        <v>1529.8</v>
+        <v>212.23</v>
       </c>
       <c r="G57" t="n">
-        <v>1011017</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1534.9</v>
+        <v>212.4</v>
       </c>
       <c r="D58" t="n">
-        <v>1572.2</v>
+        <v>213.45</v>
       </c>
       <c r="E58" t="n">
-        <v>1527.2</v>
+        <v>203</v>
       </c>
       <c r="F58" t="n">
-        <v>1558.9</v>
+        <v>203.67</v>
       </c>
       <c r="G58" t="n">
-        <v>1235837</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1559.7</v>
+        <v>203.98</v>
       </c>
       <c r="D59" t="n">
-        <v>1600.1</v>
+        <v>211.52</v>
       </c>
       <c r="E59" t="n">
-        <v>1557</v>
+        <v>201</v>
       </c>
       <c r="F59" t="n">
-        <v>1593.2</v>
+        <v>207.98</v>
       </c>
       <c r="G59" t="n">
-        <v>1871739</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1591</v>
+        <v>209</v>
       </c>
       <c r="D60" t="n">
-        <v>1593.2</v>
+        <v>216.6</v>
       </c>
       <c r="E60" t="n">
-        <v>1566</v>
+        <v>207.83</v>
       </c>
       <c r="F60" t="n">
-        <v>1577.8</v>
+        <v>212.97</v>
       </c>
       <c r="G60" t="n">
-        <v>1183077</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1577.7</v>
+        <v>214</v>
       </c>
       <c r="D61" t="n">
-        <v>1586.1</v>
+        <v>215.29</v>
       </c>
       <c r="E61" t="n">
-        <v>1561.1</v>
+        <v>209.6</v>
       </c>
       <c r="F61" t="n">
-        <v>1568.3</v>
+        <v>211.22</v>
       </c>
       <c r="G61" t="n">
-        <v>1098268</v>
+        <v>3786286</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6016,25 +6509,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1560</v>
+        <v>1554.3</v>
       </c>
       <c r="D62" t="n">
-        <v>1610</v>
+        <v>1569</v>
       </c>
       <c r="E62" t="n">
-        <v>1554.9</v>
+        <v>1551.3</v>
       </c>
       <c r="F62" t="n">
-        <v>1601.2</v>
+        <v>1557.6</v>
       </c>
       <c r="G62" t="n">
-        <v>2647403</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6043,25 +6536,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1624.8</v>
+        <v>1560.4</v>
       </c>
       <c r="D63" t="n">
-        <v>1734.5</v>
+        <v>1561</v>
       </c>
       <c r="E63" t="n">
-        <v>1617.1</v>
+        <v>1520.4</v>
       </c>
       <c r="F63" t="n">
-        <v>1713.4</v>
+        <v>1529.8</v>
       </c>
       <c r="G63" t="n">
-        <v>7989771</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6070,25 +6563,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1713</v>
+        <v>1534.9</v>
       </c>
       <c r="D64" t="n">
-        <v>1762</v>
+        <v>1572.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1707.7</v>
+        <v>1527.2</v>
       </c>
       <c r="F64" t="n">
-        <v>1758.9</v>
+        <v>1558.9</v>
       </c>
       <c r="G64" t="n">
-        <v>4407907</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6097,25 +6590,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1762</v>
+        <v>1559.7</v>
       </c>
       <c r="D65" t="n">
-        <v>1797.9</v>
+        <v>1600.1</v>
       </c>
       <c r="E65" t="n">
-        <v>1754.3</v>
+        <v>1557</v>
       </c>
       <c r="F65" t="n">
-        <v>1781.3</v>
+        <v>1593.2</v>
       </c>
       <c r="G65" t="n">
-        <v>3000811</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6124,25 +6617,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1785</v>
+        <v>1591</v>
       </c>
       <c r="D66" t="n">
-        <v>1798.9</v>
+        <v>1593.2</v>
       </c>
       <c r="E66" t="n">
-        <v>1773.3</v>
+        <v>1566</v>
       </c>
       <c r="F66" t="n">
-        <v>1781.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G66" t="n">
-        <v>2402202</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6151,25 +6644,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1785</v>
+        <v>1577.7</v>
       </c>
       <c r="D67" t="n">
-        <v>1826.6</v>
+        <v>1586.1</v>
       </c>
       <c r="E67" t="n">
-        <v>1785</v>
+        <v>1561.1</v>
       </c>
       <c r="F67" t="n">
-        <v>1816.2</v>
+        <v>1568.3</v>
       </c>
       <c r="G67" t="n">
-        <v>2502579</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6178,25 +6671,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1821</v>
+        <v>1560</v>
       </c>
       <c r="D68" t="n">
-        <v>1838.3</v>
+        <v>1610</v>
       </c>
       <c r="E68" t="n">
-        <v>1789.1</v>
+        <v>1554.9</v>
       </c>
       <c r="F68" t="n">
-        <v>1811.4</v>
+        <v>1601.2</v>
       </c>
       <c r="G68" t="n">
-        <v>1919384</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6205,25 +6698,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1811</v>
+        <v>1624.8</v>
       </c>
       <c r="D69" t="n">
-        <v>1850</v>
+        <v>1734.5</v>
       </c>
       <c r="E69" t="n">
-        <v>1806.1</v>
+        <v>1617.1</v>
       </c>
       <c r="F69" t="n">
-        <v>1850</v>
+        <v>1713.4</v>
       </c>
       <c r="G69" t="n">
-        <v>1405192</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6232,25 +6725,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1854</v>
+        <v>1713</v>
       </c>
       <c r="D70" t="n">
-        <v>1856.6</v>
+        <v>1762</v>
       </c>
       <c r="E70" t="n">
-        <v>1834.5</v>
+        <v>1707.7</v>
       </c>
       <c r="F70" t="n">
-        <v>1835</v>
+        <v>1758.9</v>
       </c>
       <c r="G70" t="n">
-        <v>2090998</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6259,25 +6752,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1843</v>
+        <v>1762</v>
       </c>
       <c r="D71" t="n">
-        <v>1854.9</v>
+        <v>1797.9</v>
       </c>
       <c r="E71" t="n">
-        <v>1837</v>
+        <v>1754.3</v>
       </c>
       <c r="F71" t="n">
-        <v>1843.2</v>
+        <v>1781.3</v>
       </c>
       <c r="G71" t="n">
-        <v>1228707</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6286,241 +6779,241 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1838</v>
+        <v>1785</v>
       </c>
       <c r="D72" t="n">
-        <v>1850</v>
+        <v>1798.9</v>
       </c>
       <c r="E72" t="n">
-        <v>1833.2</v>
+        <v>1773.3</v>
       </c>
       <c r="F72" t="n">
-        <v>1848.5</v>
+        <v>1781.3</v>
       </c>
       <c r="G72" t="n">
-        <v>587992</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>344</v>
+        <v>1785</v>
       </c>
       <c r="D73" t="n">
-        <v>346.3</v>
+        <v>1826.6</v>
       </c>
       <c r="E73" t="n">
-        <v>341.25</v>
+        <v>1785</v>
       </c>
       <c r="F73" t="n">
-        <v>342.9</v>
+        <v>1816.2</v>
       </c>
       <c r="G73" t="n">
-        <v>4465145</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>344.2</v>
+        <v>1821</v>
       </c>
       <c r="D74" t="n">
-        <v>347.75</v>
+        <v>1838.3</v>
       </c>
       <c r="E74" t="n">
-        <v>339.95</v>
+        <v>1789.1</v>
       </c>
       <c r="F74" t="n">
-        <v>342.4</v>
+        <v>1811.4</v>
       </c>
       <c r="G74" t="n">
-        <v>3803051</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>346</v>
+        <v>1811</v>
       </c>
       <c r="D75" t="n">
-        <v>351</v>
+        <v>1850</v>
       </c>
       <c r="E75" t="n">
-        <v>343.65</v>
+        <v>1806.1</v>
       </c>
       <c r="F75" t="n">
-        <v>346</v>
+        <v>1850</v>
       </c>
       <c r="G75" t="n">
-        <v>5175178</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>341.8</v>
+        <v>1854</v>
       </c>
       <c r="D76" t="n">
-        <v>344.9</v>
+        <v>1856.6</v>
       </c>
       <c r="E76" t="n">
-        <v>339.65</v>
+        <v>1834.5</v>
       </c>
       <c r="F76" t="n">
-        <v>343.9</v>
+        <v>1835</v>
       </c>
       <c r="G76" t="n">
-        <v>2253982</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>345.1</v>
+        <v>1843</v>
       </c>
       <c r="D77" t="n">
-        <v>346.05</v>
+        <v>1854.9</v>
       </c>
       <c r="E77" t="n">
-        <v>338.35</v>
+        <v>1830</v>
       </c>
       <c r="F77" t="n">
-        <v>339.35</v>
+        <v>1830</v>
       </c>
       <c r="G77" t="n">
-        <v>3868006</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>339.4</v>
+        <v>1838</v>
       </c>
       <c r="D78" t="n">
-        <v>340.2</v>
+        <v>1856</v>
       </c>
       <c r="E78" t="n">
-        <v>333</v>
+        <v>1833.2</v>
       </c>
       <c r="F78" t="n">
-        <v>334.55</v>
+        <v>1844.3</v>
       </c>
       <c r="G78" t="n">
-        <v>3721274</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>335</v>
+        <v>1845</v>
       </c>
       <c r="D79" t="n">
-        <v>346.1</v>
+        <v>1870.8</v>
       </c>
       <c r="E79" t="n">
-        <v>332</v>
+        <v>1832.8</v>
       </c>
       <c r="F79" t="n">
-        <v>344.7</v>
+        <v>1854</v>
       </c>
       <c r="G79" t="n">
-        <v>5431501</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>345.5</v>
+        <v>1851</v>
       </c>
       <c r="D80" t="n">
-        <v>349.65</v>
+        <v>1851.1</v>
       </c>
       <c r="E80" t="n">
-        <v>342.6</v>
+        <v>1834.1</v>
       </c>
       <c r="F80" t="n">
-        <v>347.65</v>
+        <v>1842.9</v>
       </c>
       <c r="G80" t="n">
-        <v>6318472</v>
+        <v>405068</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6529,25 +7022,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D81" t="n">
-        <v>355.75</v>
+        <v>346.3</v>
       </c>
       <c r="E81" t="n">
-        <v>347.65</v>
+        <v>341.25</v>
       </c>
       <c r="F81" t="n">
-        <v>350.05</v>
+        <v>342.9</v>
       </c>
       <c r="G81" t="n">
-        <v>7186013</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6556,25 +7049,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>357.95</v>
+        <v>344.2</v>
       </c>
       <c r="D82" t="n">
-        <v>369</v>
+        <v>347.75</v>
       </c>
       <c r="E82" t="n">
-        <v>353.5</v>
+        <v>339.95</v>
       </c>
       <c r="F82" t="n">
-        <v>369</v>
+        <v>342.4</v>
       </c>
       <c r="G82" t="n">
-        <v>12541474</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6583,25 +7076,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="D83" t="n">
-        <v>382.45</v>
+        <v>351</v>
       </c>
       <c r="E83" t="n">
-        <v>367.15</v>
+        <v>343.65</v>
       </c>
       <c r="F83" t="n">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="G83" t="n">
-        <v>15775994</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6610,25 +7103,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>381</v>
+        <v>341.8</v>
       </c>
       <c r="D84" t="n">
-        <v>383.9</v>
+        <v>344.9</v>
       </c>
       <c r="E84" t="n">
-        <v>375.15</v>
+        <v>339.65</v>
       </c>
       <c r="F84" t="n">
-        <v>381</v>
+        <v>343.9</v>
       </c>
       <c r="G84" t="n">
-        <v>8940938</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6637,25 +7130,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>385</v>
+        <v>345.1</v>
       </c>
       <c r="D85" t="n">
-        <v>385.05</v>
+        <v>346.05</v>
       </c>
       <c r="E85" t="n">
-        <v>378.1</v>
+        <v>338.35</v>
       </c>
       <c r="F85" t="n">
-        <v>378.9</v>
+        <v>339.35</v>
       </c>
       <c r="G85" t="n">
-        <v>3486554</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6664,295 +7157,295 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>382.5</v>
+        <v>339.4</v>
       </c>
       <c r="D86" t="n">
-        <v>382.85</v>
+        <v>340.2</v>
       </c>
       <c r="E86" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="F86" t="n">
-        <v>380.3</v>
+        <v>334.55</v>
       </c>
       <c r="G86" t="n">
-        <v>1643582</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4389.8</v>
+        <v>335</v>
       </c>
       <c r="D87" t="n">
-        <v>4485</v>
+        <v>346.1</v>
       </c>
       <c r="E87" t="n">
-        <v>4361.9</v>
+        <v>332</v>
       </c>
       <c r="F87" t="n">
-        <v>4398.1</v>
+        <v>344.7</v>
       </c>
       <c r="G87" t="n">
-        <v>1347378</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4422</v>
+        <v>345.5</v>
       </c>
       <c r="D88" t="n">
-        <v>4495</v>
+        <v>349.65</v>
       </c>
       <c r="E88" t="n">
-        <v>4358</v>
+        <v>342.6</v>
       </c>
       <c r="F88" t="n">
-        <v>4371.4</v>
+        <v>347.65</v>
       </c>
       <c r="G88" t="n">
-        <v>902264</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4387.7</v>
+        <v>352</v>
       </c>
       <c r="D89" t="n">
-        <v>4404</v>
+        <v>355.75</v>
       </c>
       <c r="E89" t="n">
-        <v>4281.9</v>
+        <v>347.65</v>
       </c>
       <c r="F89" t="n">
-        <v>4304.2</v>
+        <v>350.05</v>
       </c>
       <c r="G89" t="n">
-        <v>463349</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4285</v>
+        <v>357.95</v>
       </c>
       <c r="D90" t="n">
-        <v>4317</v>
+        <v>369</v>
       </c>
       <c r="E90" t="n">
-        <v>4220</v>
+        <v>353.5</v>
       </c>
       <c r="F90" t="n">
-        <v>4244.3</v>
+        <v>369</v>
       </c>
       <c r="G90" t="n">
-        <v>398348</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4211</v>
+        <v>373</v>
       </c>
       <c r="D91" t="n">
-        <v>4220</v>
+        <v>382.45</v>
       </c>
       <c r="E91" t="n">
-        <v>4129.3</v>
+        <v>367.15</v>
       </c>
       <c r="F91" t="n">
-        <v>4178.1</v>
+        <v>377</v>
       </c>
       <c r="G91" t="n">
-        <v>470046</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4190</v>
+        <v>381</v>
       </c>
       <c r="D92" t="n">
-        <v>4324.4</v>
+        <v>383.9</v>
       </c>
       <c r="E92" t="n">
-        <v>4190</v>
+        <v>375.15</v>
       </c>
       <c r="F92" t="n">
-        <v>4257.3</v>
+        <v>381</v>
       </c>
       <c r="G92" t="n">
-        <v>633457</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4290</v>
+        <v>385</v>
       </c>
       <c r="D93" t="n">
-        <v>4383</v>
+        <v>385.05</v>
       </c>
       <c r="E93" t="n">
-        <v>4266</v>
+        <v>376.5</v>
       </c>
       <c r="F93" t="n">
-        <v>4288.7</v>
+        <v>381</v>
       </c>
       <c r="G93" t="n">
-        <v>835107</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4299</v>
+        <v>382.5</v>
       </c>
       <c r="D94" t="n">
-        <v>4340</v>
+        <v>382.85</v>
       </c>
       <c r="E94" t="n">
-        <v>4216</v>
+        <v>377.15</v>
       </c>
       <c r="F94" t="n">
-        <v>4243.8</v>
+        <v>381</v>
       </c>
       <c r="G94" t="n">
-        <v>422024</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4201.9</v>
+        <v>381.7</v>
       </c>
       <c r="D95" t="n">
-        <v>4222</v>
+        <v>387.7</v>
       </c>
       <c r="E95" t="n">
-        <v>4115</v>
+        <v>381.1</v>
       </c>
       <c r="F95" t="n">
-        <v>4156</v>
+        <v>382.7</v>
       </c>
       <c r="G95" t="n">
-        <v>378694</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4181.8</v>
+        <v>387.15</v>
       </c>
       <c r="D96" t="n">
-        <v>4385</v>
+        <v>392.7</v>
       </c>
       <c r="E96" t="n">
-        <v>4129.4</v>
+        <v>385.6</v>
       </c>
       <c r="F96" t="n">
-        <v>4362.2</v>
+        <v>390.8</v>
       </c>
       <c r="G96" t="n">
-        <v>992864</v>
+        <v>2933352</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6961,25 +7454,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4380</v>
+        <v>4389.8</v>
       </c>
       <c r="D97" t="n">
-        <v>4478.3</v>
+        <v>4485</v>
       </c>
       <c r="E97" t="n">
-        <v>4280.1</v>
+        <v>4361.9</v>
       </c>
       <c r="F97" t="n">
-        <v>4395.7</v>
+        <v>4398.1</v>
       </c>
       <c r="G97" t="n">
-        <v>960643</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6988,25 +7481,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4500</v>
+        <v>4422</v>
       </c>
       <c r="D98" t="n">
-        <v>4544</v>
+        <v>4495</v>
       </c>
       <c r="E98" t="n">
-        <v>4322</v>
+        <v>4358</v>
       </c>
       <c r="F98" t="n">
-        <v>4364.1</v>
+        <v>4371.4</v>
       </c>
       <c r="G98" t="n">
-        <v>1616021</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7015,25 +7508,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4340.7</v>
+        <v>4387.7</v>
       </c>
       <c r="D99" t="n">
-        <v>4341.8</v>
+        <v>4404</v>
       </c>
       <c r="E99" t="n">
-        <v>4175.5</v>
+        <v>4281.9</v>
       </c>
       <c r="F99" t="n">
-        <v>4195.2</v>
+        <v>4304.2</v>
       </c>
       <c r="G99" t="n">
-        <v>648341</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7042,25 +7535,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4300</v>
+        <v>4285</v>
       </c>
       <c r="D100" t="n">
-        <v>4598</v>
+        <v>4317</v>
       </c>
       <c r="E100" t="n">
-        <v>4252</v>
+        <v>4220</v>
       </c>
       <c r="F100" t="n">
-        <v>4524</v>
+        <v>4244.3</v>
       </c>
       <c r="G100" t="n">
-        <v>4510774</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7069,25 +7562,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4560.4</v>
+        <v>4211</v>
       </c>
       <c r="D101" t="n">
-        <v>4740</v>
+        <v>4220</v>
       </c>
       <c r="E101" t="n">
-        <v>4540</v>
+        <v>4129.3</v>
       </c>
       <c r="F101" t="n">
-        <v>4586</v>
+        <v>4178.1</v>
       </c>
       <c r="G101" t="n">
-        <v>2334958</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7096,25 +7589,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4609</v>
+        <v>4190</v>
       </c>
       <c r="D102" t="n">
-        <v>4780</v>
+        <v>4324.4</v>
       </c>
       <c r="E102" t="n">
-        <v>4593.1</v>
+        <v>4190</v>
       </c>
       <c r="F102" t="n">
-        <v>4762.2</v>
+        <v>4257.3</v>
       </c>
       <c r="G102" t="n">
-        <v>1899271</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7123,25 +7616,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4820.7</v>
+        <v>4290</v>
       </c>
       <c r="D103" t="n">
-        <v>4933</v>
+        <v>4383</v>
       </c>
       <c r="E103" t="n">
-        <v>4725</v>
+        <v>4266</v>
       </c>
       <c r="F103" t="n">
-        <v>4893.8</v>
+        <v>4288.7</v>
       </c>
       <c r="G103" t="n">
-        <v>1924204</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7150,25 +7643,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4900</v>
+        <v>4299</v>
       </c>
       <c r="D104" t="n">
-        <v>4980</v>
+        <v>4340</v>
       </c>
       <c r="E104" t="n">
-        <v>4860</v>
+        <v>4216</v>
       </c>
       <c r="F104" t="n">
-        <v>4917.1</v>
+        <v>4243.8</v>
       </c>
       <c r="G104" t="n">
-        <v>658285</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7177,349 +7670,349 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4790</v>
+        <v>4201.9</v>
       </c>
       <c r="D105" t="n">
-        <v>4899</v>
+        <v>4222</v>
       </c>
       <c r="E105" t="n">
-        <v>4780</v>
+        <v>4115</v>
       </c>
       <c r="F105" t="n">
-        <v>4845</v>
+        <v>4156</v>
       </c>
       <c r="G105" t="n">
-        <v>377192</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1417</v>
+        <v>4181.8</v>
       </c>
       <c r="D106" t="n">
-        <v>1436</v>
+        <v>4385</v>
       </c>
       <c r="E106" t="n">
-        <v>1410.1</v>
+        <v>4129.4</v>
       </c>
       <c r="F106" t="n">
-        <v>1423.9</v>
+        <v>4362.2</v>
       </c>
       <c r="G106" t="n">
-        <v>623969</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1428</v>
+        <v>4380</v>
       </c>
       <c r="D107" t="n">
-        <v>1428</v>
+        <v>4478.3</v>
       </c>
       <c r="E107" t="n">
-        <v>1351.5</v>
+        <v>4280.1</v>
       </c>
       <c r="F107" t="n">
-        <v>1359.1</v>
+        <v>4395.7</v>
       </c>
       <c r="G107" t="n">
-        <v>808190</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1349.8</v>
+        <v>4497.2</v>
       </c>
       <c r="D108" t="n">
-        <v>1357.8</v>
+        <v>4541.17</v>
       </c>
       <c r="E108" t="n">
-        <v>1330.1</v>
+        <v>4319.31</v>
       </c>
       <c r="F108" t="n">
-        <v>1340.8</v>
+        <v>4361.38</v>
       </c>
       <c r="G108" t="n">
-        <v>345535</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1340.8</v>
+        <v>4338</v>
       </c>
       <c r="D109" t="n">
-        <v>1387.7</v>
+        <v>4339.1</v>
       </c>
       <c r="E109" t="n">
-        <v>1316</v>
+        <v>4172.9</v>
       </c>
       <c r="F109" t="n">
-        <v>1374.4</v>
+        <v>4192.59</v>
       </c>
       <c r="G109" t="n">
-        <v>974660</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1372.9</v>
+        <v>4297.32</v>
       </c>
       <c r="D110" t="n">
-        <v>1390</v>
+        <v>4595.14</v>
       </c>
       <c r="E110" t="n">
-        <v>1355.1</v>
+        <v>4249.35</v>
       </c>
       <c r="F110" t="n">
-        <v>1363.5</v>
+        <v>4521.18</v>
       </c>
       <c r="G110" t="n">
-        <v>479123</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1363</v>
+        <v>4557.56</v>
       </c>
       <c r="D111" t="n">
-        <v>1392</v>
+        <v>4737.05</v>
       </c>
       <c r="E111" t="n">
-        <v>1355.1</v>
+        <v>4537.17</v>
       </c>
       <c r="F111" t="n">
-        <v>1380</v>
+        <v>4583.14</v>
       </c>
       <c r="G111" t="n">
-        <v>616767</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1360</v>
+        <v>4606.13</v>
       </c>
       <c r="D112" t="n">
-        <v>1368</v>
+        <v>4777.02</v>
       </c>
       <c r="E112" t="n">
-        <v>1272.1</v>
+        <v>4590.24</v>
       </c>
       <c r="F112" t="n">
-        <v>1288.3</v>
+        <v>4759.23</v>
       </c>
       <c r="G112" t="n">
-        <v>1098492</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1300</v>
+        <v>4817.7</v>
       </c>
       <c r="D113" t="n">
-        <v>1318.5</v>
+        <v>4929.93</v>
       </c>
       <c r="E113" t="n">
-        <v>1257</v>
+        <v>4722.06</v>
       </c>
       <c r="F113" t="n">
-        <v>1316.2</v>
+        <v>4890.75</v>
       </c>
       <c r="G113" t="n">
-        <v>1172726</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1317.7</v>
+        <v>4896.95</v>
       </c>
       <c r="D114" t="n">
-        <v>1319.8</v>
+        <v>4976.9</v>
       </c>
       <c r="E114" t="n">
-        <v>1270.5</v>
+        <v>4780.02</v>
       </c>
       <c r="F114" t="n">
-        <v>1306</v>
+        <v>4813</v>
       </c>
       <c r="G114" t="n">
-        <v>832973</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1319.9</v>
+        <v>4790</v>
       </c>
       <c r="D115" t="n">
-        <v>1355.4</v>
+        <v>4968</v>
       </c>
       <c r="E115" t="n">
-        <v>1308</v>
+        <v>4780</v>
       </c>
       <c r="F115" t="n">
-        <v>1343.4</v>
+        <v>4939.2</v>
       </c>
       <c r="G115" t="n">
-        <v>1287698</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1379</v>
+        <v>4958</v>
       </c>
       <c r="D116" t="n">
-        <v>1468</v>
+        <v>5085</v>
       </c>
       <c r="E116" t="n">
-        <v>1361</v>
+        <v>4888.8</v>
       </c>
       <c r="F116" t="n">
-        <v>1377.8</v>
+        <v>4903</v>
       </c>
       <c r="G116" t="n">
-        <v>9950655</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1380.5</v>
+        <v>4903</v>
       </c>
       <c r="D117" t="n">
-        <v>1403.3</v>
+        <v>4940</v>
       </c>
       <c r="E117" t="n">
-        <v>1363</v>
+        <v>4830.2</v>
       </c>
       <c r="F117" t="n">
-        <v>1366.8</v>
+        <v>4838.8</v>
       </c>
       <c r="G117" t="n">
-        <v>1567542</v>
+        <v>299859</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7528,25 +8021,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1380</v>
+        <v>1417</v>
       </c>
       <c r="D118" t="n">
-        <v>1397.5</v>
+        <v>1436</v>
       </c>
       <c r="E118" t="n">
-        <v>1351.6</v>
+        <v>1410.1</v>
       </c>
       <c r="F118" t="n">
-        <v>1360.6</v>
+        <v>1423.9</v>
       </c>
       <c r="G118" t="n">
-        <v>1098353</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7555,25 +8048,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1360.6</v>
+        <v>1428</v>
       </c>
       <c r="D119" t="n">
         <v>1428</v>
       </c>
       <c r="E119" t="n">
-        <v>1354.5</v>
+        <v>1351.5</v>
       </c>
       <c r="F119" t="n">
-        <v>1421.6</v>
+        <v>1359.1</v>
       </c>
       <c r="G119" t="n">
-        <v>2055261</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7582,25 +8075,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1429.6</v>
+        <v>1349.8</v>
       </c>
       <c r="D120" t="n">
-        <v>1453</v>
+        <v>1357.8</v>
       </c>
       <c r="E120" t="n">
-        <v>1419</v>
+        <v>1330.1</v>
       </c>
       <c r="F120" t="n">
-        <v>1434.1</v>
+        <v>1340.8</v>
       </c>
       <c r="G120" t="n">
-        <v>1243415</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7609,46 +8102,424 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1434</v>
+        <v>1340.8</v>
       </c>
       <c r="D121" t="n">
-        <v>1460</v>
+        <v>1387.7</v>
       </c>
       <c r="E121" t="n">
-        <v>1405</v>
+        <v>1316</v>
       </c>
       <c r="F121" t="n">
-        <v>1418</v>
+        <v>1374.4</v>
       </c>
       <c r="G121" t="n">
-        <v>1123973</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1372.9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>479123</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G123" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G126" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="C134" t="n">
         <v>1413.9</v>
       </c>
-      <c r="D122" t="n">
-        <v>1433.7</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="D134" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E134" t="n">
         <v>1407.5</v>
       </c>
-      <c r="F122" t="n">
-        <v>1427.3</v>
-      </c>
-      <c r="G122" t="n">
-        <v>146478</v>
+      <c r="F134" t="n">
+        <v>1424.7</v>
+      </c>
+      <c r="G134" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1522</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1504.1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>707906</v>
       </c>
     </row>
   </sheetData>
@@ -7662,7 +8533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7802,6 +8673,21 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 11 Aug 2026 04:50</t>
+          <t>Generated 12 Aug 2026 05:15</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="D2" t="n">
-        <v>0.29</v>
+        <v>0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>54.2</v>
+        <v>51.9</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="3">
@@ -629,25 +629,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>6.11</v>
+        <v>4.94</v>
       </c>
       <c r="D3" t="n">
-        <v>4.16</v>
+        <v>2.96</v>
       </c>
       <c r="E3" t="n">
-        <v>86.7</v>
+        <v>77.8</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.35</v>
+        <v>-3.84</v>
       </c>
       <c r="H3" t="n">
-        <v>5.85</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="4">
@@ -657,25 +657,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>15.69</v>
+        <v>12.8</v>
       </c>
       <c r="D4" t="n">
-        <v>12.12</v>
+        <v>11.29</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>24.88</v>
+        <v>26.91</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08</v>
+        <v>4.07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.02</v>
+        <v>7.65</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2383,6 +2383,192 @@
         <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>193.92</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>216.81</v>
+      </c>
+      <c r="I29" t="n">
+        <v>196.21</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>237.41</v>
+      </c>
+      <c r="L29" t="n">
+        <v>258.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>99</v>
+      </c>
+      <c r="F30" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="K30" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="L30" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>99</v>
+      </c>
+      <c r="F31" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>531.64</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>605.5599999999999</v>
+      </c>
+      <c r="L31" t="n">
+        <v>642.52</v>
+      </c>
+      <c r="M31" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -2399,7 +2585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3278,6 +3464,105 @@
       </c>
       <c r="I28" t="n">
         <v>1839.02</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>216.81</v>
+      </c>
+      <c r="E29" t="n">
+        <v>196.21</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>237.41</v>
+      </c>
+      <c r="I29" t="n">
+        <v>258.01</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="I30" t="n">
+        <v>15.03</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>531.64</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="H31" t="n">
+        <v>605.5599999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>642.52</v>
       </c>
     </row>
   </sheetData>
@@ -3291,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3385,11 +3670,16 @@
           <t>hit_2r</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>sessions_to_stop</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3409,7 +3699,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>211.22</v>
+        <v>216.81</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3417,16 +3707,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.77</v>
+        <v>-0.83</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -3437,16 +3727,17 @@
       <c r="R2" t="b">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3461,7 +3752,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4838.8</v>
+        <v>13.49</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3469,16 +3760,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.18</v>
+        <v>-4.89</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -3489,16 +3780,17 @@
       <c r="R3" t="b">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3513,7 +3805,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1652.6</v>
+        <v>568.6</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3521,19 +3813,19 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1.17</v>
+        <v>0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.33</v>
+        <v>-6.86</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -3541,11 +3833,14 @@
       <c r="R4" t="b">
         <v>0</v>
       </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3565,26 +3860,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.14</v>
+        <v>3.58</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -3595,23 +3890,24 @@
       <c r="R5" t="b">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3619,26 +3915,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.12</v>
+        <v>-1.72</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.48</v>
+        <v>-1.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -3649,23 +3945,24 @@
       <c r="R6" t="b">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3673,26 +3970,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G7" t="n">
-        <v>0.45</v>
+        <v>-2.65</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.01</v>
+        <v>-3.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -3703,11 +4000,12 @@
       <c r="R7" t="b">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3727,26 +4025,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.35</v>
+        <v>6.69</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -3757,11 +4055,12 @@
       <c r="R8" t="b">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3781,26 +4080,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.99</v>
+        <v>-3.5</v>
       </c>
       <c r="N9" t="n">
         <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -3811,11 +4110,12 @@
       <c r="R9" t="b">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3838,38 +4138,39 @@
         <v>381</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>3.07</v>
+        <v>10.81</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.18</v>
+        <v>-1.01</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3889,26 +4190,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>2.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -3919,16 +4220,17 @@
       <c r="R11" t="b">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3943,26 +4245,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>3.97</v>
+        <v>3.21</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.45</v>
+        <v>-2.9</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -3973,16 +4275,17 @@
       <c r="R12" t="b">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3997,41 +4300,42 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.32</v>
+        <v>-1.18</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4051,28 +4355,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G14" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H14" t="n">
-        <v>4.16</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>6.82</v>
+        <v>4.56</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -4083,11 +4387,12 @@
       <c r="R14" t="b">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4099,7 +4404,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4107,28 +4412,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H15" t="n">
-        <v>1.67</v>
+        <v>-2.35</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>6.85</v>
+        <v>3.97</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -4139,16 +4444,17 @@
       <c r="R15" t="b">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4163,28 +4469,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G16" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H16" t="n">
-        <v>3.66</v>
+        <v>-3.84</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>4.16</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.61</v>
+        <v>-4.2</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -4195,23 +4501,24 @@
       <c r="R16" t="b">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4219,55 +4526,56 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G17" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H17" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>10.95</v>
+        <v>9.43</v>
       </c>
       <c r="M17" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4275,28 +4583,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1.76</v>
+        <v>6.85</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.62</v>
+        <v>-3.55</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -4307,23 +4615,24 @@
       <c r="R18" t="b">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4331,28 +4640,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G19" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H19" t="n">
-        <v>11.45</v>
+        <v>2.92</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>13.41</v>
+        <v>11.99</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -4363,16 +4672,17 @@
       <c r="R19" t="b">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4387,43 +4697,44 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>6.98</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>11.99</v>
+        <v>10.95</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4443,28 +4754,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.32</v>
+        <v>-4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -4475,23 +4786,24 @@
       <c r="R21" t="b">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4499,48 +4811,49 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H22" t="n">
-        <v>2.73</v>
+        <v>11.45</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>5.02</v>
+        <v>13.41</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4555,47 +4868,56 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H23" t="n">
-        <v>9.65</v>
+        <v>2.92</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>11.9</v>
+        <v>11.99</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N23" t="n">
         <v>10</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4603,35 +4925,44 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H24" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>16.59</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.32</v>
+        <v>-5.18</v>
       </c>
       <c r="N24" t="n">
         <v>10</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4643,7 +4974,7 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4654,10 +4985,10 @@
         <v>1781.3</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H25" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -4666,32 +4997,41 @@
         <v>5.02</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N25" t="n">
         <v>10</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4699,24 +5039,24 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G26" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H26" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I26" t="n">
-        <v>24.88</v>
+        <v>12.01</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>26.46</v>
+        <v>14.64</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
@@ -4725,23 +5065,24 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4749,24 +5090,24 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G27" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H27" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I27" t="n">
-        <v>12.12</v>
+        <v>9.51</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>14.97</v>
+        <v>16.59</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
@@ -4775,23 +5116,24 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4799,24 +5141,24 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I28" t="n">
-        <v>10.08</v>
+        <v>4.07</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>15.68</v>
+        <v>5.02</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
@@ -4825,6 +5167,160 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I29" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>96</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>92</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4837,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5354,46 +5850,46 @@
         <v>1672</v>
       </c>
       <c r="E19" t="n">
-        <v>1630.7</v>
+        <v>1616.1</v>
       </c>
       <c r="F19" t="n">
-        <v>1652.6</v>
+        <v>1622</v>
       </c>
       <c r="G19" t="n">
-        <v>1107616</v>
+        <v>2222288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1188.4</v>
+        <v>1628.5</v>
       </c>
       <c r="D20" t="n">
-        <v>1207.9</v>
+        <v>1629.7</v>
       </c>
       <c r="E20" t="n">
-        <v>1158</v>
+        <v>1573.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1201.8</v>
+        <v>1579</v>
       </c>
       <c r="G20" t="n">
-        <v>3482939</v>
+        <v>595462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5402,25 +5898,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E21" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F21" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G21" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5429,25 +5925,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D22" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F22" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G22" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5456,25 +5952,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D23" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E23" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F23" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G23" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5483,25 +5979,25 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F24" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D24" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G24" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5510,25 +6006,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E25" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F25" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G25" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5537,25 +6033,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D26" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E26" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5564,25 +6060,25 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F27" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D27" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G27" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5591,25 +6087,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D28" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E28" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F28" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5618,25 +6114,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D29" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E29" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F29" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5645,25 +6141,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D30" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E30" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G30" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5672,25 +6168,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D31" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E31" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G31" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5699,25 +6195,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D32" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E32" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F32" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5726,25 +6222,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D33" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E33" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F33" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G33" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5753,25 +6249,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D34" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E34" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G34" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5780,25 +6276,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D35" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E35" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F35" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G35" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5807,25 +6303,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D36" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E36" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G36" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5834,25 +6330,25 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F37" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D37" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G37" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5861,25 +6357,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D38" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E38" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F38" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G38" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5888,25 +6384,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D39" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E39" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F39" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G39" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5915,79 +6411,79 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D40" t="n">
-        <v>1512.5</v>
+        <v>1520</v>
       </c>
       <c r="E40" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F40" t="n">
-        <v>1501</v>
+        <v>1466.2</v>
       </c>
       <c r="G40" t="n">
-        <v>1599028</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>211.95</v>
+        <v>1472.4</v>
       </c>
       <c r="D41" t="n">
-        <v>214.55</v>
+        <v>1534.8</v>
       </c>
       <c r="E41" t="n">
-        <v>206.1</v>
+        <v>1472</v>
       </c>
       <c r="F41" t="n">
-        <v>212.78</v>
+        <v>1525.4</v>
       </c>
       <c r="G41" t="n">
-        <v>12863408</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>214.3</v>
+        <v>1531.7</v>
       </c>
       <c r="D42" t="n">
-        <v>223.41</v>
+        <v>1547.7</v>
       </c>
       <c r="E42" t="n">
-        <v>214.3</v>
+        <v>1511.1</v>
       </c>
       <c r="F42" t="n">
-        <v>223.08</v>
+        <v>1537.1</v>
       </c>
       <c r="G42" t="n">
-        <v>32151413</v>
+        <v>1307034</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5996,25 +6492,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D43" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E43" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F43" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G43" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6023,25 +6519,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D44" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E44" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F44" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G44" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6050,25 +6546,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D45" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E45" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F45" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G45" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6077,25 +6573,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D46" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E46" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F46" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G46" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6104,25 +6600,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D47" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E47" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F47" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G47" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6131,25 +6627,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D48" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E48" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F48" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G48" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6158,25 +6654,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D49" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E49" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F49" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G49" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6185,25 +6681,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D50" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E50" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F50" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G50" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6212,25 +6708,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D51" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E51" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F51" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G51" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6239,25 +6735,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D52" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E52" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F52" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G52" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6266,25 +6762,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D53" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E53" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F53" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G53" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6293,25 +6789,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D54" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E54" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F54" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G54" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6320,25 +6816,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D55" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E55" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F55" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G55" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6347,25 +6843,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D56" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E56" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F56" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G56" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6374,25 +6870,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D57" t="n">
-        <v>212.91</v>
+        <v>203.61</v>
       </c>
       <c r="E57" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F57" t="n">
-        <v>212.23</v>
+        <v>202.52</v>
       </c>
       <c r="G57" t="n">
-        <v>37479685</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6401,25 +6897,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>212.4</v>
+        <v>202.4</v>
       </c>
       <c r="D58" t="n">
-        <v>213.45</v>
+        <v>207</v>
       </c>
       <c r="E58" t="n">
-        <v>203</v>
+        <v>200.22</v>
       </c>
       <c r="F58" t="n">
-        <v>203.67</v>
+        <v>202.78</v>
       </c>
       <c r="G58" t="n">
-        <v>19195935</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6428,25 +6924,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>203.98</v>
+        <v>205.8</v>
       </c>
       <c r="D59" t="n">
-        <v>211.52</v>
+        <v>212.91</v>
       </c>
       <c r="E59" t="n">
-        <v>201</v>
+        <v>205.03</v>
       </c>
       <c r="F59" t="n">
-        <v>207.98</v>
+        <v>212.23</v>
       </c>
       <c r="G59" t="n">
-        <v>19489977</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6455,25 +6951,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>209</v>
+        <v>212.4</v>
       </c>
       <c r="D60" t="n">
-        <v>216.6</v>
+        <v>213.45</v>
       </c>
       <c r="E60" t="n">
-        <v>207.83</v>
+        <v>203</v>
       </c>
       <c r="F60" t="n">
-        <v>212.97</v>
+        <v>203.67</v>
       </c>
       <c r="G60" t="n">
-        <v>19215795</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6482,2044 +6978,2773 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>214</v>
+        <v>203.98</v>
       </c>
       <c r="D61" t="n">
-        <v>215.29</v>
+        <v>211.52</v>
       </c>
       <c r="E61" t="n">
-        <v>209.6</v>
+        <v>201</v>
       </c>
       <c r="F61" t="n">
-        <v>211.22</v>
+        <v>207.98</v>
       </c>
       <c r="G61" t="n">
-        <v>3786286</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1554.3</v>
+        <v>209</v>
       </c>
       <c r="D62" t="n">
-        <v>1569</v>
+        <v>216.6</v>
       </c>
       <c r="E62" t="n">
-        <v>1551.3</v>
+        <v>207.83</v>
       </c>
       <c r="F62" t="n">
-        <v>1557.6</v>
+        <v>212.97</v>
       </c>
       <c r="G62" t="n">
-        <v>1001677</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1560.4</v>
+        <v>214</v>
       </c>
       <c r="D63" t="n">
-        <v>1561</v>
+        <v>215.8</v>
       </c>
       <c r="E63" t="n">
-        <v>1520.4</v>
+        <v>209.25</v>
       </c>
       <c r="F63" t="n">
-        <v>1529.8</v>
+        <v>214.24</v>
       </c>
       <c r="G63" t="n">
-        <v>1011017</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1534.9</v>
+        <v>215.4</v>
       </c>
       <c r="D64" t="n">
-        <v>1572.2</v>
+        <v>221.9</v>
       </c>
       <c r="E64" t="n">
-        <v>1527.2</v>
+        <v>215</v>
       </c>
       <c r="F64" t="n">
-        <v>1558.9</v>
+        <v>216.81</v>
       </c>
       <c r="G64" t="n">
-        <v>1235837</v>
+        <v>10481598</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1559.7</v>
+        <v>481.25</v>
       </c>
       <c r="D65" t="n">
-        <v>1600.1</v>
+        <v>489.85</v>
       </c>
       <c r="E65" t="n">
-        <v>1557</v>
+        <v>477.5</v>
       </c>
       <c r="F65" t="n">
-        <v>1593.2</v>
+        <v>480.25</v>
       </c>
       <c r="G65" t="n">
-        <v>1871739</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1591</v>
+        <v>485.2</v>
       </c>
       <c r="D66" t="n">
-        <v>1593.2</v>
+        <v>499</v>
       </c>
       <c r="E66" t="n">
-        <v>1566</v>
+        <v>482.55</v>
       </c>
       <c r="F66" t="n">
-        <v>1577.8</v>
+        <v>491.6</v>
       </c>
       <c r="G66" t="n">
-        <v>1183077</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1577.7</v>
+        <v>495</v>
       </c>
       <c r="D67" t="n">
-        <v>1586.1</v>
+        <v>498.5</v>
       </c>
       <c r="E67" t="n">
-        <v>1561.1</v>
+        <v>491</v>
       </c>
       <c r="F67" t="n">
-        <v>1568.3</v>
+        <v>495.05</v>
       </c>
       <c r="G67" t="n">
-        <v>1098268</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1560</v>
+        <v>495.05</v>
       </c>
       <c r="D68" t="n">
-        <v>1610</v>
+        <v>504.3</v>
       </c>
       <c r="E68" t="n">
-        <v>1554.9</v>
+        <v>490.05</v>
       </c>
       <c r="F68" t="n">
-        <v>1601.2</v>
+        <v>492.35</v>
       </c>
       <c r="G68" t="n">
-        <v>2647403</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1624.8</v>
+        <v>496.2</v>
       </c>
       <c r="D69" t="n">
-        <v>1734.5</v>
+        <v>539.6</v>
       </c>
       <c r="E69" t="n">
-        <v>1617.1</v>
+        <v>495.1</v>
       </c>
       <c r="F69" t="n">
-        <v>1713.4</v>
+        <v>533.8</v>
       </c>
       <c r="G69" t="n">
-        <v>7989771</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1713</v>
+        <v>542.45</v>
       </c>
       <c r="D70" t="n">
-        <v>1762</v>
+        <v>551</v>
       </c>
       <c r="E70" t="n">
-        <v>1707.7</v>
+        <v>525.55</v>
       </c>
       <c r="F70" t="n">
-        <v>1758.9</v>
+        <v>545.95</v>
       </c>
       <c r="G70" t="n">
-        <v>4407907</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1762</v>
+        <v>543.75</v>
       </c>
       <c r="D71" t="n">
-        <v>1797.9</v>
+        <v>548</v>
       </c>
       <c r="E71" t="n">
-        <v>1754.3</v>
+        <v>532.1</v>
       </c>
       <c r="F71" t="n">
-        <v>1781.3</v>
+        <v>536.1</v>
       </c>
       <c r="G71" t="n">
-        <v>3000811</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1785</v>
+        <v>537.95</v>
       </c>
       <c r="D72" t="n">
-        <v>1798.9</v>
+        <v>552</v>
       </c>
       <c r="E72" t="n">
-        <v>1773.3</v>
+        <v>522</v>
       </c>
       <c r="F72" t="n">
-        <v>1781.3</v>
+        <v>526.25</v>
       </c>
       <c r="G72" t="n">
-        <v>2402202</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1785</v>
+        <v>531</v>
       </c>
       <c r="D73" t="n">
-        <v>1826.6</v>
+        <v>538.8</v>
       </c>
       <c r="E73" t="n">
-        <v>1785</v>
+        <v>527.7</v>
       </c>
       <c r="F73" t="n">
-        <v>1816.2</v>
+        <v>533.3</v>
       </c>
       <c r="G73" t="n">
-        <v>2502579</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1821</v>
+        <v>530.85</v>
       </c>
       <c r="D74" t="n">
-        <v>1838.3</v>
+        <v>569.85</v>
       </c>
       <c r="E74" t="n">
-        <v>1789.1</v>
+        <v>529.6</v>
       </c>
       <c r="F74" t="n">
-        <v>1811.4</v>
+        <v>568.6</v>
       </c>
       <c r="G74" t="n">
-        <v>1919384</v>
+        <v>14805733</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1811</v>
+        <v>13.05</v>
       </c>
       <c r="D75" t="n">
-        <v>1850</v>
+        <v>13.18</v>
       </c>
       <c r="E75" t="n">
-        <v>1806.1</v>
+        <v>12.85</v>
       </c>
       <c r="F75" t="n">
-        <v>1850</v>
+        <v>12.87</v>
       </c>
       <c r="G75" t="n">
-        <v>1405192</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1854</v>
+        <v>12.98</v>
       </c>
       <c r="D76" t="n">
-        <v>1856.6</v>
+        <v>13.08</v>
       </c>
       <c r="E76" t="n">
-        <v>1834.5</v>
+        <v>12.76</v>
       </c>
       <c r="F76" t="n">
-        <v>1835</v>
+        <v>13.01</v>
       </c>
       <c r="G76" t="n">
-        <v>2090998</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1843</v>
+        <v>13.01</v>
       </c>
       <c r="D77" t="n">
-        <v>1854.9</v>
+        <v>13.11</v>
       </c>
       <c r="E77" t="n">
-        <v>1830</v>
+        <v>12.82</v>
       </c>
       <c r="F77" t="n">
-        <v>1830</v>
+        <v>12.86</v>
       </c>
       <c r="G77" t="n">
-        <v>2037418</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1838</v>
+        <v>12.89</v>
       </c>
       <c r="D78" t="n">
-        <v>1856</v>
+        <v>13.05</v>
       </c>
       <c r="E78" t="n">
-        <v>1833.2</v>
+        <v>12.73</v>
       </c>
       <c r="F78" t="n">
-        <v>1844.3</v>
+        <v>12.9</v>
       </c>
       <c r="G78" t="n">
-        <v>1553067</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1845</v>
+        <v>12.91</v>
       </c>
       <c r="D79" t="n">
-        <v>1870.8</v>
+        <v>13.04</v>
       </c>
       <c r="E79" t="n">
-        <v>1832.8</v>
+        <v>12.77</v>
       </c>
       <c r="F79" t="n">
-        <v>1854</v>
+        <v>12.8</v>
       </c>
       <c r="G79" t="n">
-        <v>1386592</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1851</v>
+        <v>12.89</v>
       </c>
       <c r="D80" t="n">
-        <v>1851.1</v>
+        <v>12.9</v>
       </c>
       <c r="E80" t="n">
-        <v>1834.1</v>
+        <v>12.63</v>
       </c>
       <c r="F80" t="n">
-        <v>1842.9</v>
+        <v>12.63</v>
       </c>
       <c r="G80" t="n">
-        <v>405068</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>344</v>
+        <v>12.64</v>
       </c>
       <c r="D81" t="n">
-        <v>346.3</v>
+        <v>12.88</v>
       </c>
       <c r="E81" t="n">
-        <v>341.25</v>
+        <v>12.6</v>
       </c>
       <c r="F81" t="n">
-        <v>342.9</v>
+        <v>12.73</v>
       </c>
       <c r="G81" t="n">
-        <v>4465145</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>344.2</v>
+        <v>12.92</v>
       </c>
       <c r="D82" t="n">
-        <v>347.75</v>
+        <v>13.07</v>
       </c>
       <c r="E82" t="n">
-        <v>339.95</v>
+        <v>12.77</v>
       </c>
       <c r="F82" t="n">
-        <v>342.4</v>
+        <v>12.92</v>
       </c>
       <c r="G82" t="n">
-        <v>3803051</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>346</v>
+        <v>13.14</v>
       </c>
       <c r="D83" t="n">
-        <v>351</v>
+        <v>13.3</v>
       </c>
       <c r="E83" t="n">
-        <v>343.65</v>
+        <v>12.79</v>
       </c>
       <c r="F83" t="n">
-        <v>346</v>
+        <v>12.89</v>
       </c>
       <c r="G83" t="n">
-        <v>5175178</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>341.8</v>
+        <v>12.93</v>
       </c>
       <c r="D84" t="n">
-        <v>344.9</v>
+        <v>13.69</v>
       </c>
       <c r="E84" t="n">
-        <v>339.65</v>
+        <v>12.83</v>
       </c>
       <c r="F84" t="n">
-        <v>343.9</v>
+        <v>13.49</v>
       </c>
       <c r="G84" t="n">
-        <v>2253982</v>
+        <v>403055279</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>345.1</v>
+        <v>1554.3</v>
       </c>
       <c r="D85" t="n">
-        <v>346.05</v>
+        <v>1569</v>
       </c>
       <c r="E85" t="n">
-        <v>338.35</v>
+        <v>1551.3</v>
       </c>
       <c r="F85" t="n">
-        <v>339.35</v>
+        <v>1557.6</v>
       </c>
       <c r="G85" t="n">
-        <v>3868006</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>339.4</v>
+        <v>1560.4</v>
       </c>
       <c r="D86" t="n">
-        <v>340.2</v>
+        <v>1561</v>
       </c>
       <c r="E86" t="n">
-        <v>333</v>
+        <v>1520.4</v>
       </c>
       <c r="F86" t="n">
-        <v>334.55</v>
+        <v>1529.8</v>
       </c>
       <c r="G86" t="n">
-        <v>3721274</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>335</v>
+        <v>1534.9</v>
       </c>
       <c r="D87" t="n">
-        <v>346.1</v>
+        <v>1572.2</v>
       </c>
       <c r="E87" t="n">
-        <v>332</v>
+        <v>1527.2</v>
       </c>
       <c r="F87" t="n">
-        <v>344.7</v>
+        <v>1558.9</v>
       </c>
       <c r="G87" t="n">
-        <v>5431501</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>345.5</v>
+        <v>1559.7</v>
       </c>
       <c r="D88" t="n">
-        <v>349.65</v>
+        <v>1600.1</v>
       </c>
       <c r="E88" t="n">
-        <v>342.6</v>
+        <v>1557</v>
       </c>
       <c r="F88" t="n">
-        <v>347.65</v>
+        <v>1593.2</v>
       </c>
       <c r="G88" t="n">
-        <v>6318472</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>352</v>
+        <v>1591</v>
       </c>
       <c r="D89" t="n">
-        <v>355.75</v>
+        <v>1593.2</v>
       </c>
       <c r="E89" t="n">
-        <v>347.65</v>
+        <v>1566</v>
       </c>
       <c r="F89" t="n">
-        <v>350.05</v>
+        <v>1577.8</v>
       </c>
       <c r="G89" t="n">
-        <v>7186013</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>357.95</v>
+        <v>1577.7</v>
       </c>
       <c r="D90" t="n">
-        <v>369</v>
+        <v>1586.1</v>
       </c>
       <c r="E90" t="n">
-        <v>353.5</v>
+        <v>1561.1</v>
       </c>
       <c r="F90" t="n">
-        <v>369</v>
+        <v>1568.3</v>
       </c>
       <c r="G90" t="n">
-        <v>12541474</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>373</v>
+        <v>1560</v>
       </c>
       <c r="D91" t="n">
-        <v>382.45</v>
+        <v>1610</v>
       </c>
       <c r="E91" t="n">
-        <v>367.15</v>
+        <v>1554.9</v>
       </c>
       <c r="F91" t="n">
-        <v>377</v>
+        <v>1601.2</v>
       </c>
       <c r="G91" t="n">
-        <v>15775994</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>381</v>
+        <v>1624.8</v>
       </c>
       <c r="D92" t="n">
-        <v>383.9</v>
+        <v>1734.5</v>
       </c>
       <c r="E92" t="n">
-        <v>375.15</v>
+        <v>1617.1</v>
       </c>
       <c r="F92" t="n">
-        <v>381</v>
+        <v>1713.4</v>
       </c>
       <c r="G92" t="n">
-        <v>8940938</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>385</v>
+        <v>1713</v>
       </c>
       <c r="D93" t="n">
-        <v>385.05</v>
+        <v>1762</v>
       </c>
       <c r="E93" t="n">
-        <v>376.5</v>
+        <v>1707.7</v>
       </c>
       <c r="F93" t="n">
-        <v>381</v>
+        <v>1758.9</v>
       </c>
       <c r="G93" t="n">
-        <v>6636333</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>382.5</v>
+        <v>1762</v>
       </c>
       <c r="D94" t="n">
-        <v>382.85</v>
+        <v>1797.9</v>
       </c>
       <c r="E94" t="n">
-        <v>377.15</v>
+        <v>1754.3</v>
       </c>
       <c r="F94" t="n">
-        <v>381</v>
+        <v>1781.3</v>
       </c>
       <c r="G94" t="n">
-        <v>4423953</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>381.7</v>
+        <v>1785</v>
       </c>
       <c r="D95" t="n">
-        <v>387.7</v>
+        <v>1798.9</v>
       </c>
       <c r="E95" t="n">
-        <v>381.1</v>
+        <v>1773.3</v>
       </c>
       <c r="F95" t="n">
-        <v>382.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G95" t="n">
-        <v>5292453</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>387.15</v>
+        <v>1785</v>
       </c>
       <c r="D96" t="n">
-        <v>392.7</v>
+        <v>1826.6</v>
       </c>
       <c r="E96" t="n">
-        <v>385.6</v>
+        <v>1785</v>
       </c>
       <c r="F96" t="n">
-        <v>390.8</v>
+        <v>1816.2</v>
       </c>
       <c r="G96" t="n">
-        <v>2933352</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4389.8</v>
+        <v>1821</v>
       </c>
       <c r="D97" t="n">
-        <v>4485</v>
+        <v>1838.3</v>
       </c>
       <c r="E97" t="n">
-        <v>4361.9</v>
+        <v>1789.1</v>
       </c>
       <c r="F97" t="n">
-        <v>4398.1</v>
+        <v>1811.4</v>
       </c>
       <c r="G97" t="n">
-        <v>1347378</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4422</v>
+        <v>1811</v>
       </c>
       <c r="D98" t="n">
-        <v>4495</v>
+        <v>1850</v>
       </c>
       <c r="E98" t="n">
-        <v>4358</v>
+        <v>1806.1</v>
       </c>
       <c r="F98" t="n">
-        <v>4371.4</v>
+        <v>1850</v>
       </c>
       <c r="G98" t="n">
-        <v>902264</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4387.7</v>
+        <v>1854</v>
       </c>
       <c r="D99" t="n">
-        <v>4404</v>
+        <v>1856.6</v>
       </c>
       <c r="E99" t="n">
-        <v>4281.9</v>
+        <v>1834.5</v>
       </c>
       <c r="F99" t="n">
-        <v>4304.2</v>
+        <v>1835</v>
       </c>
       <c r="G99" t="n">
-        <v>463349</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4285</v>
+        <v>1843</v>
       </c>
       <c r="D100" t="n">
-        <v>4317</v>
+        <v>1854.9</v>
       </c>
       <c r="E100" t="n">
-        <v>4220</v>
+        <v>1830</v>
       </c>
       <c r="F100" t="n">
-        <v>4244.3</v>
+        <v>1830</v>
       </c>
       <c r="G100" t="n">
-        <v>398348</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4211</v>
+        <v>1838</v>
       </c>
       <c r="D101" t="n">
-        <v>4220</v>
+        <v>1856</v>
       </c>
       <c r="E101" t="n">
-        <v>4129.3</v>
+        <v>1833.2</v>
       </c>
       <c r="F101" t="n">
-        <v>4178.1</v>
+        <v>1844.3</v>
       </c>
       <c r="G101" t="n">
-        <v>470046</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4190</v>
+        <v>1845</v>
       </c>
       <c r="D102" t="n">
-        <v>4324.4</v>
+        <v>1870.8</v>
       </c>
       <c r="E102" t="n">
-        <v>4190</v>
+        <v>1832.8</v>
       </c>
       <c r="F102" t="n">
-        <v>4257.3</v>
+        <v>1854</v>
       </c>
       <c r="G102" t="n">
-        <v>633457</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4290</v>
+        <v>1851</v>
       </c>
       <c r="D103" t="n">
-        <v>4383</v>
+        <v>1859</v>
       </c>
       <c r="E103" t="n">
-        <v>4266</v>
+        <v>1833.1</v>
       </c>
       <c r="F103" t="n">
-        <v>4288.7</v>
+        <v>1858</v>
       </c>
       <c r="G103" t="n">
-        <v>835107</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4299</v>
+        <v>1856.3</v>
       </c>
       <c r="D104" t="n">
-        <v>4340</v>
+        <v>1862.3</v>
       </c>
       <c r="E104" t="n">
-        <v>4216</v>
+        <v>1847.2</v>
       </c>
       <c r="F104" t="n">
-        <v>4243.8</v>
+        <v>1853.8</v>
       </c>
       <c r="G104" t="n">
-        <v>422024</v>
+        <v>332074</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4201.9</v>
+        <v>344</v>
       </c>
       <c r="D105" t="n">
-        <v>4222</v>
+        <v>346.3</v>
       </c>
       <c r="E105" t="n">
-        <v>4115</v>
+        <v>341.25</v>
       </c>
       <c r="F105" t="n">
-        <v>4156</v>
+        <v>342.9</v>
       </c>
       <c r="G105" t="n">
-        <v>378694</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4181.8</v>
+        <v>344.2</v>
       </c>
       <c r="D106" t="n">
-        <v>4385</v>
+        <v>347.75</v>
       </c>
       <c r="E106" t="n">
-        <v>4129.4</v>
+        <v>339.95</v>
       </c>
       <c r="F106" t="n">
-        <v>4362.2</v>
+        <v>342.4</v>
       </c>
       <c r="G106" t="n">
-        <v>992864</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4380</v>
+        <v>346</v>
       </c>
       <c r="D107" t="n">
-        <v>4478.3</v>
+        <v>351</v>
       </c>
       <c r="E107" t="n">
-        <v>4280.1</v>
+        <v>343.65</v>
       </c>
       <c r="F107" t="n">
-        <v>4395.7</v>
+        <v>346</v>
       </c>
       <c r="G107" t="n">
-        <v>960643</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4497.2</v>
+        <v>341.8</v>
       </c>
       <c r="D108" t="n">
-        <v>4541.17</v>
+        <v>344.9</v>
       </c>
       <c r="E108" t="n">
-        <v>4319.31</v>
+        <v>339.65</v>
       </c>
       <c r="F108" t="n">
-        <v>4361.38</v>
+        <v>343.9</v>
       </c>
       <c r="G108" t="n">
-        <v>1616021</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4338</v>
+        <v>345.1</v>
       </c>
       <c r="D109" t="n">
-        <v>4339.1</v>
+        <v>346.05</v>
       </c>
       <c r="E109" t="n">
-        <v>4172.9</v>
+        <v>338.35</v>
       </c>
       <c r="F109" t="n">
-        <v>4192.59</v>
+        <v>339.35</v>
       </c>
       <c r="G109" t="n">
-        <v>648341</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4297.32</v>
+        <v>339.4</v>
       </c>
       <c r="D110" t="n">
-        <v>4595.14</v>
+        <v>340.2</v>
       </c>
       <c r="E110" t="n">
-        <v>4249.35</v>
+        <v>333</v>
       </c>
       <c r="F110" t="n">
-        <v>4521.18</v>
+        <v>334.55</v>
       </c>
       <c r="G110" t="n">
-        <v>4510774</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4557.56</v>
+        <v>335</v>
       </c>
       <c r="D111" t="n">
-        <v>4737.05</v>
+        <v>346.1</v>
       </c>
       <c r="E111" t="n">
-        <v>4537.17</v>
+        <v>332</v>
       </c>
       <c r="F111" t="n">
-        <v>4583.14</v>
+        <v>344.7</v>
       </c>
       <c r="G111" t="n">
-        <v>2334958</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4606.13</v>
+        <v>345.5</v>
       </c>
       <c r="D112" t="n">
-        <v>4777.02</v>
+        <v>349.65</v>
       </c>
       <c r="E112" t="n">
-        <v>4590.24</v>
+        <v>342.6</v>
       </c>
       <c r="F112" t="n">
-        <v>4759.23</v>
+        <v>347.65</v>
       </c>
       <c r="G112" t="n">
-        <v>1899271</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4817.7</v>
+        <v>352</v>
       </c>
       <c r="D113" t="n">
-        <v>4929.93</v>
+        <v>355.75</v>
       </c>
       <c r="E113" t="n">
-        <v>4722.06</v>
+        <v>347.65</v>
       </c>
       <c r="F113" t="n">
-        <v>4890.75</v>
+        <v>350.05</v>
       </c>
       <c r="G113" t="n">
-        <v>1924204</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4896.95</v>
+        <v>357.95</v>
       </c>
       <c r="D114" t="n">
-        <v>4976.9</v>
+        <v>369</v>
       </c>
       <c r="E114" t="n">
-        <v>4780.02</v>
+        <v>353.5</v>
       </c>
       <c r="F114" t="n">
-        <v>4813</v>
+        <v>369</v>
       </c>
       <c r="G114" t="n">
-        <v>1117424</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4790</v>
+        <v>373</v>
       </c>
       <c r="D115" t="n">
-        <v>4968</v>
+        <v>382.45</v>
       </c>
       <c r="E115" t="n">
-        <v>4780</v>
+        <v>367.15</v>
       </c>
       <c r="F115" t="n">
-        <v>4939.2</v>
+        <v>377</v>
       </c>
       <c r="G115" t="n">
-        <v>1296942</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4958</v>
+        <v>381</v>
       </c>
       <c r="D116" t="n">
-        <v>5085</v>
+        <v>383.9</v>
       </c>
       <c r="E116" t="n">
-        <v>4888.8</v>
+        <v>375.15</v>
       </c>
       <c r="F116" t="n">
-        <v>4903</v>
+        <v>381</v>
       </c>
       <c r="G116" t="n">
-        <v>1210476</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4903</v>
+        <v>385</v>
       </c>
       <c r="D117" t="n">
-        <v>4940</v>
+        <v>385.05</v>
       </c>
       <c r="E117" t="n">
-        <v>4830.2</v>
+        <v>376.5</v>
       </c>
       <c r="F117" t="n">
-        <v>4838.8</v>
+        <v>381</v>
       </c>
       <c r="G117" t="n">
-        <v>299859</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1417</v>
+        <v>382.5</v>
       </c>
       <c r="D118" t="n">
-        <v>1436</v>
+        <v>382.85</v>
       </c>
       <c r="E118" t="n">
-        <v>1410.1</v>
+        <v>377.15</v>
       </c>
       <c r="F118" t="n">
-        <v>1423.9</v>
+        <v>381</v>
       </c>
       <c r="G118" t="n">
-        <v>623969</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1428</v>
+        <v>381.7</v>
       </c>
       <c r="D119" t="n">
-        <v>1428</v>
+        <v>387.7</v>
       </c>
       <c r="E119" t="n">
-        <v>1351.5</v>
+        <v>381.1</v>
       </c>
       <c r="F119" t="n">
-        <v>1359.1</v>
+        <v>382.7</v>
       </c>
       <c r="G119" t="n">
-        <v>808190</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1349.8</v>
+        <v>387.15</v>
       </c>
       <c r="D120" t="n">
-        <v>1357.8</v>
+        <v>393.7</v>
       </c>
       <c r="E120" t="n">
-        <v>1330.1</v>
+        <v>384.5</v>
       </c>
       <c r="F120" t="n">
-        <v>1340.8</v>
+        <v>388</v>
       </c>
       <c r="G120" t="n">
-        <v>345535</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1340.8</v>
+        <v>398.5</v>
       </c>
       <c r="D121" t="n">
-        <v>1387.7</v>
+        <v>422.2</v>
       </c>
       <c r="E121" t="n">
-        <v>1316</v>
+        <v>398.5</v>
       </c>
       <c r="F121" t="n">
-        <v>1374.4</v>
+        <v>418.6</v>
       </c>
       <c r="G121" t="n">
-        <v>974660</v>
+        <v>22236726</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1372.9</v>
+        <v>4389.8</v>
       </c>
       <c r="D122" t="n">
-        <v>1390</v>
+        <v>4485</v>
       </c>
       <c r="E122" t="n">
-        <v>1355.1</v>
+        <v>4361.9</v>
       </c>
       <c r="F122" t="n">
-        <v>1363.5</v>
+        <v>4398.1</v>
       </c>
       <c r="G122" t="n">
-        <v>479123</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1363</v>
+        <v>4422</v>
       </c>
       <c r="D123" t="n">
-        <v>1392</v>
+        <v>4495</v>
       </c>
       <c r="E123" t="n">
-        <v>1355.1</v>
+        <v>4358</v>
       </c>
       <c r="F123" t="n">
-        <v>1380</v>
+        <v>4371.4</v>
       </c>
       <c r="G123" t="n">
-        <v>616767</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1360</v>
+        <v>4387.7</v>
       </c>
       <c r="D124" t="n">
-        <v>1368</v>
+        <v>4404</v>
       </c>
       <c r="E124" t="n">
-        <v>1272.1</v>
+        <v>4281.9</v>
       </c>
       <c r="F124" t="n">
-        <v>1288.3</v>
+        <v>4304.2</v>
       </c>
       <c r="G124" t="n">
-        <v>1098492</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1300</v>
+        <v>4285</v>
       </c>
       <c r="D125" t="n">
-        <v>1318.5</v>
+        <v>4317</v>
       </c>
       <c r="E125" t="n">
-        <v>1257</v>
+        <v>4220</v>
       </c>
       <c r="F125" t="n">
-        <v>1316.2</v>
+        <v>4244.3</v>
       </c>
       <c r="G125" t="n">
-        <v>1172726</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1317.7</v>
+        <v>4211</v>
       </c>
       <c r="D126" t="n">
-        <v>1319.8</v>
+        <v>4220</v>
       </c>
       <c r="E126" t="n">
-        <v>1270.5</v>
+        <v>4129.3</v>
       </c>
       <c r="F126" t="n">
-        <v>1306</v>
+        <v>4178.1</v>
       </c>
       <c r="G126" t="n">
-        <v>832973</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1319.9</v>
+        <v>4190</v>
       </c>
       <c r="D127" t="n">
-        <v>1355.4</v>
+        <v>4324.4</v>
       </c>
       <c r="E127" t="n">
-        <v>1308</v>
+        <v>4190</v>
       </c>
       <c r="F127" t="n">
-        <v>1343.4</v>
+        <v>4257.3</v>
       </c>
       <c r="G127" t="n">
-        <v>1287698</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1379</v>
+        <v>4290</v>
       </c>
       <c r="D128" t="n">
-        <v>1468</v>
+        <v>4383</v>
       </c>
       <c r="E128" t="n">
-        <v>1361</v>
+        <v>4266</v>
       </c>
       <c r="F128" t="n">
-        <v>1377.8</v>
+        <v>4288.7</v>
       </c>
       <c r="G128" t="n">
-        <v>9950655</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1380.5</v>
+        <v>4299</v>
       </c>
       <c r="D129" t="n">
-        <v>1403.3</v>
+        <v>4340</v>
       </c>
       <c r="E129" t="n">
-        <v>1363</v>
+        <v>4216</v>
       </c>
       <c r="F129" t="n">
-        <v>1366.8</v>
+        <v>4243.8</v>
       </c>
       <c r="G129" t="n">
-        <v>1567542</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1380</v>
+        <v>4201.9</v>
       </c>
       <c r="D130" t="n">
-        <v>1397.5</v>
+        <v>4222</v>
       </c>
       <c r="E130" t="n">
-        <v>1351.6</v>
+        <v>4115</v>
       </c>
       <c r="F130" t="n">
-        <v>1360.6</v>
+        <v>4156</v>
       </c>
       <c r="G130" t="n">
-        <v>1098353</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1360.6</v>
+        <v>4181.8</v>
       </c>
       <c r="D131" t="n">
-        <v>1428</v>
+        <v>4385</v>
       </c>
       <c r="E131" t="n">
-        <v>1354.5</v>
+        <v>4129.4</v>
       </c>
       <c r="F131" t="n">
-        <v>1421.6</v>
+        <v>4362.2</v>
       </c>
       <c r="G131" t="n">
-        <v>2055261</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1429.6</v>
+        <v>4380</v>
       </c>
       <c r="D132" t="n">
-        <v>1453</v>
+        <v>4478.3</v>
       </c>
       <c r="E132" t="n">
-        <v>1419</v>
+        <v>4280.1</v>
       </c>
       <c r="F132" t="n">
-        <v>1434.1</v>
+        <v>4395.7</v>
       </c>
       <c r="G132" t="n">
-        <v>1243415</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1434</v>
+        <v>4497.2</v>
       </c>
       <c r="D133" t="n">
-        <v>1460</v>
+        <v>4541.17</v>
       </c>
       <c r="E133" t="n">
-        <v>1405</v>
+        <v>4319.31</v>
       </c>
       <c r="F133" t="n">
-        <v>1418</v>
+        <v>4361.38</v>
       </c>
       <c r="G133" t="n">
-        <v>1123973</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1413.9</v>
+        <v>4338</v>
       </c>
       <c r="D134" t="n">
-        <v>1434</v>
+        <v>4339.1</v>
       </c>
       <c r="E134" t="n">
-        <v>1407.5</v>
+        <v>4172.9</v>
       </c>
       <c r="F134" t="n">
-        <v>1424.7</v>
+        <v>4192.59</v>
       </c>
       <c r="G134" t="n">
-        <v>509551</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1434.1</v>
+        <v>4297.32</v>
       </c>
       <c r="D135" t="n">
-        <v>1522</v>
+        <v>4595.14</v>
       </c>
       <c r="E135" t="n">
-        <v>1427.5</v>
+        <v>4249.35</v>
       </c>
       <c r="F135" t="n">
-        <v>1516.4</v>
+        <v>4521.18</v>
       </c>
       <c r="G135" t="n">
-        <v>3863757</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>4557.56</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4737.05</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4537.17</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4583.14</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2334958</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>4606.13</v>
+      </c>
+      <c r="D137" t="n">
+        <v>4777.02</v>
+      </c>
+      <c r="E137" t="n">
+        <v>4590.24</v>
+      </c>
+      <c r="F137" t="n">
+        <v>4759.23</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1899271</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>4817.7</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4929.93</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4722.06</v>
+      </c>
+      <c r="F138" t="n">
+        <v>4890.75</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1924204</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>4896.95</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4976.9</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4780.02</v>
+      </c>
+      <c r="F139" t="n">
+        <v>4813</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1117424</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>4790</v>
+      </c>
+      <c r="D140" t="n">
+        <v>4968</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F140" t="n">
+        <v>4939.2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1296942</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4958</v>
+      </c>
+      <c r="D141" t="n">
+        <v>5085</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4888.8</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4903</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1210476</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4903</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4940</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4792.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>4859.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>682980</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>4866</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4907.9</v>
+      </c>
+      <c r="E143" t="n">
+        <v>4769.8</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4776</v>
+      </c>
+      <c r="G143" t="n">
+        <v>320785</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C136" t="n">
+      <c r="C144" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1436</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1410.1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1423.9</v>
+      </c>
+      <c r="G144" t="n">
+        <v>623969</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1428</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1351.5</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1359.1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>808190</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1349.8</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1357.8</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="G146" t="n">
+        <v>345535</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1340.8</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1387.7</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1374.4</v>
+      </c>
+      <c r="G147" t="n">
+        <v>974660</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1372.9</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>479123</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G149" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G152" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G154" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1413.9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1407.5</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1424.7</v>
+      </c>
+      <c r="G160" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1522</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="F161" t="n">
         <v>1516.4</v>
       </c>
-      <c r="D136" t="n">
+      <c r="G161" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="D162" t="n">
         <v>1543</v>
       </c>
-      <c r="E136" t="n">
-        <v>1503</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1504.1</v>
-      </c>
-      <c r="G136" t="n">
-        <v>707906</v>
+      <c r="E162" t="n">
+        <v>1486.9</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1485.1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1497.7</v>
+      </c>
+      <c r="G163" t="n">
+        <v>302361</v>
       </c>
     </row>
   </sheetData>
@@ -8533,7 +9758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8688,6 +9913,21 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 12 Aug 2026 05:15</t>
+          <t>Generated 13 Aug 2026 05:18</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="D2" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="E2" t="n">
-        <v>51.9</v>
+        <v>56.7</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="3">
@@ -629,25 +629,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>4.94</v>
+        <v>5.34</v>
       </c>
       <c r="D3" t="n">
-        <v>2.96</v>
+        <v>4.38</v>
       </c>
       <c r="E3" t="n">
-        <v>77.8</v>
+        <v>76.2</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.84</v>
+        <v>-2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>6.12</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="4">
@@ -657,25 +657,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>12.8</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>11.29</v>
+        <v>10.56</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>26.91</v>
       </c>
       <c r="G4" t="n">
-        <v>4.07</v>
+        <v>-4.07</v>
       </c>
       <c r="H4" t="n">
-        <v>7.65</v>
+        <v>8.73</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,6 +2569,192 @@
         <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" t="n">
+        <v>206.24</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>229.55</v>
+      </c>
+      <c r="I32" t="n">
+        <v>209.53</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>249.57</v>
+      </c>
+      <c r="L32" t="n">
+        <v>269.59</v>
+      </c>
+      <c r="M32" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>99</v>
+      </c>
+      <c r="F33" t="n">
+        <v>109.98</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="K33" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="L33" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>99</v>
+      </c>
+      <c r="F34" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1591.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1491.87</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1691.13</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1790.76</v>
+      </c>
+      <c r="M34" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -2585,7 +2771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3563,6 +3749,105 @@
       </c>
       <c r="I31" t="n">
         <v>642.52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>229.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>209.53</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="H32" t="n">
+        <v>249.57</v>
+      </c>
+      <c r="I32" t="n">
+        <v>269.59</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H33" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I33" t="n">
+        <v>15.33</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1591.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1491.87</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="G34" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1691.13</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1790.76</v>
       </c>
     </row>
   </sheetData>
@@ -3576,7 +3861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,7 +3964,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3699,7 +3984,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>216.81</v>
+        <v>229.55</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3707,16 +3992,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.35</v>
+        <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.83</v>
+        <v>-3.02</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -3732,7 +4017,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3752,7 +4037,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.49</v>
+        <v>13.79</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3760,16 +4045,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>0.65</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.89</v>
+        <v>-2.39</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -3785,12 +4070,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3805,7 +4090,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>568.6</v>
+        <v>1591.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3813,19 +4098,19 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.22</v>
+        <v>2.94</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.86</v>
+        <v>-1.33</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -3833,14 +4118,12 @@
       <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3860,26 +4143,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>3.62</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>3.58</v>
+        <v>4.26</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -3895,12 +4178,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3915,26 +4198,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.72</v>
+        <v>2.15</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>2.81</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.85</v>
+        <v>-4.96</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -3950,12 +4233,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3970,29 +4253,29 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.65</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3.08</v>
+        <v>4.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.01</v>
+        <v>-3.3</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -4000,12 +4283,14 @@
       <c r="R7" t="b">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4025,26 +4310,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.69</v>
+        <v>7.8</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -4060,19 +4345,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4080,26 +4365,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>2.57</v>
+        <v>5.75</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5</v>
+        <v>-2.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -4115,19 +4400,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4135,32 +4420,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G10" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.01</v>
+        <v>-3.19</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
@@ -4170,7 +4455,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4190,32 +4475,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>8.949999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -4225,7 +4510,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4245,26 +4530,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9</v>
+        <v>-3.67</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -4280,7 +4565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4303,7 +4588,7 @@
         <v>381</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -4313,13 +4598,13 @@
         <v>10.81</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.18</v>
+        <v>-1.01</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -4328,14 +4613,14 @@
         <v>1</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4355,34 +4640,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16</v>
+        <v>12.71</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>4.56</v>
+        <v>13.39</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -4392,12 +4677,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4412,28 +4697,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.35</v>
+        <v>-1.76</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>3.97</v>
+        <v>3.21</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.45</v>
+        <v>-3.07</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -4449,12 +4734,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -4469,44 +4754,44 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.84</v>
+        <v>7.57</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.2</v>
+        <v>-1.18</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4526,28 +4811,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G17" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H17" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>9.43</v>
+        <v>8.82</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -4563,7 +4848,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4575,7 +4860,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4583,28 +4868,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H18" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>6.85</v>
+        <v>5.08</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -4620,12 +4905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4640,34 +4925,34 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G19" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H19" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.61</v>
+        <v>-4.37</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -4677,19 +4962,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4697,28 +4982,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G20" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H20" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>10.95</v>
+        <v>13.89</v>
       </c>
       <c r="M20" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N20" t="n">
         <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -4734,19 +5019,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4754,34 +5039,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>1.76</v>
+        <v>7.98</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.49</v>
+        <v>-3.55</v>
       </c>
       <c r="N21" t="n">
         <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -4791,19 +5076,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4811,28 +5096,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G22" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H22" t="n">
-        <v>11.45</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>13.41</v>
+        <v>11.99</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -4848,12 +5133,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4868,34 +5153,34 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H23" t="n">
-        <v>2.92</v>
+        <v>6.98</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>11.99</v>
+        <v>12.13</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -4905,7 +5190,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4925,28 +5210,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.18</v>
+        <v>-4.66</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -4962,19 +5247,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4982,34 +5267,34 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G25" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H25" t="n">
-        <v>2.73</v>
+        <v>11.45</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>5.02</v>
+        <v>13.41</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -5019,12 +5304,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5039,50 +5324,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H26" t="n">
-        <v>9.65</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
-        <v>12.01</v>
+        <v>7.11</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>14.64</v>
+        <v>11.99</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
       <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5090,38 +5383,46 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H27" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I27" t="n">
-        <v>9.51</v>
+        <v>-4.07</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>16.59</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.32</v>
+        <v>-5.35</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
       <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5133,7 +5434,7 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5144,13 +5445,13 @@
         <v>1781.3</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I28" t="n">
         <v>3.01</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4.07</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -5158,33 +5459,41 @@
         <v>5.02</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5192,24 +5501,24 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G29" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H29" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I29" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>28.76</v>
+        <v>19.32</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
@@ -5223,19 +5532,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5243,24 +5552,24 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G30" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H30" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I30" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>17.79</v>
+        <v>17.83</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
@@ -5274,19 +5583,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5294,24 +5603,24 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I31" t="n">
-        <v>10.56</v>
+        <v>4.07</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>15.68</v>
+        <v>5.02</v>
       </c>
       <c r="M31" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
@@ -5321,6 +5630,159 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H32" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I32" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>96</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>92</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5333,7 +5795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5877,46 +6339,46 @@
         <v>1629.7</v>
       </c>
       <c r="E20" t="n">
-        <v>1573.1</v>
+        <v>1570.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1579</v>
+        <v>1599</v>
       </c>
       <c r="G20" t="n">
-        <v>595462</v>
+        <v>1586459</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1188.4</v>
+        <v>1607</v>
       </c>
       <c r="D21" t="n">
-        <v>1207.9</v>
+        <v>1638.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1158</v>
+        <v>1570.4</v>
       </c>
       <c r="F21" t="n">
-        <v>1201.8</v>
+        <v>1591.5</v>
       </c>
       <c r="G21" t="n">
-        <v>3482939</v>
+        <v>1733631</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5925,25 +6387,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D22" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F22" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G22" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5952,25 +6414,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D23" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F23" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5979,25 +6441,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D24" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E24" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F24" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G24" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6006,25 +6468,25 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F25" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D25" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G25" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6033,25 +6495,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D26" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F26" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6060,25 +6522,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D27" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E27" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F27" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G27" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6087,25 +6549,25 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F28" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D28" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G28" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6114,25 +6576,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D29" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G29" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6141,25 +6603,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D30" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E30" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F30" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6168,25 +6630,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D31" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E31" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G31" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6195,25 +6657,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D32" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E32" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F32" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G32" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6222,25 +6684,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D33" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E33" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G33" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6249,25 +6711,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D34" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F34" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G34" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6276,25 +6738,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D35" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E35" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F35" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G35" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6303,25 +6765,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D36" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E36" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F36" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G36" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6330,25 +6792,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D37" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E37" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G37" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6357,25 +6819,25 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F38" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D38" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G38" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6384,25 +6846,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D39" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E39" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F39" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G39" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6411,25 +6873,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D40" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E40" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F40" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G40" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6438,25 +6900,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D41" t="n">
-        <v>1534.8</v>
+        <v>1520</v>
       </c>
       <c r="E41" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F41" t="n">
-        <v>1525.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G41" t="n">
-        <v>4867021</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6465,79 +6927,79 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1531.7</v>
+        <v>1472.4</v>
       </c>
       <c r="D42" t="n">
-        <v>1547.7</v>
+        <v>1534.8</v>
       </c>
       <c r="E42" t="n">
-        <v>1511.1</v>
+        <v>1472</v>
       </c>
       <c r="F42" t="n">
-        <v>1537.1</v>
+        <v>1525.4</v>
       </c>
       <c r="G42" t="n">
-        <v>1307034</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>211.95</v>
+        <v>1531.7</v>
       </c>
       <c r="D43" t="n">
-        <v>214.55</v>
+        <v>1580</v>
       </c>
       <c r="E43" t="n">
-        <v>206.1</v>
+        <v>1511.1</v>
       </c>
       <c r="F43" t="n">
-        <v>212.78</v>
+        <v>1569.4</v>
       </c>
       <c r="G43" t="n">
-        <v>12863408</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>214.3</v>
+        <v>1575</v>
       </c>
       <c r="D44" t="n">
-        <v>223.41</v>
+        <v>1575</v>
       </c>
       <c r="E44" t="n">
-        <v>214.3</v>
+        <v>1500.1</v>
       </c>
       <c r="F44" t="n">
-        <v>223.08</v>
+        <v>1525.5</v>
       </c>
       <c r="G44" t="n">
-        <v>32151413</v>
+        <v>2487069</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6546,25 +7008,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D45" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E45" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F45" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G45" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6573,25 +7035,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D46" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E46" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F46" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G46" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6600,25 +7062,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D47" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E47" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F47" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G47" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6627,25 +7089,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D48" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E48" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F48" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G48" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6654,25 +7116,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D49" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E49" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F49" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G49" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6681,25 +7143,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D50" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E50" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F50" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G50" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6708,25 +7170,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D51" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E51" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F51" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G51" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6735,25 +7197,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D52" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E52" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F52" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G52" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6762,25 +7224,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D53" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E53" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F53" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G53" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6789,25 +7251,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D54" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E54" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F54" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G54" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6816,25 +7278,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D55" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E55" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F55" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G55" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6843,25 +7305,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D56" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E56" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F56" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G56" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6870,25 +7332,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D57" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E57" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F57" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G57" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6897,25 +7359,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D58" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E58" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F58" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G58" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6924,25 +7386,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D59" t="n">
-        <v>212.91</v>
+        <v>203.61</v>
       </c>
       <c r="E59" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F59" t="n">
-        <v>212.23</v>
+        <v>202.52</v>
       </c>
       <c r="G59" t="n">
-        <v>37479685</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6951,25 +7413,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>212.4</v>
+        <v>202.4</v>
       </c>
       <c r="D60" t="n">
-        <v>213.45</v>
+        <v>207</v>
       </c>
       <c r="E60" t="n">
-        <v>203</v>
+        <v>200.22</v>
       </c>
       <c r="F60" t="n">
-        <v>203.67</v>
+        <v>202.78</v>
       </c>
       <c r="G60" t="n">
-        <v>19195935</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6978,25 +7440,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>203.98</v>
+        <v>205.8</v>
       </c>
       <c r="D61" t="n">
-        <v>211.52</v>
+        <v>212.91</v>
       </c>
       <c r="E61" t="n">
-        <v>201</v>
+        <v>205.03</v>
       </c>
       <c r="F61" t="n">
-        <v>207.98</v>
+        <v>212.23</v>
       </c>
       <c r="G61" t="n">
-        <v>19489977</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7005,25 +7467,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>209</v>
+        <v>212.4</v>
       </c>
       <c r="D62" t="n">
-        <v>216.6</v>
+        <v>213.45</v>
       </c>
       <c r="E62" t="n">
-        <v>207.83</v>
+        <v>203</v>
       </c>
       <c r="F62" t="n">
-        <v>212.97</v>
+        <v>203.67</v>
       </c>
       <c r="G62" t="n">
-        <v>19215795</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7032,25 +7494,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>214</v>
+        <v>203.98</v>
       </c>
       <c r="D63" t="n">
-        <v>215.8</v>
+        <v>211.52</v>
       </c>
       <c r="E63" t="n">
-        <v>209.25</v>
+        <v>201</v>
       </c>
       <c r="F63" t="n">
-        <v>214.24</v>
+        <v>207.98</v>
       </c>
       <c r="G63" t="n">
-        <v>15006611</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7059,106 +7521,106 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>215.4</v>
+        <v>209</v>
       </c>
       <c r="D64" t="n">
-        <v>221.9</v>
+        <v>216.6</v>
       </c>
       <c r="E64" t="n">
-        <v>215</v>
+        <v>207.83</v>
       </c>
       <c r="F64" t="n">
-        <v>216.81</v>
+        <v>212.97</v>
       </c>
       <c r="G64" t="n">
-        <v>10481598</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>481.25</v>
+        <v>214</v>
       </c>
       <c r="D65" t="n">
-        <v>489.85</v>
+        <v>215.8</v>
       </c>
       <c r="E65" t="n">
-        <v>477.5</v>
+        <v>209.25</v>
       </c>
       <c r="F65" t="n">
-        <v>480.25</v>
+        <v>214.24</v>
       </c>
       <c r="G65" t="n">
-        <v>2347659</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>485.2</v>
+        <v>215.4</v>
       </c>
       <c r="D66" t="n">
-        <v>499</v>
+        <v>223.61</v>
       </c>
       <c r="E66" t="n">
-        <v>482.55</v>
+        <v>215</v>
       </c>
       <c r="F66" t="n">
-        <v>491.6</v>
+        <v>221.52</v>
       </c>
       <c r="G66" t="n">
-        <v>7339280</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>495</v>
+        <v>223</v>
       </c>
       <c r="D67" t="n">
-        <v>498.5</v>
+        <v>230.95</v>
       </c>
       <c r="E67" t="n">
-        <v>491</v>
+        <v>222.62</v>
       </c>
       <c r="F67" t="n">
-        <v>495.05</v>
+        <v>229.55</v>
       </c>
       <c r="G67" t="n">
-        <v>2755226</v>
+        <v>13940755</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7167,25 +7629,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>495.05</v>
+        <v>481.25</v>
       </c>
       <c r="D68" t="n">
-        <v>504.3</v>
+        <v>489.85</v>
       </c>
       <c r="E68" t="n">
-        <v>490.05</v>
+        <v>477.5</v>
       </c>
       <c r="F68" t="n">
-        <v>492.35</v>
+        <v>480.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4448305</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7194,25 +7656,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>496.2</v>
+        <v>485.2</v>
       </c>
       <c r="D69" t="n">
-        <v>539.6</v>
+        <v>499</v>
       </c>
       <c r="E69" t="n">
-        <v>495.1</v>
+        <v>482.55</v>
       </c>
       <c r="F69" t="n">
-        <v>533.8</v>
+        <v>491.6</v>
       </c>
       <c r="G69" t="n">
-        <v>22701332</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7221,25 +7683,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>542.45</v>
+        <v>495</v>
       </c>
       <c r="D70" t="n">
-        <v>551</v>
+        <v>498.5</v>
       </c>
       <c r="E70" t="n">
-        <v>525.55</v>
+        <v>491</v>
       </c>
       <c r="F70" t="n">
-        <v>545.95</v>
+        <v>495.05</v>
       </c>
       <c r="G70" t="n">
-        <v>19838083</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7248,25 +7710,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>543.75</v>
+        <v>495.05</v>
       </c>
       <c r="D71" t="n">
-        <v>548</v>
+        <v>504.3</v>
       </c>
       <c r="E71" t="n">
-        <v>532.1</v>
+        <v>490.05</v>
       </c>
       <c r="F71" t="n">
-        <v>536.1</v>
+        <v>492.35</v>
       </c>
       <c r="G71" t="n">
-        <v>9431736</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7275,25 +7737,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>537.95</v>
+        <v>496.2</v>
       </c>
       <c r="D72" t="n">
-        <v>552</v>
+        <v>539.6</v>
       </c>
       <c r="E72" t="n">
-        <v>522</v>
+        <v>495.1</v>
       </c>
       <c r="F72" t="n">
-        <v>526.25</v>
+        <v>533.8</v>
       </c>
       <c r="G72" t="n">
-        <v>12427899</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7302,25 +7764,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>531</v>
+        <v>542.45</v>
       </c>
       <c r="D73" t="n">
-        <v>538.8</v>
+        <v>551</v>
       </c>
       <c r="E73" t="n">
-        <v>527.7</v>
+        <v>525.55</v>
       </c>
       <c r="F73" t="n">
-        <v>533.3</v>
+        <v>545.95</v>
       </c>
       <c r="G73" t="n">
-        <v>5547022</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7329,133 +7791,133 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>530.85</v>
+        <v>543.75</v>
       </c>
       <c r="D74" t="n">
-        <v>569.85</v>
+        <v>548</v>
       </c>
       <c r="E74" t="n">
-        <v>529.6</v>
+        <v>532.1</v>
       </c>
       <c r="F74" t="n">
-        <v>568.6</v>
+        <v>536.1</v>
       </c>
       <c r="G74" t="n">
-        <v>14805733</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13.05</v>
+        <v>537.95</v>
       </c>
       <c r="D75" t="n">
-        <v>13.18</v>
+        <v>552</v>
       </c>
       <c r="E75" t="n">
-        <v>12.85</v>
+        <v>522</v>
       </c>
       <c r="F75" t="n">
-        <v>12.87</v>
+        <v>526.25</v>
       </c>
       <c r="G75" t="n">
-        <v>230386335</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>12.98</v>
+        <v>531</v>
       </c>
       <c r="D76" t="n">
-        <v>13.08</v>
+        <v>538.8</v>
       </c>
       <c r="E76" t="n">
-        <v>12.76</v>
+        <v>527.7</v>
       </c>
       <c r="F76" t="n">
-        <v>13.01</v>
+        <v>533.3</v>
       </c>
       <c r="G76" t="n">
-        <v>387269596</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>13.01</v>
+        <v>530.85</v>
       </c>
       <c r="D77" t="n">
-        <v>13.11</v>
+        <v>569.9</v>
       </c>
       <c r="E77" t="n">
-        <v>12.82</v>
+        <v>529.6</v>
       </c>
       <c r="F77" t="n">
-        <v>12.86</v>
+        <v>547.7</v>
       </c>
       <c r="G77" t="n">
-        <v>235409728</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12.89</v>
+        <v>549</v>
       </c>
       <c r="D78" t="n">
-        <v>13.05</v>
+        <v>570.5</v>
       </c>
       <c r="E78" t="n">
-        <v>12.73</v>
+        <v>548.45</v>
       </c>
       <c r="F78" t="n">
-        <v>12.9</v>
+        <v>557</v>
       </c>
       <c r="G78" t="n">
-        <v>308781891</v>
+        <v>7311815</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7464,25 +7926,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12.91</v>
+        <v>13.05</v>
       </c>
       <c r="D79" t="n">
-        <v>13.04</v>
+        <v>13.18</v>
       </c>
       <c r="E79" t="n">
-        <v>12.77</v>
+        <v>12.85</v>
       </c>
       <c r="F79" t="n">
-        <v>12.8</v>
+        <v>12.87</v>
       </c>
       <c r="G79" t="n">
-        <v>204366752</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7491,25 +7953,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>12.89</v>
+        <v>12.98</v>
       </c>
       <c r="D80" t="n">
-        <v>12.9</v>
+        <v>13.08</v>
       </c>
       <c r="E80" t="n">
-        <v>12.63</v>
+        <v>12.76</v>
       </c>
       <c r="F80" t="n">
-        <v>12.63</v>
+        <v>13.01</v>
       </c>
       <c r="G80" t="n">
-        <v>204537429</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7518,25 +7980,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12.64</v>
+        <v>13.01</v>
       </c>
       <c r="D81" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="E81" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="F81" t="n">
-        <v>12.73</v>
+        <v>12.86</v>
       </c>
       <c r="G81" t="n">
-        <v>205855564</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7545,25 +8007,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="D82" t="n">
-        <v>13.07</v>
+        <v>13.05</v>
       </c>
       <c r="E82" t="n">
-        <v>12.77</v>
+        <v>12.73</v>
       </c>
       <c r="F82" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
       <c r="G82" t="n">
-        <v>413469644</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7572,25 +8034,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>13.14</v>
+        <v>12.91</v>
       </c>
       <c r="D83" t="n">
-        <v>13.3</v>
+        <v>13.04</v>
       </c>
       <c r="E83" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
       <c r="F83" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="G83" t="n">
-        <v>662095209</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7599,160 +8061,160 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12.93</v>
+        <v>12.89</v>
       </c>
       <c r="D84" t="n">
-        <v>13.69</v>
+        <v>12.9</v>
       </c>
       <c r="E84" t="n">
-        <v>12.83</v>
+        <v>12.63</v>
       </c>
       <c r="F84" t="n">
-        <v>13.49</v>
+        <v>12.63</v>
       </c>
       <c r="G84" t="n">
-        <v>403055279</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1554.3</v>
+        <v>12.64</v>
       </c>
       <c r="D85" t="n">
-        <v>1569</v>
+        <v>12.88</v>
       </c>
       <c r="E85" t="n">
-        <v>1551.3</v>
+        <v>12.6</v>
       </c>
       <c r="F85" t="n">
-        <v>1557.6</v>
+        <v>12.73</v>
       </c>
       <c r="G85" t="n">
-        <v>1001677</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1560.4</v>
+        <v>12.92</v>
       </c>
       <c r="D86" t="n">
-        <v>1561</v>
+        <v>13.07</v>
       </c>
       <c r="E86" t="n">
-        <v>1520.4</v>
+        <v>12.77</v>
       </c>
       <c r="F86" t="n">
-        <v>1529.8</v>
+        <v>12.92</v>
       </c>
       <c r="G86" t="n">
-        <v>1011017</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1534.9</v>
+        <v>13.14</v>
       </c>
       <c r="D87" t="n">
-        <v>1572.2</v>
+        <v>13.3</v>
       </c>
       <c r="E87" t="n">
-        <v>1527.2</v>
+        <v>12.79</v>
       </c>
       <c r="F87" t="n">
-        <v>1558.9</v>
+        <v>12.89</v>
       </c>
       <c r="G87" t="n">
-        <v>1235837</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1559.7</v>
+        <v>12.93</v>
       </c>
       <c r="D88" t="n">
-        <v>1600.1</v>
+        <v>13.69</v>
       </c>
       <c r="E88" t="n">
-        <v>1557</v>
+        <v>12.83</v>
       </c>
       <c r="F88" t="n">
-        <v>1593.2</v>
+        <v>13.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1871739</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1591</v>
+        <v>13.67</v>
       </c>
       <c r="D89" t="n">
-        <v>1593.2</v>
+        <v>13.88</v>
       </c>
       <c r="E89" t="n">
-        <v>1566</v>
+        <v>13.46</v>
       </c>
       <c r="F89" t="n">
-        <v>1577.8</v>
+        <v>13.79</v>
       </c>
       <c r="G89" t="n">
-        <v>1183077</v>
+        <v>358968218</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7761,25 +8223,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1577.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D90" t="n">
-        <v>1586.1</v>
+        <v>1569</v>
       </c>
       <c r="E90" t="n">
-        <v>1561.1</v>
+        <v>1551.3</v>
       </c>
       <c r="F90" t="n">
-        <v>1568.3</v>
+        <v>1557.6</v>
       </c>
       <c r="G90" t="n">
-        <v>1098268</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7788,25 +8250,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1560</v>
+        <v>1560.4</v>
       </c>
       <c r="D91" t="n">
-        <v>1610</v>
+        <v>1561</v>
       </c>
       <c r="E91" t="n">
-        <v>1554.9</v>
+        <v>1520.4</v>
       </c>
       <c r="F91" t="n">
-        <v>1601.2</v>
+        <v>1529.8</v>
       </c>
       <c r="G91" t="n">
-        <v>2647403</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7815,25 +8277,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1624.8</v>
+        <v>1534.9</v>
       </c>
       <c r="D92" t="n">
-        <v>1734.5</v>
+        <v>1572.2</v>
       </c>
       <c r="E92" t="n">
-        <v>1617.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F92" t="n">
-        <v>1713.4</v>
+        <v>1558.9</v>
       </c>
       <c r="G92" t="n">
-        <v>7989771</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7842,25 +8304,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1713</v>
+        <v>1559.7</v>
       </c>
       <c r="D93" t="n">
-        <v>1762</v>
+        <v>1600.1</v>
       </c>
       <c r="E93" t="n">
-        <v>1707.7</v>
+        <v>1557</v>
       </c>
       <c r="F93" t="n">
-        <v>1758.9</v>
+        <v>1593.2</v>
       </c>
       <c r="G93" t="n">
-        <v>4407907</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7869,25 +8331,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1762</v>
+        <v>1591</v>
       </c>
       <c r="D94" t="n">
-        <v>1797.9</v>
+        <v>1593.2</v>
       </c>
       <c r="E94" t="n">
-        <v>1754.3</v>
+        <v>1566</v>
       </c>
       <c r="F94" t="n">
-        <v>1781.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G94" t="n">
-        <v>3000811</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7896,25 +8358,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1785</v>
+        <v>1577.7</v>
       </c>
       <c r="D95" t="n">
-        <v>1798.9</v>
+        <v>1586.1</v>
       </c>
       <c r="E95" t="n">
-        <v>1773.3</v>
+        <v>1561.1</v>
       </c>
       <c r="F95" t="n">
-        <v>1781.3</v>
+        <v>1568.3</v>
       </c>
       <c r="G95" t="n">
-        <v>2402202</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7923,25 +8385,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1785</v>
+        <v>1560</v>
       </c>
       <c r="D96" t="n">
-        <v>1826.6</v>
+        <v>1610</v>
       </c>
       <c r="E96" t="n">
-        <v>1785</v>
+        <v>1554.9</v>
       </c>
       <c r="F96" t="n">
-        <v>1816.2</v>
+        <v>1601.2</v>
       </c>
       <c r="G96" t="n">
-        <v>2502579</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7950,25 +8412,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1821</v>
+        <v>1624.8</v>
       </c>
       <c r="D97" t="n">
-        <v>1838.3</v>
+        <v>1734.5</v>
       </c>
       <c r="E97" t="n">
-        <v>1789.1</v>
+        <v>1617.1</v>
       </c>
       <c r="F97" t="n">
-        <v>1811.4</v>
+        <v>1713.4</v>
       </c>
       <c r="G97" t="n">
-        <v>1919384</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7977,25 +8439,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1811</v>
+        <v>1713</v>
       </c>
       <c r="D98" t="n">
-        <v>1850</v>
+        <v>1762</v>
       </c>
       <c r="E98" t="n">
-        <v>1806.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F98" t="n">
-        <v>1850</v>
+        <v>1758.9</v>
       </c>
       <c r="G98" t="n">
-        <v>1405192</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8004,25 +8466,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1854</v>
+        <v>1762</v>
       </c>
       <c r="D99" t="n">
-        <v>1856.6</v>
+        <v>1797.9</v>
       </c>
       <c r="E99" t="n">
-        <v>1834.5</v>
+        <v>1754.3</v>
       </c>
       <c r="F99" t="n">
-        <v>1835</v>
+        <v>1781.3</v>
       </c>
       <c r="G99" t="n">
-        <v>2090998</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8031,25 +8493,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1843</v>
+        <v>1785</v>
       </c>
       <c r="D100" t="n">
-        <v>1854.9</v>
+        <v>1798.9</v>
       </c>
       <c r="E100" t="n">
-        <v>1830</v>
+        <v>1773.3</v>
       </c>
       <c r="F100" t="n">
-        <v>1830</v>
+        <v>1781.3</v>
       </c>
       <c r="G100" t="n">
-        <v>2037418</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8058,25 +8520,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1838</v>
+        <v>1785</v>
       </c>
       <c r="D101" t="n">
-        <v>1856</v>
+        <v>1826.6</v>
       </c>
       <c r="E101" t="n">
-        <v>1833.2</v>
+        <v>1785</v>
       </c>
       <c r="F101" t="n">
-        <v>1844.3</v>
+        <v>1816.2</v>
       </c>
       <c r="G101" t="n">
-        <v>1553067</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8085,25 +8547,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1845</v>
+        <v>1821</v>
       </c>
       <c r="D102" t="n">
-        <v>1870.8</v>
+        <v>1838.3</v>
       </c>
       <c r="E102" t="n">
-        <v>1832.8</v>
+        <v>1789.1</v>
       </c>
       <c r="F102" t="n">
-        <v>1854</v>
+        <v>1811.4</v>
       </c>
       <c r="G102" t="n">
-        <v>1386592</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8112,25 +8574,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1851</v>
+        <v>1811</v>
       </c>
       <c r="D103" t="n">
-        <v>1859</v>
+        <v>1850</v>
       </c>
       <c r="E103" t="n">
-        <v>1833.1</v>
+        <v>1806.1</v>
       </c>
       <c r="F103" t="n">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="G103" t="n">
-        <v>1514239</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8139,187 +8601,187 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1856.3</v>
+        <v>1854</v>
       </c>
       <c r="D104" t="n">
-        <v>1862.3</v>
+        <v>1856.6</v>
       </c>
       <c r="E104" t="n">
-        <v>1847.2</v>
+        <v>1834.5</v>
       </c>
       <c r="F104" t="n">
-        <v>1853.8</v>
+        <v>1835</v>
       </c>
       <c r="G104" t="n">
-        <v>332074</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>344</v>
+        <v>1843</v>
       </c>
       <c r="D105" t="n">
-        <v>346.3</v>
+        <v>1854.9</v>
       </c>
       <c r="E105" t="n">
-        <v>341.25</v>
+        <v>1830</v>
       </c>
       <c r="F105" t="n">
-        <v>342.9</v>
+        <v>1830</v>
       </c>
       <c r="G105" t="n">
-        <v>4465145</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>344.2</v>
+        <v>1838</v>
       </c>
       <c r="D106" t="n">
-        <v>347.75</v>
+        <v>1856</v>
       </c>
       <c r="E106" t="n">
-        <v>339.95</v>
+        <v>1833.2</v>
       </c>
       <c r="F106" t="n">
-        <v>342.4</v>
+        <v>1844.3</v>
       </c>
       <c r="G106" t="n">
-        <v>3803051</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>346</v>
+        <v>1845</v>
       </c>
       <c r="D107" t="n">
-        <v>351</v>
+        <v>1870.8</v>
       </c>
       <c r="E107" t="n">
-        <v>343.65</v>
+        <v>1832.8</v>
       </c>
       <c r="F107" t="n">
-        <v>346</v>
+        <v>1854</v>
       </c>
       <c r="G107" t="n">
-        <v>5175178</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>341.8</v>
+        <v>1851</v>
       </c>
       <c r="D108" t="n">
-        <v>344.9</v>
+        <v>1859</v>
       </c>
       <c r="E108" t="n">
-        <v>339.65</v>
+        <v>1833.1</v>
       </c>
       <c r="F108" t="n">
-        <v>343.9</v>
+        <v>1858</v>
       </c>
       <c r="G108" t="n">
-        <v>2253982</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>345.1</v>
+        <v>1856.3</v>
       </c>
       <c r="D109" t="n">
-        <v>346.05</v>
+        <v>1862.3</v>
       </c>
       <c r="E109" t="n">
-        <v>338.35</v>
+        <v>1847.2</v>
       </c>
       <c r="F109" t="n">
-        <v>339.35</v>
+        <v>1853.8</v>
       </c>
       <c r="G109" t="n">
-        <v>3868006</v>
+        <v>332074</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>339.4</v>
+        <v>1850</v>
       </c>
       <c r="D110" t="n">
-        <v>340.2</v>
+        <v>1850.1</v>
       </c>
       <c r="E110" t="n">
-        <v>333</v>
+        <v>1820.6</v>
       </c>
       <c r="F110" t="n">
-        <v>334.55</v>
+        <v>1835</v>
       </c>
       <c r="G110" t="n">
-        <v>3721274</v>
+        <v>548100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8328,25 +8790,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D111" t="n">
-        <v>346.1</v>
+        <v>346.3</v>
       </c>
       <c r="E111" t="n">
-        <v>332</v>
+        <v>341.25</v>
       </c>
       <c r="F111" t="n">
-        <v>344.7</v>
+        <v>342.9</v>
       </c>
       <c r="G111" t="n">
-        <v>5431501</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8355,25 +8817,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>345.5</v>
+        <v>344.2</v>
       </c>
       <c r="D112" t="n">
-        <v>349.65</v>
+        <v>347.75</v>
       </c>
       <c r="E112" t="n">
-        <v>342.6</v>
+        <v>339.95</v>
       </c>
       <c r="F112" t="n">
-        <v>347.65</v>
+        <v>342.4</v>
       </c>
       <c r="G112" t="n">
-        <v>6318472</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8382,25 +8844,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D113" t="n">
-        <v>355.75</v>
+        <v>351</v>
       </c>
       <c r="E113" t="n">
-        <v>347.65</v>
+        <v>343.65</v>
       </c>
       <c r="F113" t="n">
-        <v>350.05</v>
+        <v>346</v>
       </c>
       <c r="G113" t="n">
-        <v>7186013</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8409,25 +8871,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>357.95</v>
+        <v>341.8</v>
       </c>
       <c r="D114" t="n">
-        <v>369</v>
+        <v>344.9</v>
       </c>
       <c r="E114" t="n">
-        <v>353.5</v>
+        <v>339.65</v>
       </c>
       <c r="F114" t="n">
-        <v>369</v>
+        <v>343.9</v>
       </c>
       <c r="G114" t="n">
-        <v>12541474</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8436,25 +8898,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>373</v>
+        <v>345.1</v>
       </c>
       <c r="D115" t="n">
-        <v>382.45</v>
+        <v>346.05</v>
       </c>
       <c r="E115" t="n">
-        <v>367.15</v>
+        <v>338.35</v>
       </c>
       <c r="F115" t="n">
-        <v>377</v>
+        <v>339.35</v>
       </c>
       <c r="G115" t="n">
-        <v>15775994</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8463,25 +8925,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>381</v>
+        <v>339.4</v>
       </c>
       <c r="D116" t="n">
-        <v>383.9</v>
+        <v>340.2</v>
       </c>
       <c r="E116" t="n">
-        <v>375.15</v>
+        <v>333</v>
       </c>
       <c r="F116" t="n">
-        <v>381</v>
+        <v>334.55</v>
       </c>
       <c r="G116" t="n">
-        <v>8940938</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8490,25 +8952,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="D117" t="n">
-        <v>385.05</v>
+        <v>346.1</v>
       </c>
       <c r="E117" t="n">
-        <v>376.5</v>
+        <v>332</v>
       </c>
       <c r="F117" t="n">
-        <v>381</v>
+        <v>344.7</v>
       </c>
       <c r="G117" t="n">
-        <v>6636333</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8517,25 +8979,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>382.5</v>
+        <v>345.5</v>
       </c>
       <c r="D118" t="n">
-        <v>382.85</v>
+        <v>349.65</v>
       </c>
       <c r="E118" t="n">
-        <v>377.15</v>
+        <v>342.6</v>
       </c>
       <c r="F118" t="n">
-        <v>381</v>
+        <v>347.65</v>
       </c>
       <c r="G118" t="n">
-        <v>4423953</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8544,25 +9006,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>381.7</v>
+        <v>352</v>
       </c>
       <c r="D119" t="n">
-        <v>387.7</v>
+        <v>355.75</v>
       </c>
       <c r="E119" t="n">
-        <v>381.1</v>
+        <v>347.65</v>
       </c>
       <c r="F119" t="n">
-        <v>382.7</v>
+        <v>350.05</v>
       </c>
       <c r="G119" t="n">
-        <v>5292453</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8571,25 +9033,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>387.15</v>
+        <v>357.95</v>
       </c>
       <c r="D120" t="n">
-        <v>393.7</v>
+        <v>369</v>
       </c>
       <c r="E120" t="n">
-        <v>384.5</v>
+        <v>353.5</v>
       </c>
       <c r="F120" t="n">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="G120" t="n">
-        <v>8155315</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8598,214 +9060,214 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>398.5</v>
+        <v>373</v>
       </c>
       <c r="D121" t="n">
-        <v>422.2</v>
+        <v>382.45</v>
       </c>
       <c r="E121" t="n">
-        <v>398.5</v>
+        <v>367.15</v>
       </c>
       <c r="F121" t="n">
-        <v>418.6</v>
+        <v>377</v>
       </c>
       <c r="G121" t="n">
-        <v>22236726</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4389.8</v>
+        <v>381</v>
       </c>
       <c r="D122" t="n">
-        <v>4485</v>
+        <v>383.9</v>
       </c>
       <c r="E122" t="n">
-        <v>4361.9</v>
+        <v>375.15</v>
       </c>
       <c r="F122" t="n">
-        <v>4398.1</v>
+        <v>381</v>
       </c>
       <c r="G122" t="n">
-        <v>1347378</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4422</v>
+        <v>385</v>
       </c>
       <c r="D123" t="n">
-        <v>4495</v>
+        <v>385.05</v>
       </c>
       <c r="E123" t="n">
-        <v>4358</v>
+        <v>376.5</v>
       </c>
       <c r="F123" t="n">
-        <v>4371.4</v>
+        <v>381</v>
       </c>
       <c r="G123" t="n">
-        <v>902264</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4387.7</v>
+        <v>382.5</v>
       </c>
       <c r="D124" t="n">
-        <v>4404</v>
+        <v>382.85</v>
       </c>
       <c r="E124" t="n">
-        <v>4281.9</v>
+        <v>377.15</v>
       </c>
       <c r="F124" t="n">
-        <v>4304.2</v>
+        <v>381</v>
       </c>
       <c r="G124" t="n">
-        <v>463349</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4285</v>
+        <v>381.7</v>
       </c>
       <c r="D125" t="n">
-        <v>4317</v>
+        <v>387.7</v>
       </c>
       <c r="E125" t="n">
-        <v>4220</v>
+        <v>381.1</v>
       </c>
       <c r="F125" t="n">
-        <v>4244.3</v>
+        <v>382.7</v>
       </c>
       <c r="G125" t="n">
-        <v>398348</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4211</v>
+        <v>387.15</v>
       </c>
       <c r="D126" t="n">
-        <v>4220</v>
+        <v>393.7</v>
       </c>
       <c r="E126" t="n">
-        <v>4129.3</v>
+        <v>384.5</v>
       </c>
       <c r="F126" t="n">
-        <v>4178.1</v>
+        <v>388</v>
       </c>
       <c r="G126" t="n">
-        <v>470046</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4190</v>
+        <v>398.5</v>
       </c>
       <c r="D127" t="n">
-        <v>4324.4</v>
+        <v>422.2</v>
       </c>
       <c r="E127" t="n">
-        <v>4190</v>
+        <v>398.5</v>
       </c>
       <c r="F127" t="n">
-        <v>4257.3</v>
+        <v>420</v>
       </c>
       <c r="G127" t="n">
-        <v>633457</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4290</v>
+        <v>410.5</v>
       </c>
       <c r="D128" t="n">
-        <v>4383</v>
+        <v>413.65</v>
       </c>
       <c r="E128" t="n">
-        <v>4266</v>
+        <v>404.85</v>
       </c>
       <c r="F128" t="n">
-        <v>4288.7</v>
+        <v>409.85</v>
       </c>
       <c r="G128" t="n">
-        <v>835107</v>
+        <v>3729955</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8814,25 +9276,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4299</v>
+        <v>4389.8</v>
       </c>
       <c r="D129" t="n">
-        <v>4340</v>
+        <v>4485</v>
       </c>
       <c r="E129" t="n">
-        <v>4216</v>
+        <v>4361.9</v>
       </c>
       <c r="F129" t="n">
-        <v>4243.8</v>
+        <v>4398.1</v>
       </c>
       <c r="G129" t="n">
-        <v>422024</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8841,25 +9303,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4201.9</v>
+        <v>4422</v>
       </c>
       <c r="D130" t="n">
-        <v>4222</v>
+        <v>4495</v>
       </c>
       <c r="E130" t="n">
-        <v>4115</v>
+        <v>4358</v>
       </c>
       <c r="F130" t="n">
-        <v>4156</v>
+        <v>4371.4</v>
       </c>
       <c r="G130" t="n">
-        <v>378694</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8868,25 +9330,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4181.8</v>
+        <v>4387.7</v>
       </c>
       <c r="D131" t="n">
-        <v>4385</v>
+        <v>4404</v>
       </c>
       <c r="E131" t="n">
-        <v>4129.4</v>
+        <v>4281.9</v>
       </c>
       <c r="F131" t="n">
-        <v>4362.2</v>
+        <v>4304.2</v>
       </c>
       <c r="G131" t="n">
-        <v>992864</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8895,25 +9357,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4380</v>
+        <v>4285</v>
       </c>
       <c r="D132" t="n">
-        <v>4478.3</v>
+        <v>4317</v>
       </c>
       <c r="E132" t="n">
-        <v>4280.1</v>
+        <v>4220</v>
       </c>
       <c r="F132" t="n">
-        <v>4395.7</v>
+        <v>4244.3</v>
       </c>
       <c r="G132" t="n">
-        <v>960643</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8922,25 +9384,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4497.2</v>
+        <v>4211</v>
       </c>
       <c r="D133" t="n">
-        <v>4541.17</v>
+        <v>4220</v>
       </c>
       <c r="E133" t="n">
-        <v>4319.31</v>
+        <v>4129.3</v>
       </c>
       <c r="F133" t="n">
-        <v>4361.38</v>
+        <v>4178.1</v>
       </c>
       <c r="G133" t="n">
-        <v>1616021</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8949,25 +9411,25 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4338</v>
+        <v>4190</v>
       </c>
       <c r="D134" t="n">
-        <v>4339.1</v>
+        <v>4324.4</v>
       </c>
       <c r="E134" t="n">
-        <v>4172.9</v>
+        <v>4190</v>
       </c>
       <c r="F134" t="n">
-        <v>4192.59</v>
+        <v>4257.3</v>
       </c>
       <c r="G134" t="n">
-        <v>648341</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8976,25 +9438,25 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4297.32</v>
+        <v>4290</v>
       </c>
       <c r="D135" t="n">
-        <v>4595.14</v>
+        <v>4383</v>
       </c>
       <c r="E135" t="n">
-        <v>4249.35</v>
+        <v>4266</v>
       </c>
       <c r="F135" t="n">
-        <v>4521.18</v>
+        <v>4288.7</v>
       </c>
       <c r="G135" t="n">
-        <v>4510774</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9003,25 +9465,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4557.56</v>
+        <v>4299</v>
       </c>
       <c r="D136" t="n">
-        <v>4737.05</v>
+        <v>4340</v>
       </c>
       <c r="E136" t="n">
-        <v>4537.17</v>
+        <v>4216</v>
       </c>
       <c r="F136" t="n">
-        <v>4583.14</v>
+        <v>4243.8</v>
       </c>
       <c r="G136" t="n">
-        <v>2334958</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9030,25 +9492,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4606.13</v>
+        <v>4201.9</v>
       </c>
       <c r="D137" t="n">
-        <v>4777.02</v>
+        <v>4222</v>
       </c>
       <c r="E137" t="n">
-        <v>4590.24</v>
+        <v>4115</v>
       </c>
       <c r="F137" t="n">
-        <v>4759.23</v>
+        <v>4156</v>
       </c>
       <c r="G137" t="n">
-        <v>1899271</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9057,25 +9519,25 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4817.7</v>
+        <v>4181.8</v>
       </c>
       <c r="D138" t="n">
-        <v>4929.93</v>
+        <v>4385</v>
       </c>
       <c r="E138" t="n">
-        <v>4722.06</v>
+        <v>4129.4</v>
       </c>
       <c r="F138" t="n">
-        <v>4890.75</v>
+        <v>4362.2</v>
       </c>
       <c r="G138" t="n">
-        <v>1924204</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9084,25 +9546,25 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4896.95</v>
+        <v>4380</v>
       </c>
       <c r="D139" t="n">
-        <v>4976.9</v>
+        <v>4478.3</v>
       </c>
       <c r="E139" t="n">
-        <v>4780.02</v>
+        <v>4280.1</v>
       </c>
       <c r="F139" t="n">
-        <v>4813</v>
+        <v>4395.7</v>
       </c>
       <c r="G139" t="n">
-        <v>1117424</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9111,25 +9573,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4790</v>
+        <v>4497.2</v>
       </c>
       <c r="D140" t="n">
-        <v>4968</v>
+        <v>4541.17</v>
       </c>
       <c r="E140" t="n">
-        <v>4780</v>
+        <v>4319.31</v>
       </c>
       <c r="F140" t="n">
-        <v>4939.2</v>
+        <v>4361.38</v>
       </c>
       <c r="G140" t="n">
-        <v>1296942</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9138,25 +9600,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4958</v>
+        <v>4338</v>
       </c>
       <c r="D141" t="n">
-        <v>5085</v>
+        <v>4339.1</v>
       </c>
       <c r="E141" t="n">
-        <v>4888.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F141" t="n">
-        <v>4903</v>
+        <v>4192.59</v>
       </c>
       <c r="G141" t="n">
-        <v>1210476</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9165,25 +9627,25 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4903</v>
+        <v>4297.32</v>
       </c>
       <c r="D142" t="n">
-        <v>4940</v>
+        <v>4595.14</v>
       </c>
       <c r="E142" t="n">
-        <v>4792.5</v>
+        <v>4249.35</v>
       </c>
       <c r="F142" t="n">
-        <v>4859.8</v>
+        <v>4521.18</v>
       </c>
       <c r="G142" t="n">
-        <v>682980</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9192,241 +9654,241 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4866</v>
+        <v>4557.56</v>
       </c>
       <c r="D143" t="n">
-        <v>4907.9</v>
+        <v>4737.05</v>
       </c>
       <c r="E143" t="n">
-        <v>4769.8</v>
+        <v>4537.17</v>
       </c>
       <c r="F143" t="n">
-        <v>4776</v>
+        <v>4583.14</v>
       </c>
       <c r="G143" t="n">
-        <v>320785</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1417</v>
+        <v>4606.13</v>
       </c>
       <c r="D144" t="n">
-        <v>1436</v>
+        <v>4777.02</v>
       </c>
       <c r="E144" t="n">
-        <v>1410.1</v>
+        <v>4590.24</v>
       </c>
       <c r="F144" t="n">
-        <v>1423.9</v>
+        <v>4759.23</v>
       </c>
       <c r="G144" t="n">
-        <v>623969</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1428</v>
+        <v>4817.7</v>
       </c>
       <c r="D145" t="n">
-        <v>1428</v>
+        <v>4929.93</v>
       </c>
       <c r="E145" t="n">
-        <v>1351.5</v>
+        <v>4722.06</v>
       </c>
       <c r="F145" t="n">
-        <v>1359.1</v>
+        <v>4890.75</v>
       </c>
       <c r="G145" t="n">
-        <v>808190</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1349.8</v>
+        <v>4896.95</v>
       </c>
       <c r="D146" t="n">
-        <v>1357.8</v>
+        <v>4976.9</v>
       </c>
       <c r="E146" t="n">
-        <v>1330.1</v>
+        <v>4780.02</v>
       </c>
       <c r="F146" t="n">
-        <v>1340.8</v>
+        <v>4813</v>
       </c>
       <c r="G146" t="n">
-        <v>345535</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1340.8</v>
+        <v>4790</v>
       </c>
       <c r="D147" t="n">
-        <v>1387.7</v>
+        <v>4968</v>
       </c>
       <c r="E147" t="n">
-        <v>1316</v>
+        <v>4780</v>
       </c>
       <c r="F147" t="n">
-        <v>1374.4</v>
+        <v>4939.2</v>
       </c>
       <c r="G147" t="n">
-        <v>974660</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1372.9</v>
+        <v>4958</v>
       </c>
       <c r="D148" t="n">
-        <v>1390</v>
+        <v>5085</v>
       </c>
       <c r="E148" t="n">
-        <v>1355.1</v>
+        <v>4888.8</v>
       </c>
       <c r="F148" t="n">
-        <v>1363.5</v>
+        <v>4903</v>
       </c>
       <c r="G148" t="n">
-        <v>479123</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1363</v>
+        <v>4903</v>
       </c>
       <c r="D149" t="n">
-        <v>1392</v>
+        <v>4940</v>
       </c>
       <c r="E149" t="n">
-        <v>1355.1</v>
+        <v>4792.5</v>
       </c>
       <c r="F149" t="n">
-        <v>1380</v>
+        <v>4859.8</v>
       </c>
       <c r="G149" t="n">
-        <v>616767</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1360</v>
+        <v>4866</v>
       </c>
       <c r="D150" t="n">
-        <v>1368</v>
+        <v>4907.9</v>
       </c>
       <c r="E150" t="n">
-        <v>1272.1</v>
+        <v>4753</v>
       </c>
       <c r="F150" t="n">
-        <v>1288.3</v>
+        <v>4837.4</v>
       </c>
       <c r="G150" t="n">
-        <v>1098492</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1300</v>
+        <v>4860</v>
       </c>
       <c r="D151" t="n">
-        <v>1318.5</v>
+        <v>5139</v>
       </c>
       <c r="E151" t="n">
-        <v>1257</v>
+        <v>4860</v>
       </c>
       <c r="F151" t="n">
-        <v>1316.2</v>
+        <v>5110</v>
       </c>
       <c r="G151" t="n">
-        <v>1172726</v>
+        <v>1355375</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9435,25 +9897,25 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1317.7</v>
+        <v>1417</v>
       </c>
       <c r="D152" t="n">
-        <v>1319.8</v>
+        <v>1436</v>
       </c>
       <c r="E152" t="n">
-        <v>1270.5</v>
+        <v>1410.1</v>
       </c>
       <c r="F152" t="n">
-        <v>1306</v>
+        <v>1423.9</v>
       </c>
       <c r="G152" t="n">
-        <v>832973</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9462,25 +9924,25 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1319.9</v>
+        <v>1428</v>
       </c>
       <c r="D153" t="n">
-        <v>1355.4</v>
+        <v>1428</v>
       </c>
       <c r="E153" t="n">
-        <v>1308</v>
+        <v>1351.5</v>
       </c>
       <c r="F153" t="n">
-        <v>1343.4</v>
+        <v>1359.1</v>
       </c>
       <c r="G153" t="n">
-        <v>1287698</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9489,25 +9951,25 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1379</v>
+        <v>1349.8</v>
       </c>
       <c r="D154" t="n">
-        <v>1468</v>
+        <v>1357.8</v>
       </c>
       <c r="E154" t="n">
-        <v>1361</v>
+        <v>1330.1</v>
       </c>
       <c r="F154" t="n">
-        <v>1377.8</v>
+        <v>1340.8</v>
       </c>
       <c r="G154" t="n">
-        <v>9950655</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9516,25 +9978,25 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1380.5</v>
+        <v>1340.8</v>
       </c>
       <c r="D155" t="n">
-        <v>1403.3</v>
+        <v>1387.7</v>
       </c>
       <c r="E155" t="n">
-        <v>1363</v>
+        <v>1316</v>
       </c>
       <c r="F155" t="n">
-        <v>1366.8</v>
+        <v>1374.4</v>
       </c>
       <c r="G155" t="n">
-        <v>1567542</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9543,25 +10005,25 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1380</v>
+        <v>1372.9</v>
       </c>
       <c r="D156" t="n">
-        <v>1397.5</v>
+        <v>1390</v>
       </c>
       <c r="E156" t="n">
-        <v>1351.6</v>
+        <v>1355.1</v>
       </c>
       <c r="F156" t="n">
-        <v>1360.6</v>
+        <v>1363.5</v>
       </c>
       <c r="G156" t="n">
-        <v>1098353</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9570,25 +10032,25 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1360.6</v>
+        <v>1363</v>
       </c>
       <c r="D157" t="n">
-        <v>1428</v>
+        <v>1392</v>
       </c>
       <c r="E157" t="n">
-        <v>1354.5</v>
+        <v>1355.1</v>
       </c>
       <c r="F157" t="n">
-        <v>1421.6</v>
+        <v>1380</v>
       </c>
       <c r="G157" t="n">
-        <v>2055261</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9597,25 +10059,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1429.6</v>
+        <v>1360</v>
       </c>
       <c r="D158" t="n">
-        <v>1453</v>
+        <v>1368</v>
       </c>
       <c r="E158" t="n">
-        <v>1419</v>
+        <v>1272.1</v>
       </c>
       <c r="F158" t="n">
-        <v>1434.1</v>
+        <v>1288.3</v>
       </c>
       <c r="G158" t="n">
-        <v>1243415</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9624,25 +10086,25 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1434</v>
+        <v>1300</v>
       </c>
       <c r="D159" t="n">
-        <v>1460</v>
+        <v>1318.5</v>
       </c>
       <c r="E159" t="n">
-        <v>1405</v>
+        <v>1257</v>
       </c>
       <c r="F159" t="n">
-        <v>1418</v>
+        <v>1316.2</v>
       </c>
       <c r="G159" t="n">
-        <v>1123973</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9651,25 +10113,25 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1413.9</v>
+        <v>1317.7</v>
       </c>
       <c r="D160" t="n">
-        <v>1434</v>
+        <v>1319.8</v>
       </c>
       <c r="E160" t="n">
-        <v>1407.5</v>
+        <v>1270.5</v>
       </c>
       <c r="F160" t="n">
-        <v>1424.7</v>
+        <v>1306</v>
       </c>
       <c r="G160" t="n">
-        <v>509551</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9678,25 +10140,25 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1434.1</v>
+        <v>1319.9</v>
       </c>
       <c r="D161" t="n">
-        <v>1522</v>
+        <v>1355.4</v>
       </c>
       <c r="E161" t="n">
-        <v>1427.5</v>
+        <v>1308</v>
       </c>
       <c r="F161" t="n">
-        <v>1516.4</v>
+        <v>1343.4</v>
       </c>
       <c r="G161" t="n">
-        <v>3863757</v>
+        <v>1287698</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9705,46 +10167,289 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1516.4</v>
+        <v>1379</v>
       </c>
       <c r="D162" t="n">
-        <v>1543</v>
+        <v>1468</v>
       </c>
       <c r="E162" t="n">
-        <v>1486.9</v>
+        <v>1361</v>
       </c>
       <c r="F162" t="n">
-        <v>1494.8</v>
+        <v>1377.8</v>
       </c>
       <c r="G162" t="n">
-        <v>1508375</v>
+        <v>9950655</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1413.9</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1407.5</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1424.7</v>
+      </c>
+      <c r="G168" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1522</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="G169" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1486.9</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C163" t="n">
+      <c r="C171" t="n">
         <v>1494.8</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D171" t="n">
         <v>1514</v>
       </c>
-      <c r="E163" t="n">
-        <v>1485.1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1497.7</v>
-      </c>
-      <c r="G163" t="n">
-        <v>302361</v>
+      <c r="E171" t="n">
+        <v>1465.1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G171" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1500.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1469.7</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1475.8</v>
+      </c>
+      <c r="G172" t="n">
+        <v>286495</v>
       </c>
     </row>
   </sheetData>
@@ -9758,7 +10463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9928,6 +10633,21 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily picks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Levels" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Performance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Price history" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily picks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price history" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 13 Aug 2026 05:18</t>
+          <t>Generated 14 Aug 2026 05:16</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="D2" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>56.7</v>
+        <v>57.6</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>5.34</v>
+        <v>4.83</v>
       </c>
       <c r="D3" t="n">
-        <v>4.38</v>
+        <v>3.69</v>
       </c>
       <c r="E3" t="n">
-        <v>76.2</v>
+        <v>70.8</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
@@ -647,7 +647,7 @@
         <v>-2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>5.92</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="4">
@@ -660,7 +660,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="D4" t="n">
         <v>10.56</v>
@@ -672,10 +672,10 @@
         <v>26.91</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.07</v>
+        <v>-4.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8.73</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2755,6 +2755,192 @@
         <v>1</v>
       </c>
       <c r="P34" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>229.01</v>
+      </c>
+      <c r="I35" t="n">
+        <v>209.18</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="K35" t="n">
+        <v>248.84</v>
+      </c>
+      <c r="L35" t="n">
+        <v>268.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>99</v>
+      </c>
+      <c r="F36" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1607.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1508.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1706.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1805.32</v>
+      </c>
+      <c r="M36" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>98</v>
+      </c>
+      <c r="F37" t="n">
+        <v>109.98</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="K37" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L37" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -2771,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3848,6 +4034,105 @@
       </c>
       <c r="I34" t="n">
         <v>1790.76</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>229.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>209.18</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>248.84</v>
+      </c>
+      <c r="I35" t="n">
+        <v>268.67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1607.3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1508.29</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1706.31</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1805.32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="E37" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I37" t="n">
+        <v>15.61</v>
       </c>
     </row>
   </sheetData>
@@ -3861,7 +4146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3964,7 +4249,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3984,7 +4269,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229.55</v>
+        <v>229.01</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3992,16 +4277,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.02</v>
+        <v>-1.18</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>209.53</v>
+        <v>209.18</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -4017,12 +4302,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4037,7 +4322,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.79</v>
+        <v>1607.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -4045,16 +4330,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.39</v>
+        <v>-2.01</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>13.02</v>
+        <v>1508.29</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -4070,19 +4355,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4090,7 +4375,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1591.5</v>
+        <v>13.99</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4098,16 +4383,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.94</v>
+        <v>1.07</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.33</v>
+        <v>-3.57</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1491.87</v>
+        <v>13.18</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -4123,7 +4408,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4143,26 +4428,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>221.52</v>
+        <v>227.36</v>
       </c>
       <c r="G5" t="n">
-        <v>3.62</v>
+        <v>0.73</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.26</v>
+        <v>1.58</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.94</v>
+        <v>-2.08</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -4178,7 +4463,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4198,26 +4483,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="G6" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.81</v>
+        <v>4.66</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.96</v>
+        <v>-0.37</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -4233,12 +4518,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4253,29 +4538,29 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>547.7</v>
+        <v>1583</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>4.16</v>
+        <v>3.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.3</v>
+        <v>-0.8</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -4283,14 +4568,12 @@
       <c r="R7" t="b">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4310,26 +4593,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>7.8</v>
+        <v>4.26</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -4345,12 +4628,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4365,26 +4648,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>5.75</v>
+        <v>4.74</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -4400,12 +4683,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4420,29 +4703,29 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.42</v>
+        <v>-0.59</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>3.08</v>
+        <v>4.16</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.19</v>
+        <v>-5.97</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -4450,12 +4733,14 @@
       <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4475,32 +4760,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>11.04</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -4510,19 +4795,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4530,32 +4815,32 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>2.57</v>
+        <v>8.42</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.67</v>
+        <v>-2.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -4565,19 +4850,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4585,32 +4870,32 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G13" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.01</v>
+        <v>-3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -4620,7 +4905,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4640,28 +4925,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>12.71</v>
+        <v>10.11</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>13.39</v>
+        <v>11.04</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -4677,7 +4962,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4697,28 +4982,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.76</v>
+        <v>-1.4</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.07</v>
+        <v>-3.67</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -4734,7 +5019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4757,10 +5042,10 @@
         <v>381</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H16" t="n">
-        <v>7.57</v>
+        <v>-0.85</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -4769,13 +5054,13 @@
         <v>10.81</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.18</v>
+        <v>-1.01</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -4784,14 +5069,14 @@
         <v>1</v>
       </c>
       <c r="R16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4811,34 +5096,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>4.38</v>
+        <v>11.63</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>8.82</v>
+        <v>13.39</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -4848,12 +5133,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4868,28 +5153,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.09</v>
+        <v>-2.28</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>5.08</v>
+        <v>3.21</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.45</v>
+        <v>-3.07</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -4905,12 +5190,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4925,44 +5210,44 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.62</v>
+        <v>5.12</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.37</v>
+        <v>-1.18</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4982,34 +5267,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G20" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H20" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>13.89</v>
+        <v>8.82</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N20" t="n">
         <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -5019,7 +5304,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5031,7 +5316,7 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5039,28 +5324,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H21" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>7.98</v>
+        <v>7.73</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N21" t="n">
         <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -5076,12 +5361,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5096,34 +5381,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G22" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.61</v>
+        <v>-4.37</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -5133,19 +5418,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -5153,28 +5438,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G23" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H23" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>12.13</v>
+        <v>13.89</v>
       </c>
       <c r="M23" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N23" t="n">
         <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -5190,19 +5475,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5210,34 +5495,34 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>1.76</v>
+        <v>10.71</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.66</v>
+        <v>-3.55</v>
       </c>
       <c r="N24" t="n">
         <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -5247,19 +5532,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -5267,28 +5552,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G25" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H25" t="n">
-        <v>11.45</v>
+        <v>2.92</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>13.41</v>
+        <v>11.99</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N25" t="n">
         <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -5304,12 +5589,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5324,36 +5609,34 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H26" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7.11</v>
-      </c>
+        <v>6.98</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>11.99</v>
+        <v>14.96</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O26" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
       </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
@@ -5363,7 +5646,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5383,30 +5666,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-4.07</v>
-      </c>
+        <v>-0.91</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.35</v>
+        <v>-4.66</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -5422,19 +5703,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5442,36 +5723,34 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G28" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.01</v>
-      </c>
+        <v>11.45</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>5.02</v>
+        <v>13.41</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -5481,12 +5760,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5501,50 +5780,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H29" t="n">
-        <v>9.65</v>
+        <v>2.92</v>
       </c>
       <c r="I29" t="n">
-        <v>14.45</v>
+        <v>6.52</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>19.32</v>
+        <v>11.99</v>
       </c>
       <c r="M29" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5552,38 +5839,46 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G30" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H30" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I30" t="n">
-        <v>10.91</v>
+        <v>-4.58</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>17.83</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.32</v>
+        <v>-5.35</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
       <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5595,7 +5890,7 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5606,13 +5901,13 @@
         <v>1781.3</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I31" t="n">
         <v>3.01</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4.07</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -5620,33 +5915,41 @@
         <v>5.02</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.52</v>
+        <v>-0.45</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5654,24 +5957,24 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G32" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H32" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I32" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>31.45</v>
+        <v>19.32</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N32" t="n">
         <v>13</v>
@@ -5685,19 +5988,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5705,24 +6008,24 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G33" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H33" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I33" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>22.59</v>
+        <v>20.81</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
@@ -5736,19 +6039,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5756,24 +6059,24 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I34" t="n">
-        <v>10.56</v>
+        <v>3.86</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>16.91</v>
+        <v>5.02</v>
       </c>
       <c r="M34" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N34" t="n">
         <v>13</v>
@@ -5783,6 +6086,159 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I35" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N35" t="n">
+        <v>14</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>96</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>14</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>92</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>14</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5795,7 +6251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6369,43 +6825,43 @@
         <v>1570.4</v>
       </c>
       <c r="F21" t="n">
-        <v>1591.5</v>
+        <v>1583</v>
       </c>
       <c r="G21" t="n">
-        <v>1733631</v>
+        <v>3318810</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1188.4</v>
+        <v>1588</v>
       </c>
       <c r="D22" t="n">
-        <v>1207.9</v>
+        <v>1612.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1158</v>
+        <v>1575</v>
       </c>
       <c r="F22" t="n">
-        <v>1201.8</v>
+        <v>1607.3</v>
       </c>
       <c r="G22" t="n">
-        <v>3482939</v>
+        <v>3892957</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6414,25 +6870,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D23" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F23" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G23" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6441,25 +6897,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D24" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E24" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F24" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G24" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6468,25 +6924,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D25" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E25" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F25" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G25" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6495,25 +6951,25 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F26" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D26" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G26" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6522,25 +6978,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D27" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F27" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G27" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6549,25 +7005,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D28" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G28" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6576,25 +7032,25 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F29" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D29" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G29" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6603,25 +7059,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D30" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E30" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G30" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6630,25 +7086,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D31" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E31" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G31" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6657,25 +7113,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D32" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G32" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6684,25 +7140,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D33" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E33" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G33" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6711,25 +7167,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D34" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E34" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G34" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6738,25 +7194,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D35" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E35" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G35" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6765,25 +7221,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D36" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E36" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G36" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6792,25 +7248,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D37" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E37" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F37" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G37" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6819,25 +7275,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D38" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E38" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G38" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6846,25 +7302,25 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F39" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D39" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G39" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6873,25 +7329,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D40" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E40" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F40" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G40" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6900,25 +7356,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D41" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E41" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F41" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G41" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6927,25 +7383,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D42" t="n">
-        <v>1534.8</v>
+        <v>1520</v>
       </c>
       <c r="E42" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F42" t="n">
-        <v>1525.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G42" t="n">
-        <v>4867021</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6954,25 +7410,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1531.7</v>
+        <v>1472.4</v>
       </c>
       <c r="D43" t="n">
-        <v>1580</v>
+        <v>1534.8</v>
       </c>
       <c r="E43" t="n">
-        <v>1511.1</v>
+        <v>1472</v>
       </c>
       <c r="F43" t="n">
-        <v>1569.4</v>
+        <v>1525.4</v>
       </c>
       <c r="G43" t="n">
-        <v>4521175</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6981,79 +7437,79 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1575</v>
+        <v>1531.7</v>
       </c>
       <c r="D44" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="E44" t="n">
-        <v>1500.1</v>
+        <v>1511.1</v>
       </c>
       <c r="F44" t="n">
-        <v>1525.5</v>
+        <v>1569.4</v>
       </c>
       <c r="G44" t="n">
-        <v>2487069</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>211.95</v>
+        <v>1575</v>
       </c>
       <c r="D45" t="n">
-        <v>214.55</v>
+        <v>1575</v>
       </c>
       <c r="E45" t="n">
-        <v>206.1</v>
+        <v>1500.1</v>
       </c>
       <c r="F45" t="n">
-        <v>212.78</v>
+        <v>1525.5</v>
       </c>
       <c r="G45" t="n">
-        <v>12863408</v>
+        <v>2487069</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>214.3</v>
+        <v>1530</v>
       </c>
       <c r="D46" t="n">
-        <v>223.41</v>
+        <v>1541</v>
       </c>
       <c r="E46" t="n">
-        <v>214.3</v>
+        <v>1515</v>
       </c>
       <c r="F46" t="n">
-        <v>223.08</v>
+        <v>1525.4</v>
       </c>
       <c r="G46" t="n">
-        <v>32151413</v>
+        <v>842938</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7062,25 +7518,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D47" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E47" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F47" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G47" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7089,25 +7545,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D48" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E48" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F48" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G48" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7116,25 +7572,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D49" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E49" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F49" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G49" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7143,25 +7599,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D50" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E50" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F50" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G50" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7170,25 +7626,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D51" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E51" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F51" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G51" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7197,25 +7653,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D52" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E52" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F52" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G52" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7224,25 +7680,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D53" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E53" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F53" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G53" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7251,25 +7707,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E54" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F54" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G54" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7278,25 +7734,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D55" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E55" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F55" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G55" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7305,25 +7761,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D56" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E56" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F56" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G56" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7332,25 +7788,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D57" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E57" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F57" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G57" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7359,25 +7815,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D58" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E58" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F58" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G58" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7386,25 +7842,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D59" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E59" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F59" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G59" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7413,25 +7869,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D60" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E60" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F60" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G60" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7440,25 +7896,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D61" t="n">
-        <v>212.91</v>
+        <v>203.61</v>
       </c>
       <c r="E61" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F61" t="n">
-        <v>212.23</v>
+        <v>202.52</v>
       </c>
       <c r="G61" t="n">
-        <v>37479685</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7467,25 +7923,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>212.4</v>
+        <v>202.4</v>
       </c>
       <c r="D62" t="n">
-        <v>213.45</v>
+        <v>207</v>
       </c>
       <c r="E62" t="n">
-        <v>203</v>
+        <v>200.22</v>
       </c>
       <c r="F62" t="n">
-        <v>203.67</v>
+        <v>202.78</v>
       </c>
       <c r="G62" t="n">
-        <v>19195935</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7494,25 +7950,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>203.98</v>
+        <v>205.8</v>
       </c>
       <c r="D63" t="n">
-        <v>211.52</v>
+        <v>212.91</v>
       </c>
       <c r="E63" t="n">
-        <v>201</v>
+        <v>205.03</v>
       </c>
       <c r="F63" t="n">
-        <v>207.98</v>
+        <v>212.23</v>
       </c>
       <c r="G63" t="n">
-        <v>19489977</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7521,25 +7977,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>209</v>
+        <v>212.4</v>
       </c>
       <c r="D64" t="n">
-        <v>216.6</v>
+        <v>213.45</v>
       </c>
       <c r="E64" t="n">
-        <v>207.83</v>
+        <v>203</v>
       </c>
       <c r="F64" t="n">
-        <v>212.97</v>
+        <v>203.67</v>
       </c>
       <c r="G64" t="n">
-        <v>19215795</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7548,25 +8004,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>214</v>
+        <v>203.98</v>
       </c>
       <c r="D65" t="n">
-        <v>215.8</v>
+        <v>211.52</v>
       </c>
       <c r="E65" t="n">
-        <v>209.25</v>
+        <v>201</v>
       </c>
       <c r="F65" t="n">
-        <v>214.24</v>
+        <v>207.98</v>
       </c>
       <c r="G65" t="n">
-        <v>15006611</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7575,25 +8031,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>215.4</v>
+        <v>209</v>
       </c>
       <c r="D66" t="n">
-        <v>223.61</v>
+        <v>216.6</v>
       </c>
       <c r="E66" t="n">
-        <v>215</v>
+        <v>207.83</v>
       </c>
       <c r="F66" t="n">
-        <v>221.52</v>
+        <v>212.97</v>
       </c>
       <c r="G66" t="n">
-        <v>28062533</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7602,106 +8058,106 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D67" t="n">
-        <v>230.95</v>
+        <v>215.8</v>
       </c>
       <c r="E67" t="n">
-        <v>222.62</v>
+        <v>209.25</v>
       </c>
       <c r="F67" t="n">
-        <v>229.55</v>
+        <v>214.24</v>
       </c>
       <c r="G67" t="n">
-        <v>13940755</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>481.25</v>
+        <v>215.4</v>
       </c>
       <c r="D68" t="n">
-        <v>489.85</v>
+        <v>223.61</v>
       </c>
       <c r="E68" t="n">
-        <v>477.5</v>
+        <v>215</v>
       </c>
       <c r="F68" t="n">
-        <v>480.25</v>
+        <v>221.52</v>
       </c>
       <c r="G68" t="n">
-        <v>2347659</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>485.2</v>
+        <v>223</v>
       </c>
       <c r="D69" t="n">
-        <v>499</v>
+        <v>230.95</v>
       </c>
       <c r="E69" t="n">
-        <v>482.55</v>
+        <v>222.62</v>
       </c>
       <c r="F69" t="n">
-        <v>491.6</v>
+        <v>227.36</v>
       </c>
       <c r="G69" t="n">
-        <v>7339280</v>
+        <v>23585794</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>495</v>
+        <v>228</v>
       </c>
       <c r="D70" t="n">
-        <v>498.5</v>
+        <v>230.7</v>
       </c>
       <c r="E70" t="n">
-        <v>491</v>
+        <v>226.3</v>
       </c>
       <c r="F70" t="n">
-        <v>495.05</v>
+        <v>229.01</v>
       </c>
       <c r="G70" t="n">
-        <v>2755226</v>
+        <v>6329222</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7710,25 +8166,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>495.05</v>
+        <v>481.25</v>
       </c>
       <c r="D71" t="n">
-        <v>504.3</v>
+        <v>489.85</v>
       </c>
       <c r="E71" t="n">
-        <v>490.05</v>
+        <v>477.5</v>
       </c>
       <c r="F71" t="n">
-        <v>492.35</v>
+        <v>480.25</v>
       </c>
       <c r="G71" t="n">
-        <v>4448305</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7737,25 +8193,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>496.2</v>
+        <v>485.2</v>
       </c>
       <c r="D72" t="n">
-        <v>539.6</v>
+        <v>499</v>
       </c>
       <c r="E72" t="n">
-        <v>495.1</v>
+        <v>482.55</v>
       </c>
       <c r="F72" t="n">
-        <v>533.8</v>
+        <v>491.6</v>
       </c>
       <c r="G72" t="n">
-        <v>22701332</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7764,25 +8220,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>542.45</v>
+        <v>495</v>
       </c>
       <c r="D73" t="n">
-        <v>551</v>
+        <v>498.5</v>
       </c>
       <c r="E73" t="n">
-        <v>525.55</v>
+        <v>491</v>
       </c>
       <c r="F73" t="n">
-        <v>545.95</v>
+        <v>495.05</v>
       </c>
       <c r="G73" t="n">
-        <v>19838083</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7791,25 +8247,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>543.75</v>
+        <v>495.05</v>
       </c>
       <c r="D74" t="n">
-        <v>548</v>
+        <v>504.3</v>
       </c>
       <c r="E74" t="n">
-        <v>532.1</v>
+        <v>490.05</v>
       </c>
       <c r="F74" t="n">
-        <v>536.1</v>
+        <v>492.35</v>
       </c>
       <c r="G74" t="n">
-        <v>9431736</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7818,25 +8274,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>537.95</v>
+        <v>496.2</v>
       </c>
       <c r="D75" t="n">
-        <v>552</v>
+        <v>539.6</v>
       </c>
       <c r="E75" t="n">
-        <v>522</v>
+        <v>495.1</v>
       </c>
       <c r="F75" t="n">
-        <v>526.25</v>
+        <v>533.8</v>
       </c>
       <c r="G75" t="n">
-        <v>12427899</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7845,25 +8301,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>531</v>
+        <v>542.45</v>
       </c>
       <c r="D76" t="n">
-        <v>538.8</v>
+        <v>551</v>
       </c>
       <c r="E76" t="n">
-        <v>527.7</v>
+        <v>525.55</v>
       </c>
       <c r="F76" t="n">
-        <v>533.3</v>
+        <v>545.95</v>
       </c>
       <c r="G76" t="n">
-        <v>5547022</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7872,25 +8328,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>530.85</v>
+        <v>543.75</v>
       </c>
       <c r="D77" t="n">
-        <v>569.9</v>
+        <v>548</v>
       </c>
       <c r="E77" t="n">
-        <v>529.6</v>
+        <v>532.1</v>
       </c>
       <c r="F77" t="n">
-        <v>547.7</v>
+        <v>536.1</v>
       </c>
       <c r="G77" t="n">
-        <v>36903374</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7899,133 +8355,133 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>549</v>
+        <v>537.95</v>
       </c>
       <c r="D78" t="n">
-        <v>570.5</v>
+        <v>552</v>
       </c>
       <c r="E78" t="n">
-        <v>548.45</v>
+        <v>522</v>
       </c>
       <c r="F78" t="n">
-        <v>557</v>
+        <v>526.25</v>
       </c>
       <c r="G78" t="n">
-        <v>7311815</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>13.05</v>
+        <v>531</v>
       </c>
       <c r="D79" t="n">
-        <v>13.18</v>
+        <v>538.8</v>
       </c>
       <c r="E79" t="n">
-        <v>12.85</v>
+        <v>527.7</v>
       </c>
       <c r="F79" t="n">
-        <v>12.87</v>
+        <v>533.3</v>
       </c>
       <c r="G79" t="n">
-        <v>230386335</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>12.98</v>
+        <v>530.85</v>
       </c>
       <c r="D80" t="n">
-        <v>13.08</v>
+        <v>569.9</v>
       </c>
       <c r="E80" t="n">
-        <v>12.76</v>
+        <v>529.6</v>
       </c>
       <c r="F80" t="n">
-        <v>13.01</v>
+        <v>547.7</v>
       </c>
       <c r="G80" t="n">
-        <v>387269596</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13.01</v>
+        <v>549</v>
       </c>
       <c r="D81" t="n">
-        <v>13.11</v>
+        <v>570.5</v>
       </c>
       <c r="E81" t="n">
-        <v>12.82</v>
+        <v>542</v>
       </c>
       <c r="F81" t="n">
-        <v>12.86</v>
+        <v>544.45</v>
       </c>
       <c r="G81" t="n">
-        <v>235409728</v>
+        <v>14649216</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12.89</v>
+        <v>546.5</v>
       </c>
       <c r="D82" t="n">
-        <v>13.05</v>
+        <v>546.7</v>
       </c>
       <c r="E82" t="n">
-        <v>12.73</v>
+        <v>515</v>
       </c>
       <c r="F82" t="n">
-        <v>12.9</v>
+        <v>516.55</v>
       </c>
       <c r="G82" t="n">
-        <v>308781891</v>
+        <v>4662594</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8034,25 +8490,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12.91</v>
+        <v>13.05</v>
       </c>
       <c r="D83" t="n">
-        <v>13.04</v>
+        <v>13.18</v>
       </c>
       <c r="E83" t="n">
-        <v>12.77</v>
+        <v>12.85</v>
       </c>
       <c r="F83" t="n">
-        <v>12.8</v>
+        <v>12.87</v>
       </c>
       <c r="G83" t="n">
-        <v>204366752</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8061,25 +8517,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12.89</v>
+        <v>12.98</v>
       </c>
       <c r="D84" t="n">
-        <v>12.9</v>
+        <v>13.08</v>
       </c>
       <c r="E84" t="n">
-        <v>12.63</v>
+        <v>12.76</v>
       </c>
       <c r="F84" t="n">
-        <v>12.63</v>
+        <v>13.01</v>
       </c>
       <c r="G84" t="n">
-        <v>204537429</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8088,25 +8544,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12.64</v>
+        <v>13.01</v>
       </c>
       <c r="D85" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="E85" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="F85" t="n">
-        <v>12.73</v>
+        <v>12.86</v>
       </c>
       <c r="G85" t="n">
-        <v>205855564</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8115,25 +8571,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="D86" t="n">
-        <v>13.07</v>
+        <v>13.05</v>
       </c>
       <c r="E86" t="n">
-        <v>12.77</v>
+        <v>12.73</v>
       </c>
       <c r="F86" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
       <c r="G86" t="n">
-        <v>413469644</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8142,25 +8598,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>13.14</v>
+        <v>12.91</v>
       </c>
       <c r="D87" t="n">
-        <v>13.3</v>
+        <v>13.04</v>
       </c>
       <c r="E87" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
       <c r="F87" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="G87" t="n">
-        <v>662095209</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8169,25 +8625,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12.93</v>
+        <v>12.89</v>
       </c>
       <c r="D88" t="n">
-        <v>13.69</v>
+        <v>12.9</v>
       </c>
       <c r="E88" t="n">
-        <v>12.83</v>
+        <v>12.63</v>
       </c>
       <c r="F88" t="n">
-        <v>13.5</v>
+        <v>12.63</v>
       </c>
       <c r="G88" t="n">
-        <v>772547405</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8196,160 +8652,160 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13.67</v>
+        <v>12.64</v>
       </c>
       <c r="D89" t="n">
-        <v>13.88</v>
+        <v>12.88</v>
       </c>
       <c r="E89" t="n">
-        <v>13.46</v>
+        <v>12.6</v>
       </c>
       <c r="F89" t="n">
-        <v>13.79</v>
+        <v>12.73</v>
       </c>
       <c r="G89" t="n">
-        <v>358968218</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1554.3</v>
+        <v>12.92</v>
       </c>
       <c r="D90" t="n">
-        <v>1569</v>
+        <v>13.07</v>
       </c>
       <c r="E90" t="n">
-        <v>1551.3</v>
+        <v>12.77</v>
       </c>
       <c r="F90" t="n">
-        <v>1557.6</v>
+        <v>12.92</v>
       </c>
       <c r="G90" t="n">
-        <v>1001677</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1560.4</v>
+        <v>13.14</v>
       </c>
       <c r="D91" t="n">
-        <v>1561</v>
+        <v>13.3</v>
       </c>
       <c r="E91" t="n">
-        <v>1520.4</v>
+        <v>12.79</v>
       </c>
       <c r="F91" t="n">
-        <v>1529.8</v>
+        <v>12.89</v>
       </c>
       <c r="G91" t="n">
-        <v>1011017</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1534.9</v>
+        <v>12.93</v>
       </c>
       <c r="D92" t="n">
-        <v>1572.2</v>
+        <v>13.69</v>
       </c>
       <c r="E92" t="n">
-        <v>1527.2</v>
+        <v>12.83</v>
       </c>
       <c r="F92" t="n">
-        <v>1558.9</v>
+        <v>13.5</v>
       </c>
       <c r="G92" t="n">
-        <v>1235837</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1559.7</v>
+        <v>13.67</v>
       </c>
       <c r="D93" t="n">
-        <v>1600.1</v>
+        <v>13.88</v>
       </c>
       <c r="E93" t="n">
-        <v>1557</v>
+        <v>13.46</v>
       </c>
       <c r="F93" t="n">
-        <v>1593.2</v>
+        <v>13.51</v>
       </c>
       <c r="G93" t="n">
-        <v>1871739</v>
+        <v>547253456</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1591</v>
+        <v>13.53</v>
       </c>
       <c r="D94" t="n">
-        <v>1593.2</v>
+        <v>14.14</v>
       </c>
       <c r="E94" t="n">
-        <v>1566</v>
+        <v>13.49</v>
       </c>
       <c r="F94" t="n">
-        <v>1577.8</v>
+        <v>13.99</v>
       </c>
       <c r="G94" t="n">
-        <v>1183077</v>
+        <v>374572510</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8358,25 +8814,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1577.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D95" t="n">
-        <v>1586.1</v>
+        <v>1569</v>
       </c>
       <c r="E95" t="n">
-        <v>1561.1</v>
+        <v>1551.3</v>
       </c>
       <c r="F95" t="n">
-        <v>1568.3</v>
+        <v>1557.6</v>
       </c>
       <c r="G95" t="n">
-        <v>1098268</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8385,25 +8841,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1560</v>
+        <v>1560.4</v>
       </c>
       <c r="D96" t="n">
-        <v>1610</v>
+        <v>1561</v>
       </c>
       <c r="E96" t="n">
-        <v>1554.9</v>
+        <v>1520.4</v>
       </c>
       <c r="F96" t="n">
-        <v>1601.2</v>
+        <v>1529.8</v>
       </c>
       <c r="G96" t="n">
-        <v>2647403</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8412,25 +8868,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1624.8</v>
+        <v>1534.9</v>
       </c>
       <c r="D97" t="n">
-        <v>1734.5</v>
+        <v>1572.2</v>
       </c>
       <c r="E97" t="n">
-        <v>1617.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F97" t="n">
-        <v>1713.4</v>
+        <v>1558.9</v>
       </c>
       <c r="G97" t="n">
-        <v>7989771</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8439,25 +8895,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1713</v>
+        <v>1559.7</v>
       </c>
       <c r="D98" t="n">
-        <v>1762</v>
+        <v>1600.1</v>
       </c>
       <c r="E98" t="n">
-        <v>1707.7</v>
+        <v>1557</v>
       </c>
       <c r="F98" t="n">
-        <v>1758.9</v>
+        <v>1593.2</v>
       </c>
       <c r="G98" t="n">
-        <v>4407907</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8466,25 +8922,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1762</v>
+        <v>1591</v>
       </c>
       <c r="D99" t="n">
-        <v>1797.9</v>
+        <v>1593.2</v>
       </c>
       <c r="E99" t="n">
-        <v>1754.3</v>
+        <v>1566</v>
       </c>
       <c r="F99" t="n">
-        <v>1781.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G99" t="n">
-        <v>3000811</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8493,25 +8949,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1785</v>
+        <v>1577.7</v>
       </c>
       <c r="D100" t="n">
-        <v>1798.9</v>
+        <v>1586.1</v>
       </c>
       <c r="E100" t="n">
-        <v>1773.3</v>
+        <v>1561.1</v>
       </c>
       <c r="F100" t="n">
-        <v>1781.3</v>
+        <v>1568.3</v>
       </c>
       <c r="G100" t="n">
-        <v>2402202</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8520,25 +8976,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1785</v>
+        <v>1560</v>
       </c>
       <c r="D101" t="n">
-        <v>1826.6</v>
+        <v>1610</v>
       </c>
       <c r="E101" t="n">
-        <v>1785</v>
+        <v>1554.9</v>
       </c>
       <c r="F101" t="n">
-        <v>1816.2</v>
+        <v>1601.2</v>
       </c>
       <c r="G101" t="n">
-        <v>2502579</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8547,25 +9003,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1821</v>
+        <v>1624.8</v>
       </c>
       <c r="D102" t="n">
-        <v>1838.3</v>
+        <v>1734.5</v>
       </c>
       <c r="E102" t="n">
-        <v>1789.1</v>
+        <v>1617.1</v>
       </c>
       <c r="F102" t="n">
-        <v>1811.4</v>
+        <v>1713.4</v>
       </c>
       <c r="G102" t="n">
-        <v>1919384</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8574,25 +9030,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1811</v>
+        <v>1713</v>
       </c>
       <c r="D103" t="n">
-        <v>1850</v>
+        <v>1762</v>
       </c>
       <c r="E103" t="n">
-        <v>1806.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F103" t="n">
-        <v>1850</v>
+        <v>1758.9</v>
       </c>
       <c r="G103" t="n">
-        <v>1405192</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8601,25 +9057,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1854</v>
+        <v>1762</v>
       </c>
       <c r="D104" t="n">
-        <v>1856.6</v>
+        <v>1797.9</v>
       </c>
       <c r="E104" t="n">
-        <v>1834.5</v>
+        <v>1754.3</v>
       </c>
       <c r="F104" t="n">
-        <v>1835</v>
+        <v>1781.3</v>
       </c>
       <c r="G104" t="n">
-        <v>2090998</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8628,25 +9084,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1843</v>
+        <v>1785</v>
       </c>
       <c r="D105" t="n">
-        <v>1854.9</v>
+        <v>1798.9</v>
       </c>
       <c r="E105" t="n">
-        <v>1830</v>
+        <v>1773.3</v>
       </c>
       <c r="F105" t="n">
-        <v>1830</v>
+        <v>1781.3</v>
       </c>
       <c r="G105" t="n">
-        <v>2037418</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8655,25 +9111,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1838</v>
+        <v>1785</v>
       </c>
       <c r="D106" t="n">
-        <v>1856</v>
+        <v>1826.6</v>
       </c>
       <c r="E106" t="n">
-        <v>1833.2</v>
+        <v>1785</v>
       </c>
       <c r="F106" t="n">
-        <v>1844.3</v>
+        <v>1816.2</v>
       </c>
       <c r="G106" t="n">
-        <v>1553067</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8682,25 +9138,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1845</v>
+        <v>1821</v>
       </c>
       <c r="D107" t="n">
-        <v>1870.8</v>
+        <v>1838.3</v>
       </c>
       <c r="E107" t="n">
-        <v>1832.8</v>
+        <v>1789.1</v>
       </c>
       <c r="F107" t="n">
-        <v>1854</v>
+        <v>1811.4</v>
       </c>
       <c r="G107" t="n">
-        <v>1386592</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8709,25 +9165,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1851</v>
+        <v>1811</v>
       </c>
       <c r="D108" t="n">
-        <v>1859</v>
+        <v>1850</v>
       </c>
       <c r="E108" t="n">
-        <v>1833.1</v>
+        <v>1806.1</v>
       </c>
       <c r="F108" t="n">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="G108" t="n">
-        <v>1514239</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8736,25 +9192,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1856.3</v>
+        <v>1854</v>
       </c>
       <c r="D109" t="n">
-        <v>1862.3</v>
+        <v>1856.6</v>
       </c>
       <c r="E109" t="n">
-        <v>1847.2</v>
+        <v>1834.5</v>
       </c>
       <c r="F109" t="n">
-        <v>1853.8</v>
+        <v>1835</v>
       </c>
       <c r="G109" t="n">
-        <v>332074</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8763,187 +9219,187 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1850</v>
+        <v>1843</v>
       </c>
       <c r="D110" t="n">
-        <v>1850.1</v>
+        <v>1854.9</v>
       </c>
       <c r="E110" t="n">
-        <v>1820.6</v>
+        <v>1830</v>
       </c>
       <c r="F110" t="n">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="G110" t="n">
-        <v>548100</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>344</v>
+        <v>1838</v>
       </c>
       <c r="D111" t="n">
-        <v>346.3</v>
+        <v>1856</v>
       </c>
       <c r="E111" t="n">
-        <v>341.25</v>
+        <v>1833.2</v>
       </c>
       <c r="F111" t="n">
-        <v>342.9</v>
+        <v>1844.3</v>
       </c>
       <c r="G111" t="n">
-        <v>4465145</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>344.2</v>
+        <v>1845</v>
       </c>
       <c r="D112" t="n">
-        <v>347.75</v>
+        <v>1870.8</v>
       </c>
       <c r="E112" t="n">
-        <v>339.95</v>
+        <v>1832.8</v>
       </c>
       <c r="F112" t="n">
-        <v>342.4</v>
+        <v>1854</v>
       </c>
       <c r="G112" t="n">
-        <v>3803051</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>346</v>
+        <v>1851</v>
       </c>
       <c r="D113" t="n">
-        <v>351</v>
+        <v>1859</v>
       </c>
       <c r="E113" t="n">
-        <v>343.65</v>
+        <v>1833.1</v>
       </c>
       <c r="F113" t="n">
-        <v>346</v>
+        <v>1858</v>
       </c>
       <c r="G113" t="n">
-        <v>5175178</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>341.8</v>
+        <v>1856.3</v>
       </c>
       <c r="D114" t="n">
-        <v>344.9</v>
+        <v>1862.3</v>
       </c>
       <c r="E114" t="n">
-        <v>339.65</v>
+        <v>1835</v>
       </c>
       <c r="F114" t="n">
-        <v>343.9</v>
+        <v>1850</v>
       </c>
       <c r="G114" t="n">
-        <v>2253982</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>345.1</v>
+        <v>1850</v>
       </c>
       <c r="D115" t="n">
-        <v>346.05</v>
+        <v>1850.1</v>
       </c>
       <c r="E115" t="n">
-        <v>338.35</v>
+        <v>1820.6</v>
       </c>
       <c r="F115" t="n">
-        <v>339.35</v>
+        <v>1835</v>
       </c>
       <c r="G115" t="n">
-        <v>3868006</v>
+        <v>548100</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>339.4</v>
+        <v>1849.9</v>
       </c>
       <c r="D116" t="n">
-        <v>340.2</v>
+        <v>1853.2</v>
       </c>
       <c r="E116" t="n">
-        <v>333</v>
+        <v>1824.6</v>
       </c>
       <c r="F116" t="n">
-        <v>334.55</v>
+        <v>1825.4</v>
       </c>
       <c r="G116" t="n">
-        <v>3721274</v>
+        <v>435709</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8952,25 +9408,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D117" t="n">
-        <v>346.1</v>
+        <v>346.3</v>
       </c>
       <c r="E117" t="n">
-        <v>332</v>
+        <v>341.25</v>
       </c>
       <c r="F117" t="n">
-        <v>344.7</v>
+        <v>342.9</v>
       </c>
       <c r="G117" t="n">
-        <v>5431501</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8979,25 +9435,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>345.5</v>
+        <v>344.2</v>
       </c>
       <c r="D118" t="n">
-        <v>349.65</v>
+        <v>347.75</v>
       </c>
       <c r="E118" t="n">
-        <v>342.6</v>
+        <v>339.95</v>
       </c>
       <c r="F118" t="n">
-        <v>347.65</v>
+        <v>342.4</v>
       </c>
       <c r="G118" t="n">
-        <v>6318472</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9006,25 +9462,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D119" t="n">
-        <v>355.75</v>
+        <v>351</v>
       </c>
       <c r="E119" t="n">
-        <v>347.65</v>
+        <v>343.65</v>
       </c>
       <c r="F119" t="n">
-        <v>350.05</v>
+        <v>346</v>
       </c>
       <c r="G119" t="n">
-        <v>7186013</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9033,25 +9489,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>357.95</v>
+        <v>341.8</v>
       </c>
       <c r="D120" t="n">
-        <v>369</v>
+        <v>344.9</v>
       </c>
       <c r="E120" t="n">
-        <v>353.5</v>
+        <v>339.65</v>
       </c>
       <c r="F120" t="n">
-        <v>369</v>
+        <v>343.9</v>
       </c>
       <c r="G120" t="n">
-        <v>12541474</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9060,25 +9516,25 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>373</v>
+        <v>345.1</v>
       </c>
       <c r="D121" t="n">
-        <v>382.45</v>
+        <v>346.05</v>
       </c>
       <c r="E121" t="n">
-        <v>367.15</v>
+        <v>338.35</v>
       </c>
       <c r="F121" t="n">
-        <v>377</v>
+        <v>339.35</v>
       </c>
       <c r="G121" t="n">
-        <v>15775994</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9087,25 +9543,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>381</v>
+        <v>339.4</v>
       </c>
       <c r="D122" t="n">
-        <v>383.9</v>
+        <v>340.2</v>
       </c>
       <c r="E122" t="n">
-        <v>375.15</v>
+        <v>333</v>
       </c>
       <c r="F122" t="n">
-        <v>381</v>
+        <v>334.55</v>
       </c>
       <c r="G122" t="n">
-        <v>8940938</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9114,25 +9570,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="D123" t="n">
-        <v>385.05</v>
+        <v>346.1</v>
       </c>
       <c r="E123" t="n">
-        <v>376.5</v>
+        <v>332</v>
       </c>
       <c r="F123" t="n">
-        <v>381</v>
+        <v>344.7</v>
       </c>
       <c r="G123" t="n">
-        <v>6636333</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9141,25 +9597,25 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>382.5</v>
+        <v>345.5</v>
       </c>
       <c r="D124" t="n">
-        <v>382.85</v>
+        <v>349.65</v>
       </c>
       <c r="E124" t="n">
-        <v>377.15</v>
+        <v>342.6</v>
       </c>
       <c r="F124" t="n">
-        <v>381</v>
+        <v>347.65</v>
       </c>
       <c r="G124" t="n">
-        <v>4423953</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9168,25 +9624,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>381.7</v>
+        <v>352</v>
       </c>
       <c r="D125" t="n">
-        <v>387.7</v>
+        <v>355.75</v>
       </c>
       <c r="E125" t="n">
-        <v>381.1</v>
+        <v>347.65</v>
       </c>
       <c r="F125" t="n">
-        <v>382.7</v>
+        <v>350.05</v>
       </c>
       <c r="G125" t="n">
-        <v>5292453</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9195,25 +9651,25 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>387.15</v>
+        <v>357.95</v>
       </c>
       <c r="D126" t="n">
-        <v>393.7</v>
+        <v>369</v>
       </c>
       <c r="E126" t="n">
-        <v>384.5</v>
+        <v>353.5</v>
       </c>
       <c r="F126" t="n">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="G126" t="n">
-        <v>8155315</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9222,25 +9678,25 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>398.5</v>
+        <v>373</v>
       </c>
       <c r="D127" t="n">
-        <v>422.2</v>
+        <v>382.45</v>
       </c>
       <c r="E127" t="n">
-        <v>398.5</v>
+        <v>367.15</v>
       </c>
       <c r="F127" t="n">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="G127" t="n">
-        <v>34388331</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9249,214 +9705,214 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>410.5</v>
+        <v>381</v>
       </c>
       <c r="D128" t="n">
-        <v>413.65</v>
+        <v>383.9</v>
       </c>
       <c r="E128" t="n">
-        <v>404.85</v>
+        <v>375.15</v>
       </c>
       <c r="F128" t="n">
-        <v>409.85</v>
+        <v>381</v>
       </c>
       <c r="G128" t="n">
-        <v>3729955</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4389.8</v>
+        <v>385</v>
       </c>
       <c r="D129" t="n">
-        <v>4485</v>
+        <v>385.05</v>
       </c>
       <c r="E129" t="n">
-        <v>4361.9</v>
+        <v>376.5</v>
       </c>
       <c r="F129" t="n">
-        <v>4398.1</v>
+        <v>381</v>
       </c>
       <c r="G129" t="n">
-        <v>1347378</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4422</v>
+        <v>382.5</v>
       </c>
       <c r="D130" t="n">
-        <v>4495</v>
+        <v>382.85</v>
       </c>
       <c r="E130" t="n">
-        <v>4358</v>
+        <v>377.15</v>
       </c>
       <c r="F130" t="n">
-        <v>4371.4</v>
+        <v>381</v>
       </c>
       <c r="G130" t="n">
-        <v>902264</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4387.7</v>
+        <v>381.7</v>
       </c>
       <c r="D131" t="n">
-        <v>4404</v>
+        <v>387.7</v>
       </c>
       <c r="E131" t="n">
-        <v>4281.9</v>
+        <v>381.1</v>
       </c>
       <c r="F131" t="n">
-        <v>4304.2</v>
+        <v>382.7</v>
       </c>
       <c r="G131" t="n">
-        <v>463349</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4285</v>
+        <v>387.15</v>
       </c>
       <c r="D132" t="n">
-        <v>4317</v>
+        <v>393.7</v>
       </c>
       <c r="E132" t="n">
-        <v>4220</v>
+        <v>384.5</v>
       </c>
       <c r="F132" t="n">
-        <v>4244.3</v>
+        <v>388</v>
       </c>
       <c r="G132" t="n">
-        <v>398348</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4211</v>
+        <v>398.5</v>
       </c>
       <c r="D133" t="n">
-        <v>4220</v>
+        <v>422.2</v>
       </c>
       <c r="E133" t="n">
-        <v>4129.3</v>
+        <v>398.5</v>
       </c>
       <c r="F133" t="n">
-        <v>4178.1</v>
+        <v>420</v>
       </c>
       <c r="G133" t="n">
-        <v>470046</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4190</v>
+        <v>410.5</v>
       </c>
       <c r="D134" t="n">
-        <v>4324.4</v>
+        <v>413.65</v>
       </c>
       <c r="E134" t="n">
-        <v>4190</v>
+        <v>400</v>
       </c>
       <c r="F134" t="n">
-        <v>4257.3</v>
+        <v>400.5</v>
       </c>
       <c r="G134" t="n">
-        <v>633457</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4290</v>
+        <v>378.6</v>
       </c>
       <c r="D135" t="n">
-        <v>4383</v>
+        <v>384.95</v>
       </c>
       <c r="E135" t="n">
-        <v>4266</v>
+        <v>377.15</v>
       </c>
       <c r="F135" t="n">
-        <v>4288.7</v>
+        <v>377.75</v>
       </c>
       <c r="G135" t="n">
-        <v>835107</v>
+        <v>9666647</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9465,25 +9921,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4299</v>
+        <v>4389.8</v>
       </c>
       <c r="D136" t="n">
-        <v>4340</v>
+        <v>4485</v>
       </c>
       <c r="E136" t="n">
-        <v>4216</v>
+        <v>4361.9</v>
       </c>
       <c r="F136" t="n">
-        <v>4243.8</v>
+        <v>4398.1</v>
       </c>
       <c r="G136" t="n">
-        <v>422024</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9492,25 +9948,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4201.9</v>
+        <v>4422</v>
       </c>
       <c r="D137" t="n">
-        <v>4222</v>
+        <v>4495</v>
       </c>
       <c r="E137" t="n">
-        <v>4115</v>
+        <v>4358</v>
       </c>
       <c r="F137" t="n">
-        <v>4156</v>
+        <v>4371.4</v>
       </c>
       <c r="G137" t="n">
-        <v>378694</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9519,25 +9975,25 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4181.8</v>
+        <v>4387.7</v>
       </c>
       <c r="D138" t="n">
-        <v>4385</v>
+        <v>4404</v>
       </c>
       <c r="E138" t="n">
-        <v>4129.4</v>
+        <v>4281.9</v>
       </c>
       <c r="F138" t="n">
-        <v>4362.2</v>
+        <v>4304.2</v>
       </c>
       <c r="G138" t="n">
-        <v>992864</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9546,25 +10002,25 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4380</v>
+        <v>4285</v>
       </c>
       <c r="D139" t="n">
-        <v>4478.3</v>
+        <v>4317</v>
       </c>
       <c r="E139" t="n">
-        <v>4280.1</v>
+        <v>4220</v>
       </c>
       <c r="F139" t="n">
-        <v>4395.7</v>
+        <v>4244.3</v>
       </c>
       <c r="G139" t="n">
-        <v>960643</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9573,25 +10029,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4497.2</v>
+        <v>4211</v>
       </c>
       <c r="D140" t="n">
-        <v>4541.17</v>
+        <v>4220</v>
       </c>
       <c r="E140" t="n">
-        <v>4319.31</v>
+        <v>4129.3</v>
       </c>
       <c r="F140" t="n">
-        <v>4361.38</v>
+        <v>4178.1</v>
       </c>
       <c r="G140" t="n">
-        <v>1616021</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9600,25 +10056,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4338</v>
+        <v>4190</v>
       </c>
       <c r="D141" t="n">
-        <v>4339.1</v>
+        <v>4324.4</v>
       </c>
       <c r="E141" t="n">
-        <v>4172.9</v>
+        <v>4190</v>
       </c>
       <c r="F141" t="n">
-        <v>4192.59</v>
+        <v>4257.3</v>
       </c>
       <c r="G141" t="n">
-        <v>648341</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9627,25 +10083,25 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4297.32</v>
+        <v>4290</v>
       </c>
       <c r="D142" t="n">
-        <v>4595.14</v>
+        <v>4383</v>
       </c>
       <c r="E142" t="n">
-        <v>4249.35</v>
+        <v>4266</v>
       </c>
       <c r="F142" t="n">
-        <v>4521.18</v>
+        <v>4288.7</v>
       </c>
       <c r="G142" t="n">
-        <v>4510774</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9654,25 +10110,25 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4557.56</v>
+        <v>4299</v>
       </c>
       <c r="D143" t="n">
-        <v>4737.05</v>
+        <v>4340</v>
       </c>
       <c r="E143" t="n">
-        <v>4537.17</v>
+        <v>4216</v>
       </c>
       <c r="F143" t="n">
-        <v>4583.14</v>
+        <v>4243.8</v>
       </c>
       <c r="G143" t="n">
-        <v>2334958</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9681,25 +10137,25 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4606.13</v>
+        <v>4201.9</v>
       </c>
       <c r="D144" t="n">
-        <v>4777.02</v>
+        <v>4222</v>
       </c>
       <c r="E144" t="n">
-        <v>4590.24</v>
+        <v>4115</v>
       </c>
       <c r="F144" t="n">
-        <v>4759.23</v>
+        <v>4156</v>
       </c>
       <c r="G144" t="n">
-        <v>1899271</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9708,25 +10164,25 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4817.7</v>
+        <v>4181.8</v>
       </c>
       <c r="D145" t="n">
-        <v>4929.93</v>
+        <v>4385</v>
       </c>
       <c r="E145" t="n">
-        <v>4722.06</v>
+        <v>4129.4</v>
       </c>
       <c r="F145" t="n">
-        <v>4890.75</v>
+        <v>4362.2</v>
       </c>
       <c r="G145" t="n">
-        <v>1924204</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9735,25 +10191,25 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4896.95</v>
+        <v>4380</v>
       </c>
       <c r="D146" t="n">
-        <v>4976.9</v>
+        <v>4478.3</v>
       </c>
       <c r="E146" t="n">
-        <v>4780.02</v>
+        <v>4280.1</v>
       </c>
       <c r="F146" t="n">
-        <v>4813</v>
+        <v>4395.7</v>
       </c>
       <c r="G146" t="n">
-        <v>1117424</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9762,25 +10218,25 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4790</v>
+        <v>4497.2</v>
       </c>
       <c r="D147" t="n">
-        <v>4968</v>
+        <v>4541.17</v>
       </c>
       <c r="E147" t="n">
-        <v>4780</v>
+        <v>4319.31</v>
       </c>
       <c r="F147" t="n">
-        <v>4939.2</v>
+        <v>4361.38</v>
       </c>
       <c r="G147" t="n">
-        <v>1296942</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9789,25 +10245,25 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4958</v>
+        <v>4338</v>
       </c>
       <c r="D148" t="n">
-        <v>5085</v>
+        <v>4339.1</v>
       </c>
       <c r="E148" t="n">
-        <v>4888.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F148" t="n">
-        <v>4903</v>
+        <v>4192.59</v>
       </c>
       <c r="G148" t="n">
-        <v>1210476</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9816,25 +10272,25 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4903</v>
+        <v>4297.32</v>
       </c>
       <c r="D149" t="n">
-        <v>4940</v>
+        <v>4595.14</v>
       </c>
       <c r="E149" t="n">
-        <v>4792.5</v>
+        <v>4249.35</v>
       </c>
       <c r="F149" t="n">
-        <v>4859.8</v>
+        <v>4521.18</v>
       </c>
       <c r="G149" t="n">
-        <v>682980</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9843,25 +10299,25 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4866</v>
+        <v>4557.56</v>
       </c>
       <c r="D150" t="n">
-        <v>4907.9</v>
+        <v>4737.05</v>
       </c>
       <c r="E150" t="n">
-        <v>4753</v>
+        <v>4537.17</v>
       </c>
       <c r="F150" t="n">
-        <v>4837.4</v>
+        <v>4583.14</v>
       </c>
       <c r="G150" t="n">
-        <v>613049</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9870,241 +10326,241 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4860</v>
+        <v>4606.13</v>
       </c>
       <c r="D151" t="n">
-        <v>5139</v>
+        <v>4777.02</v>
       </c>
       <c r="E151" t="n">
-        <v>4860</v>
+        <v>4590.24</v>
       </c>
       <c r="F151" t="n">
-        <v>5110</v>
+        <v>4759.23</v>
       </c>
       <c r="G151" t="n">
-        <v>1355375</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1417</v>
+        <v>4817.7</v>
       </c>
       <c r="D152" t="n">
-        <v>1436</v>
+        <v>4929.93</v>
       </c>
       <c r="E152" t="n">
-        <v>1410.1</v>
+        <v>4722.06</v>
       </c>
       <c r="F152" t="n">
-        <v>1423.9</v>
+        <v>4890.75</v>
       </c>
       <c r="G152" t="n">
-        <v>623969</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1428</v>
+        <v>4896.95</v>
       </c>
       <c r="D153" t="n">
-        <v>1428</v>
+        <v>4976.9</v>
       </c>
       <c r="E153" t="n">
-        <v>1351.5</v>
+        <v>4780.02</v>
       </c>
       <c r="F153" t="n">
-        <v>1359.1</v>
+        <v>4813</v>
       </c>
       <c r="G153" t="n">
-        <v>808190</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1349.8</v>
+        <v>4790</v>
       </c>
       <c r="D154" t="n">
-        <v>1357.8</v>
+        <v>4968</v>
       </c>
       <c r="E154" t="n">
-        <v>1330.1</v>
+        <v>4780</v>
       </c>
       <c r="F154" t="n">
-        <v>1340.8</v>
+        <v>4939.2</v>
       </c>
       <c r="G154" t="n">
-        <v>345535</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1340.8</v>
+        <v>4958</v>
       </c>
       <c r="D155" t="n">
-        <v>1387.7</v>
+        <v>5085</v>
       </c>
       <c r="E155" t="n">
-        <v>1316</v>
+        <v>4888.8</v>
       </c>
       <c r="F155" t="n">
-        <v>1374.4</v>
+        <v>4903</v>
       </c>
       <c r="G155" t="n">
-        <v>974660</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1372.9</v>
+        <v>4903</v>
       </c>
       <c r="D156" t="n">
-        <v>1390</v>
+        <v>4940</v>
       </c>
       <c r="E156" t="n">
-        <v>1355.1</v>
+        <v>4792.5</v>
       </c>
       <c r="F156" t="n">
-        <v>1363.5</v>
+        <v>4859.8</v>
       </c>
       <c r="G156" t="n">
-        <v>479123</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1363</v>
+        <v>4866</v>
       </c>
       <c r="D157" t="n">
-        <v>1392</v>
+        <v>4907.9</v>
       </c>
       <c r="E157" t="n">
-        <v>1355.1</v>
+        <v>4753</v>
       </c>
       <c r="F157" t="n">
-        <v>1380</v>
+        <v>4837.4</v>
       </c>
       <c r="G157" t="n">
-        <v>616767</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1360</v>
+        <v>4860</v>
       </c>
       <c r="D158" t="n">
-        <v>1368</v>
+        <v>5200</v>
       </c>
       <c r="E158" t="n">
-        <v>1272.1</v>
+        <v>4860</v>
       </c>
       <c r="F158" t="n">
-        <v>1288.3</v>
+        <v>5181</v>
       </c>
       <c r="G158" t="n">
-        <v>1098492</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1300</v>
+        <v>5200</v>
       </c>
       <c r="D159" t="n">
-        <v>1318.5</v>
+        <v>5269</v>
       </c>
       <c r="E159" t="n">
-        <v>1257</v>
+        <v>5062</v>
       </c>
       <c r="F159" t="n">
-        <v>1316.2</v>
+        <v>5091.1</v>
       </c>
       <c r="G159" t="n">
-        <v>1172726</v>
+        <v>959836</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10113,25 +10569,25 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1317.7</v>
+        <v>1417</v>
       </c>
       <c r="D160" t="n">
-        <v>1319.8</v>
+        <v>1436</v>
       </c>
       <c r="E160" t="n">
-        <v>1270.5</v>
+        <v>1410.1</v>
       </c>
       <c r="F160" t="n">
-        <v>1306</v>
+        <v>1423.9</v>
       </c>
       <c r="G160" t="n">
-        <v>832973</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10140,25 +10596,25 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1319.9</v>
+        <v>1428</v>
       </c>
       <c r="D161" t="n">
-        <v>1355.4</v>
+        <v>1428</v>
       </c>
       <c r="E161" t="n">
-        <v>1308</v>
+        <v>1351.5</v>
       </c>
       <c r="F161" t="n">
-        <v>1343.4</v>
+        <v>1359.1</v>
       </c>
       <c r="G161" t="n">
-        <v>1287698</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10167,25 +10623,25 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1379</v>
+        <v>1349.8</v>
       </c>
       <c r="D162" t="n">
-        <v>1468</v>
+        <v>1357.8</v>
       </c>
       <c r="E162" t="n">
-        <v>1361</v>
+        <v>1330.1</v>
       </c>
       <c r="F162" t="n">
-        <v>1377.8</v>
+        <v>1340.8</v>
       </c>
       <c r="G162" t="n">
-        <v>9950655</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10194,25 +10650,25 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1380.5</v>
+        <v>1340.8</v>
       </c>
       <c r="D163" t="n">
-        <v>1403.3</v>
+        <v>1387.7</v>
       </c>
       <c r="E163" t="n">
-        <v>1363</v>
+        <v>1316</v>
       </c>
       <c r="F163" t="n">
-        <v>1366.8</v>
+        <v>1374.4</v>
       </c>
       <c r="G163" t="n">
-        <v>1567542</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10221,25 +10677,25 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1380</v>
+        <v>1372.9</v>
       </c>
       <c r="D164" t="n">
-        <v>1397.5</v>
+        <v>1390</v>
       </c>
       <c r="E164" t="n">
-        <v>1351.6</v>
+        <v>1355.1</v>
       </c>
       <c r="F164" t="n">
-        <v>1360.6</v>
+        <v>1363.5</v>
       </c>
       <c r="G164" t="n">
-        <v>1098353</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10248,25 +10704,25 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1360.6</v>
+        <v>1363</v>
       </c>
       <c r="D165" t="n">
-        <v>1428</v>
+        <v>1392</v>
       </c>
       <c r="E165" t="n">
-        <v>1354.5</v>
+        <v>1355.1</v>
       </c>
       <c r="F165" t="n">
-        <v>1421.6</v>
+        <v>1380</v>
       </c>
       <c r="G165" t="n">
-        <v>2055261</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10275,25 +10731,25 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1429.6</v>
+        <v>1360</v>
       </c>
       <c r="D166" t="n">
-        <v>1453</v>
+        <v>1368</v>
       </c>
       <c r="E166" t="n">
-        <v>1419</v>
+        <v>1272.1</v>
       </c>
       <c r="F166" t="n">
-        <v>1434.1</v>
+        <v>1288.3</v>
       </c>
       <c r="G166" t="n">
-        <v>1243415</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10302,25 +10758,25 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1434</v>
+        <v>1300</v>
       </c>
       <c r="D167" t="n">
-        <v>1460</v>
+        <v>1318.5</v>
       </c>
       <c r="E167" t="n">
-        <v>1405</v>
+        <v>1257</v>
       </c>
       <c r="F167" t="n">
-        <v>1418</v>
+        <v>1316.2</v>
       </c>
       <c r="G167" t="n">
-        <v>1123973</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10329,25 +10785,25 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1413.9</v>
+        <v>1317.7</v>
       </c>
       <c r="D168" t="n">
-        <v>1434</v>
+        <v>1319.8</v>
       </c>
       <c r="E168" t="n">
-        <v>1407.5</v>
+        <v>1270.5</v>
       </c>
       <c r="F168" t="n">
-        <v>1424.7</v>
+        <v>1306</v>
       </c>
       <c r="G168" t="n">
-        <v>509551</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10356,25 +10812,25 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1434.1</v>
+        <v>1319.9</v>
       </c>
       <c r="D169" t="n">
-        <v>1522</v>
+        <v>1355.4</v>
       </c>
       <c r="E169" t="n">
-        <v>1427.5</v>
+        <v>1308</v>
       </c>
       <c r="F169" t="n">
-        <v>1516.4</v>
+        <v>1343.4</v>
       </c>
       <c r="G169" t="n">
-        <v>3863757</v>
+        <v>1287698</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10383,25 +10839,25 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1516.4</v>
+        <v>1379</v>
       </c>
       <c r="D170" t="n">
-        <v>1543</v>
+        <v>1468</v>
       </c>
       <c r="E170" t="n">
-        <v>1486.9</v>
+        <v>1361</v>
       </c>
       <c r="F170" t="n">
-        <v>1494.8</v>
+        <v>1377.8</v>
       </c>
       <c r="G170" t="n">
-        <v>1508375</v>
+        <v>9950655</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10410,46 +10866,289 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1494.8</v>
+        <v>1380.5</v>
       </c>
       <c r="D171" t="n">
-        <v>1514</v>
+        <v>1403.3</v>
       </c>
       <c r="E171" t="n">
-        <v>1465.1</v>
+        <v>1363</v>
       </c>
       <c r="F171" t="n">
-        <v>1473.3</v>
+        <v>1366.8</v>
       </c>
       <c r="G171" t="n">
-        <v>749197</v>
+        <v>1567542</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1429.6</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1453</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1434</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1460</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1413.9</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1407.5</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1424.7</v>
+      </c>
+      <c r="G176" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1434.1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1522</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1516.4</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1486.9</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1514</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1465.1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G179" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="C180" t="n">
         <v>1481.9</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D180" t="n">
         <v>1500.5</v>
       </c>
-      <c r="E172" t="n">
-        <v>1469.7</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1475.8</v>
-      </c>
-      <c r="G172" t="n">
-        <v>286495</v>
+      <c r="E180" t="n">
+        <v>1451</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1467.7</v>
+      </c>
+      <c r="G180" t="n">
+        <v>742118</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1506.7</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1461.5</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1470.5</v>
+      </c>
+      <c r="G181" t="n">
+        <v>414426</v>
       </c>
     </row>
   </sheetData>
@@ -10463,7 +11162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10648,6 +11347,21 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 14 Aug 2026 05:16</t>
+          <t>Generated 18 Aug 2026 04:09</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>57.6</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="3">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>4.83</v>
+        <v>4.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3.69</v>
+        <v>4.38</v>
       </c>
       <c r="E3" t="n">
-        <v>70.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
@@ -647,7 +647,7 @@
         <v>-2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>5.86</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="4">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>9.48</v>
+        <v>8.75</v>
       </c>
       <c r="D4" t="n">
         <v>10.56</v>
       </c>
       <c r="E4" t="n">
-        <v>88.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F4" t="n">
         <v>26.91</v>
@@ -675,7 +675,35 @@
         <v>-4.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8.869999999999999</v>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15d</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.26</v>
       </c>
     </row>
   </sheetData>
@@ -689,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,6 +2969,192 @@
         <v>1</v>
       </c>
       <c r="P37" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100</v>
+      </c>
+      <c r="F38" t="n">
+        <v>207.01</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>227.48</v>
+      </c>
+      <c r="I38" t="n">
+        <v>207.19</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-8.92</v>
+      </c>
+      <c r="K38" t="n">
+        <v>247.77</v>
+      </c>
+      <c r="L38" t="n">
+        <v>268.06</v>
+      </c>
+      <c r="M38" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>99</v>
+      </c>
+      <c r="F39" t="n">
+        <v>112.42</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="K39" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="L39" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>99</v>
+      </c>
+      <c r="F40" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1599.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1505.54</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1693.66</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1787.72</v>
+      </c>
+      <c r="M40" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -2957,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4133,6 +4347,105 @@
       </c>
       <c r="I37" t="n">
         <v>15.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>227.48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>207.19</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-8.92</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="H38" t="n">
+        <v>247.77</v>
+      </c>
+      <c r="I38" t="n">
+        <v>268.06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="I39" t="n">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1599.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1505.54</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="G40" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1693.66</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1787.72</v>
       </c>
     </row>
   </sheetData>
@@ -4146,7 +4459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4249,7 +4562,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4269,7 +4582,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229.01</v>
+        <v>227.48</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4277,16 +4590,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.74</v>
+        <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.18</v>
+        <v>-4.16</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>209.18</v>
+        <v>207.19</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -4302,12 +4615,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4322,7 +4635,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1607.3</v>
+        <v>13.76</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -4330,16 +4643,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.01</v>
+        <v>-1.89</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1508.29</v>
+        <v>12.95</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -4355,19 +4668,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4375,7 +4688,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.99</v>
+        <v>1599.6</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4383,16 +4696,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1.07</v>
+        <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.57</v>
+        <v>-1.03</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>13.18</v>
+        <v>1505.54</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -4408,7 +4721,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4428,26 +4741,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>227.36</v>
+        <v>223.11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.73</v>
+        <v>-1.62</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.08</v>
+        <v>-2.36</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>209.53</v>
+        <v>209.18</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -4463,12 +4776,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4483,26 +4796,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.51</v>
+        <v>1616</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>-1.66</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>4.66</v>
+        <v>0.74</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.37</v>
+        <v>-2.54</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>13.02</v>
+        <v>1508.29</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -4518,19 +4831,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4538,26 +4851,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1583</v>
+        <v>14.11</v>
       </c>
       <c r="G7" t="n">
-        <v>1.54</v>
+        <v>-2.83</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3.49</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8</v>
+        <v>-4.39</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1491.87</v>
+        <v>13.18</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -4573,7 +4886,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4593,26 +4906,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>221.52</v>
+        <v>227.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>-1.87</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>4.26</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.94</v>
+        <v>-4.18</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -4628,7 +4941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4648,26 +4961,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>4.74</v>
+        <v>5.03</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.96</v>
+        <v>-0.37</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -4683,12 +4996,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4703,29 +5016,29 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>547.7</v>
+        <v>1583</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.59</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>4.16</v>
+        <v>3.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.97</v>
+        <v>-0.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -4733,14 +5046,12 @@
       <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4760,26 +5071,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>7.8</v>
+        <v>4.26</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -4795,12 +5106,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4815,32 +5126,32 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>8.42</v>
+        <v>5.11</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -4850,12 +5161,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4870,29 +5181,29 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.42</v>
+        <v>-0.59</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>3.08</v>
+        <v>4.97</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.19</v>
+        <v>-5.97</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -4900,12 +5211,14 @@
       <c r="R13" t="b">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4925,34 +5238,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>10.11</v>
+        <v>6.18</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>11.04</v>
+        <v>7.8</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -4962,19 +5275,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4982,34 +5295,34 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>9.76</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.67</v>
+        <v>-2.2</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -5019,19 +5332,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5039,34 +5352,34 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.85</v>
+        <v>-1.38</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.01</v>
+        <v>-3.19</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
@@ -5076,7 +5389,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5096,28 +5409,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G17" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.63</v>
+        <v>7.27</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>13.39</v>
+        <v>11.04</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -5133,7 +5446,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5153,28 +5466,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.28</v>
+        <v>-0.86</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.07</v>
+        <v>-3.67</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -5190,7 +5503,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5213,10 +5526,10 @@
         <v>381</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
-        <v>5.12</v>
+        <v>-1.31</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -5225,13 +5538,13 @@
         <v>10.81</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.18</v>
+        <v>-1.57</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -5240,14 +5553,14 @@
         <v>1</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5267,34 +5580,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
-        <v>4.38</v>
+        <v>11.63</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>8.82</v>
+        <v>13.39</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -5304,12 +5617,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5324,34 +5637,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.09</v>
+        <v>-2.28</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>7.73</v>
+        <v>3.21</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.45</v>
+        <v>-3.07</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -5361,12 +5674,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5381,44 +5694,44 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.62</v>
+        <v>5.12</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.37</v>
+        <v>-1.57</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
       </c>
       <c r="Q22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5438,34 +5751,34 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G23" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H23" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>13.89</v>
+        <v>8.82</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -5475,7 +5788,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5487,7 +5800,7 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5495,28 +5808,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G24" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H24" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>10.71</v>
+        <v>9.06</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -5532,12 +5845,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5552,34 +5865,34 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G25" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H25" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.61</v>
+        <v>-4.37</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -5589,19 +5902,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -5609,28 +5922,30 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G26" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H26" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>5.65</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12.18</v>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>14.96</v>
+        <v>13.89</v>
       </c>
       <c r="M26" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -5646,19 +5961,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5666,34 +5981,36 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>2.11</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.59</v>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>12.08</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.66</v>
+        <v>-3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
       </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
@@ -5703,19 +6020,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5723,28 +6040,30 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G28" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H28" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>2.92</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.28</v>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>13.41</v>
+        <v>11.99</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -5760,12 +6079,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5780,46 +6099,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H29" t="n">
-        <v>2.92</v>
+        <v>6.98</v>
       </c>
       <c r="I29" t="n">
-        <v>6.52</v>
+        <v>13.73</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>11.99</v>
+        <v>16.38</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
       <c r="O29" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
       </c>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5839,30 +6158,30 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-4.58</v>
+        <v>-3.52</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M30" t="n">
-        <v>-5.35</v>
+        <v>-4.66</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -5878,19 +6197,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5898,36 +6217,36 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H31" t="n">
-        <v>2.73</v>
+        <v>11.34</v>
       </c>
       <c r="I31" t="n">
-        <v>3.01</v>
+        <v>7.78</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>5.02</v>
+        <v>13.29</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.45</v>
+        <v>-0.66</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -5937,12 +6256,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5957,50 +6276,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G32" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H32" t="n">
-        <v>9.65</v>
+        <v>2.81</v>
       </c>
       <c r="I32" t="n">
-        <v>14.45</v>
+        <v>6.42</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>19.32</v>
+        <v>11.88</v>
       </c>
       <c r="M32" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N32" t="n">
-        <v>13</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6008,38 +6335,46 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G33" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H33" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I33" t="n">
-        <v>10.91</v>
+        <v>-4.58</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>20.81</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
-        <v>-4.32</v>
+        <v>-5.35</v>
       </c>
       <c r="N33" t="n">
-        <v>13</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
       <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6051,7 +6386,7 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6062,13 +6397,13 @@
         <v>1781.3</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H34" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -6076,33 +6411,41 @@
         <v>5.02</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.52</v>
+        <v>-0.67</v>
       </c>
       <c r="N34" t="n">
-        <v>13</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
       <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -6110,27 +6453,27 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G35" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H35" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I35" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>31.45</v>
+        <v>19.32</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -6141,19 +6484,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -6161,27 +6504,27 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G36" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H36" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I36" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>22.59</v>
+        <v>22.3</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -6192,19 +6535,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6212,33 +6555,192 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I37" t="n">
-        <v>10.56</v>
+        <v>3.86</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>19.87</v>
+        <v>5.02</v>
       </c>
       <c r="M37" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H38" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I38" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J38" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N38" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>96</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J39" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>16</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>92</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J40" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N40" t="n">
+        <v>16</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6846,76 +7348,76 @@
         <v>1588</v>
       </c>
       <c r="D22" t="n">
-        <v>1612.9</v>
+        <v>1624</v>
       </c>
       <c r="E22" t="n">
         <v>1575</v>
       </c>
       <c r="F22" t="n">
-        <v>1607.3</v>
+        <v>1616</v>
       </c>
       <c r="G22" t="n">
-        <v>3892957</v>
+        <v>7047548</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1188.4</v>
+        <v>1621</v>
       </c>
       <c r="D23" t="n">
-        <v>1207.9</v>
+        <v>1627.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1158</v>
+        <v>1585.4</v>
       </c>
       <c r="F23" t="n">
-        <v>1201.8</v>
+        <v>1589.1</v>
       </c>
       <c r="G23" t="n">
-        <v>3482939</v>
+        <v>2016844</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1225</v>
+        <v>1589</v>
       </c>
       <c r="D24" t="n">
-        <v>1318.9</v>
+        <v>1601.6</v>
       </c>
       <c r="E24" t="n">
-        <v>1225</v>
+        <v>1583.1</v>
       </c>
       <c r="F24" t="n">
-        <v>1296.4</v>
+        <v>1599.6</v>
       </c>
       <c r="G24" t="n">
-        <v>17106822</v>
+        <v>327119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6924,25 +7426,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1325</v>
+        <v>1188.4</v>
       </c>
       <c r="D25" t="n">
-        <v>1345</v>
+        <v>1207.9</v>
       </c>
       <c r="E25" t="n">
-        <v>1251.5</v>
+        <v>1158</v>
       </c>
       <c r="F25" t="n">
-        <v>1267.1</v>
+        <v>1201.8</v>
       </c>
       <c r="G25" t="n">
-        <v>10436460</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6951,25 +7453,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1270</v>
+        <v>1225</v>
       </c>
       <c r="D26" t="n">
-        <v>1285</v>
+        <v>1318.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1246.1</v>
+        <v>1225</v>
       </c>
       <c r="F26" t="n">
-        <v>1282.2</v>
+        <v>1296.4</v>
       </c>
       <c r="G26" t="n">
-        <v>4135957</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6978,25 +7480,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1282.2</v>
+        <v>1325</v>
       </c>
       <c r="D27" t="n">
-        <v>1333.9</v>
+        <v>1345</v>
       </c>
       <c r="E27" t="n">
-        <v>1272.6</v>
+        <v>1251.5</v>
       </c>
       <c r="F27" t="n">
-        <v>1296.7</v>
+        <v>1267.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5275779</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7005,25 +7507,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1302.7</v>
+        <v>1270</v>
       </c>
       <c r="D28" t="n">
-        <v>1315.8</v>
+        <v>1285</v>
       </c>
       <c r="E28" t="n">
-        <v>1257.1</v>
+        <v>1246.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1288.4</v>
+        <v>1282.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3844546</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7032,25 +7534,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1290</v>
+        <v>1282.2</v>
       </c>
       <c r="D29" t="n">
-        <v>1312</v>
+        <v>1333.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1262</v>
+        <v>1272.6</v>
       </c>
       <c r="F29" t="n">
-        <v>1268.2</v>
+        <v>1296.7</v>
       </c>
       <c r="G29" t="n">
-        <v>2691508</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7059,25 +7561,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1268.2</v>
+        <v>1302.7</v>
       </c>
       <c r="D30" t="n">
-        <v>1271.5</v>
+        <v>1315.8</v>
       </c>
       <c r="E30" t="n">
-        <v>1221.2</v>
+        <v>1257.1</v>
       </c>
       <c r="F30" t="n">
-        <v>1233.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G30" t="n">
-        <v>2619436</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7086,25 +7588,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1224.1</v>
+        <v>1290</v>
       </c>
       <c r="D31" t="n">
-        <v>1224.7</v>
+        <v>1312</v>
       </c>
       <c r="E31" t="n">
-        <v>1188.1</v>
+        <v>1262</v>
       </c>
       <c r="F31" t="n">
-        <v>1208.7</v>
+        <v>1268.2</v>
       </c>
       <c r="G31" t="n">
-        <v>3613338</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7113,25 +7615,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1214.9</v>
+        <v>1268.2</v>
       </c>
       <c r="D32" t="n">
-        <v>1233.9</v>
+        <v>1271.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1196.5</v>
+        <v>1221.2</v>
       </c>
       <c r="F32" t="n">
-        <v>1214.9</v>
+        <v>1233.2</v>
       </c>
       <c r="G32" t="n">
-        <v>1911132</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7140,25 +7642,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1213</v>
+        <v>1224.1</v>
       </c>
       <c r="D33" t="n">
-        <v>1229</v>
+        <v>1224.7</v>
       </c>
       <c r="E33" t="n">
-        <v>1196.1</v>
+        <v>1188.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1202</v>
+        <v>1208.7</v>
       </c>
       <c r="G33" t="n">
-        <v>2067763</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7167,25 +7669,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1207.2</v>
+        <v>1214.9</v>
       </c>
       <c r="D34" t="n">
-        <v>1252</v>
+        <v>1233.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1191.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F34" t="n">
-        <v>1246.1</v>
+        <v>1214.9</v>
       </c>
       <c r="G34" t="n">
-        <v>3306087</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7194,25 +7696,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1253</v>
+        <v>1213</v>
       </c>
       <c r="D35" t="n">
-        <v>1265.9</v>
+        <v>1229</v>
       </c>
       <c r="E35" t="n">
-        <v>1232.5</v>
+        <v>1196.1</v>
       </c>
       <c r="F35" t="n">
-        <v>1240.9</v>
+        <v>1202</v>
       </c>
       <c r="G35" t="n">
-        <v>2463994</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7221,25 +7723,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1247</v>
+        <v>1207.2</v>
       </c>
       <c r="D36" t="n">
-        <v>1274.6</v>
+        <v>1252</v>
       </c>
       <c r="E36" t="n">
-        <v>1232.1</v>
+        <v>1191.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1260.3</v>
+        <v>1246.1</v>
       </c>
       <c r="G36" t="n">
-        <v>3182495</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7248,25 +7750,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1269</v>
+        <v>1253</v>
       </c>
       <c r="D37" t="n">
-        <v>1289.9</v>
+        <v>1265.9</v>
       </c>
       <c r="E37" t="n">
-        <v>1242</v>
+        <v>1232.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1272.7</v>
+        <v>1240.9</v>
       </c>
       <c r="G37" t="n">
-        <v>3918512</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7275,25 +7777,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1341.2</v>
+        <v>1247</v>
       </c>
       <c r="D38" t="n">
-        <v>1500</v>
+        <v>1274.6</v>
       </c>
       <c r="E38" t="n">
-        <v>1336.5</v>
+        <v>1232.1</v>
       </c>
       <c r="F38" t="n">
-        <v>1450.4</v>
+        <v>1260.3</v>
       </c>
       <c r="G38" t="n">
-        <v>23853424</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7302,25 +7804,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1465</v>
+        <v>1269</v>
       </c>
       <c r="D39" t="n">
-        <v>1479.5</v>
+        <v>1289.9</v>
       </c>
       <c r="E39" t="n">
-        <v>1405</v>
+        <v>1242</v>
       </c>
       <c r="F39" t="n">
-        <v>1470.8</v>
+        <v>1272.7</v>
       </c>
       <c r="G39" t="n">
-        <v>6958528</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7329,25 +7831,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1470.8</v>
+        <v>1341.2</v>
       </c>
       <c r="D40" t="n">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="E40" t="n">
-        <v>1440</v>
+        <v>1336.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1453.2</v>
+        <v>1450.4</v>
       </c>
       <c r="G40" t="n">
-        <v>4844393</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7356,25 +7858,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1450</v>
+        <v>1465</v>
       </c>
       <c r="D41" t="n">
-        <v>1508</v>
+        <v>1479.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1446</v>
+        <v>1405</v>
       </c>
       <c r="F41" t="n">
-        <v>1481.5</v>
+        <v>1470.8</v>
       </c>
       <c r="G41" t="n">
-        <v>4646531</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7383,25 +7885,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1488</v>
+        <v>1470.8</v>
       </c>
       <c r="D42" t="n">
-        <v>1520</v>
+        <v>1505</v>
       </c>
       <c r="E42" t="n">
-        <v>1457</v>
+        <v>1440</v>
       </c>
       <c r="F42" t="n">
-        <v>1466.2</v>
+        <v>1453.2</v>
       </c>
       <c r="G42" t="n">
-        <v>3972989</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7410,25 +7912,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1472.4</v>
+        <v>1450</v>
       </c>
       <c r="D43" t="n">
-        <v>1534.8</v>
+        <v>1508</v>
       </c>
       <c r="E43" t="n">
-        <v>1472</v>
+        <v>1446</v>
       </c>
       <c r="F43" t="n">
-        <v>1525.4</v>
+        <v>1481.5</v>
       </c>
       <c r="G43" t="n">
-        <v>4867021</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7437,25 +7939,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1531.7</v>
+        <v>1488</v>
       </c>
       <c r="D44" t="n">
-        <v>1580</v>
+        <v>1520</v>
       </c>
       <c r="E44" t="n">
-        <v>1511.1</v>
+        <v>1457</v>
       </c>
       <c r="F44" t="n">
-        <v>1569.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G44" t="n">
-        <v>4521175</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7464,25 +7966,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1575</v>
+        <v>1472.4</v>
       </c>
       <c r="D45" t="n">
-        <v>1575</v>
+        <v>1534.8</v>
       </c>
       <c r="E45" t="n">
-        <v>1500.1</v>
+        <v>1472</v>
       </c>
       <c r="F45" t="n">
-        <v>1525.5</v>
+        <v>1525.4</v>
       </c>
       <c r="G45" t="n">
-        <v>2487069</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7491,133 +7993,133 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1530</v>
+        <v>1531.7</v>
       </c>
       <c r="D46" t="n">
-        <v>1541</v>
+        <v>1580</v>
       </c>
       <c r="E46" t="n">
-        <v>1515</v>
+        <v>1511.1</v>
       </c>
       <c r="F46" t="n">
-        <v>1525.4</v>
+        <v>1569.4</v>
       </c>
       <c r="G46" t="n">
-        <v>842938</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>211.95</v>
+        <v>1575</v>
       </c>
       <c r="D47" t="n">
-        <v>214.55</v>
+        <v>1575</v>
       </c>
       <c r="E47" t="n">
-        <v>206.1</v>
+        <v>1500.1</v>
       </c>
       <c r="F47" t="n">
-        <v>212.78</v>
+        <v>1526.5</v>
       </c>
       <c r="G47" t="n">
-        <v>12863408</v>
+        <v>4013245</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>214.3</v>
+        <v>1530</v>
       </c>
       <c r="D48" t="n">
-        <v>223.41</v>
+        <v>1541</v>
       </c>
       <c r="E48" t="n">
-        <v>214.3</v>
+        <v>1501.9</v>
       </c>
       <c r="F48" t="n">
-        <v>223.08</v>
+        <v>1511.5</v>
       </c>
       <c r="G48" t="n">
-        <v>32151413</v>
+        <v>2250949</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>226</v>
+        <v>1511.5</v>
       </c>
       <c r="D49" t="n">
-        <v>229.4</v>
+        <v>1533</v>
       </c>
       <c r="E49" t="n">
-        <v>221.18</v>
+        <v>1475</v>
       </c>
       <c r="F49" t="n">
-        <v>224.38</v>
+        <v>1485.2</v>
       </c>
       <c r="G49" t="n">
-        <v>14379534</v>
+        <v>2475472</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>217.24</v>
+        <v>1484.7</v>
       </c>
       <c r="D50" t="n">
-        <v>219.7</v>
+        <v>1499</v>
       </c>
       <c r="E50" t="n">
-        <v>213.17</v>
+        <v>1480.3</v>
       </c>
       <c r="F50" t="n">
-        <v>213.17</v>
+        <v>1498.9</v>
       </c>
       <c r="G50" t="n">
-        <v>14642282</v>
+        <v>507345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7626,25 +8128,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>208.25</v>
+        <v>211.95</v>
       </c>
       <c r="D51" t="n">
-        <v>213.7</v>
+        <v>214.55</v>
       </c>
       <c r="E51" t="n">
-        <v>203.16</v>
+        <v>206.1</v>
       </c>
       <c r="F51" t="n">
-        <v>208.03</v>
+        <v>212.78</v>
       </c>
       <c r="G51" t="n">
-        <v>18348510</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7653,25 +8155,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="D52" t="n">
-        <v>218.43</v>
+        <v>223.41</v>
       </c>
       <c r="E52" t="n">
-        <v>209</v>
+        <v>214.3</v>
       </c>
       <c r="F52" t="n">
-        <v>217.97</v>
+        <v>223.08</v>
       </c>
       <c r="G52" t="n">
-        <v>20144780</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7680,25 +8182,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D53" t="n">
-        <v>228</v>
+        <v>229.4</v>
       </c>
       <c r="E53" t="n">
-        <v>214.11</v>
+        <v>221.18</v>
       </c>
       <c r="F53" t="n">
-        <v>217.9</v>
+        <v>224.38</v>
       </c>
       <c r="G53" t="n">
-        <v>55935312</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7707,25 +8209,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>221.96</v>
+        <v>217.24</v>
       </c>
       <c r="D54" t="n">
-        <v>222.4</v>
+        <v>219.7</v>
       </c>
       <c r="E54" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="F54" t="n">
-        <v>207.01</v>
+        <v>213.17</v>
       </c>
       <c r="G54" t="n">
-        <v>29190459</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7734,25 +8236,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>202</v>
+        <v>208.25</v>
       </c>
       <c r="D55" t="n">
-        <v>204.78</v>
+        <v>213.7</v>
       </c>
       <c r="E55" t="n">
-        <v>196.66</v>
+        <v>203.16</v>
       </c>
       <c r="F55" t="n">
-        <v>196.85</v>
+        <v>208.03</v>
       </c>
       <c r="G55" t="n">
-        <v>31552378</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7761,25 +8263,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D56" t="n">
-        <v>200.9</v>
+        <v>218.43</v>
       </c>
       <c r="E56" t="n">
-        <v>191.1</v>
+        <v>209</v>
       </c>
       <c r="F56" t="n">
-        <v>192.54</v>
+        <v>217.97</v>
       </c>
       <c r="G56" t="n">
-        <v>26152896</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7788,25 +8290,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D57" t="n">
-        <v>196.9</v>
+        <v>228</v>
       </c>
       <c r="E57" t="n">
-        <v>182.92</v>
+        <v>214.11</v>
       </c>
       <c r="F57" t="n">
-        <v>188.39</v>
+        <v>217.9</v>
       </c>
       <c r="G57" t="n">
-        <v>42541118</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7815,25 +8317,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>189</v>
+        <v>221.96</v>
       </c>
       <c r="D58" t="n">
-        <v>195.5</v>
+        <v>222.4</v>
       </c>
       <c r="E58" t="n">
-        <v>181.05</v>
+        <v>207.01</v>
       </c>
       <c r="F58" t="n">
-        <v>193.56</v>
+        <v>207.01</v>
       </c>
       <c r="G58" t="n">
-        <v>40104195</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7842,25 +8344,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D59" t="n">
-        <v>195.53</v>
+        <v>204.78</v>
       </c>
       <c r="E59" t="n">
-        <v>183.9</v>
+        <v>196.66</v>
       </c>
       <c r="F59" t="n">
-        <v>184.69</v>
+        <v>196.85</v>
       </c>
       <c r="G59" t="n">
-        <v>21043194</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7869,25 +8371,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>193.92</v>
+        <v>200</v>
       </c>
       <c r="D60" t="n">
-        <v>193.92</v>
+        <v>200.9</v>
       </c>
       <c r="E60" t="n">
-        <v>191.01</v>
+        <v>191.1</v>
       </c>
       <c r="F60" t="n">
-        <v>193.92</v>
+        <v>192.54</v>
       </c>
       <c r="G60" t="n">
-        <v>33053426</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7896,25 +8398,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>196.95</v>
+        <v>187</v>
       </c>
       <c r="D61" t="n">
-        <v>203.61</v>
+        <v>196.9</v>
       </c>
       <c r="E61" t="n">
-        <v>195.7</v>
+        <v>182.92</v>
       </c>
       <c r="F61" t="n">
-        <v>202.52</v>
+        <v>188.39</v>
       </c>
       <c r="G61" t="n">
-        <v>39140552</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7923,25 +8425,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>202.4</v>
+        <v>189</v>
       </c>
       <c r="D62" t="n">
-        <v>207</v>
+        <v>195.5</v>
       </c>
       <c r="E62" t="n">
-        <v>200.22</v>
+        <v>181.05</v>
       </c>
       <c r="F62" t="n">
-        <v>202.78</v>
+        <v>193.56</v>
       </c>
       <c r="G62" t="n">
-        <v>19636718</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7950,25 +8452,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>205.8</v>
+        <v>193</v>
       </c>
       <c r="D63" t="n">
-        <v>212.91</v>
+        <v>195.53</v>
       </c>
       <c r="E63" t="n">
-        <v>205.03</v>
+        <v>183.9</v>
       </c>
       <c r="F63" t="n">
-        <v>212.23</v>
+        <v>184.69</v>
       </c>
       <c r="G63" t="n">
-        <v>37479685</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7977,25 +8479,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>212.4</v>
+        <v>193.92</v>
       </c>
       <c r="D64" t="n">
-        <v>213.45</v>
+        <v>193.92</v>
       </c>
       <c r="E64" t="n">
-        <v>203</v>
+        <v>191.01</v>
       </c>
       <c r="F64" t="n">
-        <v>203.67</v>
+        <v>193.92</v>
       </c>
       <c r="G64" t="n">
-        <v>19195935</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8004,25 +8506,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>203.98</v>
+        <v>196.95</v>
       </c>
       <c r="D65" t="n">
-        <v>211.52</v>
+        <v>203.61</v>
       </c>
       <c r="E65" t="n">
-        <v>201</v>
+        <v>195.7</v>
       </c>
       <c r="F65" t="n">
-        <v>207.98</v>
+        <v>202.52</v>
       </c>
       <c r="G65" t="n">
-        <v>19489977</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8031,25 +8533,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>209</v>
+        <v>202.4</v>
       </c>
       <c r="D66" t="n">
-        <v>216.6</v>
+        <v>207</v>
       </c>
       <c r="E66" t="n">
-        <v>207.83</v>
+        <v>200.22</v>
       </c>
       <c r="F66" t="n">
-        <v>212.97</v>
+        <v>202.78</v>
       </c>
       <c r="G66" t="n">
-        <v>19215795</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8058,25 +8560,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>214</v>
+        <v>205.8</v>
       </c>
       <c r="D67" t="n">
-        <v>215.8</v>
+        <v>212.91</v>
       </c>
       <c r="E67" t="n">
-        <v>209.25</v>
+        <v>205.03</v>
       </c>
       <c r="F67" t="n">
-        <v>214.24</v>
+        <v>212.23</v>
       </c>
       <c r="G67" t="n">
-        <v>15006611</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8085,25 +8587,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>215.4</v>
+        <v>212.4</v>
       </c>
       <c r="D68" t="n">
-        <v>223.61</v>
+        <v>213.45</v>
       </c>
       <c r="E68" t="n">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F68" t="n">
-        <v>221.52</v>
+        <v>203.67</v>
       </c>
       <c r="G68" t="n">
-        <v>28062533</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8112,25 +8614,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>223</v>
+        <v>203.98</v>
       </c>
       <c r="D69" t="n">
-        <v>230.95</v>
+        <v>211.52</v>
       </c>
       <c r="E69" t="n">
-        <v>222.62</v>
+        <v>201</v>
       </c>
       <c r="F69" t="n">
-        <v>227.36</v>
+        <v>207.98</v>
       </c>
       <c r="G69" t="n">
-        <v>23585794</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8139,187 +8641,187 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D70" t="n">
-        <v>230.7</v>
+        <v>216.6</v>
       </c>
       <c r="E70" t="n">
-        <v>226.3</v>
+        <v>207.83</v>
       </c>
       <c r="F70" t="n">
-        <v>229.01</v>
+        <v>212.97</v>
       </c>
       <c r="G70" t="n">
-        <v>6329222</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>481.25</v>
+        <v>214</v>
       </c>
       <c r="D71" t="n">
-        <v>489.85</v>
+        <v>215.8</v>
       </c>
       <c r="E71" t="n">
-        <v>477.5</v>
+        <v>209.25</v>
       </c>
       <c r="F71" t="n">
-        <v>480.25</v>
+        <v>214.24</v>
       </c>
       <c r="G71" t="n">
-        <v>2347659</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>485.2</v>
+        <v>215.4</v>
       </c>
       <c r="D72" t="n">
-        <v>499</v>
+        <v>223.61</v>
       </c>
       <c r="E72" t="n">
-        <v>482.55</v>
+        <v>215</v>
       </c>
       <c r="F72" t="n">
-        <v>491.6</v>
+        <v>221.52</v>
       </c>
       <c r="G72" t="n">
-        <v>7339280</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>495</v>
+        <v>223</v>
       </c>
       <c r="D73" t="n">
-        <v>498.5</v>
+        <v>230.95</v>
       </c>
       <c r="E73" t="n">
-        <v>491</v>
+        <v>222.62</v>
       </c>
       <c r="F73" t="n">
-        <v>495.05</v>
+        <v>227.36</v>
       </c>
       <c r="G73" t="n">
-        <v>2755226</v>
+        <v>23585794</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>495.05</v>
+        <v>228</v>
       </c>
       <c r="D74" t="n">
-        <v>504.3</v>
+        <v>230.7</v>
       </c>
       <c r="E74" t="n">
-        <v>490.05</v>
+        <v>220.7</v>
       </c>
       <c r="F74" t="n">
-        <v>492.35</v>
+        <v>223.11</v>
       </c>
       <c r="G74" t="n">
-        <v>4448305</v>
+        <v>16693107</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>496.2</v>
+        <v>223.9</v>
       </c>
       <c r="D75" t="n">
-        <v>539.6</v>
+        <v>225.95</v>
       </c>
       <c r="E75" t="n">
-        <v>495.1</v>
+        <v>217.85</v>
       </c>
       <c r="F75" t="n">
-        <v>533.8</v>
+        <v>219.5</v>
       </c>
       <c r="G75" t="n">
-        <v>22701332</v>
+        <v>9863534</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>542.45</v>
+        <v>218.01</v>
       </c>
       <c r="D76" t="n">
-        <v>551</v>
+        <v>228</v>
       </c>
       <c r="E76" t="n">
-        <v>525.55</v>
+        <v>218.01</v>
       </c>
       <c r="F76" t="n">
-        <v>545.95</v>
+        <v>227.48</v>
       </c>
       <c r="G76" t="n">
-        <v>19838083</v>
+        <v>4963249</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8328,25 +8830,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>543.75</v>
+        <v>481.25</v>
       </c>
       <c r="D77" t="n">
-        <v>548</v>
+        <v>489.85</v>
       </c>
       <c r="E77" t="n">
-        <v>532.1</v>
+        <v>477.5</v>
       </c>
       <c r="F77" t="n">
-        <v>536.1</v>
+        <v>480.25</v>
       </c>
       <c r="G77" t="n">
-        <v>9431736</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8355,25 +8857,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>537.95</v>
+        <v>485.2</v>
       </c>
       <c r="D78" t="n">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="E78" t="n">
-        <v>522</v>
+        <v>482.55</v>
       </c>
       <c r="F78" t="n">
-        <v>526.25</v>
+        <v>491.6</v>
       </c>
       <c r="G78" t="n">
-        <v>12427899</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8382,25 +8884,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="D79" t="n">
-        <v>538.8</v>
+        <v>498.5</v>
       </c>
       <c r="E79" t="n">
-        <v>527.7</v>
+        <v>491</v>
       </c>
       <c r="F79" t="n">
-        <v>533.3</v>
+        <v>495.05</v>
       </c>
       <c r="G79" t="n">
-        <v>5547022</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8409,25 +8911,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>530.85</v>
+        <v>495.05</v>
       </c>
       <c r="D80" t="n">
-        <v>569.9</v>
+        <v>504.3</v>
       </c>
       <c r="E80" t="n">
-        <v>529.6</v>
+        <v>490.05</v>
       </c>
       <c r="F80" t="n">
-        <v>547.7</v>
+        <v>492.35</v>
       </c>
       <c r="G80" t="n">
-        <v>36903374</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8436,25 +8938,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>549</v>
+        <v>496.2</v>
       </c>
       <c r="D81" t="n">
-        <v>570.5</v>
+        <v>539.6</v>
       </c>
       <c r="E81" t="n">
-        <v>542</v>
+        <v>495.1</v>
       </c>
       <c r="F81" t="n">
-        <v>544.45</v>
+        <v>533.8</v>
       </c>
       <c r="G81" t="n">
-        <v>14649216</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8463,241 +8965,241 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>546.5</v>
+        <v>542.45</v>
       </c>
       <c r="D82" t="n">
-        <v>546.7</v>
+        <v>551</v>
       </c>
       <c r="E82" t="n">
-        <v>515</v>
+        <v>525.55</v>
       </c>
       <c r="F82" t="n">
-        <v>516.55</v>
+        <v>545.95</v>
       </c>
       <c r="G82" t="n">
-        <v>4662594</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>13.05</v>
+        <v>543.75</v>
       </c>
       <c r="D83" t="n">
-        <v>13.18</v>
+        <v>548</v>
       </c>
       <c r="E83" t="n">
-        <v>12.85</v>
+        <v>532.1</v>
       </c>
       <c r="F83" t="n">
-        <v>12.87</v>
+        <v>536.1</v>
       </c>
       <c r="G83" t="n">
-        <v>230386335</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12.98</v>
+        <v>537.95</v>
       </c>
       <c r="D84" t="n">
-        <v>13.08</v>
+        <v>552</v>
       </c>
       <c r="E84" t="n">
-        <v>12.76</v>
+        <v>522</v>
       </c>
       <c r="F84" t="n">
-        <v>13.01</v>
+        <v>526.25</v>
       </c>
       <c r="G84" t="n">
-        <v>387269596</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13.01</v>
+        <v>531</v>
       </c>
       <c r="D85" t="n">
-        <v>13.11</v>
+        <v>538.8</v>
       </c>
       <c r="E85" t="n">
-        <v>12.82</v>
+        <v>527.7</v>
       </c>
       <c r="F85" t="n">
-        <v>12.86</v>
+        <v>533.3</v>
       </c>
       <c r="G85" t="n">
-        <v>235409728</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12.89</v>
+        <v>530.85</v>
       </c>
       <c r="D86" t="n">
-        <v>13.05</v>
+        <v>569.9</v>
       </c>
       <c r="E86" t="n">
-        <v>12.73</v>
+        <v>529.6</v>
       </c>
       <c r="F86" t="n">
-        <v>12.9</v>
+        <v>547.7</v>
       </c>
       <c r="G86" t="n">
-        <v>308781891</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12.91</v>
+        <v>549</v>
       </c>
       <c r="D87" t="n">
-        <v>13.04</v>
+        <v>570.5</v>
       </c>
       <c r="E87" t="n">
-        <v>12.77</v>
+        <v>542</v>
       </c>
       <c r="F87" t="n">
-        <v>12.8</v>
+        <v>544.45</v>
       </c>
       <c r="G87" t="n">
-        <v>204366752</v>
+        <v>14649216</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12.89</v>
+        <v>546.5</v>
       </c>
       <c r="D88" t="n">
-        <v>12.9</v>
+        <v>546.7</v>
       </c>
       <c r="E88" t="n">
-        <v>12.63</v>
+        <v>515</v>
       </c>
       <c r="F88" t="n">
-        <v>12.63</v>
+        <v>529.05</v>
       </c>
       <c r="G88" t="n">
-        <v>204537429</v>
+        <v>8696054</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12.64</v>
+        <v>535</v>
       </c>
       <c r="D89" t="n">
-        <v>12.88</v>
+        <v>574.9</v>
       </c>
       <c r="E89" t="n">
-        <v>12.6</v>
+        <v>534.1</v>
       </c>
       <c r="F89" t="n">
-        <v>12.73</v>
+        <v>572.65</v>
       </c>
       <c r="G89" t="n">
-        <v>205855564</v>
+        <v>29333771</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>12.92</v>
+        <v>568.6</v>
       </c>
       <c r="D90" t="n">
-        <v>13.07</v>
+        <v>574.8</v>
       </c>
       <c r="E90" t="n">
-        <v>12.77</v>
+        <v>560.05</v>
       </c>
       <c r="F90" t="n">
-        <v>12.92</v>
+        <v>560.95</v>
       </c>
       <c r="G90" t="n">
-        <v>413469644</v>
+        <v>3221002</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8706,25 +9208,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13.14</v>
+        <v>13.05</v>
       </c>
       <c r="D91" t="n">
-        <v>13.3</v>
+        <v>13.18</v>
       </c>
       <c r="E91" t="n">
-        <v>12.79</v>
+        <v>12.85</v>
       </c>
       <c r="F91" t="n">
-        <v>12.89</v>
+        <v>12.87</v>
       </c>
       <c r="G91" t="n">
-        <v>662095209</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8733,25 +9235,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12.93</v>
+        <v>12.98</v>
       </c>
       <c r="D92" t="n">
-        <v>13.69</v>
+        <v>13.08</v>
       </c>
       <c r="E92" t="n">
-        <v>12.83</v>
+        <v>12.76</v>
       </c>
       <c r="F92" t="n">
-        <v>13.5</v>
+        <v>13.01</v>
       </c>
       <c r="G92" t="n">
-        <v>772547405</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8760,25 +9262,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>13.67</v>
+        <v>13.01</v>
       </c>
       <c r="D93" t="n">
-        <v>13.88</v>
+        <v>13.11</v>
       </c>
       <c r="E93" t="n">
-        <v>13.46</v>
+        <v>12.82</v>
       </c>
       <c r="F93" t="n">
-        <v>13.51</v>
+        <v>12.86</v>
       </c>
       <c r="G93" t="n">
-        <v>547253456</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8787,295 +9289,295 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>13.53</v>
+        <v>12.89</v>
       </c>
       <c r="D94" t="n">
-        <v>14.14</v>
+        <v>13.05</v>
       </c>
       <c r="E94" t="n">
-        <v>13.49</v>
+        <v>12.73</v>
       </c>
       <c r="F94" t="n">
-        <v>13.99</v>
+        <v>12.9</v>
       </c>
       <c r="G94" t="n">
-        <v>374572510</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1554.3</v>
+        <v>12.91</v>
       </c>
       <c r="D95" t="n">
-        <v>1569</v>
+        <v>13.04</v>
       </c>
       <c r="E95" t="n">
-        <v>1551.3</v>
+        <v>12.77</v>
       </c>
       <c r="F95" t="n">
-        <v>1557.6</v>
+        <v>12.8</v>
       </c>
       <c r="G95" t="n">
-        <v>1001677</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1560.4</v>
+        <v>12.89</v>
       </c>
       <c r="D96" t="n">
-        <v>1561</v>
+        <v>12.9</v>
       </c>
       <c r="E96" t="n">
-        <v>1520.4</v>
+        <v>12.63</v>
       </c>
       <c r="F96" t="n">
-        <v>1529.8</v>
+        <v>12.63</v>
       </c>
       <c r="G96" t="n">
-        <v>1011017</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1534.9</v>
+        <v>12.64</v>
       </c>
       <c r="D97" t="n">
-        <v>1572.2</v>
+        <v>12.88</v>
       </c>
       <c r="E97" t="n">
-        <v>1527.2</v>
+        <v>12.6</v>
       </c>
       <c r="F97" t="n">
-        <v>1558.9</v>
+        <v>12.73</v>
       </c>
       <c r="G97" t="n">
-        <v>1235837</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1559.7</v>
+        <v>12.92</v>
       </c>
       <c r="D98" t="n">
-        <v>1600.1</v>
+        <v>13.07</v>
       </c>
       <c r="E98" t="n">
-        <v>1557</v>
+        <v>12.77</v>
       </c>
       <c r="F98" t="n">
-        <v>1593.2</v>
+        <v>12.92</v>
       </c>
       <c r="G98" t="n">
-        <v>1871739</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1591</v>
+        <v>13.14</v>
       </c>
       <c r="D99" t="n">
-        <v>1593.2</v>
+        <v>13.3</v>
       </c>
       <c r="E99" t="n">
-        <v>1566</v>
+        <v>12.79</v>
       </c>
       <c r="F99" t="n">
-        <v>1577.8</v>
+        <v>12.89</v>
       </c>
       <c r="G99" t="n">
-        <v>1183077</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1577.7</v>
+        <v>12.93</v>
       </c>
       <c r="D100" t="n">
-        <v>1586.1</v>
+        <v>13.69</v>
       </c>
       <c r="E100" t="n">
-        <v>1561.1</v>
+        <v>12.83</v>
       </c>
       <c r="F100" t="n">
-        <v>1568.3</v>
+        <v>13.5</v>
       </c>
       <c r="G100" t="n">
-        <v>1098268</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1560</v>
+        <v>13.67</v>
       </c>
       <c r="D101" t="n">
-        <v>1610</v>
+        <v>13.88</v>
       </c>
       <c r="E101" t="n">
-        <v>1554.9</v>
+        <v>13.46</v>
       </c>
       <c r="F101" t="n">
-        <v>1601.2</v>
+        <v>13.51</v>
       </c>
       <c r="G101" t="n">
-        <v>2647403</v>
+        <v>547253456</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1624.8</v>
+        <v>13.53</v>
       </c>
       <c r="D102" t="n">
-        <v>1734.5</v>
+        <v>14.19</v>
       </c>
       <c r="E102" t="n">
-        <v>1617.1</v>
+        <v>13.49</v>
       </c>
       <c r="F102" t="n">
-        <v>1713.4</v>
+        <v>14.11</v>
       </c>
       <c r="G102" t="n">
-        <v>7989771</v>
+        <v>778908986</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1713</v>
+        <v>14.11</v>
       </c>
       <c r="D103" t="n">
-        <v>1762</v>
+        <v>14.14</v>
       </c>
       <c r="E103" t="n">
-        <v>1707.7</v>
+        <v>13.66</v>
       </c>
       <c r="F103" t="n">
-        <v>1758.9</v>
+        <v>13.71</v>
       </c>
       <c r="G103" t="n">
-        <v>4407907</v>
+        <v>310430357</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1762</v>
+        <v>13.65</v>
       </c>
       <c r="D104" t="n">
-        <v>1797.9</v>
+        <v>13.8</v>
       </c>
       <c r="E104" t="n">
-        <v>1754.3</v>
+        <v>13.5</v>
       </c>
       <c r="F104" t="n">
-        <v>1781.3</v>
+        <v>13.76</v>
       </c>
       <c r="G104" t="n">
-        <v>3000811</v>
+        <v>256016664</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9084,25 +9586,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1785</v>
+        <v>1554.3</v>
       </c>
       <c r="D105" t="n">
-        <v>1798.9</v>
+        <v>1569</v>
       </c>
       <c r="E105" t="n">
-        <v>1773.3</v>
+        <v>1551.3</v>
       </c>
       <c r="F105" t="n">
-        <v>1781.3</v>
+        <v>1557.6</v>
       </c>
       <c r="G105" t="n">
-        <v>2402202</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9111,25 +9613,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1785</v>
+        <v>1560.4</v>
       </c>
       <c r="D106" t="n">
-        <v>1826.6</v>
+        <v>1561</v>
       </c>
       <c r="E106" t="n">
-        <v>1785</v>
+        <v>1520.4</v>
       </c>
       <c r="F106" t="n">
-        <v>1816.2</v>
+        <v>1529.8</v>
       </c>
       <c r="G106" t="n">
-        <v>2502579</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9138,25 +9640,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1821</v>
+        <v>1534.9</v>
       </c>
       <c r="D107" t="n">
-        <v>1838.3</v>
+        <v>1572.2</v>
       </c>
       <c r="E107" t="n">
-        <v>1789.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F107" t="n">
-        <v>1811.4</v>
+        <v>1558.9</v>
       </c>
       <c r="G107" t="n">
-        <v>1919384</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9165,25 +9667,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1811</v>
+        <v>1559.7</v>
       </c>
       <c r="D108" t="n">
-        <v>1850</v>
+        <v>1600.1</v>
       </c>
       <c r="E108" t="n">
-        <v>1806.1</v>
+        <v>1557</v>
       </c>
       <c r="F108" t="n">
-        <v>1850</v>
+        <v>1593.2</v>
       </c>
       <c r="G108" t="n">
-        <v>1405192</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9192,25 +9694,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1854</v>
+        <v>1591</v>
       </c>
       <c r="D109" t="n">
-        <v>1856.6</v>
+        <v>1593.2</v>
       </c>
       <c r="E109" t="n">
-        <v>1834.5</v>
+        <v>1566</v>
       </c>
       <c r="F109" t="n">
-        <v>1835</v>
+        <v>1577.8</v>
       </c>
       <c r="G109" t="n">
-        <v>2090998</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9219,25 +9721,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1843</v>
+        <v>1577.7</v>
       </c>
       <c r="D110" t="n">
-        <v>1854.9</v>
+        <v>1586.1</v>
       </c>
       <c r="E110" t="n">
-        <v>1830</v>
+        <v>1561.1</v>
       </c>
       <c r="F110" t="n">
-        <v>1830</v>
+        <v>1568.3</v>
       </c>
       <c r="G110" t="n">
-        <v>2037418</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9246,25 +9748,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1838</v>
+        <v>1560</v>
       </c>
       <c r="D111" t="n">
-        <v>1856</v>
+        <v>1610</v>
       </c>
       <c r="E111" t="n">
-        <v>1833.2</v>
+        <v>1554.9</v>
       </c>
       <c r="F111" t="n">
-        <v>1844.3</v>
+        <v>1601.2</v>
       </c>
       <c r="G111" t="n">
-        <v>1553067</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9273,25 +9775,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1845</v>
+        <v>1624.8</v>
       </c>
       <c r="D112" t="n">
-        <v>1870.8</v>
+        <v>1734.5</v>
       </c>
       <c r="E112" t="n">
-        <v>1832.8</v>
+        <v>1617.1</v>
       </c>
       <c r="F112" t="n">
-        <v>1854</v>
+        <v>1713.4</v>
       </c>
       <c r="G112" t="n">
-        <v>1386592</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9300,25 +9802,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1851</v>
+        <v>1713</v>
       </c>
       <c r="D113" t="n">
-        <v>1859</v>
+        <v>1762</v>
       </c>
       <c r="E113" t="n">
-        <v>1833.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F113" t="n">
-        <v>1858</v>
+        <v>1758.9</v>
       </c>
       <c r="G113" t="n">
-        <v>1514239</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9327,25 +9829,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1856.3</v>
+        <v>1762</v>
       </c>
       <c r="D114" t="n">
-        <v>1862.3</v>
+        <v>1797.9</v>
       </c>
       <c r="E114" t="n">
-        <v>1835</v>
+        <v>1754.3</v>
       </c>
       <c r="F114" t="n">
-        <v>1850</v>
+        <v>1781.3</v>
       </c>
       <c r="G114" t="n">
-        <v>1088545</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9354,25 +9856,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1850</v>
+        <v>1785</v>
       </c>
       <c r="D115" t="n">
-        <v>1850.1</v>
+        <v>1798.9</v>
       </c>
       <c r="E115" t="n">
-        <v>1820.6</v>
+        <v>1773.3</v>
       </c>
       <c r="F115" t="n">
-        <v>1835</v>
+        <v>1781.3</v>
       </c>
       <c r="G115" t="n">
-        <v>548100</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9381,349 +9883,349 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1849.9</v>
+        <v>1785</v>
       </c>
       <c r="D116" t="n">
-        <v>1853.2</v>
+        <v>1826.6</v>
       </c>
       <c r="E116" t="n">
-        <v>1824.6</v>
+        <v>1785</v>
       </c>
       <c r="F116" t="n">
-        <v>1825.4</v>
+        <v>1816.2</v>
       </c>
       <c r="G116" t="n">
-        <v>435709</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>344</v>
+        <v>1821</v>
       </c>
       <c r="D117" t="n">
-        <v>346.3</v>
+        <v>1838.3</v>
       </c>
       <c r="E117" t="n">
-        <v>341.25</v>
+        <v>1789.1</v>
       </c>
       <c r="F117" t="n">
-        <v>342.9</v>
+        <v>1811.4</v>
       </c>
       <c r="G117" t="n">
-        <v>4465145</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>344.2</v>
+        <v>1811</v>
       </c>
       <c r="D118" t="n">
-        <v>347.75</v>
+        <v>1850</v>
       </c>
       <c r="E118" t="n">
-        <v>339.95</v>
+        <v>1806.1</v>
       </c>
       <c r="F118" t="n">
-        <v>342.4</v>
+        <v>1850</v>
       </c>
       <c r="G118" t="n">
-        <v>3803051</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>346</v>
+        <v>1854</v>
       </c>
       <c r="D119" t="n">
-        <v>351</v>
+        <v>1856.6</v>
       </c>
       <c r="E119" t="n">
-        <v>343.65</v>
+        <v>1834.5</v>
       </c>
       <c r="F119" t="n">
-        <v>346</v>
+        <v>1835</v>
       </c>
       <c r="G119" t="n">
-        <v>5175178</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>341.8</v>
+        <v>1843</v>
       </c>
       <c r="D120" t="n">
-        <v>344.9</v>
+        <v>1854.9</v>
       </c>
       <c r="E120" t="n">
-        <v>339.65</v>
+        <v>1830</v>
       </c>
       <c r="F120" t="n">
-        <v>343.9</v>
+        <v>1830</v>
       </c>
       <c r="G120" t="n">
-        <v>2253982</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>345.1</v>
+        <v>1838</v>
       </c>
       <c r="D121" t="n">
-        <v>346.05</v>
+        <v>1856</v>
       </c>
       <c r="E121" t="n">
-        <v>338.35</v>
+        <v>1833.2</v>
       </c>
       <c r="F121" t="n">
-        <v>339.35</v>
+        <v>1844.3</v>
       </c>
       <c r="G121" t="n">
-        <v>3868006</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>339.4</v>
+        <v>1845</v>
       </c>
       <c r="D122" t="n">
-        <v>340.2</v>
+        <v>1870.8</v>
       </c>
       <c r="E122" t="n">
-        <v>333</v>
+        <v>1832.8</v>
       </c>
       <c r="F122" t="n">
-        <v>334.55</v>
+        <v>1854</v>
       </c>
       <c r="G122" t="n">
-        <v>3721274</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>335</v>
+        <v>1851</v>
       </c>
       <c r="D123" t="n">
-        <v>346.1</v>
+        <v>1859</v>
       </c>
       <c r="E123" t="n">
-        <v>332</v>
+        <v>1833.1</v>
       </c>
       <c r="F123" t="n">
-        <v>344.7</v>
+        <v>1858</v>
       </c>
       <c r="G123" t="n">
-        <v>5431501</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>345.5</v>
+        <v>1856.3</v>
       </c>
       <c r="D124" t="n">
-        <v>349.65</v>
+        <v>1862.3</v>
       </c>
       <c r="E124" t="n">
-        <v>342.6</v>
+        <v>1835</v>
       </c>
       <c r="F124" t="n">
-        <v>347.65</v>
+        <v>1850</v>
       </c>
       <c r="G124" t="n">
-        <v>6318472</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>352</v>
+        <v>1850</v>
       </c>
       <c r="D125" t="n">
-        <v>355.75</v>
+        <v>1851.7</v>
       </c>
       <c r="E125" t="n">
-        <v>347.65</v>
+        <v>1820.6</v>
       </c>
       <c r="F125" t="n">
-        <v>350.05</v>
+        <v>1851.7</v>
       </c>
       <c r="G125" t="n">
-        <v>7186013</v>
+        <v>1345856</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>357.95</v>
+        <v>1849.9</v>
       </c>
       <c r="D126" t="n">
-        <v>369</v>
+        <v>1853.2</v>
       </c>
       <c r="E126" t="n">
-        <v>353.5</v>
+        <v>1777.7</v>
       </c>
       <c r="F126" t="n">
-        <v>369</v>
+        <v>1787.3</v>
       </c>
       <c r="G126" t="n">
-        <v>12541474</v>
+        <v>1581352</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>373</v>
+        <v>1770</v>
       </c>
       <c r="D127" t="n">
-        <v>382.45</v>
+        <v>1824</v>
       </c>
       <c r="E127" t="n">
-        <v>367.15</v>
+        <v>1769.4</v>
       </c>
       <c r="F127" t="n">
-        <v>377</v>
+        <v>1809.7</v>
       </c>
       <c r="G127" t="n">
-        <v>15775994</v>
+        <v>1631767</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>381</v>
+        <v>1810</v>
       </c>
       <c r="D128" t="n">
-        <v>383.9</v>
+        <v>1815</v>
       </c>
       <c r="E128" t="n">
-        <v>375.15</v>
+        <v>1803.5</v>
       </c>
       <c r="F128" t="n">
-        <v>381</v>
+        <v>1807</v>
       </c>
       <c r="G128" t="n">
-        <v>8940938</v>
+        <v>161331</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9732,25 +10234,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="D129" t="n">
-        <v>385.05</v>
+        <v>346.3</v>
       </c>
       <c r="E129" t="n">
-        <v>376.5</v>
+        <v>341.25</v>
       </c>
       <c r="F129" t="n">
-        <v>381</v>
+        <v>342.9</v>
       </c>
       <c r="G129" t="n">
-        <v>6636333</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9759,25 +10261,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>382.5</v>
+        <v>344.2</v>
       </c>
       <c r="D130" t="n">
-        <v>382.85</v>
+        <v>347.75</v>
       </c>
       <c r="E130" t="n">
-        <v>377.15</v>
+        <v>339.95</v>
       </c>
       <c r="F130" t="n">
-        <v>381</v>
+        <v>342.4</v>
       </c>
       <c r="G130" t="n">
-        <v>4423953</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9786,25 +10288,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>381.7</v>
+        <v>346</v>
       </c>
       <c r="D131" t="n">
-        <v>387.7</v>
+        <v>351</v>
       </c>
       <c r="E131" t="n">
-        <v>381.1</v>
+        <v>343.65</v>
       </c>
       <c r="F131" t="n">
-        <v>382.7</v>
+        <v>346</v>
       </c>
       <c r="G131" t="n">
-        <v>5292453</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9813,25 +10315,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>387.15</v>
+        <v>341.8</v>
       </c>
       <c r="D132" t="n">
-        <v>393.7</v>
+        <v>344.9</v>
       </c>
       <c r="E132" t="n">
-        <v>384.5</v>
+        <v>339.65</v>
       </c>
       <c r="F132" t="n">
-        <v>388</v>
+        <v>343.9</v>
       </c>
       <c r="G132" t="n">
-        <v>8155315</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9840,25 +10342,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>398.5</v>
+        <v>345.1</v>
       </c>
       <c r="D133" t="n">
-        <v>422.2</v>
+        <v>346.05</v>
       </c>
       <c r="E133" t="n">
-        <v>398.5</v>
+        <v>338.35</v>
       </c>
       <c r="F133" t="n">
-        <v>420</v>
+        <v>339.35</v>
       </c>
       <c r="G133" t="n">
-        <v>34388331</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9867,25 +10369,25 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>410.5</v>
+        <v>339.4</v>
       </c>
       <c r="D134" t="n">
-        <v>413.65</v>
+        <v>340.2</v>
       </c>
       <c r="E134" t="n">
-        <v>400</v>
+        <v>333</v>
       </c>
       <c r="F134" t="n">
-        <v>400.5</v>
+        <v>334.55</v>
       </c>
       <c r="G134" t="n">
-        <v>9738984</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9894,403 +10396,403 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>378.6</v>
+        <v>335</v>
       </c>
       <c r="D135" t="n">
-        <v>384.95</v>
+        <v>346.1</v>
       </c>
       <c r="E135" t="n">
-        <v>377.15</v>
+        <v>332</v>
       </c>
       <c r="F135" t="n">
-        <v>377.75</v>
+        <v>344.7</v>
       </c>
       <c r="G135" t="n">
-        <v>9666647</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4389.8</v>
+        <v>345.5</v>
       </c>
       <c r="D136" t="n">
-        <v>4485</v>
+        <v>349.65</v>
       </c>
       <c r="E136" t="n">
-        <v>4361.9</v>
+        <v>342.6</v>
       </c>
       <c r="F136" t="n">
-        <v>4398.1</v>
+        <v>347.65</v>
       </c>
       <c r="G136" t="n">
-        <v>1347378</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4422</v>
+        <v>352</v>
       </c>
       <c r="D137" t="n">
-        <v>4495</v>
+        <v>355.75</v>
       </c>
       <c r="E137" t="n">
-        <v>4358</v>
+        <v>347.65</v>
       </c>
       <c r="F137" t="n">
-        <v>4371.4</v>
+        <v>350.05</v>
       </c>
       <c r="G137" t="n">
-        <v>902264</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4387.7</v>
+        <v>357.95</v>
       </c>
       <c r="D138" t="n">
-        <v>4404</v>
+        <v>369</v>
       </c>
       <c r="E138" t="n">
-        <v>4281.9</v>
+        <v>353.5</v>
       </c>
       <c r="F138" t="n">
-        <v>4304.2</v>
+        <v>369</v>
       </c>
       <c r="G138" t="n">
-        <v>463349</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4285</v>
+        <v>373</v>
       </c>
       <c r="D139" t="n">
-        <v>4317</v>
+        <v>382.45</v>
       </c>
       <c r="E139" t="n">
-        <v>4220</v>
+        <v>367.15</v>
       </c>
       <c r="F139" t="n">
-        <v>4244.3</v>
+        <v>377</v>
       </c>
       <c r="G139" t="n">
-        <v>398348</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4211</v>
+        <v>381</v>
       </c>
       <c r="D140" t="n">
-        <v>4220</v>
+        <v>383.9</v>
       </c>
       <c r="E140" t="n">
-        <v>4129.3</v>
+        <v>375.15</v>
       </c>
       <c r="F140" t="n">
-        <v>4178.1</v>
+        <v>381</v>
       </c>
       <c r="G140" t="n">
-        <v>470046</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4190</v>
+        <v>385</v>
       </c>
       <c r="D141" t="n">
-        <v>4324.4</v>
+        <v>385.05</v>
       </c>
       <c r="E141" t="n">
-        <v>4190</v>
+        <v>376.5</v>
       </c>
       <c r="F141" t="n">
-        <v>4257.3</v>
+        <v>381</v>
       </c>
       <c r="G141" t="n">
-        <v>633457</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4290</v>
+        <v>382.5</v>
       </c>
       <c r="D142" t="n">
-        <v>4383</v>
+        <v>382.85</v>
       </c>
       <c r="E142" t="n">
-        <v>4266</v>
+        <v>377.15</v>
       </c>
       <c r="F142" t="n">
-        <v>4288.7</v>
+        <v>381</v>
       </c>
       <c r="G142" t="n">
-        <v>835107</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4299</v>
+        <v>381.7</v>
       </c>
       <c r="D143" t="n">
-        <v>4340</v>
+        <v>387.7</v>
       </c>
       <c r="E143" t="n">
-        <v>4216</v>
+        <v>381.1</v>
       </c>
       <c r="F143" t="n">
-        <v>4243.8</v>
+        <v>382.7</v>
       </c>
       <c r="G143" t="n">
-        <v>422024</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4201.9</v>
+        <v>387.15</v>
       </c>
       <c r="D144" t="n">
-        <v>4222</v>
+        <v>393.7</v>
       </c>
       <c r="E144" t="n">
-        <v>4115</v>
+        <v>384.5</v>
       </c>
       <c r="F144" t="n">
-        <v>4156</v>
+        <v>388</v>
       </c>
       <c r="G144" t="n">
-        <v>378694</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4181.8</v>
+        <v>398.5</v>
       </c>
       <c r="D145" t="n">
-        <v>4385</v>
+        <v>422.2</v>
       </c>
       <c r="E145" t="n">
-        <v>4129.4</v>
+        <v>398.5</v>
       </c>
       <c r="F145" t="n">
-        <v>4362.2</v>
+        <v>420</v>
       </c>
       <c r="G145" t="n">
-        <v>992864</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>4380</v>
+        <v>410.5</v>
       </c>
       <c r="D146" t="n">
-        <v>4478.3</v>
+        <v>413.65</v>
       </c>
       <c r="E146" t="n">
-        <v>4280.1</v>
+        <v>400</v>
       </c>
       <c r="F146" t="n">
-        <v>4395.7</v>
+        <v>400.5</v>
       </c>
       <c r="G146" t="n">
-        <v>960643</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4497.2</v>
+        <v>378.6</v>
       </c>
       <c r="D147" t="n">
-        <v>4541.17</v>
+        <v>384.95</v>
       </c>
       <c r="E147" t="n">
-        <v>4319.31</v>
+        <v>375</v>
       </c>
       <c r="F147" t="n">
-        <v>4361.38</v>
+        <v>376</v>
       </c>
       <c r="G147" t="n">
-        <v>1616021</v>
+        <v>14954594</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>4338</v>
+        <v>377.9</v>
       </c>
       <c r="D148" t="n">
-        <v>4339.1</v>
+        <v>391.5</v>
       </c>
       <c r="E148" t="n">
-        <v>4172.9</v>
+        <v>376.5</v>
       </c>
       <c r="F148" t="n">
-        <v>4192.59</v>
+        <v>387.55</v>
       </c>
       <c r="G148" t="n">
-        <v>648341</v>
+        <v>9724992</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4297.32</v>
+        <v>386.8</v>
       </c>
       <c r="D149" t="n">
-        <v>4595.14</v>
+        <v>389.9</v>
       </c>
       <c r="E149" t="n">
-        <v>4249.35</v>
+        <v>385.8</v>
       </c>
       <c r="F149" t="n">
-        <v>4521.18</v>
+        <v>389.35</v>
       </c>
       <c r="G149" t="n">
-        <v>4510774</v>
+        <v>572397</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10299,25 +10801,25 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4557.56</v>
+        <v>4389.8</v>
       </c>
       <c r="D150" t="n">
-        <v>4737.05</v>
+        <v>4485</v>
       </c>
       <c r="E150" t="n">
-        <v>4537.17</v>
+        <v>4361.9</v>
       </c>
       <c r="F150" t="n">
-        <v>4583.14</v>
+        <v>4398.1</v>
       </c>
       <c r="G150" t="n">
-        <v>2334958</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10326,25 +10828,25 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4606.13</v>
+        <v>4422</v>
       </c>
       <c r="D151" t="n">
-        <v>4777.02</v>
+        <v>4495</v>
       </c>
       <c r="E151" t="n">
-        <v>4590.24</v>
+        <v>4358</v>
       </c>
       <c r="F151" t="n">
-        <v>4759.23</v>
+        <v>4371.4</v>
       </c>
       <c r="G151" t="n">
-        <v>1899271</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10353,25 +10855,25 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4817.7</v>
+        <v>4387.7</v>
       </c>
       <c r="D152" t="n">
-        <v>4929.93</v>
+        <v>4404</v>
       </c>
       <c r="E152" t="n">
-        <v>4722.06</v>
+        <v>4281.9</v>
       </c>
       <c r="F152" t="n">
-        <v>4890.75</v>
+        <v>4304.2</v>
       </c>
       <c r="G152" t="n">
-        <v>1924204</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10380,25 +10882,25 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4896.95</v>
+        <v>4285</v>
       </c>
       <c r="D153" t="n">
-        <v>4976.9</v>
+        <v>4317</v>
       </c>
       <c r="E153" t="n">
-        <v>4780.02</v>
+        <v>4220</v>
       </c>
       <c r="F153" t="n">
-        <v>4813</v>
+        <v>4244.3</v>
       </c>
       <c r="G153" t="n">
-        <v>1117424</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10407,25 +10909,25 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4790</v>
+        <v>4211</v>
       </c>
       <c r="D154" t="n">
-        <v>4968</v>
+        <v>4220</v>
       </c>
       <c r="E154" t="n">
-        <v>4780</v>
+        <v>4129.3</v>
       </c>
       <c r="F154" t="n">
-        <v>4939.2</v>
+        <v>4178.1</v>
       </c>
       <c r="G154" t="n">
-        <v>1296942</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10434,25 +10936,25 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4958</v>
+        <v>4190</v>
       </c>
       <c r="D155" t="n">
-        <v>5085</v>
+        <v>4324.4</v>
       </c>
       <c r="E155" t="n">
-        <v>4888.8</v>
+        <v>4190</v>
       </c>
       <c r="F155" t="n">
-        <v>4903</v>
+        <v>4257.3</v>
       </c>
       <c r="G155" t="n">
-        <v>1210476</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10461,25 +10963,25 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4903</v>
+        <v>4290</v>
       </c>
       <c r="D156" t="n">
-        <v>4940</v>
+        <v>4383</v>
       </c>
       <c r="E156" t="n">
-        <v>4792.5</v>
+        <v>4266</v>
       </c>
       <c r="F156" t="n">
-        <v>4859.8</v>
+        <v>4288.7</v>
       </c>
       <c r="G156" t="n">
-        <v>682980</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10488,25 +10990,25 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4866</v>
+        <v>4299</v>
       </c>
       <c r="D157" t="n">
-        <v>4907.9</v>
+        <v>4340</v>
       </c>
       <c r="E157" t="n">
-        <v>4753</v>
+        <v>4216</v>
       </c>
       <c r="F157" t="n">
-        <v>4837.4</v>
+        <v>4243.8</v>
       </c>
       <c r="G157" t="n">
-        <v>613049</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10515,25 +11017,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4860</v>
+        <v>4201.9</v>
       </c>
       <c r="D158" t="n">
-        <v>5200</v>
+        <v>4222</v>
       </c>
       <c r="E158" t="n">
-        <v>4860</v>
+        <v>4115</v>
       </c>
       <c r="F158" t="n">
-        <v>5181</v>
+        <v>4156</v>
       </c>
       <c r="G158" t="n">
-        <v>3457670</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10542,457 +11044,457 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5200</v>
+        <v>4181.8</v>
       </c>
       <c r="D159" t="n">
-        <v>5269</v>
+        <v>4385</v>
       </c>
       <c r="E159" t="n">
-        <v>5062</v>
+        <v>4129.4</v>
       </c>
       <c r="F159" t="n">
-        <v>5091.1</v>
+        <v>4362.2</v>
       </c>
       <c r="G159" t="n">
-        <v>959836</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1417</v>
+        <v>4380</v>
       </c>
       <c r="D160" t="n">
-        <v>1436</v>
+        <v>4478.3</v>
       </c>
       <c r="E160" t="n">
-        <v>1410.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F160" t="n">
-        <v>1423.9</v>
+        <v>4395.7</v>
       </c>
       <c r="G160" t="n">
-        <v>623969</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1428</v>
+        <v>4497.2</v>
       </c>
       <c r="D161" t="n">
-        <v>1428</v>
+        <v>4541.17</v>
       </c>
       <c r="E161" t="n">
-        <v>1351.5</v>
+        <v>4319.31</v>
       </c>
       <c r="F161" t="n">
-        <v>1359.1</v>
+        <v>4361.38</v>
       </c>
       <c r="G161" t="n">
-        <v>808190</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1349.8</v>
+        <v>4338</v>
       </c>
       <c r="D162" t="n">
-        <v>1357.8</v>
+        <v>4339.1</v>
       </c>
       <c r="E162" t="n">
-        <v>1330.1</v>
+        <v>4172.9</v>
       </c>
       <c r="F162" t="n">
-        <v>1340.8</v>
+        <v>4192.59</v>
       </c>
       <c r="G162" t="n">
-        <v>345535</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1340.8</v>
+        <v>4297.32</v>
       </c>
       <c r="D163" t="n">
-        <v>1387.7</v>
+        <v>4595.14</v>
       </c>
       <c r="E163" t="n">
-        <v>1316</v>
+        <v>4249.35</v>
       </c>
       <c r="F163" t="n">
-        <v>1374.4</v>
+        <v>4521.18</v>
       </c>
       <c r="G163" t="n">
-        <v>974660</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1372.9</v>
+        <v>4557.56</v>
       </c>
       <c r="D164" t="n">
-        <v>1390</v>
+        <v>4737.05</v>
       </c>
       <c r="E164" t="n">
-        <v>1355.1</v>
+        <v>4537.17</v>
       </c>
       <c r="F164" t="n">
-        <v>1363.5</v>
+        <v>4583.14</v>
       </c>
       <c r="G164" t="n">
-        <v>479123</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1363</v>
+        <v>4606.13</v>
       </c>
       <c r="D165" t="n">
-        <v>1392</v>
+        <v>4777.02</v>
       </c>
       <c r="E165" t="n">
-        <v>1355.1</v>
+        <v>4590.24</v>
       </c>
       <c r="F165" t="n">
-        <v>1380</v>
+        <v>4759.23</v>
       </c>
       <c r="G165" t="n">
-        <v>616767</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1360</v>
+        <v>4817.7</v>
       </c>
       <c r="D166" t="n">
-        <v>1368</v>
+        <v>4929.93</v>
       </c>
       <c r="E166" t="n">
-        <v>1272.1</v>
+        <v>4722.06</v>
       </c>
       <c r="F166" t="n">
-        <v>1288.3</v>
+        <v>4890.75</v>
       </c>
       <c r="G166" t="n">
-        <v>1098492</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1300</v>
+        <v>4896.95</v>
       </c>
       <c r="D167" t="n">
-        <v>1318.5</v>
+        <v>4976.9</v>
       </c>
       <c r="E167" t="n">
-        <v>1257</v>
+        <v>4780.02</v>
       </c>
       <c r="F167" t="n">
-        <v>1316.2</v>
+        <v>4813</v>
       </c>
       <c r="G167" t="n">
-        <v>1172726</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1317.7</v>
+        <v>4790</v>
       </c>
       <c r="D168" t="n">
-        <v>1319.8</v>
+        <v>4968</v>
       </c>
       <c r="E168" t="n">
-        <v>1270.5</v>
+        <v>4780</v>
       </c>
       <c r="F168" t="n">
-        <v>1306</v>
+        <v>4939.2</v>
       </c>
       <c r="G168" t="n">
-        <v>832973</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1319.9</v>
+        <v>4958</v>
       </c>
       <c r="D169" t="n">
-        <v>1355.4</v>
+        <v>5085</v>
       </c>
       <c r="E169" t="n">
-        <v>1308</v>
+        <v>4888.8</v>
       </c>
       <c r="F169" t="n">
-        <v>1343.4</v>
+        <v>4903</v>
       </c>
       <c r="G169" t="n">
-        <v>1287698</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1379</v>
+        <v>4903</v>
       </c>
       <c r="D170" t="n">
-        <v>1468</v>
+        <v>4940</v>
       </c>
       <c r="E170" t="n">
-        <v>1361</v>
+        <v>4792.5</v>
       </c>
       <c r="F170" t="n">
-        <v>1377.8</v>
+        <v>4859.8</v>
       </c>
       <c r="G170" t="n">
-        <v>9950655</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1380.5</v>
+        <v>4866</v>
       </c>
       <c r="D171" t="n">
-        <v>1403.3</v>
+        <v>4907.9</v>
       </c>
       <c r="E171" t="n">
-        <v>1363</v>
+        <v>4753</v>
       </c>
       <c r="F171" t="n">
-        <v>1366.8</v>
+        <v>4837.4</v>
       </c>
       <c r="G171" t="n">
-        <v>1567542</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1380</v>
+        <v>4860</v>
       </c>
       <c r="D172" t="n">
-        <v>1397.5</v>
+        <v>5200</v>
       </c>
       <c r="E172" t="n">
-        <v>1351.6</v>
+        <v>4860</v>
       </c>
       <c r="F172" t="n">
-        <v>1360.6</v>
+        <v>5181</v>
       </c>
       <c r="G172" t="n">
-        <v>1098353</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1360.6</v>
+        <v>5200</v>
       </c>
       <c r="D173" t="n">
-        <v>1428</v>
+        <v>5269</v>
       </c>
       <c r="E173" t="n">
-        <v>1354.5</v>
+        <v>4991.3</v>
       </c>
       <c r="F173" t="n">
-        <v>1421.6</v>
+        <v>5007.2</v>
       </c>
       <c r="G173" t="n">
-        <v>2055261</v>
+        <v>1695255</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1429.6</v>
+        <v>5022</v>
       </c>
       <c r="D174" t="n">
-        <v>1453</v>
+        <v>5225</v>
       </c>
       <c r="E174" t="n">
-        <v>1419</v>
+        <v>5008.3</v>
       </c>
       <c r="F174" t="n">
-        <v>1434.1</v>
+        <v>5212.4</v>
       </c>
       <c r="G174" t="n">
-        <v>1243415</v>
+        <v>1438746</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1434</v>
+        <v>5110</v>
       </c>
       <c r="D175" t="n">
-        <v>1460</v>
+        <v>5334</v>
       </c>
       <c r="E175" t="n">
-        <v>1405</v>
+        <v>5092.8</v>
       </c>
       <c r="F175" t="n">
-        <v>1418</v>
+        <v>5311</v>
       </c>
       <c r="G175" t="n">
-        <v>1123973</v>
+        <v>614537</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11001,25 +11503,25 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1413.9</v>
+        <v>1417</v>
       </c>
       <c r="D176" t="n">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E176" t="n">
-        <v>1407.5</v>
+        <v>1410.1</v>
       </c>
       <c r="F176" t="n">
-        <v>1424.7</v>
+        <v>1423.9</v>
       </c>
       <c r="G176" t="n">
-        <v>509551</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11028,25 +11530,25 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1434.1</v>
+        <v>1428</v>
       </c>
       <c r="D177" t="n">
-        <v>1522</v>
+        <v>1428</v>
       </c>
       <c r="E177" t="n">
-        <v>1427.5</v>
+        <v>1351.5</v>
       </c>
       <c r="F177" t="n">
-        <v>1516.4</v>
+        <v>1359.1</v>
       </c>
       <c r="G177" t="n">
-        <v>3863757</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11055,25 +11557,25 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1516.4</v>
+        <v>1349.8</v>
       </c>
       <c r="D178" t="n">
-        <v>1543</v>
+        <v>1357.8</v>
       </c>
       <c r="E178" t="n">
-        <v>1486.9</v>
+        <v>1330.1</v>
       </c>
       <c r="F178" t="n">
-        <v>1494.8</v>
+        <v>1340.8</v>
       </c>
       <c r="G178" t="n">
-        <v>1508375</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11082,25 +11584,25 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1494.8</v>
+        <v>1340.8</v>
       </c>
       <c r="D179" t="n">
-        <v>1514</v>
+        <v>1387.7</v>
       </c>
       <c r="E179" t="n">
-        <v>1465.1</v>
+        <v>1316</v>
       </c>
       <c r="F179" t="n">
-        <v>1473.3</v>
+        <v>1374.4</v>
       </c>
       <c r="G179" t="n">
-        <v>749197</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11109,46 +11611,532 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1481.9</v>
+        <v>1372.9</v>
       </c>
       <c r="D180" t="n">
-        <v>1500.5</v>
+        <v>1390</v>
       </c>
       <c r="E180" t="n">
-        <v>1451</v>
+        <v>1355.1</v>
       </c>
       <c r="F180" t="n">
-        <v>1467.7</v>
+        <v>1363.5</v>
       </c>
       <c r="G180" t="n">
-        <v>742118</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1355.1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G181" t="n">
+        <v>616767</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G184" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G186" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1428.14</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1451.52</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1417.55</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1458.51</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1403.56</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1416.55</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1412.46</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1406.06</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1423.24</v>
+      </c>
+      <c r="G192" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1520.44</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1426.04</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="G193" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1541.42</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1485.38</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1512.45</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1463.6</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1471.79</v>
+      </c>
+      <c r="G195" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1480.39</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1498.97</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1449.52</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1466.2</v>
+      </c>
+      <c r="G196" t="n">
+        <v>742118</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C181" t="n">
-        <v>1480</v>
-      </c>
-      <c r="D181" t="n">
-        <v>1506.7</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1461.5</v>
-      </c>
-      <c r="F181" t="n">
-        <v>1470.5</v>
-      </c>
-      <c r="G181" t="n">
-        <v>414426</v>
+      <c r="C197" t="n">
+        <v>1478.49</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1505.16</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1450.52</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="G197" t="n">
+        <v>811337</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1475.79</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1502.06</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1457.01</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1466.4</v>
+      </c>
+      <c r="G198" t="n">
+        <v>972670</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1489.9</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1516</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1488.9</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1515.3</v>
+      </c>
+      <c r="G199" t="n">
+        <v>799062</v>
       </c>
     </row>
   </sheetData>
@@ -11162,7 +12150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11362,6 +12350,21 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 18 Aug 2026 04:09</t>
+          <t>Generated 19 Aug 2026 04:08</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>0.42</v>
+        <v>0.28</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="3">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="D3" t="n">
-        <v>4.38</v>
+        <v>3.39</v>
       </c>
       <c r="E3" t="n">
-        <v>70.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
@@ -647,7 +647,7 @@
         <v>-2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
@@ -657,25 +657,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8.75</v>
+        <v>7.67</v>
       </c>
       <c r="D4" t="n">
-        <v>10.56</v>
+        <v>7.11</v>
       </c>
       <c r="E4" t="n">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="F4" t="n">
         <v>26.91</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.58</v>
+        <v>-5.41</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="5">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>22.09</v>
+        <v>16.7</v>
       </c>
       <c r="D5" t="n">
-        <v>20.82</v>
+        <v>19.43</v>
       </c>
       <c r="E5" t="n">
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>24.7</v>
+        <v>21.95</v>
       </c>
       <c r="G5" t="n">
-        <v>20.75</v>
+        <v>0.89</v>
       </c>
       <c r="H5" t="n">
-        <v>2.26</v>
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3155,6 +3155,192 @@
         <v>1</v>
       </c>
       <c r="P40" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" t="n">
+        <v>190.96</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>205.43</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="K41" t="n">
+        <v>246.37</v>
+      </c>
+      <c r="L41" t="n">
+        <v>266.84</v>
+      </c>
+      <c r="M41" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>99</v>
+      </c>
+      <c r="F42" t="n">
+        <v>112.42</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="K42" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="L42" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>98</v>
+      </c>
+      <c r="F43" t="n">
+        <v>106.41</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="I43" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="K43" t="n">
+        <v>606.35</v>
+      </c>
+      <c r="L43" t="n">
+        <v>648.55</v>
+      </c>
+      <c r="M43" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -3171,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4446,6 +4632,105 @@
       </c>
       <c r="I40" t="n">
         <v>1787.72</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>205.43</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="H41" t="n">
+        <v>246.37</v>
+      </c>
+      <c r="I41" t="n">
+        <v>266.84</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="I42" t="n">
+        <v>15.71</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="G43" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>606.35</v>
+      </c>
+      <c r="I43" t="n">
+        <v>648.55</v>
       </c>
     </row>
   </sheetData>
@@ -4459,7 +4744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4562,7 +4847,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4582,7 +4867,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>227.48</v>
+        <v>225.9</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4590,16 +4875,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.23</v>
+        <v>3.76</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>207.19</v>
+        <v>205.43</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -4615,7 +4900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4635,7 +4920,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.76</v>
+        <v>14.01</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -4643,16 +4928,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.29</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.89</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>12.95</v>
+        <v>13.16</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -4668,19 +4953,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4688,7 +4973,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1599.6</v>
+        <v>564.15</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4696,16 +4981,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.13</v>
+        <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.03</v>
+        <v>-1.07</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1505.54</v>
+        <v>521.95</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -4721,7 +5006,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4741,26 +5026,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>223.11</v>
+        <v>227.48</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.62</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.36</v>
+        <v>-4.16</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>209.18</v>
+        <v>207.19</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -4776,12 +5061,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4796,26 +5081,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1616</v>
+        <v>14.12</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.66</v>
+        <v>-0.78</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.54</v>
+        <v>-4.39</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1508.29</v>
+        <v>12.95</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -4831,19 +5116,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4851,26 +5136,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14.11</v>
+        <v>1599.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.83</v>
+        <v>-2.91</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.39</v>
+        <v>-3.22</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>13.18</v>
+        <v>1505.54</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -4886,7 +5171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4906,26 +5191,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>227.36</v>
+        <v>223.11</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.87</v>
+        <v>-1.62</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>5.06</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.18</v>
+        <v>-2.36</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>209.53</v>
+        <v>209.18</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -4941,12 +5226,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4961,26 +5246,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13.51</v>
+        <v>1616</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>-1.66</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>5.03</v>
+        <v>0.74</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.37</v>
+        <v>-4.2</v>
       </c>
       <c r="N9" t="n">
         <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>13.02</v>
+        <v>1508.29</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -4996,19 +5281,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5016,26 +5301,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1583</v>
+        <v>14.11</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>-2.83</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>3.49</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8</v>
+        <v>-4.39</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1491.87</v>
+        <v>13.18</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -5051,7 +5336,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5071,26 +5356,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>221.52</v>
+        <v>227.36</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>-1.87</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.94</v>
+        <v>-4.18</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -5106,7 +5391,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5126,26 +5411,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>5.11</v>
+        <v>5.92</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.96</v>
+        <v>-0.37</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -5161,12 +5446,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5181,29 +5466,29 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>547.7</v>
+        <v>1583</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.59</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>4.97</v>
+        <v>3.49</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.97</v>
+        <v>-2.2</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -5211,14 +5496,12 @@
       <c r="R13" t="b">
         <v>0</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5238,28 +5521,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="H14" t="n">
-        <v>6.18</v>
+        <v>1.98</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>7.8</v>
+        <v>5.81</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -5275,12 +5558,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5295,28 +5578,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>9.279999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>9.76</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -5332,12 +5615,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5352,31 +5635,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.42</v>
+        <v>-0.59</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.38</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>3.08</v>
+        <v>5.29</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.19</v>
+        <v>-5.97</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -5384,12 +5667,14 @@
       <c r="R16" t="b">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5409,28 +5694,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>7.27</v>
+        <v>6.18</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>11.04</v>
+        <v>9.41</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -5446,19 +5731,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5466,34 +5751,34 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.86</v>
+        <v>10.18</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>2.57</v>
+        <v>11.04</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.67</v>
+        <v>-2.2</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -5503,19 +5788,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -5523,44 +5808,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.31</v>
+        <v>-1.38</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.57</v>
+        <v>-4.56</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
         <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5580,28 +5867,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>11.63</v>
+        <v>7.27</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>13.39</v>
+        <v>12.7</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N20" t="n">
         <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -5617,7 +5904,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5637,28 +5924,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.28</v>
+        <v>-0.86</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.07</v>
+        <v>-5.03</v>
       </c>
       <c r="N21" t="n">
         <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -5674,7 +5961,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5697,10 +5984,10 @@
         <v>381</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H22" t="n">
-        <v>5.12</v>
+        <v>-1.31</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -5715,7 +6002,7 @@
         <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -5724,14 +6011,14 @@
         <v>1</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5751,34 +6038,34 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>4.38</v>
+        <v>11.63</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>8.82</v>
+        <v>15.09</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N23" t="n">
         <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -5788,12 +6075,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5808,34 +6095,34 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.09</v>
+        <v>-2.28</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>9.06</v>
+        <v>3.21</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.45</v>
+        <v>-4.44</v>
       </c>
       <c r="N24" t="n">
         <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
       </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -5845,12 +6132,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5865,44 +6152,44 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.62</v>
+        <v>5.12</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.37</v>
+        <v>-1.57</v>
       </c>
       <c r="N25" t="n">
         <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5922,30 +6209,30 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G26" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H26" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I26" t="n">
-        <v>12.18</v>
+        <v>6.44</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>13.89</v>
+        <v>10.45</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -5961,7 +6248,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5973,7 +6260,7 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5981,30 +6268,30 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G27" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H27" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>11.59</v>
+        <v>5.31</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>12.08</v>
+        <v>10.34</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -6020,12 +6307,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6040,36 +6327,36 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G28" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I28" t="n">
-        <v>3.28</v>
+        <v>-5.41</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.61</v>
+        <v>-5.72</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -6079,19 +6366,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6099,30 +6386,30 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G29" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H29" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I29" t="n">
-        <v>13.73</v>
+        <v>12.18</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>16.38</v>
+        <v>15.59</v>
       </c>
       <c r="M29" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
       <c r="O29" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -6131,26 +6418,26 @@
         <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6158,36 +6445,36 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.52</v>
+        <v>12.51</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>1.76</v>
+        <v>13.39</v>
       </c>
       <c r="M30" t="n">
-        <v>-4.66</v>
+        <v>-3.55</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
       </c>
       <c r="Q30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
@@ -6197,19 +6484,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -6217,30 +6504,30 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G31" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H31" t="n">
-        <v>11.34</v>
+        <v>2.92</v>
       </c>
       <c r="I31" t="n">
-        <v>7.78</v>
+        <v>2.92</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>13.29</v>
+        <v>11.99</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
@@ -6256,12 +6543,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -6276,46 +6563,46 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H32" t="n">
-        <v>2.81</v>
+        <v>6.98</v>
       </c>
       <c r="I32" t="n">
-        <v>6.42</v>
+        <v>13.73</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>11.88</v>
+        <v>17.74</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
       </c>
       <c r="Q32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6335,30 +6622,30 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-4.58</v>
+        <v>-3.52</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M33" t="n">
-        <v>-5.35</v>
+        <v>-6</v>
       </c>
       <c r="N33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -6374,19 +6661,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6394,36 +6681,36 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G34" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H34" t="n">
-        <v>2.73</v>
+        <v>11.34</v>
       </c>
       <c r="I34" t="n">
-        <v>3.95</v>
+        <v>7.78</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>5.02</v>
+        <v>13.29</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O34" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
       </c>
       <c r="Q34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
@@ -6433,12 +6720,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -6453,50 +6740,58 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H35" t="n">
-        <v>9.65</v>
+        <v>2.81</v>
       </c>
       <c r="I35" t="n">
-        <v>14.45</v>
+        <v>6.42</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>19.32</v>
+        <v>11.88</v>
       </c>
       <c r="M35" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N35" t="n">
         <v>15</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
       <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -6504,38 +6799,48 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G36" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H36" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I36" t="n">
-        <v>10.91</v>
+        <v>-4.58</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>22.3</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
-        <v>-4.32</v>
+        <v>-6.68</v>
       </c>
       <c r="N36" t="n">
         <v>15</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6547,7 +6852,7 @@
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6558,13 +6863,13 @@
         <v>1781.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H37" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I37" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -6572,33 +6877,41 @@
         <v>5.02</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.52</v>
+        <v>-0.67</v>
       </c>
       <c r="N37" t="n">
         <v>15</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
       <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -6606,26 +6919,26 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G38" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H38" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I38" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J38" t="n">
-        <v>24.7</v>
+        <v>16.71</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>31.45</v>
+        <v>21.1</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N38" t="n">
         <v>16</v>
@@ -6639,19 +6952,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -6659,26 +6972,26 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G39" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H39" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I39" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J39" t="n">
-        <v>20.75</v>
+        <v>18.1</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>22.59</v>
+        <v>23.73</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N39" t="n">
         <v>16</v>
@@ -6692,19 +7005,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -6712,26 +7025,26 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I40" t="n">
-        <v>10.56</v>
+        <v>3.86</v>
       </c>
       <c r="J40" t="n">
-        <v>20.82</v>
+        <v>0.89</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>21.35</v>
+        <v>5.02</v>
       </c>
       <c r="M40" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N40" t="n">
         <v>16</v>
@@ -6741,6 +7054,165 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I41" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J41" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N41" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>96</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J42" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>17</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J43" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N43" t="n">
+        <v>17</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6753,7 +7225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7417,34 +7889,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1188.4</v>
+        <v>1604.8</v>
       </c>
       <c r="D25" t="n">
-        <v>1207.9</v>
+        <v>1604.8</v>
       </c>
       <c r="E25" t="n">
-        <v>1158</v>
+        <v>1548.1</v>
       </c>
       <c r="F25" t="n">
-        <v>1201.8</v>
+        <v>1553.1</v>
       </c>
       <c r="G25" t="n">
-        <v>3482939</v>
+        <v>694969</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7453,25 +7925,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D26" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F26" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G26" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7480,25 +7952,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D27" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F27" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G27" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7507,25 +7979,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D28" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E28" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F28" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G28" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7534,25 +8006,25 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F29" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D29" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G29" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7561,25 +8033,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D30" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E30" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F30" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G30" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7588,25 +8060,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D31" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E31" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F31" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G31" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7615,25 +8087,25 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F32" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D32" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G32" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7642,25 +8114,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D33" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F33" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G33" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7669,25 +8141,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D34" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E34" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G34" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7696,25 +8168,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D35" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E35" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G35" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7723,25 +8195,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D36" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E36" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G36" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7750,25 +8222,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D37" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E37" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F37" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G37" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7777,25 +8249,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D38" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E38" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G38" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7804,25 +8276,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D39" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E39" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F39" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G39" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7831,25 +8303,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D40" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E40" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F40" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G40" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7858,25 +8330,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D41" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E41" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G41" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7885,25 +8357,25 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F42" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D42" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G42" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7912,25 +8384,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D43" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E43" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F43" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G43" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7939,25 +8411,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D44" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E44" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F44" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G44" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7966,25 +8438,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D45" t="n">
-        <v>1534.8</v>
+        <v>1520</v>
       </c>
       <c r="E45" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F45" t="n">
-        <v>1525.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G45" t="n">
-        <v>4867021</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7993,25 +8465,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1531.7</v>
+        <v>1472.4</v>
       </c>
       <c r="D46" t="n">
-        <v>1580</v>
+        <v>1534.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1511.1</v>
+        <v>1472</v>
       </c>
       <c r="F46" t="n">
-        <v>1569.4</v>
+        <v>1525.4</v>
       </c>
       <c r="G46" t="n">
-        <v>4521175</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8020,25 +8492,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1575</v>
+        <v>1531.7</v>
       </c>
       <c r="D47" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="E47" t="n">
-        <v>1500.1</v>
+        <v>1511.1</v>
       </c>
       <c r="F47" t="n">
-        <v>1526.5</v>
+        <v>1569.4</v>
       </c>
       <c r="G47" t="n">
-        <v>4013245</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8047,25 +8519,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1530</v>
+        <v>1575</v>
       </c>
       <c r="D48" t="n">
-        <v>1541</v>
+        <v>1575</v>
       </c>
       <c r="E48" t="n">
-        <v>1501.9</v>
+        <v>1500.1</v>
       </c>
       <c r="F48" t="n">
-        <v>1511.5</v>
+        <v>1526.5</v>
       </c>
       <c r="G48" t="n">
-        <v>2250949</v>
+        <v>4013245</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8074,25 +8546,25 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>1530</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1541</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1501.9</v>
+      </c>
+      <c r="F49" t="n">
         <v>1511.5</v>
       </c>
-      <c r="D49" t="n">
-        <v>1533</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1475</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1485.2</v>
-      </c>
       <c r="G49" t="n">
-        <v>2475472</v>
+        <v>2250949</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8101,79 +8573,79 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1484.7</v>
+        <v>1511.5</v>
       </c>
       <c r="D50" t="n">
-        <v>1499</v>
+        <v>1533</v>
       </c>
       <c r="E50" t="n">
-        <v>1480.3</v>
+        <v>1475</v>
       </c>
       <c r="F50" t="n">
-        <v>1498.9</v>
+        <v>1485.2</v>
       </c>
       <c r="G50" t="n">
-        <v>507345</v>
+        <v>2475472</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>211.95</v>
+        <v>1484.7</v>
       </c>
       <c r="D51" t="n">
-        <v>214.55</v>
+        <v>1504</v>
       </c>
       <c r="E51" t="n">
-        <v>206.1</v>
+        <v>1455</v>
       </c>
       <c r="F51" t="n">
-        <v>212.78</v>
+        <v>1465.8</v>
       </c>
       <c r="G51" t="n">
-        <v>12863408</v>
+        <v>2760706</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>214.3</v>
+        <v>1468.1</v>
       </c>
       <c r="D52" t="n">
-        <v>223.41</v>
+        <v>1471.8</v>
       </c>
       <c r="E52" t="n">
-        <v>214.3</v>
+        <v>1451</v>
       </c>
       <c r="F52" t="n">
-        <v>223.08</v>
+        <v>1459.4</v>
       </c>
       <c r="G52" t="n">
-        <v>32151413</v>
+        <v>315565</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8182,25 +8654,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>226</v>
+        <v>211.95</v>
       </c>
       <c r="D53" t="n">
-        <v>229.4</v>
+        <v>214.55</v>
       </c>
       <c r="E53" t="n">
-        <v>221.18</v>
+        <v>206.1</v>
       </c>
       <c r="F53" t="n">
-        <v>224.38</v>
+        <v>212.78</v>
       </c>
       <c r="G53" t="n">
-        <v>14379534</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8209,25 +8681,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>217.24</v>
+        <v>214.3</v>
       </c>
       <c r="D54" t="n">
-        <v>219.7</v>
+        <v>223.41</v>
       </c>
       <c r="E54" t="n">
-        <v>213.17</v>
+        <v>214.3</v>
       </c>
       <c r="F54" t="n">
-        <v>213.17</v>
+        <v>223.08</v>
       </c>
       <c r="G54" t="n">
-        <v>14642282</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8236,25 +8708,25 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>208.25</v>
+        <v>226</v>
       </c>
       <c r="D55" t="n">
-        <v>213.7</v>
+        <v>229.4</v>
       </c>
       <c r="E55" t="n">
-        <v>203.16</v>
+        <v>221.18</v>
       </c>
       <c r="F55" t="n">
-        <v>208.03</v>
+        <v>224.38</v>
       </c>
       <c r="G55" t="n">
-        <v>18348510</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8263,25 +8735,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>209</v>
+        <v>217.24</v>
       </c>
       <c r="D56" t="n">
-        <v>218.43</v>
+        <v>219.7</v>
       </c>
       <c r="E56" t="n">
-        <v>209</v>
+        <v>213.17</v>
       </c>
       <c r="F56" t="n">
-        <v>217.97</v>
+        <v>213.17</v>
       </c>
       <c r="G56" t="n">
-        <v>20144780</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8290,25 +8762,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>222</v>
+        <v>208.25</v>
       </c>
       <c r="D57" t="n">
-        <v>228</v>
+        <v>213.7</v>
       </c>
       <c r="E57" t="n">
-        <v>214.11</v>
+        <v>203.16</v>
       </c>
       <c r="F57" t="n">
-        <v>217.9</v>
+        <v>208.03</v>
       </c>
       <c r="G57" t="n">
-        <v>55935312</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8317,25 +8789,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>221.96</v>
+        <v>209</v>
       </c>
       <c r="D58" t="n">
-        <v>222.4</v>
+        <v>218.43</v>
       </c>
       <c r="E58" t="n">
-        <v>207.01</v>
+        <v>209</v>
       </c>
       <c r="F58" t="n">
-        <v>207.01</v>
+        <v>217.97</v>
       </c>
       <c r="G58" t="n">
-        <v>29190459</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8344,25 +8816,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D59" t="n">
-        <v>204.78</v>
+        <v>228</v>
       </c>
       <c r="E59" t="n">
-        <v>196.66</v>
+        <v>214.11</v>
       </c>
       <c r="F59" t="n">
-        <v>196.85</v>
+        <v>217.9</v>
       </c>
       <c r="G59" t="n">
-        <v>31552378</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8371,25 +8843,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>200</v>
+        <v>221.96</v>
       </c>
       <c r="D60" t="n">
-        <v>200.9</v>
+        <v>222.4</v>
       </c>
       <c r="E60" t="n">
-        <v>191.1</v>
+        <v>207.01</v>
       </c>
       <c r="F60" t="n">
-        <v>192.54</v>
+        <v>207.01</v>
       </c>
       <c r="G60" t="n">
-        <v>26152896</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8398,25 +8870,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D61" t="n">
-        <v>196.9</v>
+        <v>204.78</v>
       </c>
       <c r="E61" t="n">
-        <v>182.92</v>
+        <v>196.66</v>
       </c>
       <c r="F61" t="n">
-        <v>188.39</v>
+        <v>196.85</v>
       </c>
       <c r="G61" t="n">
-        <v>42541118</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8425,25 +8897,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D62" t="n">
-        <v>195.5</v>
+        <v>200.9</v>
       </c>
       <c r="E62" t="n">
-        <v>181.05</v>
+        <v>191.1</v>
       </c>
       <c r="F62" t="n">
-        <v>193.56</v>
+        <v>192.54</v>
       </c>
       <c r="G62" t="n">
-        <v>40104195</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8452,25 +8924,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D63" t="n">
-        <v>195.53</v>
+        <v>196.9</v>
       </c>
       <c r="E63" t="n">
-        <v>183.9</v>
+        <v>182.92</v>
       </c>
       <c r="F63" t="n">
-        <v>184.69</v>
+        <v>188.39</v>
       </c>
       <c r="G63" t="n">
-        <v>21043194</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8479,25 +8951,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>193.92</v>
+        <v>189</v>
       </c>
       <c r="D64" t="n">
-        <v>193.92</v>
+        <v>195.5</v>
       </c>
       <c r="E64" t="n">
-        <v>191.01</v>
+        <v>181.05</v>
       </c>
       <c r="F64" t="n">
-        <v>193.92</v>
+        <v>193.56</v>
       </c>
       <c r="G64" t="n">
-        <v>33053426</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8506,25 +8978,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>196.95</v>
+        <v>193</v>
       </c>
       <c r="D65" t="n">
-        <v>203.61</v>
+        <v>195.53</v>
       </c>
       <c r="E65" t="n">
-        <v>195.7</v>
+        <v>183.9</v>
       </c>
       <c r="F65" t="n">
-        <v>202.52</v>
+        <v>184.69</v>
       </c>
       <c r="G65" t="n">
-        <v>39140552</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8533,25 +9005,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>202.4</v>
+        <v>193.92</v>
       </c>
       <c r="D66" t="n">
-        <v>207</v>
+        <v>193.92</v>
       </c>
       <c r="E66" t="n">
-        <v>200.22</v>
+        <v>191.01</v>
       </c>
       <c r="F66" t="n">
-        <v>202.78</v>
+        <v>193.92</v>
       </c>
       <c r="G66" t="n">
-        <v>19636718</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8560,25 +9032,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>205.8</v>
+        <v>196.95</v>
       </c>
       <c r="D67" t="n">
-        <v>212.91</v>
+        <v>203.61</v>
       </c>
       <c r="E67" t="n">
-        <v>205.03</v>
+        <v>195.7</v>
       </c>
       <c r="F67" t="n">
-        <v>212.23</v>
+        <v>202.52</v>
       </c>
       <c r="G67" t="n">
-        <v>37479685</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8587,25 +9059,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>212.4</v>
+        <v>202.4</v>
       </c>
       <c r="D68" t="n">
-        <v>213.45</v>
+        <v>207</v>
       </c>
       <c r="E68" t="n">
-        <v>203</v>
+        <v>200.22</v>
       </c>
       <c r="F68" t="n">
-        <v>203.67</v>
+        <v>202.78</v>
       </c>
       <c r="G68" t="n">
-        <v>19195935</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8614,25 +9086,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>203.98</v>
+        <v>205.8</v>
       </c>
       <c r="D69" t="n">
-        <v>211.52</v>
+        <v>212.91</v>
       </c>
       <c r="E69" t="n">
-        <v>201</v>
+        <v>205.03</v>
       </c>
       <c r="F69" t="n">
-        <v>207.98</v>
+        <v>212.23</v>
       </c>
       <c r="G69" t="n">
-        <v>19489977</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8641,25 +9113,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>209</v>
+        <v>212.4</v>
       </c>
       <c r="D70" t="n">
-        <v>216.6</v>
+        <v>213.45</v>
       </c>
       <c r="E70" t="n">
-        <v>207.83</v>
+        <v>203</v>
       </c>
       <c r="F70" t="n">
-        <v>212.97</v>
+        <v>203.67</v>
       </c>
       <c r="G70" t="n">
-        <v>19215795</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8668,25 +9140,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>214</v>
+        <v>203.98</v>
       </c>
       <c r="D71" t="n">
-        <v>215.8</v>
+        <v>211.52</v>
       </c>
       <c r="E71" t="n">
-        <v>209.25</v>
+        <v>201</v>
       </c>
       <c r="F71" t="n">
-        <v>214.24</v>
+        <v>207.98</v>
       </c>
       <c r="G71" t="n">
-        <v>15006611</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8695,25 +9167,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>215.4</v>
+        <v>209</v>
       </c>
       <c r="D72" t="n">
-        <v>223.61</v>
+        <v>216.6</v>
       </c>
       <c r="E72" t="n">
-        <v>215</v>
+        <v>207.83</v>
       </c>
       <c r="F72" t="n">
-        <v>221.52</v>
+        <v>212.97</v>
       </c>
       <c r="G72" t="n">
-        <v>28062533</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8722,25 +9194,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D73" t="n">
-        <v>230.95</v>
+        <v>215.8</v>
       </c>
       <c r="E73" t="n">
-        <v>222.62</v>
+        <v>209.25</v>
       </c>
       <c r="F73" t="n">
-        <v>227.36</v>
+        <v>214.24</v>
       </c>
       <c r="G73" t="n">
-        <v>23585794</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8749,25 +9221,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>228</v>
+        <v>215.4</v>
       </c>
       <c r="D74" t="n">
-        <v>230.7</v>
+        <v>223.61</v>
       </c>
       <c r="E74" t="n">
-        <v>220.7</v>
+        <v>215</v>
       </c>
       <c r="F74" t="n">
-        <v>223.11</v>
+        <v>221.52</v>
       </c>
       <c r="G74" t="n">
-        <v>16693107</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8776,25 +9248,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>223.9</v>
+        <v>223</v>
       </c>
       <c r="D75" t="n">
-        <v>225.95</v>
+        <v>230.95</v>
       </c>
       <c r="E75" t="n">
-        <v>217.85</v>
+        <v>222.62</v>
       </c>
       <c r="F75" t="n">
-        <v>219.5</v>
+        <v>227.36</v>
       </c>
       <c r="G75" t="n">
-        <v>9863534</v>
+        <v>23585794</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8803,106 +9275,106 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>218.01</v>
+        <v>228</v>
       </c>
       <c r="D76" t="n">
-        <v>228</v>
+        <v>230.7</v>
       </c>
       <c r="E76" t="n">
-        <v>218.01</v>
+        <v>220.7</v>
       </c>
       <c r="F76" t="n">
-        <v>227.48</v>
+        <v>223.11</v>
       </c>
       <c r="G76" t="n">
-        <v>4963249</v>
+        <v>16693107</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>481.25</v>
+        <v>223.9</v>
       </c>
       <c r="D77" t="n">
-        <v>489.85</v>
+        <v>225.95</v>
       </c>
       <c r="E77" t="n">
-        <v>477.5</v>
+        <v>217.85</v>
       </c>
       <c r="F77" t="n">
-        <v>480.25</v>
+        <v>219.5</v>
       </c>
       <c r="G77" t="n">
-        <v>2347659</v>
+        <v>9863534</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>485.2</v>
+        <v>218.01</v>
       </c>
       <c r="D78" t="n">
-        <v>499</v>
+        <v>228</v>
       </c>
       <c r="E78" t="n">
-        <v>482.55</v>
+        <v>218.01</v>
       </c>
       <c r="F78" t="n">
-        <v>491.6</v>
+        <v>227.48</v>
       </c>
       <c r="G78" t="n">
-        <v>7339280</v>
+        <v>4963249</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="D79" t="n">
-        <v>498.5</v>
+        <v>234.4</v>
       </c>
       <c r="E79" t="n">
-        <v>491</v>
+        <v>225.51</v>
       </c>
       <c r="F79" t="n">
-        <v>495.05</v>
+        <v>225.9</v>
       </c>
       <c r="G79" t="n">
-        <v>2755226</v>
+        <v>5519216</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8911,25 +9383,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>495.05</v>
+        <v>481.25</v>
       </c>
       <c r="D80" t="n">
-        <v>504.3</v>
+        <v>489.85</v>
       </c>
       <c r="E80" t="n">
-        <v>490.05</v>
+        <v>477.5</v>
       </c>
       <c r="F80" t="n">
-        <v>492.35</v>
+        <v>480.25</v>
       </c>
       <c r="G80" t="n">
-        <v>4448305</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8938,25 +9410,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>496.2</v>
+        <v>485.2</v>
       </c>
       <c r="D81" t="n">
-        <v>539.6</v>
+        <v>499</v>
       </c>
       <c r="E81" t="n">
-        <v>495.1</v>
+        <v>482.55</v>
       </c>
       <c r="F81" t="n">
-        <v>533.8</v>
+        <v>491.6</v>
       </c>
       <c r="G81" t="n">
-        <v>22701332</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8965,25 +9437,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>542.45</v>
+        <v>495</v>
       </c>
       <c r="D82" t="n">
-        <v>551</v>
+        <v>498.5</v>
       </c>
       <c r="E82" t="n">
-        <v>525.55</v>
+        <v>491</v>
       </c>
       <c r="F82" t="n">
-        <v>545.95</v>
+        <v>495.05</v>
       </c>
       <c r="G82" t="n">
-        <v>19838083</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8992,25 +9464,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>543.75</v>
+        <v>495.05</v>
       </c>
       <c r="D83" t="n">
-        <v>548</v>
+        <v>504.3</v>
       </c>
       <c r="E83" t="n">
-        <v>532.1</v>
+        <v>490.05</v>
       </c>
       <c r="F83" t="n">
-        <v>536.1</v>
+        <v>492.35</v>
       </c>
       <c r="G83" t="n">
-        <v>9431736</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9019,25 +9491,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>537.95</v>
+        <v>496.2</v>
       </c>
       <c r="D84" t="n">
-        <v>552</v>
+        <v>539.6</v>
       </c>
       <c r="E84" t="n">
-        <v>522</v>
+        <v>495.1</v>
       </c>
       <c r="F84" t="n">
-        <v>526.25</v>
+        <v>533.8</v>
       </c>
       <c r="G84" t="n">
-        <v>12427899</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9046,25 +9518,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>531</v>
+        <v>542.45</v>
       </c>
       <c r="D85" t="n">
-        <v>538.8</v>
+        <v>551</v>
       </c>
       <c r="E85" t="n">
-        <v>527.7</v>
+        <v>525.55</v>
       </c>
       <c r="F85" t="n">
-        <v>533.3</v>
+        <v>545.95</v>
       </c>
       <c r="G85" t="n">
-        <v>5547022</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9073,25 +9545,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>530.85</v>
+        <v>543.75</v>
       </c>
       <c r="D86" t="n">
-        <v>569.9</v>
+        <v>548</v>
       </c>
       <c r="E86" t="n">
-        <v>529.6</v>
+        <v>532.1</v>
       </c>
       <c r="F86" t="n">
-        <v>547.7</v>
+        <v>536.1</v>
       </c>
       <c r="G86" t="n">
-        <v>36903374</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9100,25 +9572,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>549</v>
+        <v>537.95</v>
       </c>
       <c r="D87" t="n">
-        <v>570.5</v>
+        <v>552</v>
       </c>
       <c r="E87" t="n">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="F87" t="n">
-        <v>544.45</v>
+        <v>526.25</v>
       </c>
       <c r="G87" t="n">
-        <v>14649216</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9127,25 +9599,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>546.5</v>
+        <v>531</v>
       </c>
       <c r="D88" t="n">
-        <v>546.7</v>
+        <v>538.8</v>
       </c>
       <c r="E88" t="n">
-        <v>515</v>
+        <v>527.7</v>
       </c>
       <c r="F88" t="n">
-        <v>529.05</v>
+        <v>533.3</v>
       </c>
       <c r="G88" t="n">
-        <v>8696054</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9154,25 +9626,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>535</v>
+        <v>530.85</v>
       </c>
       <c r="D89" t="n">
-        <v>574.9</v>
+        <v>569.9</v>
       </c>
       <c r="E89" t="n">
-        <v>534.1</v>
+        <v>529.6</v>
       </c>
       <c r="F89" t="n">
-        <v>572.65</v>
+        <v>547.7</v>
       </c>
       <c r="G89" t="n">
-        <v>29333771</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9181,133 +9653,133 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>568.6</v>
+        <v>549</v>
       </c>
       <c r="D90" t="n">
-        <v>574.8</v>
+        <v>570.5</v>
       </c>
       <c r="E90" t="n">
-        <v>560.05</v>
+        <v>542</v>
       </c>
       <c r="F90" t="n">
-        <v>560.95</v>
+        <v>544.45</v>
       </c>
       <c r="G90" t="n">
-        <v>3221002</v>
+        <v>14649216</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13.05</v>
+        <v>546.5</v>
       </c>
       <c r="D91" t="n">
-        <v>13.18</v>
+        <v>546.7</v>
       </c>
       <c r="E91" t="n">
-        <v>12.85</v>
+        <v>515</v>
       </c>
       <c r="F91" t="n">
-        <v>12.87</v>
+        <v>529.05</v>
       </c>
       <c r="G91" t="n">
-        <v>230386335</v>
+        <v>8696054</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12.98</v>
+        <v>535</v>
       </c>
       <c r="D92" t="n">
-        <v>13.08</v>
+        <v>574.9</v>
       </c>
       <c r="E92" t="n">
-        <v>12.76</v>
+        <v>534.1</v>
       </c>
       <c r="F92" t="n">
-        <v>13.01</v>
+        <v>572.65</v>
       </c>
       <c r="G92" t="n">
-        <v>387269596</v>
+        <v>29333771</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>13.01</v>
+        <v>568.6</v>
       </c>
       <c r="D93" t="n">
-        <v>13.11</v>
+        <v>576.7</v>
       </c>
       <c r="E93" t="n">
-        <v>12.82</v>
+        <v>555.55</v>
       </c>
       <c r="F93" t="n">
-        <v>12.86</v>
+        <v>566.35</v>
       </c>
       <c r="G93" t="n">
-        <v>235409728</v>
+        <v>15501582</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12.89</v>
+        <v>560</v>
       </c>
       <c r="D94" t="n">
-        <v>13.05</v>
+        <v>569</v>
       </c>
       <c r="E94" t="n">
-        <v>12.73</v>
+        <v>558.1</v>
       </c>
       <c r="F94" t="n">
-        <v>12.9</v>
+        <v>564.15</v>
       </c>
       <c r="G94" t="n">
-        <v>308781891</v>
+        <v>1471666</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9316,25 +9788,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>12.91</v>
+        <v>13.05</v>
       </c>
       <c r="D95" t="n">
-        <v>13.04</v>
+        <v>13.18</v>
       </c>
       <c r="E95" t="n">
-        <v>12.77</v>
+        <v>12.85</v>
       </c>
       <c r="F95" t="n">
-        <v>12.8</v>
+        <v>12.87</v>
       </c>
       <c r="G95" t="n">
-        <v>204366752</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9343,25 +9815,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12.89</v>
+        <v>12.98</v>
       </c>
       <c r="D96" t="n">
-        <v>12.9</v>
+        <v>13.08</v>
       </c>
       <c r="E96" t="n">
-        <v>12.63</v>
+        <v>12.76</v>
       </c>
       <c r="F96" t="n">
-        <v>12.63</v>
+        <v>13.01</v>
       </c>
       <c r="G96" t="n">
-        <v>204537429</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9370,25 +9842,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>12.64</v>
+        <v>13.01</v>
       </c>
       <c r="D97" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="E97" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="F97" t="n">
-        <v>12.73</v>
+        <v>12.86</v>
       </c>
       <c r="G97" t="n">
-        <v>205855564</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9397,25 +9869,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="D98" t="n">
-        <v>13.07</v>
+        <v>13.05</v>
       </c>
       <c r="E98" t="n">
-        <v>12.77</v>
+        <v>12.73</v>
       </c>
       <c r="F98" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
       <c r="G98" t="n">
-        <v>413469644</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9424,25 +9896,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>13.14</v>
+        <v>12.91</v>
       </c>
       <c r="D99" t="n">
-        <v>13.3</v>
+        <v>13.04</v>
       </c>
       <c r="E99" t="n">
-        <v>12.79</v>
+        <v>12.77</v>
       </c>
       <c r="F99" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="G99" t="n">
-        <v>662095209</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9451,25 +9923,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12.93</v>
+        <v>12.89</v>
       </c>
       <c r="D100" t="n">
-        <v>13.69</v>
+        <v>12.9</v>
       </c>
       <c r="E100" t="n">
-        <v>12.83</v>
+        <v>12.63</v>
       </c>
       <c r="F100" t="n">
-        <v>13.5</v>
+        <v>12.63</v>
       </c>
       <c r="G100" t="n">
-        <v>772547405</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9478,25 +9950,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>13.67</v>
+        <v>12.64</v>
       </c>
       <c r="D101" t="n">
-        <v>13.88</v>
+        <v>12.88</v>
       </c>
       <c r="E101" t="n">
-        <v>13.46</v>
+        <v>12.6</v>
       </c>
       <c r="F101" t="n">
-        <v>13.51</v>
+        <v>12.73</v>
       </c>
       <c r="G101" t="n">
-        <v>547253456</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9505,25 +9977,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13.53</v>
+        <v>12.92</v>
       </c>
       <c r="D102" t="n">
-        <v>14.19</v>
+        <v>13.07</v>
       </c>
       <c r="E102" t="n">
-        <v>13.49</v>
+        <v>12.77</v>
       </c>
       <c r="F102" t="n">
-        <v>14.11</v>
+        <v>12.92</v>
       </c>
       <c r="G102" t="n">
-        <v>778908986</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9532,25 +10004,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>14.11</v>
+        <v>13.14</v>
       </c>
       <c r="D103" t="n">
-        <v>14.14</v>
+        <v>13.3</v>
       </c>
       <c r="E103" t="n">
-        <v>13.66</v>
+        <v>12.79</v>
       </c>
       <c r="F103" t="n">
-        <v>13.71</v>
+        <v>12.89</v>
       </c>
       <c r="G103" t="n">
-        <v>310430357</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9559,160 +10031,160 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>13.65</v>
+        <v>12.93</v>
       </c>
       <c r="D104" t="n">
-        <v>13.8</v>
+        <v>13.69</v>
       </c>
       <c r="E104" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="F104" t="n">
         <v>13.5</v>
       </c>
-      <c r="F104" t="n">
-        <v>13.76</v>
-      </c>
       <c r="G104" t="n">
-        <v>256016664</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1554.3</v>
+        <v>13.67</v>
       </c>
       <c r="D105" t="n">
-        <v>1569</v>
+        <v>13.88</v>
       </c>
       <c r="E105" t="n">
-        <v>1551.3</v>
+        <v>13.46</v>
       </c>
       <c r="F105" t="n">
-        <v>1557.6</v>
+        <v>13.51</v>
       </c>
       <c r="G105" t="n">
-        <v>1001677</v>
+        <v>547253456</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1560.4</v>
+        <v>13.53</v>
       </c>
       <c r="D106" t="n">
-        <v>1561</v>
+        <v>14.19</v>
       </c>
       <c r="E106" t="n">
-        <v>1520.4</v>
+        <v>13.49</v>
       </c>
       <c r="F106" t="n">
-        <v>1529.8</v>
+        <v>14.11</v>
       </c>
       <c r="G106" t="n">
-        <v>1011017</v>
+        <v>778908986</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1534.9</v>
+        <v>14.11</v>
       </c>
       <c r="D107" t="n">
-        <v>1572.2</v>
+        <v>14.14</v>
       </c>
       <c r="E107" t="n">
-        <v>1527.2</v>
+        <v>13.66</v>
       </c>
       <c r="F107" t="n">
-        <v>1558.9</v>
+        <v>13.71</v>
       </c>
       <c r="G107" t="n">
-        <v>1235837</v>
+        <v>310430357</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1559.7</v>
+        <v>13.65</v>
       </c>
       <c r="D108" t="n">
-        <v>1600.1</v>
+        <v>14.31</v>
       </c>
       <c r="E108" t="n">
-        <v>1557</v>
+        <v>13.5</v>
       </c>
       <c r="F108" t="n">
-        <v>1593.2</v>
+        <v>14.12</v>
       </c>
       <c r="G108" t="n">
-        <v>1871739</v>
+        <v>820797167</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1591</v>
+        <v>14.12</v>
       </c>
       <c r="D109" t="n">
-        <v>1593.2</v>
+        <v>14.22</v>
       </c>
       <c r="E109" t="n">
-        <v>1566</v>
+        <v>14</v>
       </c>
       <c r="F109" t="n">
-        <v>1577.8</v>
+        <v>14.01</v>
       </c>
       <c r="G109" t="n">
-        <v>1183077</v>
+        <v>86391090</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9721,25 +10193,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1577.7</v>
+        <v>1554.3</v>
       </c>
       <c r="D110" t="n">
-        <v>1586.1</v>
+        <v>1569</v>
       </c>
       <c r="E110" t="n">
-        <v>1561.1</v>
+        <v>1551.3</v>
       </c>
       <c r="F110" t="n">
-        <v>1568.3</v>
+        <v>1557.6</v>
       </c>
       <c r="G110" t="n">
-        <v>1098268</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9748,25 +10220,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1560</v>
+        <v>1560.4</v>
       </c>
       <c r="D111" t="n">
-        <v>1610</v>
+        <v>1561</v>
       </c>
       <c r="E111" t="n">
-        <v>1554.9</v>
+        <v>1520.4</v>
       </c>
       <c r="F111" t="n">
-        <v>1601.2</v>
+        <v>1529.8</v>
       </c>
       <c r="G111" t="n">
-        <v>2647403</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9775,25 +10247,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1624.8</v>
+        <v>1534.9</v>
       </c>
       <c r="D112" t="n">
-        <v>1734.5</v>
+        <v>1572.2</v>
       </c>
       <c r="E112" t="n">
-        <v>1617.1</v>
+        <v>1527.2</v>
       </c>
       <c r="F112" t="n">
-        <v>1713.4</v>
+        <v>1558.9</v>
       </c>
       <c r="G112" t="n">
-        <v>7989771</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9802,25 +10274,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1713</v>
+        <v>1559.7</v>
       </c>
       <c r="D113" t="n">
-        <v>1762</v>
+        <v>1600.1</v>
       </c>
       <c r="E113" t="n">
-        <v>1707.7</v>
+        <v>1557</v>
       </c>
       <c r="F113" t="n">
-        <v>1758.9</v>
+        <v>1593.2</v>
       </c>
       <c r="G113" t="n">
-        <v>4407907</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9829,25 +10301,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1762</v>
+        <v>1591</v>
       </c>
       <c r="D114" t="n">
-        <v>1797.9</v>
+        <v>1593.2</v>
       </c>
       <c r="E114" t="n">
-        <v>1754.3</v>
+        <v>1566</v>
       </c>
       <c r="F114" t="n">
-        <v>1781.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G114" t="n">
-        <v>3000811</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9856,25 +10328,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1785</v>
+        <v>1577.7</v>
       </c>
       <c r="D115" t="n">
-        <v>1798.9</v>
+        <v>1586.1</v>
       </c>
       <c r="E115" t="n">
-        <v>1773.3</v>
+        <v>1561.1</v>
       </c>
       <c r="F115" t="n">
-        <v>1781.3</v>
+        <v>1568.3</v>
       </c>
       <c r="G115" t="n">
-        <v>2402202</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9883,25 +10355,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1785</v>
+        <v>1560</v>
       </c>
       <c r="D116" t="n">
-        <v>1826.6</v>
+        <v>1610</v>
       </c>
       <c r="E116" t="n">
-        <v>1785</v>
+        <v>1554.9</v>
       </c>
       <c r="F116" t="n">
-        <v>1816.2</v>
+        <v>1601.2</v>
       </c>
       <c r="G116" t="n">
-        <v>2502579</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9910,25 +10382,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1821</v>
+        <v>1624.8</v>
       </c>
       <c r="D117" t="n">
-        <v>1838.3</v>
+        <v>1734.5</v>
       </c>
       <c r="E117" t="n">
-        <v>1789.1</v>
+        <v>1617.1</v>
       </c>
       <c r="F117" t="n">
-        <v>1811.4</v>
+        <v>1713.4</v>
       </c>
       <c r="G117" t="n">
-        <v>1919384</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9937,25 +10409,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1811</v>
+        <v>1713</v>
       </c>
       <c r="D118" t="n">
-        <v>1850</v>
+        <v>1762</v>
       </c>
       <c r="E118" t="n">
-        <v>1806.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F118" t="n">
-        <v>1850</v>
+        <v>1758.9</v>
       </c>
       <c r="G118" t="n">
-        <v>1405192</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9964,25 +10436,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1854</v>
+        <v>1762</v>
       </c>
       <c r="D119" t="n">
-        <v>1856.6</v>
+        <v>1797.9</v>
       </c>
       <c r="E119" t="n">
-        <v>1834.5</v>
+        <v>1754.3</v>
       </c>
       <c r="F119" t="n">
-        <v>1835</v>
+        <v>1781.3</v>
       </c>
       <c r="G119" t="n">
-        <v>2090998</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9991,25 +10463,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1843</v>
+        <v>1785</v>
       </c>
       <c r="D120" t="n">
-        <v>1854.9</v>
+        <v>1798.9</v>
       </c>
       <c r="E120" t="n">
-        <v>1830</v>
+        <v>1773.3</v>
       </c>
       <c r="F120" t="n">
-        <v>1830</v>
+        <v>1781.3</v>
       </c>
       <c r="G120" t="n">
-        <v>2037418</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10018,25 +10490,25 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1838</v>
+        <v>1785</v>
       </c>
       <c r="D121" t="n">
-        <v>1856</v>
+        <v>1826.6</v>
       </c>
       <c r="E121" t="n">
-        <v>1833.2</v>
+        <v>1785</v>
       </c>
       <c r="F121" t="n">
-        <v>1844.3</v>
+        <v>1816.2</v>
       </c>
       <c r="G121" t="n">
-        <v>1553067</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10045,25 +10517,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1845</v>
+        <v>1821</v>
       </c>
       <c r="D122" t="n">
-        <v>1870.8</v>
+        <v>1838.3</v>
       </c>
       <c r="E122" t="n">
-        <v>1832.8</v>
+        <v>1789.1</v>
       </c>
       <c r="F122" t="n">
-        <v>1854</v>
+        <v>1811.4</v>
       </c>
       <c r="G122" t="n">
-        <v>1386592</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10072,25 +10544,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1851</v>
+        <v>1811</v>
       </c>
       <c r="D123" t="n">
-        <v>1859</v>
+        <v>1850</v>
       </c>
       <c r="E123" t="n">
-        <v>1833.1</v>
+        <v>1806.1</v>
       </c>
       <c r="F123" t="n">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="G123" t="n">
-        <v>1514239</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10099,25 +10571,25 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1856.3</v>
+        <v>1854</v>
       </c>
       <c r="D124" t="n">
-        <v>1862.3</v>
+        <v>1856.6</v>
       </c>
       <c r="E124" t="n">
+        <v>1834.5</v>
+      </c>
+      <c r="F124" t="n">
         <v>1835</v>
       </c>
-      <c r="F124" t="n">
-        <v>1850</v>
-      </c>
       <c r="G124" t="n">
-        <v>1088545</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10126,25 +10598,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1850</v>
+        <v>1843</v>
       </c>
       <c r="D125" t="n">
-        <v>1851.7</v>
+        <v>1854.9</v>
       </c>
       <c r="E125" t="n">
-        <v>1820.6</v>
+        <v>1830</v>
       </c>
       <c r="F125" t="n">
-        <v>1851.7</v>
+        <v>1830</v>
       </c>
       <c r="G125" t="n">
-        <v>1345856</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10153,25 +10625,25 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1849.9</v>
+        <v>1838</v>
       </c>
       <c r="D126" t="n">
-        <v>1853.2</v>
+        <v>1856</v>
       </c>
       <c r="E126" t="n">
-        <v>1777.7</v>
+        <v>1833.2</v>
       </c>
       <c r="F126" t="n">
-        <v>1787.3</v>
+        <v>1844.3</v>
       </c>
       <c r="G126" t="n">
-        <v>1581352</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10180,25 +10652,25 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1770</v>
+        <v>1845</v>
       </c>
       <c r="D127" t="n">
-        <v>1824</v>
+        <v>1870.8</v>
       </c>
       <c r="E127" t="n">
-        <v>1769.4</v>
+        <v>1832.8</v>
       </c>
       <c r="F127" t="n">
-        <v>1809.7</v>
+        <v>1854</v>
       </c>
       <c r="G127" t="n">
-        <v>1631767</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10207,187 +10679,187 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1810</v>
+        <v>1851</v>
       </c>
       <c r="D128" t="n">
-        <v>1815</v>
+        <v>1859</v>
       </c>
       <c r="E128" t="n">
-        <v>1803.5</v>
+        <v>1833.1</v>
       </c>
       <c r="F128" t="n">
-        <v>1807</v>
+        <v>1858</v>
       </c>
       <c r="G128" t="n">
-        <v>161331</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>344</v>
+        <v>1856.3</v>
       </c>
       <c r="D129" t="n">
-        <v>346.3</v>
+        <v>1862.3</v>
       </c>
       <c r="E129" t="n">
-        <v>341.25</v>
+        <v>1835</v>
       </c>
       <c r="F129" t="n">
-        <v>342.9</v>
+        <v>1850</v>
       </c>
       <c r="G129" t="n">
-        <v>4465145</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>344.2</v>
+        <v>1850</v>
       </c>
       <c r="D130" t="n">
-        <v>347.75</v>
+        <v>1851.7</v>
       </c>
       <c r="E130" t="n">
-        <v>339.95</v>
+        <v>1820.6</v>
       </c>
       <c r="F130" t="n">
-        <v>342.4</v>
+        <v>1851.7</v>
       </c>
       <c r="G130" t="n">
-        <v>3803051</v>
+        <v>1345856</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>346</v>
+        <v>1849.9</v>
       </c>
       <c r="D131" t="n">
-        <v>351</v>
+        <v>1853.2</v>
       </c>
       <c r="E131" t="n">
-        <v>343.65</v>
+        <v>1777.7</v>
       </c>
       <c r="F131" t="n">
-        <v>346</v>
+        <v>1787.3</v>
       </c>
       <c r="G131" t="n">
-        <v>5175178</v>
+        <v>1581352</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>341.8</v>
+        <v>1770</v>
       </c>
       <c r="D132" t="n">
-        <v>344.9</v>
+        <v>1824</v>
       </c>
       <c r="E132" t="n">
-        <v>339.65</v>
+        <v>1769.4</v>
       </c>
       <c r="F132" t="n">
-        <v>343.9</v>
+        <v>1809.7</v>
       </c>
       <c r="G132" t="n">
-        <v>2253982</v>
+        <v>1631767</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>345.1</v>
+        <v>1810</v>
       </c>
       <c r="D133" t="n">
-        <v>346.05</v>
+        <v>1824.6</v>
       </c>
       <c r="E133" t="n">
-        <v>338.35</v>
+        <v>1802.1</v>
       </c>
       <c r="F133" t="n">
-        <v>339.35</v>
+        <v>1814</v>
       </c>
       <c r="G133" t="n">
-        <v>3868006</v>
+        <v>1291914</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>339.4</v>
+        <v>1814</v>
       </c>
       <c r="D134" t="n">
-        <v>340.2</v>
+        <v>1818</v>
       </c>
       <c r="E134" t="n">
-        <v>333</v>
+        <v>1796.8</v>
       </c>
       <c r="F134" t="n">
-        <v>334.55</v>
+        <v>1797.2</v>
       </c>
       <c r="G134" t="n">
-        <v>3721274</v>
+        <v>209921</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10396,25 +10868,25 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D135" t="n">
-        <v>346.1</v>
+        <v>346.3</v>
       </c>
       <c r="E135" t="n">
-        <v>332</v>
+        <v>341.25</v>
       </c>
       <c r="F135" t="n">
-        <v>344.7</v>
+        <v>342.9</v>
       </c>
       <c r="G135" t="n">
-        <v>5431501</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10423,25 +10895,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>345.5</v>
+        <v>344.2</v>
       </c>
       <c r="D136" t="n">
-        <v>349.65</v>
+        <v>347.75</v>
       </c>
       <c r="E136" t="n">
-        <v>342.6</v>
+        <v>339.95</v>
       </c>
       <c r="F136" t="n">
-        <v>347.65</v>
+        <v>342.4</v>
       </c>
       <c r="G136" t="n">
-        <v>6318472</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10450,25 +10922,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D137" t="n">
-        <v>355.75</v>
+        <v>351</v>
       </c>
       <c r="E137" t="n">
-        <v>347.65</v>
+        <v>343.65</v>
       </c>
       <c r="F137" t="n">
-        <v>350.05</v>
+        <v>346</v>
       </c>
       <c r="G137" t="n">
-        <v>7186013</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10477,25 +10949,25 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>357.95</v>
+        <v>341.8</v>
       </c>
       <c r="D138" t="n">
-        <v>369</v>
+        <v>344.9</v>
       </c>
       <c r="E138" t="n">
-        <v>353.5</v>
+        <v>339.65</v>
       </c>
       <c r="F138" t="n">
-        <v>369</v>
+        <v>343.9</v>
       </c>
       <c r="G138" t="n">
-        <v>12541474</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10504,25 +10976,25 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>373</v>
+        <v>345.1</v>
       </c>
       <c r="D139" t="n">
-        <v>382.45</v>
+        <v>346.05</v>
       </c>
       <c r="E139" t="n">
-        <v>367.15</v>
+        <v>338.35</v>
       </c>
       <c r="F139" t="n">
-        <v>377</v>
+        <v>339.35</v>
       </c>
       <c r="G139" t="n">
-        <v>15775994</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10531,25 +11003,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>381</v>
+        <v>339.4</v>
       </c>
       <c r="D140" t="n">
-        <v>383.9</v>
+        <v>340.2</v>
       </c>
       <c r="E140" t="n">
-        <v>375.15</v>
+        <v>333</v>
       </c>
       <c r="F140" t="n">
-        <v>381</v>
+        <v>334.55</v>
       </c>
       <c r="G140" t="n">
-        <v>8940938</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10558,25 +11030,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="D141" t="n">
-        <v>385.05</v>
+        <v>346.1</v>
       </c>
       <c r="E141" t="n">
-        <v>376.5</v>
+        <v>332</v>
       </c>
       <c r="F141" t="n">
-        <v>381</v>
+        <v>344.7</v>
       </c>
       <c r="G141" t="n">
-        <v>6636333</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10585,25 +11057,25 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>382.5</v>
+        <v>345.5</v>
       </c>
       <c r="D142" t="n">
-        <v>382.85</v>
+        <v>349.65</v>
       </c>
       <c r="E142" t="n">
-        <v>377.15</v>
+        <v>342.6</v>
       </c>
       <c r="F142" t="n">
-        <v>381</v>
+        <v>347.65</v>
       </c>
       <c r="G142" t="n">
-        <v>4423953</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10612,25 +11084,25 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>381.7</v>
+        <v>352</v>
       </c>
       <c r="D143" t="n">
-        <v>387.7</v>
+        <v>355.75</v>
       </c>
       <c r="E143" t="n">
-        <v>381.1</v>
+        <v>347.65</v>
       </c>
       <c r="F143" t="n">
-        <v>382.7</v>
+        <v>350.05</v>
       </c>
       <c r="G143" t="n">
-        <v>5292453</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10639,25 +11111,25 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>387.15</v>
+        <v>357.95</v>
       </c>
       <c r="D144" t="n">
-        <v>393.7</v>
+        <v>369</v>
       </c>
       <c r="E144" t="n">
-        <v>384.5</v>
+        <v>353.5</v>
       </c>
       <c r="F144" t="n">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="G144" t="n">
-        <v>8155315</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10666,25 +11138,25 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>398.5</v>
+        <v>373</v>
       </c>
       <c r="D145" t="n">
-        <v>422.2</v>
+        <v>382.45</v>
       </c>
       <c r="E145" t="n">
-        <v>398.5</v>
+        <v>367.15</v>
       </c>
       <c r="F145" t="n">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="G145" t="n">
-        <v>34388331</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10693,25 +11165,25 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>410.5</v>
+        <v>381</v>
       </c>
       <c r="D146" t="n">
-        <v>413.65</v>
+        <v>383.9</v>
       </c>
       <c r="E146" t="n">
-        <v>400</v>
+        <v>375.15</v>
       </c>
       <c r="F146" t="n">
-        <v>400.5</v>
+        <v>381</v>
       </c>
       <c r="G146" t="n">
-        <v>9738984</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10720,25 +11192,25 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>378.6</v>
+        <v>385</v>
       </c>
       <c r="D147" t="n">
-        <v>384.95</v>
+        <v>385.05</v>
       </c>
       <c r="E147" t="n">
-        <v>375</v>
+        <v>376.5</v>
       </c>
       <c r="F147" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G147" t="n">
-        <v>14954594</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10747,25 +11219,25 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>377.9</v>
+        <v>382.5</v>
       </c>
       <c r="D148" t="n">
-        <v>391.5</v>
+        <v>382.85</v>
       </c>
       <c r="E148" t="n">
-        <v>376.5</v>
+        <v>377.15</v>
       </c>
       <c r="F148" t="n">
-        <v>387.55</v>
+        <v>381</v>
       </c>
       <c r="G148" t="n">
-        <v>9724992</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10774,214 +11246,214 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>386.8</v>
+        <v>381.7</v>
       </c>
       <c r="D149" t="n">
-        <v>389.9</v>
+        <v>387.7</v>
       </c>
       <c r="E149" t="n">
-        <v>385.8</v>
+        <v>381.1</v>
       </c>
       <c r="F149" t="n">
-        <v>389.35</v>
+        <v>382.7</v>
       </c>
       <c r="G149" t="n">
-        <v>572397</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4389.8</v>
+        <v>387.15</v>
       </c>
       <c r="D150" t="n">
-        <v>4485</v>
+        <v>393.7</v>
       </c>
       <c r="E150" t="n">
-        <v>4361.9</v>
+        <v>384.5</v>
       </c>
       <c r="F150" t="n">
-        <v>4398.1</v>
+        <v>388</v>
       </c>
       <c r="G150" t="n">
-        <v>1347378</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4422</v>
+        <v>398.5</v>
       </c>
       <c r="D151" t="n">
-        <v>4495</v>
+        <v>422.2</v>
       </c>
       <c r="E151" t="n">
-        <v>4358</v>
+        <v>398.5</v>
       </c>
       <c r="F151" t="n">
-        <v>4371.4</v>
+        <v>420</v>
       </c>
       <c r="G151" t="n">
-        <v>902264</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4387.7</v>
+        <v>410.5</v>
       </c>
       <c r="D152" t="n">
-        <v>4404</v>
+        <v>413.65</v>
       </c>
       <c r="E152" t="n">
-        <v>4281.9</v>
+        <v>400</v>
       </c>
       <c r="F152" t="n">
-        <v>4304.2</v>
+        <v>400.5</v>
       </c>
       <c r="G152" t="n">
-        <v>463349</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>4285</v>
+        <v>378.6</v>
       </c>
       <c r="D153" t="n">
-        <v>4317</v>
+        <v>384.95</v>
       </c>
       <c r="E153" t="n">
-        <v>4220</v>
+        <v>375</v>
       </c>
       <c r="F153" t="n">
-        <v>4244.3</v>
+        <v>376</v>
       </c>
       <c r="G153" t="n">
-        <v>398348</v>
+        <v>14954594</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4211</v>
+        <v>377.9</v>
       </c>
       <c r="D154" t="n">
-        <v>4220</v>
+        <v>391.5</v>
       </c>
       <c r="E154" t="n">
-        <v>4129.3</v>
+        <v>376.5</v>
       </c>
       <c r="F154" t="n">
-        <v>4178.1</v>
+        <v>387.55</v>
       </c>
       <c r="G154" t="n">
-        <v>470046</v>
+        <v>9724992</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4190</v>
+        <v>386.8</v>
       </c>
       <c r="D155" t="n">
-        <v>4324.4</v>
+        <v>390.85</v>
       </c>
       <c r="E155" t="n">
-        <v>4190</v>
+        <v>385.8</v>
       </c>
       <c r="F155" t="n">
-        <v>4257.3</v>
+        <v>388</v>
       </c>
       <c r="G155" t="n">
-        <v>633457</v>
+        <v>2824411</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4290</v>
+        <v>382</v>
       </c>
       <c r="D156" t="n">
-        <v>4383</v>
+        <v>383</v>
       </c>
       <c r="E156" t="n">
-        <v>4266</v>
+        <v>379</v>
       </c>
       <c r="F156" t="n">
-        <v>4288.7</v>
+        <v>380.25</v>
       </c>
       <c r="G156" t="n">
-        <v>835107</v>
+        <v>880356</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10990,25 +11462,25 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4299</v>
+        <v>4389.8</v>
       </c>
       <c r="D157" t="n">
-        <v>4340</v>
+        <v>4485</v>
       </c>
       <c r="E157" t="n">
-        <v>4216</v>
+        <v>4361.9</v>
       </c>
       <c r="F157" t="n">
-        <v>4243.8</v>
+        <v>4398.1</v>
       </c>
       <c r="G157" t="n">
-        <v>422024</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11017,25 +11489,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4201.9</v>
+        <v>4422</v>
       </c>
       <c r="D158" t="n">
-        <v>4222</v>
+        <v>4495</v>
       </c>
       <c r="E158" t="n">
-        <v>4115</v>
+        <v>4358</v>
       </c>
       <c r="F158" t="n">
-        <v>4156</v>
+        <v>4371.4</v>
       </c>
       <c r="G158" t="n">
-        <v>378694</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11044,25 +11516,25 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4181.8</v>
+        <v>4387.7</v>
       </c>
       <c r="D159" t="n">
-        <v>4385</v>
+        <v>4404</v>
       </c>
       <c r="E159" t="n">
-        <v>4129.4</v>
+        <v>4281.9</v>
       </c>
       <c r="F159" t="n">
-        <v>4362.2</v>
+        <v>4304.2</v>
       </c>
       <c r="G159" t="n">
-        <v>992864</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11071,25 +11543,25 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4380</v>
+        <v>4285</v>
       </c>
       <c r="D160" t="n">
-        <v>4478.3</v>
+        <v>4317</v>
       </c>
       <c r="E160" t="n">
-        <v>4280.1</v>
+        <v>4220</v>
       </c>
       <c r="F160" t="n">
-        <v>4395.7</v>
+        <v>4244.3</v>
       </c>
       <c r="G160" t="n">
-        <v>960643</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11098,25 +11570,25 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4497.2</v>
+        <v>4211</v>
       </c>
       <c r="D161" t="n">
-        <v>4541.17</v>
+        <v>4220</v>
       </c>
       <c r="E161" t="n">
-        <v>4319.31</v>
+        <v>4129.3</v>
       </c>
       <c r="F161" t="n">
-        <v>4361.38</v>
+        <v>4178.1</v>
       </c>
       <c r="G161" t="n">
-        <v>1616021</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11125,25 +11597,25 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4338</v>
+        <v>4190</v>
       </c>
       <c r="D162" t="n">
-        <v>4339.1</v>
+        <v>4324.4</v>
       </c>
       <c r="E162" t="n">
-        <v>4172.9</v>
+        <v>4190</v>
       </c>
       <c r="F162" t="n">
-        <v>4192.59</v>
+        <v>4257.3</v>
       </c>
       <c r="G162" t="n">
-        <v>648341</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11152,25 +11624,25 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4297.32</v>
+        <v>4290</v>
       </c>
       <c r="D163" t="n">
-        <v>4595.14</v>
+        <v>4383</v>
       </c>
       <c r="E163" t="n">
-        <v>4249.35</v>
+        <v>4266</v>
       </c>
       <c r="F163" t="n">
-        <v>4521.18</v>
+        <v>4288.7</v>
       </c>
       <c r="G163" t="n">
-        <v>4510774</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11179,25 +11651,25 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4557.56</v>
+        <v>4299</v>
       </c>
       <c r="D164" t="n">
-        <v>4737.05</v>
+        <v>4340</v>
       </c>
       <c r="E164" t="n">
-        <v>4537.17</v>
+        <v>4216</v>
       </c>
       <c r="F164" t="n">
-        <v>4583.14</v>
+        <v>4243.8</v>
       </c>
       <c r="G164" t="n">
-        <v>2334958</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11206,25 +11678,25 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4606.13</v>
+        <v>4201.9</v>
       </c>
       <c r="D165" t="n">
-        <v>4777.02</v>
+        <v>4222</v>
       </c>
       <c r="E165" t="n">
-        <v>4590.24</v>
+        <v>4115</v>
       </c>
       <c r="F165" t="n">
-        <v>4759.23</v>
+        <v>4156</v>
       </c>
       <c r="G165" t="n">
-        <v>1899271</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11233,25 +11705,25 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4817.7</v>
+        <v>4181.8</v>
       </c>
       <c r="D166" t="n">
-        <v>4929.93</v>
+        <v>4385</v>
       </c>
       <c r="E166" t="n">
-        <v>4722.06</v>
+        <v>4129.4</v>
       </c>
       <c r="F166" t="n">
-        <v>4890.75</v>
+        <v>4362.2</v>
       </c>
       <c r="G166" t="n">
-        <v>1924204</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11260,25 +11732,25 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4896.95</v>
+        <v>4380</v>
       </c>
       <c r="D167" t="n">
-        <v>4976.9</v>
+        <v>4478.3</v>
       </c>
       <c r="E167" t="n">
-        <v>4780.02</v>
+        <v>4280.1</v>
       </c>
       <c r="F167" t="n">
-        <v>4813</v>
+        <v>4395.7</v>
       </c>
       <c r="G167" t="n">
-        <v>1117424</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11287,25 +11759,25 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4790</v>
+        <v>4497.2</v>
       </c>
       <c r="D168" t="n">
-        <v>4968</v>
+        <v>4541.17</v>
       </c>
       <c r="E168" t="n">
-        <v>4780</v>
+        <v>4319.31</v>
       </c>
       <c r="F168" t="n">
-        <v>4939.2</v>
+        <v>4361.38</v>
       </c>
       <c r="G168" t="n">
-        <v>1296942</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11314,25 +11786,25 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4958</v>
+        <v>4338</v>
       </c>
       <c r="D169" t="n">
-        <v>5085</v>
+        <v>4339.1</v>
       </c>
       <c r="E169" t="n">
-        <v>4888.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F169" t="n">
-        <v>4903</v>
+        <v>4192.59</v>
       </c>
       <c r="G169" t="n">
-        <v>1210476</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11341,25 +11813,25 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4903</v>
+        <v>4297.32</v>
       </c>
       <c r="D170" t="n">
-        <v>4940</v>
+        <v>4595.14</v>
       </c>
       <c r="E170" t="n">
-        <v>4792.5</v>
+        <v>4249.35</v>
       </c>
       <c r="F170" t="n">
-        <v>4859.8</v>
+        <v>4521.18</v>
       </c>
       <c r="G170" t="n">
-        <v>682980</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11368,25 +11840,25 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4866</v>
+        <v>4557.56</v>
       </c>
       <c r="D171" t="n">
-        <v>4907.9</v>
+        <v>4737.05</v>
       </c>
       <c r="E171" t="n">
-        <v>4753</v>
+        <v>4537.17</v>
       </c>
       <c r="F171" t="n">
-        <v>4837.4</v>
+        <v>4583.14</v>
       </c>
       <c r="G171" t="n">
-        <v>613049</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11395,25 +11867,25 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4860</v>
+        <v>4606.13</v>
       </c>
       <c r="D172" t="n">
-        <v>5200</v>
+        <v>4777.02</v>
       </c>
       <c r="E172" t="n">
-        <v>4860</v>
+        <v>4590.24</v>
       </c>
       <c r="F172" t="n">
-        <v>5181</v>
+        <v>4759.23</v>
       </c>
       <c r="G172" t="n">
-        <v>3457670</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11422,25 +11894,25 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5200</v>
+        <v>4817.7</v>
       </c>
       <c r="D173" t="n">
-        <v>5269</v>
+        <v>4929.93</v>
       </c>
       <c r="E173" t="n">
-        <v>4991.3</v>
+        <v>4722.06</v>
       </c>
       <c r="F173" t="n">
-        <v>5007.2</v>
+        <v>4890.75</v>
       </c>
       <c r="G173" t="n">
-        <v>1695255</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11449,25 +11921,25 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5022</v>
+        <v>4896.95</v>
       </c>
       <c r="D174" t="n">
-        <v>5225</v>
+        <v>4976.9</v>
       </c>
       <c r="E174" t="n">
-        <v>5008.3</v>
+        <v>4780.02</v>
       </c>
       <c r="F174" t="n">
-        <v>5212.4</v>
+        <v>4813</v>
       </c>
       <c r="G174" t="n">
-        <v>1438746</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11476,241 +11948,241 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5110</v>
+        <v>4790</v>
       </c>
       <c r="D175" t="n">
-        <v>5334</v>
+        <v>4968</v>
       </c>
       <c r="E175" t="n">
-        <v>5092.8</v>
+        <v>4780</v>
       </c>
       <c r="F175" t="n">
-        <v>5311</v>
+        <v>4939.2</v>
       </c>
       <c r="G175" t="n">
-        <v>614537</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1417</v>
+        <v>4958</v>
       </c>
       <c r="D176" t="n">
-        <v>1436</v>
+        <v>5085</v>
       </c>
       <c r="E176" t="n">
-        <v>1410.1</v>
+        <v>4888.8</v>
       </c>
       <c r="F176" t="n">
-        <v>1423.9</v>
+        <v>4903</v>
       </c>
       <c r="G176" t="n">
-        <v>623969</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1428</v>
+        <v>4903</v>
       </c>
       <c r="D177" t="n">
-        <v>1428</v>
+        <v>4940</v>
       </c>
       <c r="E177" t="n">
-        <v>1351.5</v>
+        <v>4792.5</v>
       </c>
       <c r="F177" t="n">
-        <v>1359.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G177" t="n">
-        <v>808190</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1349.8</v>
+        <v>4866</v>
       </c>
       <c r="D178" t="n">
-        <v>1357.8</v>
+        <v>4907.9</v>
       </c>
       <c r="E178" t="n">
-        <v>1330.1</v>
+        <v>4753</v>
       </c>
       <c r="F178" t="n">
-        <v>1340.8</v>
+        <v>4837.4</v>
       </c>
       <c r="G178" t="n">
-        <v>345535</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1340.8</v>
+        <v>4860</v>
       </c>
       <c r="D179" t="n">
-        <v>1387.7</v>
+        <v>5200</v>
       </c>
       <c r="E179" t="n">
-        <v>1316</v>
+        <v>4860</v>
       </c>
       <c r="F179" t="n">
-        <v>1374.4</v>
+        <v>5181</v>
       </c>
       <c r="G179" t="n">
-        <v>974660</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1372.9</v>
+        <v>5200</v>
       </c>
       <c r="D180" t="n">
-        <v>1390</v>
+        <v>5269</v>
       </c>
       <c r="E180" t="n">
-        <v>1355.1</v>
+        <v>4991.3</v>
       </c>
       <c r="F180" t="n">
-        <v>1363.5</v>
+        <v>5007.2</v>
       </c>
       <c r="G180" t="n">
-        <v>479123</v>
+        <v>1695255</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1363</v>
+        <v>5022</v>
       </c>
       <c r="D181" t="n">
-        <v>1392</v>
+        <v>5225</v>
       </c>
       <c r="E181" t="n">
-        <v>1355.1</v>
+        <v>5008.3</v>
       </c>
       <c r="F181" t="n">
-        <v>1380</v>
+        <v>5212.4</v>
       </c>
       <c r="G181" t="n">
-        <v>616767</v>
+        <v>1438746</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1360</v>
+        <v>5110</v>
       </c>
       <c r="D182" t="n">
-        <v>1368</v>
+        <v>5396.4</v>
       </c>
       <c r="E182" t="n">
-        <v>1272.1</v>
+        <v>5092.8</v>
       </c>
       <c r="F182" t="n">
-        <v>1288.3</v>
+        <v>5354.5</v>
       </c>
       <c r="G182" t="n">
-        <v>1098492</v>
+        <v>2395703</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1300</v>
+        <v>5324.9</v>
       </c>
       <c r="D183" t="n">
-        <v>1318.5</v>
+        <v>5338</v>
       </c>
       <c r="E183" t="n">
-        <v>1257</v>
+        <v>5122</v>
       </c>
       <c r="F183" t="n">
-        <v>1316.2</v>
+        <v>5150.6</v>
       </c>
       <c r="G183" t="n">
-        <v>1172726</v>
+        <v>473476</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11719,25 +12191,25 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1317.7</v>
+        <v>1417</v>
       </c>
       <c r="D184" t="n">
-        <v>1319.8</v>
+        <v>1436</v>
       </c>
       <c r="E184" t="n">
-        <v>1270.5</v>
+        <v>1410.1</v>
       </c>
       <c r="F184" t="n">
-        <v>1306</v>
+        <v>1423.9</v>
       </c>
       <c r="G184" t="n">
-        <v>832973</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11746,25 +12218,25 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1319.9</v>
+        <v>1428</v>
       </c>
       <c r="D185" t="n">
-        <v>1355.4</v>
+        <v>1428</v>
       </c>
       <c r="E185" t="n">
-        <v>1308</v>
+        <v>1351.5</v>
       </c>
       <c r="F185" t="n">
-        <v>1343.4</v>
+        <v>1359.1</v>
       </c>
       <c r="G185" t="n">
-        <v>1287698</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11773,25 +12245,25 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1379</v>
+        <v>1349.8</v>
       </c>
       <c r="D186" t="n">
-        <v>1468</v>
+        <v>1357.8</v>
       </c>
       <c r="E186" t="n">
-        <v>1361</v>
+        <v>1330.1</v>
       </c>
       <c r="F186" t="n">
-        <v>1377.8</v>
+        <v>1340.8</v>
       </c>
       <c r="G186" t="n">
-        <v>9950655</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11800,25 +12272,25 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1380.5</v>
+        <v>1340.8</v>
       </c>
       <c r="D187" t="n">
-        <v>1403.3</v>
+        <v>1387.7</v>
       </c>
       <c r="E187" t="n">
-        <v>1363</v>
+        <v>1316</v>
       </c>
       <c r="F187" t="n">
-        <v>1366.8</v>
+        <v>1374.4</v>
       </c>
       <c r="G187" t="n">
-        <v>1567542</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11827,25 +12299,25 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1380</v>
+        <v>1372.9</v>
       </c>
       <c r="D188" t="n">
-        <v>1397.5</v>
+        <v>1390</v>
       </c>
       <c r="E188" t="n">
-        <v>1351.6</v>
+        <v>1355.1</v>
       </c>
       <c r="F188" t="n">
-        <v>1360.6</v>
+        <v>1363.5</v>
       </c>
       <c r="G188" t="n">
-        <v>1098353</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11854,25 +12326,25 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1360.6</v>
+        <v>1363</v>
       </c>
       <c r="D189" t="n">
-        <v>1428</v>
+        <v>1392</v>
       </c>
       <c r="E189" t="n">
-        <v>1354.5</v>
+        <v>1355.1</v>
       </c>
       <c r="F189" t="n">
-        <v>1421.6</v>
+        <v>1380</v>
       </c>
       <c r="G189" t="n">
-        <v>2055261</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11881,25 +12353,25 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1428.14</v>
+        <v>1360</v>
       </c>
       <c r="D190" t="n">
-        <v>1451.52</v>
+        <v>1368</v>
       </c>
       <c r="E190" t="n">
-        <v>1417.55</v>
+        <v>1272.1</v>
       </c>
       <c r="F190" t="n">
-        <v>1432.63</v>
+        <v>1288.3</v>
       </c>
       <c r="G190" t="n">
-        <v>1243415</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11908,25 +12380,25 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1432.53</v>
+        <v>1300</v>
       </c>
       <c r="D191" t="n">
-        <v>1458.51</v>
+        <v>1318.5</v>
       </c>
       <c r="E191" t="n">
-        <v>1403.56</v>
+        <v>1257</v>
       </c>
       <c r="F191" t="n">
-        <v>1416.55</v>
+        <v>1316.2</v>
       </c>
       <c r="G191" t="n">
-        <v>1123973</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11935,25 +12407,25 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1412.46</v>
+        <v>1317.7</v>
       </c>
       <c r="D192" t="n">
-        <v>1432.53</v>
+        <v>1319.8</v>
       </c>
       <c r="E192" t="n">
-        <v>1406.06</v>
+        <v>1270.5</v>
       </c>
       <c r="F192" t="n">
-        <v>1423.24</v>
+        <v>1306</v>
       </c>
       <c r="G192" t="n">
-        <v>509551</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11962,25 +12434,25 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1432.63</v>
+        <v>1319.9</v>
       </c>
       <c r="D193" t="n">
-        <v>1520.44</v>
+        <v>1355.4</v>
       </c>
       <c r="E193" t="n">
-        <v>1426.04</v>
+        <v>1308</v>
       </c>
       <c r="F193" t="n">
-        <v>1514.85</v>
+        <v>1343.4</v>
       </c>
       <c r="G193" t="n">
-        <v>3863757</v>
+        <v>1287698</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11989,25 +12461,25 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1514.85</v>
+        <v>1379</v>
       </c>
       <c r="D194" t="n">
-        <v>1541.42</v>
+        <v>1468</v>
       </c>
       <c r="E194" t="n">
-        <v>1485.38</v>
+        <v>1361</v>
       </c>
       <c r="F194" t="n">
-        <v>1493.27</v>
+        <v>1377.8</v>
       </c>
       <c r="G194" t="n">
-        <v>1508375</v>
+        <v>9950655</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12016,25 +12488,25 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1493.27</v>
+        <v>1380.5</v>
       </c>
       <c r="D195" t="n">
-        <v>1512.45</v>
+        <v>1403.3</v>
       </c>
       <c r="E195" t="n">
-        <v>1463.6</v>
+        <v>1363</v>
       </c>
       <c r="F195" t="n">
-        <v>1471.79</v>
+        <v>1366.8</v>
       </c>
       <c r="G195" t="n">
-        <v>749197</v>
+        <v>1567542</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12043,25 +12515,25 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1480.39</v>
+        <v>1380</v>
       </c>
       <c r="D196" t="n">
-        <v>1498.97</v>
+        <v>1397.5</v>
       </c>
       <c r="E196" t="n">
-        <v>1449.52</v>
+        <v>1351.6</v>
       </c>
       <c r="F196" t="n">
-        <v>1466.2</v>
+        <v>1360.6</v>
       </c>
       <c r="G196" t="n">
-        <v>742118</v>
+        <v>1098353</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12070,25 +12542,25 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1478.49</v>
+        <v>1360.6</v>
       </c>
       <c r="D197" t="n">
-        <v>1505.16</v>
+        <v>1428</v>
       </c>
       <c r="E197" t="n">
-        <v>1450.52</v>
+        <v>1354.5</v>
       </c>
       <c r="F197" t="n">
-        <v>1463.7</v>
+        <v>1421.6</v>
       </c>
       <c r="G197" t="n">
-        <v>811337</v>
+        <v>2055261</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12097,46 +12569,289 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1475.79</v>
+        <v>1428.14</v>
       </c>
       <c r="D198" t="n">
-        <v>1502.06</v>
+        <v>1451.52</v>
       </c>
       <c r="E198" t="n">
-        <v>1457.01</v>
+        <v>1417.55</v>
       </c>
       <c r="F198" t="n">
-        <v>1466.4</v>
+        <v>1432.63</v>
       </c>
       <c r="G198" t="n">
-        <v>972670</v>
+        <v>1243415</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1458.51</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1403.56</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1416.55</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1412.46</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1406.06</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1423.24</v>
+      </c>
+      <c r="G200" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1520.44</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1426.04</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1541.42</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1485.38</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1512.45</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1463.6</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1471.79</v>
+      </c>
+      <c r="G203" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1480.39</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1498.97</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1449.52</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1466.2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>742118</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1478.49</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1505.16</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1450.52</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="G205" t="n">
+        <v>811337</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1475.79</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1502.06</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1457.01</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1466.4</v>
+      </c>
+      <c r="G206" t="n">
+        <v>972670</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C199" t="n">
+      <c r="C207" t="n">
         <v>1489.9</v>
       </c>
-      <c r="D199" t="n">
-        <v>1516</v>
-      </c>
-      <c r="E199" t="n">
+      <c r="D207" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E207" t="n">
         <v>1488.9</v>
       </c>
-      <c r="F199" t="n">
-        <v>1515.3</v>
-      </c>
-      <c r="G199" t="n">
-        <v>799062</v>
+      <c r="F207" t="n">
+        <v>1500.1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2323890</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1507.9</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1514.6</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1491</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1504.4</v>
+      </c>
+      <c r="G208" t="n">
+        <v>182467</v>
       </c>
     </row>
   </sheetData>
@@ -12150,7 +12865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12365,6 +13080,21 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 19 Aug 2026 04:08</t>
+          <t>Generated 20 Aug 2026 04:08</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>46.2</v>
+        <v>47.6</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="3">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>4.55</v>
+        <v>4.23</v>
       </c>
       <c r="D3" t="n">
-        <v>3.39</v>
+        <v>3.01</v>
       </c>
       <c r="E3" t="n">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
@@ -647,7 +647,7 @@
         <v>-2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="4">
@@ -657,25 +657,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7.11</v>
+        <v>6.74</v>
       </c>
       <c r="E4" t="n">
-        <v>83.3</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
         <v>26.91</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.41</v>
+        <v>-6.17</v>
       </c>
       <c r="H4" t="n">
-        <v>7.89</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>16.7</v>
+        <v>11.73</v>
       </c>
       <c r="D5" t="n">
-        <v>19.43</v>
+        <v>16.13</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>21.95</v>
+        <v>22.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.89</v>
+        <v>-6.45</v>
       </c>
       <c r="H5" t="n">
-        <v>8.02</v>
+        <v>10.61</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,6 +3341,192 @@
         <v>1</v>
       </c>
       <c r="P43" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>208.57</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="L44" t="n">
+        <v>268.36</v>
+      </c>
+      <c r="M44" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O44" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>99</v>
+      </c>
+      <c r="F45" t="n">
+        <v>110.22</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1384.6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1528.6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1672.6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>144</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>98</v>
+      </c>
+      <c r="F46" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="K46" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="L46" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -3357,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4731,6 +4917,105 @@
       </c>
       <c r="I43" t="n">
         <v>648.55</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>208.57</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="G44" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="H44" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="I44" t="n">
+        <v>268.36</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1384.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>144</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1528.6</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1672.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="E46" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H46" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="I46" t="n">
+        <v>15.71</v>
       </c>
     </row>
   </sheetData>
@@ -4744,7 +5029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4847,7 +5132,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4867,7 +5152,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225.9</v>
+        <v>228.5</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -4875,16 +5160,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>3.76</v>
+        <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.17</v>
+        <v>-1.33</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>205.43</v>
+        <v>208.57</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -4900,12 +5185,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4920,7 +5205,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14.01</v>
+        <v>1384.6</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -4928,16 +5213,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>5.88</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.36</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>13.16</v>
+        <v>1240.6</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -4953,12 +5238,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4973,7 +5258,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>564.15</v>
+        <v>14.05</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -4981,16 +5266,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.07</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>521.95</v>
+        <v>13.22</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -5006,7 +5291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5026,26 +5311,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>227.48</v>
+        <v>226.53</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>3.04</v>
+        <v>3.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.16</v>
+        <v>-1.12</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>207.19</v>
+        <v>205.43</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -5061,7 +5346,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5081,26 +5366,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14.12</v>
+        <v>14.07</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.39</v>
+        <v>-1.35</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>12.95</v>
+        <v>13.16</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -5116,19 +5401,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5136,26 +5421,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1599.6</v>
+        <v>554.85</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.91</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>3.58</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.22</v>
+        <v>-0.33</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1505.54</v>
+        <v>521.95</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -5171,7 +5456,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5191,26 +5476,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>223.11</v>
+        <v>230.03</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.62</v>
+        <v>-1.52</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>5.06</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.36</v>
+        <v>-5.23</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>209.18</v>
+        <v>207.19</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -5226,12 +5511,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5246,26 +5531,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1616</v>
+        <v>14.12</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.66</v>
+        <v>-0.35</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.2</v>
+        <v>-4.39</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1508.29</v>
+        <v>12.95</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -5281,19 +5566,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5301,26 +5586,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14.11</v>
+        <v>1603</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.83</v>
+        <v>-3.89</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.39</v>
+        <v>-4.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>13.18</v>
+        <v>1505.54</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -5336,7 +5621,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5356,26 +5641,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>227.36</v>
+        <v>223.11</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.87</v>
+        <v>-1.62</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>5.06</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.18</v>
+        <v>-2.36</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>209.53</v>
+        <v>209.18</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -5391,12 +5676,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5411,26 +5696,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.51</v>
+        <v>1616</v>
       </c>
       <c r="G12" t="n">
-        <v>4.44</v>
+        <v>-1.66</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>5.92</v>
+        <v>0.87</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.37</v>
+        <v>-4.92</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>13.02</v>
+        <v>1508.29</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -5446,19 +5731,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5466,26 +5751,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1583</v>
+        <v>14.11</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>-2.83</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>3.49</v>
+        <v>1.42</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2</v>
+        <v>-4.39</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>1491.87</v>
+        <v>13.18</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -5501,7 +5786,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5521,28 +5806,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>221.52</v>
+        <v>227.36</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>-1.87</v>
       </c>
       <c r="H14" t="n">
-        <v>1.98</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>5.81</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.94</v>
+        <v>-4.18</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -5558,7 +5843,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5578,34 +5863,34 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="H15" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.96</v>
+        <v>-0.37</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -5615,12 +5900,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5635,31 +5920,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>547.7</v>
+        <v>1583</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.59</v>
+        <v>2.08</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>-1.96</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>5.29</v>
+        <v>3.49</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.97</v>
+        <v>-2.94</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -5667,14 +5952,12 @@
       <c r="R16" t="b">
         <v>0</v>
       </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5694,34 +5977,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>6.18</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>9.41</v>
+        <v>5.81</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -5731,12 +6014,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5751,28 +6034,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>10.18</v>
+        <v>4.22</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>11.04</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -5788,12 +6071,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5808,28 +6091,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.42</v>
+        <v>-0.59</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.38</v>
+        <v>1.31</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>3.08</v>
+        <v>5.29</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.56</v>
+        <v>-5.97</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -5841,13 +6124,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5867,28 +6150,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>7.27</v>
+        <v>7.37</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>12.7</v>
+        <v>9.41</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -5904,19 +6187,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5924,34 +6207,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.86</v>
+        <v>10.18</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>2.57</v>
+        <v>11.04</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.03</v>
+        <v>-2.2</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -5961,19 +6244,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -5981,44 +6264,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G22" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.31</v>
+        <v>-1.17</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.57</v>
+        <v>-5.27</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
         <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6038,28 +6323,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="n">
-        <v>11.63</v>
+        <v>7.27</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>15.09</v>
+        <v>12.7</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N23" t="n">
         <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -6075,7 +6360,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6095,31 +6380,31 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.28</v>
+        <v>-0.86</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.44</v>
+        <v>-5.74</v>
       </c>
       <c r="N24" t="n">
         <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -6127,12 +6412,14 @@
       <c r="R24" t="b">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6155,10 +6442,10 @@
         <v>381</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H25" t="n">
-        <v>5.12</v>
+        <v>-1.31</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -6173,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -6182,14 +6469,14 @@
         <v>1</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6209,30 +6496,30 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>4.38</v>
+        <v>11.63</v>
       </c>
       <c r="I26" t="n">
-        <v>6.44</v>
+        <v>12.19</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>10.45</v>
+        <v>15.09</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -6248,12 +6535,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6268,51 +6555,53 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.09</v>
+        <v>-2.28</v>
       </c>
       <c r="I27" t="n">
-        <v>5.31</v>
+        <v>-4.2</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>10.34</v>
+        <v>3.21</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.45</v>
+        <v>-5.15</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
         <v>0</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6327,46 +6616,46 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.62</v>
+        <v>5.12</v>
       </c>
       <c r="I28" t="n">
-        <v>-5.41</v>
+        <v>1.84</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.72</v>
+        <v>-1.57</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6386,30 +6675,30 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G29" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H29" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I29" t="n">
-        <v>12.18</v>
+        <v>6.74</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>15.59</v>
+        <v>10.45</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
       <c r="O29" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -6425,7 +6714,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6437,7 +6726,7 @@
         <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6445,30 +6734,30 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H30" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I30" t="n">
-        <v>12.51</v>
+        <v>3.56</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>13.39</v>
+        <v>10.34</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -6484,12 +6773,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6504,36 +6793,36 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G31" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H31" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I31" t="n">
-        <v>2.92</v>
+        <v>-6.17</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.61</v>
+        <v>-6.43</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -6543,19 +6832,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -6563,30 +6852,30 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G32" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H32" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I32" t="n">
-        <v>13.73</v>
+        <v>13.44</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>17.74</v>
+        <v>15.59</v>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N32" t="n">
         <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -6595,26 +6884,26 @@
         <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6622,36 +6911,36 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.52</v>
+        <v>12.51</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>1.76</v>
+        <v>13.39</v>
       </c>
       <c r="M33" t="n">
-        <v>-6</v>
+        <v>-3.55</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
       </c>
       <c r="Q33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
@@ -6661,19 +6950,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6681,30 +6970,30 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G34" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H34" t="n">
-        <v>11.34</v>
+        <v>2.92</v>
       </c>
       <c r="I34" t="n">
-        <v>7.78</v>
+        <v>2.92</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>13.29</v>
+        <v>11.99</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N34" t="n">
         <v>13</v>
       </c>
       <c r="O34" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
@@ -6720,12 +7009,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -6740,46 +7029,46 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H35" t="n">
-        <v>2.81</v>
+        <v>6.98</v>
       </c>
       <c r="I35" t="n">
-        <v>6.42</v>
+        <v>13.73</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>11.88</v>
+        <v>17.74</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O35" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
       </c>
       <c r="Q35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6799,30 +7088,30 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I36" t="n">
-        <v>-4.58</v>
+        <v>-3.52</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M36" t="n">
-        <v>-6.68</v>
+        <v>-6.71</v>
       </c>
       <c r="N36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -6834,25 +7123,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6860,36 +7149,36 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G37" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H37" t="n">
-        <v>2.73</v>
+        <v>11.34</v>
       </c>
       <c r="I37" t="n">
-        <v>3.95</v>
+        <v>7.78</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>5.02</v>
+        <v>13.29</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O37" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
       </c>
       <c r="Q37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -6899,12 +7188,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -6919,52 +7208,60 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G38" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H38" t="n">
-        <v>9.65</v>
+        <v>2.81</v>
       </c>
       <c r="I38" t="n">
-        <v>14.45</v>
+        <v>6.42</v>
       </c>
       <c r="J38" t="n">
-        <v>16.71</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>21.1</v>
+        <v>11.88</v>
       </c>
       <c r="M38" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N38" t="n">
         <v>16</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
       <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -6972,40 +7269,50 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G39" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H39" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I39" t="n">
-        <v>10.91</v>
+        <v>-4.58</v>
       </c>
       <c r="J39" t="n">
-        <v>18.1</v>
+        <v>-6.45</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>23.73</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>-4.32</v>
+        <v>-7.38</v>
       </c>
       <c r="N39" t="n">
         <v>16</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7017,7 +7324,7 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -7028,49 +7335,57 @@
         <v>1781.3</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H40" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I40" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="J40" t="n">
-        <v>0.89</v>
+        <v>2.08</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>5.02</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.52</v>
+        <v>-0.67</v>
       </c>
       <c r="N40" t="n">
         <v>16</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
       <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -7078,26 +7393,26 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G41" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H41" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I41" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J41" t="n">
-        <v>21.95</v>
+        <v>17.03</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>31.45</v>
+        <v>21.1</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N41" t="n">
         <v>17</v>
@@ -7111,19 +7426,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -7131,26 +7446,26 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G42" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H42" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I42" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J42" t="n">
-        <v>20.75</v>
+        <v>16.13</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>24.42</v>
+        <v>23.73</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N42" t="n">
         <v>17</v>
@@ -7164,19 +7479,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7184,26 +7499,26 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I43" t="n">
-        <v>10.56</v>
+        <v>3.86</v>
       </c>
       <c r="J43" t="n">
-        <v>21.81</v>
+        <v>1.15</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>22.77</v>
+        <v>5.02</v>
       </c>
       <c r="M43" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N43" t="n">
         <v>17</v>
@@ -7213,6 +7528,165 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H44" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I44" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J44" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N44" t="n">
+        <v>18</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>96</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J45" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N45" t="n">
+        <v>18</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>92</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J46" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N46" t="n">
+        <v>18</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7225,7 +7699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7874,16 +8348,16 @@
         <v>1589</v>
       </c>
       <c r="D24" t="n">
-        <v>1601.6</v>
+        <v>1630</v>
       </c>
       <c r="E24" t="n">
         <v>1583.1</v>
       </c>
       <c r="F24" t="n">
-        <v>1599.6</v>
+        <v>1603</v>
       </c>
       <c r="G24" t="n">
-        <v>327119</v>
+        <v>2294009</v>
       </c>
     </row>
     <row r="25">
@@ -7904,46 +8378,46 @@
         <v>1604.8</v>
       </c>
       <c r="E25" t="n">
-        <v>1548.1</v>
+        <v>1536.5</v>
       </c>
       <c r="F25" t="n">
-        <v>1553.1</v>
+        <v>1540.7</v>
       </c>
       <c r="G25" t="n">
-        <v>694969</v>
+        <v>3477602</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1188.4</v>
+        <v>1550</v>
       </c>
       <c r="D26" t="n">
-        <v>1207.9</v>
+        <v>1561</v>
       </c>
       <c r="E26" t="n">
-        <v>1158</v>
+        <v>1542.8</v>
       </c>
       <c r="F26" t="n">
-        <v>1201.8</v>
+        <v>1552</v>
       </c>
       <c r="G26" t="n">
-        <v>3482939</v>
+        <v>332616</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7952,25 +8426,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D27" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F27" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G27" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7979,25 +8453,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D28" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E28" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F28" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G28" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8006,25 +8480,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D29" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E29" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G29" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8033,25 +8507,25 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F30" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D30" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G30" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8060,25 +8534,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E31" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F31" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G31" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8087,25 +8561,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D32" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E32" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F32" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G32" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8114,25 +8588,25 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F33" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D33" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G33" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8141,25 +8615,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D34" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E34" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G34" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8168,25 +8642,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D35" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E35" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F35" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G35" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8195,25 +8669,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D36" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E36" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G36" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8222,25 +8696,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D37" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E37" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F37" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G37" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8249,25 +8723,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D38" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E38" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F38" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G38" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8276,25 +8750,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D39" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E39" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G39" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8303,25 +8777,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D40" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E40" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F40" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G40" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8330,25 +8804,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D41" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E41" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F41" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G41" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8357,25 +8831,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D42" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E42" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F42" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G42" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8384,25 +8858,25 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F43" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D43" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G43" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8411,25 +8885,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D44" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E44" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F44" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G44" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8438,25 +8912,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D45" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E45" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F45" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G45" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8465,25 +8939,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D46" t="n">
-        <v>1534.8</v>
+        <v>1520</v>
       </c>
       <c r="E46" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F46" t="n">
-        <v>1525.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G46" t="n">
-        <v>4867021</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8492,25 +8966,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1531.7</v>
+        <v>1472.4</v>
       </c>
       <c r="D47" t="n">
-        <v>1580</v>
+        <v>1534.8</v>
       </c>
       <c r="E47" t="n">
-        <v>1511.1</v>
+        <v>1472</v>
       </c>
       <c r="F47" t="n">
-        <v>1569.4</v>
+        <v>1525.4</v>
       </c>
       <c r="G47" t="n">
-        <v>4521175</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8519,25 +8993,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1575</v>
+        <v>1531.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="E48" t="n">
-        <v>1500.1</v>
+        <v>1511.1</v>
       </c>
       <c r="F48" t="n">
-        <v>1526.5</v>
+        <v>1569.4</v>
       </c>
       <c r="G48" t="n">
-        <v>4013245</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8546,25 +9020,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1530</v>
+        <v>1575</v>
       </c>
       <c r="D49" t="n">
-        <v>1541</v>
+        <v>1575</v>
       </c>
       <c r="E49" t="n">
-        <v>1501.9</v>
+        <v>1500.1</v>
       </c>
       <c r="F49" t="n">
-        <v>1511.5</v>
+        <v>1526.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2250949</v>
+        <v>4013245</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8573,25 +9047,25 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>1530</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1541</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1501.9</v>
+      </c>
+      <c r="F50" t="n">
         <v>1511.5</v>
       </c>
-      <c r="D50" t="n">
-        <v>1533</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1475</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1485.2</v>
-      </c>
       <c r="G50" t="n">
-        <v>2475472</v>
+        <v>2250949</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8600,25 +9074,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1484.7</v>
+        <v>1511.5</v>
       </c>
       <c r="D51" t="n">
-        <v>1504</v>
+        <v>1533</v>
       </c>
       <c r="E51" t="n">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="F51" t="n">
-        <v>1465.8</v>
+        <v>1485.2</v>
       </c>
       <c r="G51" t="n">
-        <v>2760706</v>
+        <v>2475472</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8627,349 +9101,349 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1468.1</v>
+        <v>1484.7</v>
       </c>
       <c r="D52" t="n">
-        <v>1471.8</v>
+        <v>1504</v>
       </c>
       <c r="E52" t="n">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="F52" t="n">
-        <v>1459.4</v>
+        <v>1465.8</v>
       </c>
       <c r="G52" t="n">
-        <v>315565</v>
+        <v>2760706</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>211.95</v>
+        <v>1468.1</v>
       </c>
       <c r="D53" t="n">
-        <v>214.55</v>
+        <v>1473.3</v>
       </c>
       <c r="E53" t="n">
-        <v>206.1</v>
+        <v>1431</v>
       </c>
       <c r="F53" t="n">
-        <v>212.78</v>
+        <v>1438.2</v>
       </c>
       <c r="G53" t="n">
-        <v>12863408</v>
+        <v>1688332</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>214.3</v>
+        <v>1445.5</v>
       </c>
       <c r="D54" t="n">
-        <v>223.41</v>
+        <v>1467</v>
       </c>
       <c r="E54" t="n">
-        <v>214.3</v>
+        <v>1442.2</v>
       </c>
       <c r="F54" t="n">
-        <v>223.08</v>
+        <v>1442.2</v>
       </c>
       <c r="G54" t="n">
-        <v>32151413</v>
+        <v>297401</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>226</v>
+        <v>1235.9</v>
       </c>
       <c r="D55" t="n">
-        <v>229.4</v>
+        <v>1285.8</v>
       </c>
       <c r="E55" t="n">
-        <v>221.18</v>
+        <v>1220.3</v>
       </c>
       <c r="F55" t="n">
-        <v>224.38</v>
+        <v>1275.4</v>
       </c>
       <c r="G55" t="n">
-        <v>14379534</v>
+        <v>1468654</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>217.24</v>
+        <v>1270</v>
       </c>
       <c r="D56" t="n">
-        <v>219.7</v>
+        <v>1270</v>
       </c>
       <c r="E56" t="n">
-        <v>213.17</v>
+        <v>1235</v>
       </c>
       <c r="F56" t="n">
-        <v>213.17</v>
+        <v>1240.1</v>
       </c>
       <c r="G56" t="n">
-        <v>14642282</v>
+        <v>782776</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>208.25</v>
+        <v>1249</v>
       </c>
       <c r="D57" t="n">
-        <v>213.7</v>
+        <v>1449</v>
       </c>
       <c r="E57" t="n">
-        <v>203.16</v>
+        <v>1237</v>
       </c>
       <c r="F57" t="n">
-        <v>208.03</v>
+        <v>1426.1</v>
       </c>
       <c r="G57" t="n">
-        <v>18348510</v>
+        <v>17236108</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>209</v>
+        <v>1418</v>
       </c>
       <c r="D58" t="n">
-        <v>218.43</v>
+        <v>1444</v>
       </c>
       <c r="E58" t="n">
-        <v>209</v>
+        <v>1370.1</v>
       </c>
       <c r="F58" t="n">
-        <v>217.97</v>
+        <v>1379.5</v>
       </c>
       <c r="G58" t="n">
-        <v>20144780</v>
+        <v>2824270</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>222</v>
+        <v>1377.1</v>
       </c>
       <c r="D59" t="n">
-        <v>228</v>
+        <v>1378.9</v>
       </c>
       <c r="E59" t="n">
-        <v>214.11</v>
+        <v>1308</v>
       </c>
       <c r="F59" t="n">
-        <v>217.9</v>
+        <v>1341.8</v>
       </c>
       <c r="G59" t="n">
-        <v>55935312</v>
+        <v>1846258</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>221.96</v>
+        <v>1341.8</v>
       </c>
       <c r="D60" t="n">
-        <v>222.4</v>
+        <v>1368.8</v>
       </c>
       <c r="E60" t="n">
-        <v>207.01</v>
+        <v>1311</v>
       </c>
       <c r="F60" t="n">
-        <v>207.01</v>
+        <v>1321.9</v>
       </c>
       <c r="G60" t="n">
-        <v>29190459</v>
+        <v>755166</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>202</v>
+        <v>1332.1</v>
       </c>
       <c r="D61" t="n">
-        <v>204.78</v>
+        <v>1397.3</v>
       </c>
       <c r="E61" t="n">
-        <v>196.66</v>
+        <v>1309.1</v>
       </c>
       <c r="F61" t="n">
-        <v>196.85</v>
+        <v>1382.4</v>
       </c>
       <c r="G61" t="n">
-        <v>31552378</v>
+        <v>2149658</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="D62" t="n">
-        <v>200.9</v>
+        <v>1454.5</v>
       </c>
       <c r="E62" t="n">
-        <v>191.1</v>
+        <v>1384.9</v>
       </c>
       <c r="F62" t="n">
-        <v>192.54</v>
+        <v>1404</v>
       </c>
       <c r="G62" t="n">
-        <v>26152896</v>
+        <v>3584947</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>187</v>
+        <v>1429</v>
       </c>
       <c r="D63" t="n">
-        <v>196.9</v>
+        <v>1489.7</v>
       </c>
       <c r="E63" t="n">
-        <v>182.92</v>
+        <v>1421.2</v>
       </c>
       <c r="F63" t="n">
-        <v>188.39</v>
+        <v>1440.3</v>
       </c>
       <c r="G63" t="n">
-        <v>42541118</v>
+        <v>5720727</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>189</v>
+        <v>1457</v>
       </c>
       <c r="D64" t="n">
-        <v>195.5</v>
+        <v>1466</v>
       </c>
       <c r="E64" t="n">
-        <v>181.05</v>
+        <v>1379.6</v>
       </c>
       <c r="F64" t="n">
-        <v>193.56</v>
+        <v>1384.6</v>
       </c>
       <c r="G64" t="n">
-        <v>40104195</v>
+        <v>715693</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8978,25 +9452,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>193</v>
+        <v>211.95</v>
       </c>
       <c r="D65" t="n">
-        <v>195.53</v>
+        <v>214.55</v>
       </c>
       <c r="E65" t="n">
-        <v>183.9</v>
+        <v>206.1</v>
       </c>
       <c r="F65" t="n">
-        <v>184.69</v>
+        <v>212.78</v>
       </c>
       <c r="G65" t="n">
-        <v>21043194</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9005,25 +9479,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>193.92</v>
+        <v>214.3</v>
       </c>
       <c r="D66" t="n">
-        <v>193.92</v>
+        <v>223.41</v>
       </c>
       <c r="E66" t="n">
-        <v>191.01</v>
+        <v>214.3</v>
       </c>
       <c r="F66" t="n">
-        <v>193.92</v>
+        <v>223.08</v>
       </c>
       <c r="G66" t="n">
-        <v>33053426</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9032,25 +9506,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>196.95</v>
+        <v>226</v>
       </c>
       <c r="D67" t="n">
-        <v>203.61</v>
+        <v>229.4</v>
       </c>
       <c r="E67" t="n">
-        <v>195.7</v>
+        <v>221.18</v>
       </c>
       <c r="F67" t="n">
-        <v>202.52</v>
+        <v>224.38</v>
       </c>
       <c r="G67" t="n">
-        <v>39140552</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9059,25 +9533,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>202.4</v>
+        <v>217.24</v>
       </c>
       <c r="D68" t="n">
-        <v>207</v>
+        <v>219.7</v>
       </c>
       <c r="E68" t="n">
-        <v>200.22</v>
+        <v>213.17</v>
       </c>
       <c r="F68" t="n">
-        <v>202.78</v>
+        <v>213.17</v>
       </c>
       <c r="G68" t="n">
-        <v>19636718</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9086,25 +9560,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>205.8</v>
+        <v>208.25</v>
       </c>
       <c r="D69" t="n">
-        <v>212.91</v>
+        <v>213.7</v>
       </c>
       <c r="E69" t="n">
-        <v>205.03</v>
+        <v>203.16</v>
       </c>
       <c r="F69" t="n">
-        <v>212.23</v>
+        <v>208.03</v>
       </c>
       <c r="G69" t="n">
-        <v>37479685</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9113,25 +9587,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>212.4</v>
+        <v>209</v>
       </c>
       <c r="D70" t="n">
-        <v>213.45</v>
+        <v>218.43</v>
       </c>
       <c r="E70" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F70" t="n">
-        <v>203.67</v>
+        <v>217.97</v>
       </c>
       <c r="G70" t="n">
-        <v>19195935</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9140,25 +9614,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>203.98</v>
+        <v>222</v>
       </c>
       <c r="D71" t="n">
-        <v>211.52</v>
+        <v>228</v>
       </c>
       <c r="E71" t="n">
-        <v>201</v>
+        <v>214.11</v>
       </c>
       <c r="F71" t="n">
-        <v>207.98</v>
+        <v>217.9</v>
       </c>
       <c r="G71" t="n">
-        <v>19489977</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9167,25 +9641,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>209</v>
+        <v>221.96</v>
       </c>
       <c r="D72" t="n">
-        <v>216.6</v>
+        <v>222.4</v>
       </c>
       <c r="E72" t="n">
-        <v>207.83</v>
+        <v>207.01</v>
       </c>
       <c r="F72" t="n">
-        <v>212.97</v>
+        <v>207.01</v>
       </c>
       <c r="G72" t="n">
-        <v>19215795</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9194,25 +9668,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D73" t="n">
-        <v>215.8</v>
+        <v>204.78</v>
       </c>
       <c r="E73" t="n">
-        <v>209.25</v>
+        <v>196.66</v>
       </c>
       <c r="F73" t="n">
-        <v>214.24</v>
+        <v>196.85</v>
       </c>
       <c r="G73" t="n">
-        <v>15006611</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9221,25 +9695,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>215.4</v>
+        <v>200</v>
       </c>
       <c r="D74" t="n">
-        <v>223.61</v>
+        <v>200.9</v>
       </c>
       <c r="E74" t="n">
-        <v>215</v>
+        <v>191.1</v>
       </c>
       <c r="F74" t="n">
-        <v>221.52</v>
+        <v>192.54</v>
       </c>
       <c r="G74" t="n">
-        <v>28062533</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9248,25 +9722,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="D75" t="n">
-        <v>230.95</v>
+        <v>196.9</v>
       </c>
       <c r="E75" t="n">
-        <v>222.62</v>
+        <v>182.92</v>
       </c>
       <c r="F75" t="n">
-        <v>227.36</v>
+        <v>188.39</v>
       </c>
       <c r="G75" t="n">
-        <v>23585794</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9275,25 +9749,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="D76" t="n">
-        <v>230.7</v>
+        <v>195.5</v>
       </c>
       <c r="E76" t="n">
-        <v>220.7</v>
+        <v>181.05</v>
       </c>
       <c r="F76" t="n">
-        <v>223.11</v>
+        <v>193.56</v>
       </c>
       <c r="G76" t="n">
-        <v>16693107</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9302,25 +9776,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>223.9</v>
+        <v>193</v>
       </c>
       <c r="D77" t="n">
-        <v>225.95</v>
+        <v>195.53</v>
       </c>
       <c r="E77" t="n">
-        <v>217.85</v>
+        <v>183.9</v>
       </c>
       <c r="F77" t="n">
-        <v>219.5</v>
+        <v>184.69</v>
       </c>
       <c r="G77" t="n">
-        <v>9863534</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9329,25 +9803,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>218.01</v>
+        <v>193.92</v>
       </c>
       <c r="D78" t="n">
-        <v>228</v>
+        <v>193.92</v>
       </c>
       <c r="E78" t="n">
-        <v>218.01</v>
+        <v>191.01</v>
       </c>
       <c r="F78" t="n">
-        <v>227.48</v>
+        <v>193.92</v>
       </c>
       <c r="G78" t="n">
-        <v>4963249</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9356,376 +9830,376 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>233</v>
+        <v>196.95</v>
       </c>
       <c r="D79" t="n">
-        <v>234.4</v>
+        <v>203.61</v>
       </c>
       <c r="E79" t="n">
-        <v>225.51</v>
+        <v>195.7</v>
       </c>
       <c r="F79" t="n">
-        <v>225.9</v>
+        <v>202.52</v>
       </c>
       <c r="G79" t="n">
-        <v>5519216</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>481.25</v>
+        <v>202.4</v>
       </c>
       <c r="D80" t="n">
-        <v>489.85</v>
+        <v>207</v>
       </c>
       <c r="E80" t="n">
-        <v>477.5</v>
+        <v>200.22</v>
       </c>
       <c r="F80" t="n">
-        <v>480.25</v>
+        <v>202.78</v>
       </c>
       <c r="G80" t="n">
-        <v>2347659</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>485.2</v>
+        <v>205.8</v>
       </c>
       <c r="D81" t="n">
-        <v>499</v>
+        <v>212.91</v>
       </c>
       <c r="E81" t="n">
-        <v>482.55</v>
+        <v>205.03</v>
       </c>
       <c r="F81" t="n">
-        <v>491.6</v>
+        <v>212.23</v>
       </c>
       <c r="G81" t="n">
-        <v>7339280</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>495</v>
+        <v>212.4</v>
       </c>
       <c r="D82" t="n">
-        <v>498.5</v>
+        <v>213.45</v>
       </c>
       <c r="E82" t="n">
-        <v>491</v>
+        <v>203</v>
       </c>
       <c r="F82" t="n">
-        <v>495.05</v>
+        <v>203.67</v>
       </c>
       <c r="G82" t="n">
-        <v>2755226</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>495.05</v>
+        <v>203.98</v>
       </c>
       <c r="D83" t="n">
-        <v>504.3</v>
+        <v>211.52</v>
       </c>
       <c r="E83" t="n">
-        <v>490.05</v>
+        <v>201</v>
       </c>
       <c r="F83" t="n">
-        <v>492.35</v>
+        <v>207.98</v>
       </c>
       <c r="G83" t="n">
-        <v>4448305</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>496.2</v>
+        <v>209</v>
       </c>
       <c r="D84" t="n">
-        <v>539.6</v>
+        <v>216.6</v>
       </c>
       <c r="E84" t="n">
-        <v>495.1</v>
+        <v>207.83</v>
       </c>
       <c r="F84" t="n">
-        <v>533.8</v>
+        <v>212.97</v>
       </c>
       <c r="G84" t="n">
-        <v>22701332</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>542.45</v>
+        <v>214</v>
       </c>
       <c r="D85" t="n">
-        <v>551</v>
+        <v>215.8</v>
       </c>
       <c r="E85" t="n">
-        <v>525.55</v>
+        <v>209.25</v>
       </c>
       <c r="F85" t="n">
-        <v>545.95</v>
+        <v>214.24</v>
       </c>
       <c r="G85" t="n">
-        <v>19838083</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>543.75</v>
+        <v>215.4</v>
       </c>
       <c r="D86" t="n">
-        <v>548</v>
+        <v>223.61</v>
       </c>
       <c r="E86" t="n">
-        <v>532.1</v>
+        <v>215</v>
       </c>
       <c r="F86" t="n">
-        <v>536.1</v>
+        <v>221.52</v>
       </c>
       <c r="G86" t="n">
-        <v>9431736</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>537.95</v>
+        <v>223</v>
       </c>
       <c r="D87" t="n">
-        <v>552</v>
+        <v>230.95</v>
       </c>
       <c r="E87" t="n">
-        <v>522</v>
+        <v>222.62</v>
       </c>
       <c r="F87" t="n">
-        <v>526.25</v>
+        <v>227.36</v>
       </c>
       <c r="G87" t="n">
-        <v>12427899</v>
+        <v>23585794</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>531</v>
+        <v>228</v>
       </c>
       <c r="D88" t="n">
-        <v>538.8</v>
+        <v>230.7</v>
       </c>
       <c r="E88" t="n">
-        <v>527.7</v>
+        <v>220.7</v>
       </c>
       <c r="F88" t="n">
-        <v>533.3</v>
+        <v>223.11</v>
       </c>
       <c r="G88" t="n">
-        <v>5547022</v>
+        <v>16693107</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>530.85</v>
+        <v>223.9</v>
       </c>
       <c r="D89" t="n">
-        <v>569.9</v>
+        <v>225.95</v>
       </c>
       <c r="E89" t="n">
-        <v>529.6</v>
+        <v>217.85</v>
       </c>
       <c r="F89" t="n">
-        <v>547.7</v>
+        <v>219.5</v>
       </c>
       <c r="G89" t="n">
-        <v>36903374</v>
+        <v>9863534</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>549</v>
+        <v>218.01</v>
       </c>
       <c r="D90" t="n">
-        <v>570.5</v>
+        <v>230.47</v>
       </c>
       <c r="E90" t="n">
-        <v>542</v>
+        <v>218.01</v>
       </c>
       <c r="F90" t="n">
-        <v>544.45</v>
+        <v>230.03</v>
       </c>
       <c r="G90" t="n">
-        <v>14649216</v>
+        <v>35739264</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>546.5</v>
+        <v>233</v>
       </c>
       <c r="D91" t="n">
-        <v>546.7</v>
+        <v>234.4</v>
       </c>
       <c r="E91" t="n">
-        <v>515</v>
+        <v>224</v>
       </c>
       <c r="F91" t="n">
-        <v>529.05</v>
+        <v>226.53</v>
       </c>
       <c r="G91" t="n">
-        <v>8696054</v>
+        <v>14962246</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>535</v>
+        <v>227.95</v>
       </c>
       <c r="D92" t="n">
-        <v>574.9</v>
+        <v>229.8</v>
       </c>
       <c r="E92" t="n">
-        <v>534.1</v>
+        <v>225.46</v>
       </c>
       <c r="F92" t="n">
-        <v>572.65</v>
+        <v>228.5</v>
       </c>
       <c r="G92" t="n">
-        <v>29333771</v>
+        <v>2643323</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9734,25 +10208,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>568.6</v>
+        <v>481.25</v>
       </c>
       <c r="D93" t="n">
-        <v>576.7</v>
+        <v>489.85</v>
       </c>
       <c r="E93" t="n">
-        <v>555.55</v>
+        <v>477.5</v>
       </c>
       <c r="F93" t="n">
-        <v>566.35</v>
+        <v>480.25</v>
       </c>
       <c r="G93" t="n">
-        <v>15501582</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9761,403 +10235,403 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>560</v>
+        <v>485.2</v>
       </c>
       <c r="D94" t="n">
-        <v>569</v>
+        <v>499</v>
       </c>
       <c r="E94" t="n">
-        <v>558.1</v>
+        <v>482.55</v>
       </c>
       <c r="F94" t="n">
-        <v>564.15</v>
+        <v>491.6</v>
       </c>
       <c r="G94" t="n">
-        <v>1471666</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>13.05</v>
+        <v>495</v>
       </c>
       <c r="D95" t="n">
-        <v>13.18</v>
+        <v>498.5</v>
       </c>
       <c r="E95" t="n">
-        <v>12.85</v>
+        <v>491</v>
       </c>
       <c r="F95" t="n">
-        <v>12.87</v>
+        <v>495.05</v>
       </c>
       <c r="G95" t="n">
-        <v>230386335</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12.98</v>
+        <v>495.05</v>
       </c>
       <c r="D96" t="n">
-        <v>13.08</v>
+        <v>504.3</v>
       </c>
       <c r="E96" t="n">
-        <v>12.76</v>
+        <v>490.05</v>
       </c>
       <c r="F96" t="n">
-        <v>13.01</v>
+        <v>492.35</v>
       </c>
       <c r="G96" t="n">
-        <v>387269596</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>13.01</v>
+        <v>496.2</v>
       </c>
       <c r="D97" t="n">
-        <v>13.11</v>
+        <v>539.6</v>
       </c>
       <c r="E97" t="n">
-        <v>12.82</v>
+        <v>495.1</v>
       </c>
       <c r="F97" t="n">
-        <v>12.86</v>
+        <v>533.8</v>
       </c>
       <c r="G97" t="n">
-        <v>235409728</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>12.89</v>
+        <v>542.45</v>
       </c>
       <c r="D98" t="n">
-        <v>13.05</v>
+        <v>551</v>
       </c>
       <c r="E98" t="n">
-        <v>12.73</v>
+        <v>525.55</v>
       </c>
       <c r="F98" t="n">
-        <v>12.9</v>
+        <v>545.95</v>
       </c>
       <c r="G98" t="n">
-        <v>308781891</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12.91</v>
+        <v>543.75</v>
       </c>
       <c r="D99" t="n">
-        <v>13.04</v>
+        <v>548</v>
       </c>
       <c r="E99" t="n">
-        <v>12.77</v>
+        <v>532.1</v>
       </c>
       <c r="F99" t="n">
-        <v>12.8</v>
+        <v>536.1</v>
       </c>
       <c r="G99" t="n">
-        <v>204366752</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12.89</v>
+        <v>537.95</v>
       </c>
       <c r="D100" t="n">
-        <v>12.9</v>
+        <v>552</v>
       </c>
       <c r="E100" t="n">
-        <v>12.63</v>
+        <v>522</v>
       </c>
       <c r="F100" t="n">
-        <v>12.63</v>
+        <v>526.25</v>
       </c>
       <c r="G100" t="n">
-        <v>204537429</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>12.64</v>
+        <v>531</v>
       </c>
       <c r="D101" t="n">
-        <v>12.88</v>
+        <v>538.8</v>
       </c>
       <c r="E101" t="n">
-        <v>12.6</v>
+        <v>527.7</v>
       </c>
       <c r="F101" t="n">
-        <v>12.73</v>
+        <v>533.3</v>
       </c>
       <c r="G101" t="n">
-        <v>205855564</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>12.92</v>
+        <v>530.85</v>
       </c>
       <c r="D102" t="n">
-        <v>13.07</v>
+        <v>569.9</v>
       </c>
       <c r="E102" t="n">
-        <v>12.77</v>
+        <v>529.6</v>
       </c>
       <c r="F102" t="n">
-        <v>12.92</v>
+        <v>547.7</v>
       </c>
       <c r="G102" t="n">
-        <v>413469644</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13.14</v>
+        <v>549</v>
       </c>
       <c r="D103" t="n">
-        <v>13.3</v>
+        <v>570.5</v>
       </c>
       <c r="E103" t="n">
-        <v>12.79</v>
+        <v>542</v>
       </c>
       <c r="F103" t="n">
-        <v>12.89</v>
+        <v>544.45</v>
       </c>
       <c r="G103" t="n">
-        <v>662095209</v>
+        <v>14649216</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>12.93</v>
+        <v>546.5</v>
       </c>
       <c r="D104" t="n">
-        <v>13.69</v>
+        <v>546.7</v>
       </c>
       <c r="E104" t="n">
-        <v>12.83</v>
+        <v>515</v>
       </c>
       <c r="F104" t="n">
-        <v>13.5</v>
+        <v>529.05</v>
       </c>
       <c r="G104" t="n">
-        <v>772547405</v>
+        <v>8696054</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>13.67</v>
+        <v>535</v>
       </c>
       <c r="D105" t="n">
-        <v>13.88</v>
+        <v>574.9</v>
       </c>
       <c r="E105" t="n">
-        <v>13.46</v>
+        <v>534.1</v>
       </c>
       <c r="F105" t="n">
-        <v>13.51</v>
+        <v>572.65</v>
       </c>
       <c r="G105" t="n">
-        <v>547253456</v>
+        <v>29333771</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13.53</v>
+        <v>568.6</v>
       </c>
       <c r="D106" t="n">
-        <v>14.19</v>
+        <v>576.7</v>
       </c>
       <c r="E106" t="n">
-        <v>13.49</v>
+        <v>555.55</v>
       </c>
       <c r="F106" t="n">
-        <v>14.11</v>
+        <v>566.35</v>
       </c>
       <c r="G106" t="n">
-        <v>778908986</v>
+        <v>15501582</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>14.11</v>
+        <v>560</v>
       </c>
       <c r="D107" t="n">
-        <v>14.14</v>
+        <v>569</v>
       </c>
       <c r="E107" t="n">
-        <v>13.66</v>
+        <v>553</v>
       </c>
       <c r="F107" t="n">
-        <v>13.71</v>
+        <v>554.85</v>
       </c>
       <c r="G107" t="n">
-        <v>310430357</v>
+        <v>5929490</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>13.65</v>
+        <v>565</v>
       </c>
       <c r="D108" t="n">
-        <v>14.31</v>
+        <v>574.7</v>
       </c>
       <c r="E108" t="n">
-        <v>13.5</v>
+        <v>558.9</v>
       </c>
       <c r="F108" t="n">
-        <v>14.12</v>
+        <v>560.95</v>
       </c>
       <c r="G108" t="n">
-        <v>820797167</v>
+        <v>3461008</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10166,430 +10640,430 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14.12</v>
+        <v>13.05</v>
       </c>
       <c r="D109" t="n">
-        <v>14.22</v>
+        <v>13.18</v>
       </c>
       <c r="E109" t="n">
-        <v>14</v>
+        <v>12.85</v>
       </c>
       <c r="F109" t="n">
-        <v>14.01</v>
+        <v>12.87</v>
       </c>
       <c r="G109" t="n">
-        <v>86391090</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1554.3</v>
+        <v>12.98</v>
       </c>
       <c r="D110" t="n">
-        <v>1569</v>
+        <v>13.08</v>
       </c>
       <c r="E110" t="n">
-        <v>1551.3</v>
+        <v>12.76</v>
       </c>
       <c r="F110" t="n">
-        <v>1557.6</v>
+        <v>13.01</v>
       </c>
       <c r="G110" t="n">
-        <v>1001677</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1560.4</v>
+        <v>13.01</v>
       </c>
       <c r="D111" t="n">
-        <v>1561</v>
+        <v>13.11</v>
       </c>
       <c r="E111" t="n">
-        <v>1520.4</v>
+        <v>12.82</v>
       </c>
       <c r="F111" t="n">
-        <v>1529.8</v>
+        <v>12.86</v>
       </c>
       <c r="G111" t="n">
-        <v>1011017</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1534.9</v>
+        <v>12.89</v>
       </c>
       <c r="D112" t="n">
-        <v>1572.2</v>
+        <v>13.05</v>
       </c>
       <c r="E112" t="n">
-        <v>1527.2</v>
+        <v>12.73</v>
       </c>
       <c r="F112" t="n">
-        <v>1558.9</v>
+        <v>12.9</v>
       </c>
       <c r="G112" t="n">
-        <v>1235837</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1559.7</v>
+        <v>12.91</v>
       </c>
       <c r="D113" t="n">
-        <v>1600.1</v>
+        <v>13.04</v>
       </c>
       <c r="E113" t="n">
-        <v>1557</v>
+        <v>12.77</v>
       </c>
       <c r="F113" t="n">
-        <v>1593.2</v>
+        <v>12.8</v>
       </c>
       <c r="G113" t="n">
-        <v>1871739</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1591</v>
+        <v>12.89</v>
       </c>
       <c r="D114" t="n">
-        <v>1593.2</v>
+        <v>12.9</v>
       </c>
       <c r="E114" t="n">
-        <v>1566</v>
+        <v>12.63</v>
       </c>
       <c r="F114" t="n">
-        <v>1577.8</v>
+        <v>12.63</v>
       </c>
       <c r="G114" t="n">
-        <v>1183077</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1577.7</v>
+        <v>12.64</v>
       </c>
       <c r="D115" t="n">
-        <v>1586.1</v>
+        <v>12.88</v>
       </c>
       <c r="E115" t="n">
-        <v>1561.1</v>
+        <v>12.6</v>
       </c>
       <c r="F115" t="n">
-        <v>1568.3</v>
+        <v>12.73</v>
       </c>
       <c r="G115" t="n">
-        <v>1098268</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1560</v>
+        <v>12.92</v>
       </c>
       <c r="D116" t="n">
-        <v>1610</v>
+        <v>13.07</v>
       </c>
       <c r="E116" t="n">
-        <v>1554.9</v>
+        <v>12.77</v>
       </c>
       <c r="F116" t="n">
-        <v>1601.2</v>
+        <v>12.92</v>
       </c>
       <c r="G116" t="n">
-        <v>2647403</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1624.8</v>
+        <v>13.14</v>
       </c>
       <c r="D117" t="n">
-        <v>1734.5</v>
+        <v>13.3</v>
       </c>
       <c r="E117" t="n">
-        <v>1617.1</v>
+        <v>12.79</v>
       </c>
       <c r="F117" t="n">
-        <v>1713.4</v>
+        <v>12.89</v>
       </c>
       <c r="G117" t="n">
-        <v>7989771</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1713</v>
+        <v>12.93</v>
       </c>
       <c r="D118" t="n">
-        <v>1762</v>
+        <v>13.69</v>
       </c>
       <c r="E118" t="n">
-        <v>1707.7</v>
+        <v>12.83</v>
       </c>
       <c r="F118" t="n">
-        <v>1758.9</v>
+        <v>13.5</v>
       </c>
       <c r="G118" t="n">
-        <v>4407907</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1762</v>
+        <v>13.67</v>
       </c>
       <c r="D119" t="n">
-        <v>1797.9</v>
+        <v>13.88</v>
       </c>
       <c r="E119" t="n">
-        <v>1754.3</v>
+        <v>13.46</v>
       </c>
       <c r="F119" t="n">
-        <v>1781.3</v>
+        <v>13.51</v>
       </c>
       <c r="G119" t="n">
-        <v>3000811</v>
+        <v>547253456</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1785</v>
+        <v>13.53</v>
       </c>
       <c r="D120" t="n">
-        <v>1798.9</v>
+        <v>14.19</v>
       </c>
       <c r="E120" t="n">
-        <v>1773.3</v>
+        <v>13.49</v>
       </c>
       <c r="F120" t="n">
-        <v>1781.3</v>
+        <v>14.11</v>
       </c>
       <c r="G120" t="n">
-        <v>2402202</v>
+        <v>778908986</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1785</v>
+        <v>14.11</v>
       </c>
       <c r="D121" t="n">
-        <v>1826.6</v>
+        <v>14.14</v>
       </c>
       <c r="E121" t="n">
-        <v>1785</v>
+        <v>13.66</v>
       </c>
       <c r="F121" t="n">
-        <v>1816.2</v>
+        <v>13.71</v>
       </c>
       <c r="G121" t="n">
-        <v>2502579</v>
+        <v>310430357</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1821</v>
+        <v>13.65</v>
       </c>
       <c r="D122" t="n">
-        <v>1838.3</v>
+        <v>14.31</v>
       </c>
       <c r="E122" t="n">
-        <v>1789.1</v>
+        <v>13.5</v>
       </c>
       <c r="F122" t="n">
-        <v>1811.4</v>
+        <v>14.12</v>
       </c>
       <c r="G122" t="n">
-        <v>1919384</v>
+        <v>820797167</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1811</v>
+        <v>14.12</v>
       </c>
       <c r="D123" t="n">
-        <v>1850</v>
+        <v>14.22</v>
       </c>
       <c r="E123" t="n">
-        <v>1806.1</v>
+        <v>13.88</v>
       </c>
       <c r="F123" t="n">
-        <v>1850</v>
+        <v>14.07</v>
       </c>
       <c r="G123" t="n">
-        <v>1405192</v>
+        <v>320742876</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1854</v>
+        <v>14.14</v>
       </c>
       <c r="D124" t="n">
-        <v>1856.6</v>
+        <v>14.19</v>
       </c>
       <c r="E124" t="n">
-        <v>1834.5</v>
+        <v>14.05</v>
       </c>
       <c r="F124" t="n">
-        <v>1835</v>
+        <v>14.05</v>
       </c>
       <c r="G124" t="n">
-        <v>2090998</v>
+        <v>58825145</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10598,25 +11072,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1843</v>
+        <v>1554.3</v>
       </c>
       <c r="D125" t="n">
-        <v>1854.9</v>
+        <v>1569</v>
       </c>
       <c r="E125" t="n">
-        <v>1830</v>
+        <v>1551.3</v>
       </c>
       <c r="F125" t="n">
-        <v>1830</v>
+        <v>1557.6</v>
       </c>
       <c r="G125" t="n">
-        <v>2037418</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10625,25 +11099,25 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1838</v>
+        <v>1560.4</v>
       </c>
       <c r="D126" t="n">
-        <v>1856</v>
+        <v>1561</v>
       </c>
       <c r="E126" t="n">
-        <v>1833.2</v>
+        <v>1520.4</v>
       </c>
       <c r="F126" t="n">
-        <v>1844.3</v>
+        <v>1529.8</v>
       </c>
       <c r="G126" t="n">
-        <v>1553067</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10652,25 +11126,25 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1845</v>
+        <v>1534.9</v>
       </c>
       <c r="D127" t="n">
-        <v>1870.8</v>
+        <v>1572.2</v>
       </c>
       <c r="E127" t="n">
-        <v>1832.8</v>
+        <v>1527.2</v>
       </c>
       <c r="F127" t="n">
-        <v>1854</v>
+        <v>1558.9</v>
       </c>
       <c r="G127" t="n">
-        <v>1386592</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10679,25 +11153,25 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1851</v>
+        <v>1559.7</v>
       </c>
       <c r="D128" t="n">
-        <v>1859</v>
+        <v>1600.1</v>
       </c>
       <c r="E128" t="n">
-        <v>1833.1</v>
+        <v>1557</v>
       </c>
       <c r="F128" t="n">
-        <v>1858</v>
+        <v>1593.2</v>
       </c>
       <c r="G128" t="n">
-        <v>1514239</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10706,25 +11180,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1856.3</v>
+        <v>1591</v>
       </c>
       <c r="D129" t="n">
-        <v>1862.3</v>
+        <v>1593.2</v>
       </c>
       <c r="E129" t="n">
-        <v>1835</v>
+        <v>1566</v>
       </c>
       <c r="F129" t="n">
-        <v>1850</v>
+        <v>1577.8</v>
       </c>
       <c r="G129" t="n">
-        <v>1088545</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10733,25 +11207,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1850</v>
+        <v>1577.7</v>
       </c>
       <c r="D130" t="n">
-        <v>1851.7</v>
+        <v>1586.1</v>
       </c>
       <c r="E130" t="n">
-        <v>1820.6</v>
+        <v>1561.1</v>
       </c>
       <c r="F130" t="n">
-        <v>1851.7</v>
+        <v>1568.3</v>
       </c>
       <c r="G130" t="n">
-        <v>1345856</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10760,25 +11234,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1849.9</v>
+        <v>1560</v>
       </c>
       <c r="D131" t="n">
-        <v>1853.2</v>
+        <v>1610</v>
       </c>
       <c r="E131" t="n">
-        <v>1777.7</v>
+        <v>1554.9</v>
       </c>
       <c r="F131" t="n">
-        <v>1787.3</v>
+        <v>1601.2</v>
       </c>
       <c r="G131" t="n">
-        <v>1581352</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10787,25 +11261,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1770</v>
+        <v>1624.8</v>
       </c>
       <c r="D132" t="n">
-        <v>1824</v>
+        <v>1734.5</v>
       </c>
       <c r="E132" t="n">
-        <v>1769.4</v>
+        <v>1617.1</v>
       </c>
       <c r="F132" t="n">
-        <v>1809.7</v>
+        <v>1713.4</v>
       </c>
       <c r="G132" t="n">
-        <v>1631767</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10814,25 +11288,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1810</v>
+        <v>1713</v>
       </c>
       <c r="D133" t="n">
-        <v>1824.6</v>
+        <v>1762</v>
       </c>
       <c r="E133" t="n">
-        <v>1802.1</v>
+        <v>1707.7</v>
       </c>
       <c r="F133" t="n">
-        <v>1814</v>
+        <v>1758.9</v>
       </c>
       <c r="G133" t="n">
-        <v>1291914</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10841,457 +11315,457 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1814</v>
+        <v>1762</v>
       </c>
       <c r="D134" t="n">
-        <v>1818</v>
+        <v>1797.9</v>
       </c>
       <c r="E134" t="n">
-        <v>1796.8</v>
+        <v>1754.3</v>
       </c>
       <c r="F134" t="n">
-        <v>1797.2</v>
+        <v>1781.3</v>
       </c>
       <c r="G134" t="n">
-        <v>209921</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>344</v>
+        <v>1785</v>
       </c>
       <c r="D135" t="n">
-        <v>346.3</v>
+        <v>1798.9</v>
       </c>
       <c r="E135" t="n">
-        <v>341.25</v>
+        <v>1773.3</v>
       </c>
       <c r="F135" t="n">
-        <v>342.9</v>
+        <v>1781.3</v>
       </c>
       <c r="G135" t="n">
-        <v>4465145</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>344.2</v>
+        <v>1785</v>
       </c>
       <c r="D136" t="n">
-        <v>347.75</v>
+        <v>1826.6</v>
       </c>
       <c r="E136" t="n">
-        <v>339.95</v>
+        <v>1785</v>
       </c>
       <c r="F136" t="n">
-        <v>342.4</v>
+        <v>1816.2</v>
       </c>
       <c r="G136" t="n">
-        <v>3803051</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>346</v>
+        <v>1821</v>
       </c>
       <c r="D137" t="n">
-        <v>351</v>
+        <v>1838.3</v>
       </c>
       <c r="E137" t="n">
-        <v>343.65</v>
+        <v>1789.1</v>
       </c>
       <c r="F137" t="n">
-        <v>346</v>
+        <v>1811.4</v>
       </c>
       <c r="G137" t="n">
-        <v>5175178</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>341.8</v>
+        <v>1811</v>
       </c>
       <c r="D138" t="n">
-        <v>344.9</v>
+        <v>1850</v>
       </c>
       <c r="E138" t="n">
-        <v>339.65</v>
+        <v>1806.1</v>
       </c>
       <c r="F138" t="n">
-        <v>343.9</v>
+        <v>1850</v>
       </c>
       <c r="G138" t="n">
-        <v>2253982</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>345.1</v>
+        <v>1854</v>
       </c>
       <c r="D139" t="n">
-        <v>346.05</v>
+        <v>1856.6</v>
       </c>
       <c r="E139" t="n">
-        <v>338.35</v>
+        <v>1834.5</v>
       </c>
       <c r="F139" t="n">
-        <v>339.35</v>
+        <v>1835</v>
       </c>
       <c r="G139" t="n">
-        <v>3868006</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>339.4</v>
+        <v>1843</v>
       </c>
       <c r="D140" t="n">
-        <v>340.2</v>
+        <v>1854.9</v>
       </c>
       <c r="E140" t="n">
-        <v>333</v>
+        <v>1830</v>
       </c>
       <c r="F140" t="n">
-        <v>334.55</v>
+        <v>1830</v>
       </c>
       <c r="G140" t="n">
-        <v>3721274</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>335</v>
+        <v>1838</v>
       </c>
       <c r="D141" t="n">
-        <v>346.1</v>
+        <v>1856</v>
       </c>
       <c r="E141" t="n">
-        <v>332</v>
+        <v>1833.2</v>
       </c>
       <c r="F141" t="n">
-        <v>344.7</v>
+        <v>1844.3</v>
       </c>
       <c r="G141" t="n">
-        <v>5431501</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>345.5</v>
+        <v>1845</v>
       </c>
       <c r="D142" t="n">
-        <v>349.65</v>
+        <v>1870.8</v>
       </c>
       <c r="E142" t="n">
-        <v>342.6</v>
+        <v>1832.8</v>
       </c>
       <c r="F142" t="n">
-        <v>347.65</v>
+        <v>1854</v>
       </c>
       <c r="G142" t="n">
-        <v>6318472</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>352</v>
+        <v>1851</v>
       </c>
       <c r="D143" t="n">
-        <v>355.75</v>
+        <v>1859</v>
       </c>
       <c r="E143" t="n">
-        <v>347.65</v>
+        <v>1833.1</v>
       </c>
       <c r="F143" t="n">
-        <v>350.05</v>
+        <v>1858</v>
       </c>
       <c r="G143" t="n">
-        <v>7186013</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>357.95</v>
+        <v>1856.3</v>
       </c>
       <c r="D144" t="n">
-        <v>369</v>
+        <v>1862.3</v>
       </c>
       <c r="E144" t="n">
-        <v>353.5</v>
+        <v>1835</v>
       </c>
       <c r="F144" t="n">
-        <v>369</v>
+        <v>1850</v>
       </c>
       <c r="G144" t="n">
-        <v>12541474</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>373</v>
+        <v>1850</v>
       </c>
       <c r="D145" t="n">
-        <v>382.45</v>
+        <v>1851.7</v>
       </c>
       <c r="E145" t="n">
-        <v>367.15</v>
+        <v>1820.6</v>
       </c>
       <c r="F145" t="n">
-        <v>377</v>
+        <v>1851.7</v>
       </c>
       <c r="G145" t="n">
-        <v>15775994</v>
+        <v>1345856</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>381</v>
+        <v>1849.9</v>
       </c>
       <c r="D146" t="n">
-        <v>383.9</v>
+        <v>1853.2</v>
       </c>
       <c r="E146" t="n">
-        <v>375.15</v>
+        <v>1777.7</v>
       </c>
       <c r="F146" t="n">
-        <v>381</v>
+        <v>1787.3</v>
       </c>
       <c r="G146" t="n">
-        <v>8940938</v>
+        <v>1581352</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>385</v>
+        <v>1770</v>
       </c>
       <c r="D147" t="n">
-        <v>385.05</v>
+        <v>1824</v>
       </c>
       <c r="E147" t="n">
-        <v>376.5</v>
+        <v>1769.4</v>
       </c>
       <c r="F147" t="n">
-        <v>381</v>
+        <v>1809.7</v>
       </c>
       <c r="G147" t="n">
-        <v>6636333</v>
+        <v>1631767</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>382.5</v>
+        <v>1810</v>
       </c>
       <c r="D148" t="n">
-        <v>382.85</v>
+        <v>1824.6</v>
       </c>
       <c r="E148" t="n">
-        <v>377.15</v>
+        <v>1802.1</v>
       </c>
       <c r="F148" t="n">
-        <v>381</v>
+        <v>1814</v>
       </c>
       <c r="G148" t="n">
-        <v>4423953</v>
+        <v>1291914</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>381.7</v>
+        <v>1814</v>
       </c>
       <c r="D149" t="n">
-        <v>387.7</v>
+        <v>1818</v>
       </c>
       <c r="E149" t="n">
-        <v>381.1</v>
+        <v>1789.9</v>
       </c>
       <c r="F149" t="n">
-        <v>382.7</v>
+        <v>1801.8</v>
       </c>
       <c r="G149" t="n">
-        <v>5292453</v>
+        <v>1426377</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>387.15</v>
+        <v>1819</v>
       </c>
       <c r="D150" t="n">
-        <v>393.7</v>
+        <v>1832</v>
       </c>
       <c r="E150" t="n">
-        <v>384.5</v>
+        <v>1813.8</v>
       </c>
       <c r="F150" t="n">
-        <v>388</v>
+        <v>1818.4</v>
       </c>
       <c r="G150" t="n">
-        <v>8155315</v>
+        <v>293760</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11300,25 +11774,25 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>398.5</v>
+        <v>344</v>
       </c>
       <c r="D151" t="n">
-        <v>422.2</v>
+        <v>346.3</v>
       </c>
       <c r="E151" t="n">
-        <v>398.5</v>
+        <v>341.25</v>
       </c>
       <c r="F151" t="n">
-        <v>420</v>
+        <v>342.9</v>
       </c>
       <c r="G151" t="n">
-        <v>34388331</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11327,25 +11801,25 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>410.5</v>
+        <v>344.2</v>
       </c>
       <c r="D152" t="n">
-        <v>413.65</v>
+        <v>347.75</v>
       </c>
       <c r="E152" t="n">
-        <v>400</v>
+        <v>339.95</v>
       </c>
       <c r="F152" t="n">
-        <v>400.5</v>
+        <v>342.4</v>
       </c>
       <c r="G152" t="n">
-        <v>9738984</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11354,25 +11828,25 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>378.6</v>
+        <v>346</v>
       </c>
       <c r="D153" t="n">
-        <v>384.95</v>
+        <v>351</v>
       </c>
       <c r="E153" t="n">
-        <v>375</v>
+        <v>343.65</v>
       </c>
       <c r="F153" t="n">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="G153" t="n">
-        <v>14954594</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11381,25 +11855,25 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>377.9</v>
+        <v>341.8</v>
       </c>
       <c r="D154" t="n">
-        <v>391.5</v>
+        <v>344.9</v>
       </c>
       <c r="E154" t="n">
-        <v>376.5</v>
+        <v>339.65</v>
       </c>
       <c r="F154" t="n">
-        <v>387.55</v>
+        <v>343.9</v>
       </c>
       <c r="G154" t="n">
-        <v>9724992</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11408,25 +11882,25 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>386.8</v>
+        <v>345.1</v>
       </c>
       <c r="D155" t="n">
-        <v>390.85</v>
+        <v>346.05</v>
       </c>
       <c r="E155" t="n">
-        <v>385.8</v>
+        <v>338.35</v>
       </c>
       <c r="F155" t="n">
-        <v>388</v>
+        <v>339.35</v>
       </c>
       <c r="G155" t="n">
-        <v>2824411</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11435,484 +11909,484 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>382</v>
+        <v>339.4</v>
       </c>
       <c r="D156" t="n">
-        <v>383</v>
+        <v>340.2</v>
       </c>
       <c r="E156" t="n">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="F156" t="n">
-        <v>380.25</v>
+        <v>334.55</v>
       </c>
       <c r="G156" t="n">
-        <v>880356</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4389.8</v>
+        <v>335</v>
       </c>
       <c r="D157" t="n">
-        <v>4485</v>
+        <v>346.1</v>
       </c>
       <c r="E157" t="n">
-        <v>4361.9</v>
+        <v>332</v>
       </c>
       <c r="F157" t="n">
-        <v>4398.1</v>
+        <v>344.7</v>
       </c>
       <c r="G157" t="n">
-        <v>1347378</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4422</v>
+        <v>345.5</v>
       </c>
       <c r="D158" t="n">
-        <v>4495</v>
+        <v>349.65</v>
       </c>
       <c r="E158" t="n">
-        <v>4358</v>
+        <v>342.6</v>
       </c>
       <c r="F158" t="n">
-        <v>4371.4</v>
+        <v>347.65</v>
       </c>
       <c r="G158" t="n">
-        <v>902264</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4387.7</v>
+        <v>352</v>
       </c>
       <c r="D159" t="n">
-        <v>4404</v>
+        <v>355.75</v>
       </c>
       <c r="E159" t="n">
-        <v>4281.9</v>
+        <v>347.65</v>
       </c>
       <c r="F159" t="n">
-        <v>4304.2</v>
+        <v>350.05</v>
       </c>
       <c r="G159" t="n">
-        <v>463349</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4285</v>
+        <v>357.95</v>
       </c>
       <c r="D160" t="n">
-        <v>4317</v>
+        <v>369</v>
       </c>
       <c r="E160" t="n">
-        <v>4220</v>
+        <v>353.5</v>
       </c>
       <c r="F160" t="n">
-        <v>4244.3</v>
+        <v>369</v>
       </c>
       <c r="G160" t="n">
-        <v>398348</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4211</v>
+        <v>373</v>
       </c>
       <c r="D161" t="n">
-        <v>4220</v>
+        <v>382.45</v>
       </c>
       <c r="E161" t="n">
-        <v>4129.3</v>
+        <v>367.15</v>
       </c>
       <c r="F161" t="n">
-        <v>4178.1</v>
+        <v>377</v>
       </c>
       <c r="G161" t="n">
-        <v>470046</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4190</v>
+        <v>381</v>
       </c>
       <c r="D162" t="n">
-        <v>4324.4</v>
+        <v>383.9</v>
       </c>
       <c r="E162" t="n">
-        <v>4190</v>
+        <v>375.15</v>
       </c>
       <c r="F162" t="n">
-        <v>4257.3</v>
+        <v>381</v>
       </c>
       <c r="G162" t="n">
-        <v>633457</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4290</v>
+        <v>385</v>
       </c>
       <c r="D163" t="n">
-        <v>4383</v>
+        <v>385.05</v>
       </c>
       <c r="E163" t="n">
-        <v>4266</v>
+        <v>376.5</v>
       </c>
       <c r="F163" t="n">
-        <v>4288.7</v>
+        <v>381</v>
       </c>
       <c r="G163" t="n">
-        <v>835107</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4299</v>
+        <v>382.5</v>
       </c>
       <c r="D164" t="n">
-        <v>4340</v>
+        <v>382.85</v>
       </c>
       <c r="E164" t="n">
-        <v>4216</v>
+        <v>377.15</v>
       </c>
       <c r="F164" t="n">
-        <v>4243.8</v>
+        <v>381</v>
       </c>
       <c r="G164" t="n">
-        <v>422024</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4201.9</v>
+        <v>381.7</v>
       </c>
       <c r="D165" t="n">
-        <v>4222</v>
+        <v>387.7</v>
       </c>
       <c r="E165" t="n">
-        <v>4115</v>
+        <v>381.1</v>
       </c>
       <c r="F165" t="n">
-        <v>4156</v>
+        <v>382.7</v>
       </c>
       <c r="G165" t="n">
-        <v>378694</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4181.8</v>
+        <v>387.15</v>
       </c>
       <c r="D166" t="n">
-        <v>4385</v>
+        <v>393.7</v>
       </c>
       <c r="E166" t="n">
-        <v>4129.4</v>
+        <v>384.5</v>
       </c>
       <c r="F166" t="n">
-        <v>4362.2</v>
+        <v>388</v>
       </c>
       <c r="G166" t="n">
-        <v>992864</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4380</v>
+        <v>398.5</v>
       </c>
       <c r="D167" t="n">
-        <v>4478.3</v>
+        <v>422.2</v>
       </c>
       <c r="E167" t="n">
-        <v>4280.1</v>
+        <v>398.5</v>
       </c>
       <c r="F167" t="n">
-        <v>4395.7</v>
+        <v>420</v>
       </c>
       <c r="G167" t="n">
-        <v>960643</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4497.2</v>
+        <v>410.5</v>
       </c>
       <c r="D168" t="n">
-        <v>4541.17</v>
+        <v>413.65</v>
       </c>
       <c r="E168" t="n">
-        <v>4319.31</v>
+        <v>400</v>
       </c>
       <c r="F168" t="n">
-        <v>4361.38</v>
+        <v>400.5</v>
       </c>
       <c r="G168" t="n">
-        <v>1616021</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4338</v>
+        <v>378.6</v>
       </c>
       <c r="D169" t="n">
-        <v>4339.1</v>
+        <v>384.95</v>
       </c>
       <c r="E169" t="n">
-        <v>4172.9</v>
+        <v>375</v>
       </c>
       <c r="F169" t="n">
-        <v>4192.59</v>
+        <v>376</v>
       </c>
       <c r="G169" t="n">
-        <v>648341</v>
+        <v>14954594</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4297.32</v>
+        <v>377.9</v>
       </c>
       <c r="D170" t="n">
-        <v>4595.14</v>
+        <v>391.5</v>
       </c>
       <c r="E170" t="n">
-        <v>4249.35</v>
+        <v>376.5</v>
       </c>
       <c r="F170" t="n">
-        <v>4521.18</v>
+        <v>387.55</v>
       </c>
       <c r="G170" t="n">
-        <v>4510774</v>
+        <v>9724992</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4557.56</v>
+        <v>386.8</v>
       </c>
       <c r="D171" t="n">
-        <v>4737.05</v>
+        <v>390.85</v>
       </c>
       <c r="E171" t="n">
-        <v>4537.17</v>
+        <v>385.8</v>
       </c>
       <c r="F171" t="n">
-        <v>4583.14</v>
+        <v>388</v>
       </c>
       <c r="G171" t="n">
-        <v>2334958</v>
+        <v>2824411</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4606.13</v>
+        <v>382</v>
       </c>
       <c r="D172" t="n">
-        <v>4777.02</v>
+        <v>386.55</v>
       </c>
       <c r="E172" t="n">
-        <v>4590.24</v>
+        <v>379</v>
       </c>
       <c r="F172" t="n">
-        <v>4759.23</v>
+        <v>386.55</v>
       </c>
       <c r="G172" t="n">
-        <v>1899271</v>
+        <v>3939022</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4817.7</v>
+        <v>392</v>
       </c>
       <c r="D173" t="n">
-        <v>4929.93</v>
+        <v>395.75</v>
       </c>
       <c r="E173" t="n">
-        <v>4722.06</v>
+        <v>387.4</v>
       </c>
       <c r="F173" t="n">
-        <v>4890.75</v>
+        <v>388</v>
       </c>
       <c r="G173" t="n">
-        <v>1924204</v>
+        <v>1481893</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11921,25 +12395,25 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4896.95</v>
+        <v>4389.8</v>
       </c>
       <c r="D174" t="n">
-        <v>4976.9</v>
+        <v>4485</v>
       </c>
       <c r="E174" t="n">
-        <v>4780.02</v>
+        <v>4361.9</v>
       </c>
       <c r="F174" t="n">
-        <v>4813</v>
+        <v>4398.1</v>
       </c>
       <c r="G174" t="n">
-        <v>1117424</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11948,25 +12422,25 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>4790</v>
+        <v>4422</v>
       </c>
       <c r="D175" t="n">
-        <v>4968</v>
+        <v>4495</v>
       </c>
       <c r="E175" t="n">
-        <v>4780</v>
+        <v>4358</v>
       </c>
       <c r="F175" t="n">
-        <v>4939.2</v>
+        <v>4371.4</v>
       </c>
       <c r="G175" t="n">
-        <v>1296942</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11975,25 +12449,25 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4958</v>
+        <v>4387.7</v>
       </c>
       <c r="D176" t="n">
-        <v>5085</v>
+        <v>4404</v>
       </c>
       <c r="E176" t="n">
-        <v>4888.8</v>
+        <v>4281.9</v>
       </c>
       <c r="F176" t="n">
-        <v>4903</v>
+        <v>4304.2</v>
       </c>
       <c r="G176" t="n">
-        <v>1210476</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12002,25 +12476,25 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4903</v>
+        <v>4285</v>
       </c>
       <c r="D177" t="n">
-        <v>4940</v>
+        <v>4317</v>
       </c>
       <c r="E177" t="n">
-        <v>4792.5</v>
+        <v>4220</v>
       </c>
       <c r="F177" t="n">
-        <v>4859.8</v>
+        <v>4244.3</v>
       </c>
       <c r="G177" t="n">
-        <v>682980</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12029,25 +12503,25 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4866</v>
+        <v>4211</v>
       </c>
       <c r="D178" t="n">
-        <v>4907.9</v>
+        <v>4220</v>
       </c>
       <c r="E178" t="n">
-        <v>4753</v>
+        <v>4129.3</v>
       </c>
       <c r="F178" t="n">
-        <v>4837.4</v>
+        <v>4178.1</v>
       </c>
       <c r="G178" t="n">
-        <v>613049</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12056,25 +12530,25 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>4860</v>
+        <v>4190</v>
       </c>
       <c r="D179" t="n">
-        <v>5200</v>
+        <v>4324.4</v>
       </c>
       <c r="E179" t="n">
-        <v>4860</v>
+        <v>4190</v>
       </c>
       <c r="F179" t="n">
-        <v>5181</v>
+        <v>4257.3</v>
       </c>
       <c r="G179" t="n">
-        <v>3457670</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12083,25 +12557,25 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5200</v>
+        <v>4290</v>
       </c>
       <c r="D180" t="n">
-        <v>5269</v>
+        <v>4383</v>
       </c>
       <c r="E180" t="n">
-        <v>4991.3</v>
+        <v>4266</v>
       </c>
       <c r="F180" t="n">
-        <v>5007.2</v>
+        <v>4288.7</v>
       </c>
       <c r="G180" t="n">
-        <v>1695255</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12110,25 +12584,25 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5022</v>
+        <v>4299</v>
       </c>
       <c r="D181" t="n">
-        <v>5225</v>
+        <v>4340</v>
       </c>
       <c r="E181" t="n">
-        <v>5008.3</v>
+        <v>4216</v>
       </c>
       <c r="F181" t="n">
-        <v>5212.4</v>
+        <v>4243.8</v>
       </c>
       <c r="G181" t="n">
-        <v>1438746</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12137,25 +12611,25 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>5110</v>
+        <v>4201.9</v>
       </c>
       <c r="D182" t="n">
-        <v>5396.4</v>
+        <v>4222</v>
       </c>
       <c r="E182" t="n">
-        <v>5092.8</v>
+        <v>4115</v>
       </c>
       <c r="F182" t="n">
-        <v>5354.5</v>
+        <v>4156</v>
       </c>
       <c r="G182" t="n">
-        <v>2395703</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12164,511 +12638,511 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5324.9</v>
+        <v>4181.8</v>
       </c>
       <c r="D183" t="n">
-        <v>5338</v>
+        <v>4385</v>
       </c>
       <c r="E183" t="n">
-        <v>5122</v>
+        <v>4129.4</v>
       </c>
       <c r="F183" t="n">
-        <v>5150.6</v>
+        <v>4362.2</v>
       </c>
       <c r="G183" t="n">
-        <v>473476</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1417</v>
+        <v>4380</v>
       </c>
       <c r="D184" t="n">
-        <v>1436</v>
+        <v>4478.3</v>
       </c>
       <c r="E184" t="n">
-        <v>1410.1</v>
+        <v>4280.1</v>
       </c>
       <c r="F184" t="n">
-        <v>1423.9</v>
+        <v>4395.7</v>
       </c>
       <c r="G184" t="n">
-        <v>623969</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1428</v>
+        <v>4497.2</v>
       </c>
       <c r="D185" t="n">
-        <v>1428</v>
+        <v>4541.17</v>
       </c>
       <c r="E185" t="n">
-        <v>1351.5</v>
+        <v>4319.31</v>
       </c>
       <c r="F185" t="n">
-        <v>1359.1</v>
+        <v>4361.38</v>
       </c>
       <c r="G185" t="n">
-        <v>808190</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1349.8</v>
+        <v>4338</v>
       </c>
       <c r="D186" t="n">
-        <v>1357.8</v>
+        <v>4339.1</v>
       </c>
       <c r="E186" t="n">
-        <v>1330.1</v>
+        <v>4172.9</v>
       </c>
       <c r="F186" t="n">
-        <v>1340.8</v>
+        <v>4192.59</v>
       </c>
       <c r="G186" t="n">
-        <v>345535</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1340.8</v>
+        <v>4297.32</v>
       </c>
       <c r="D187" t="n">
-        <v>1387.7</v>
+        <v>4595.14</v>
       </c>
       <c r="E187" t="n">
-        <v>1316</v>
+        <v>4249.35</v>
       </c>
       <c r="F187" t="n">
-        <v>1374.4</v>
+        <v>4521.18</v>
       </c>
       <c r="G187" t="n">
-        <v>974660</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1372.9</v>
+        <v>4557.56</v>
       </c>
       <c r="D188" t="n">
-        <v>1390</v>
+        <v>4737.05</v>
       </c>
       <c r="E188" t="n">
-        <v>1355.1</v>
+        <v>4537.17</v>
       </c>
       <c r="F188" t="n">
-        <v>1363.5</v>
+        <v>4583.14</v>
       </c>
       <c r="G188" t="n">
-        <v>479123</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1363</v>
+        <v>4606.13</v>
       </c>
       <c r="D189" t="n">
-        <v>1392</v>
+        <v>4777.02</v>
       </c>
       <c r="E189" t="n">
-        <v>1355.1</v>
+        <v>4590.24</v>
       </c>
       <c r="F189" t="n">
-        <v>1380</v>
+        <v>4759.23</v>
       </c>
       <c r="G189" t="n">
-        <v>616767</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1360</v>
+        <v>4817.7</v>
       </c>
       <c r="D190" t="n">
-        <v>1368</v>
+        <v>4929.93</v>
       </c>
       <c r="E190" t="n">
-        <v>1272.1</v>
+        <v>4722.06</v>
       </c>
       <c r="F190" t="n">
-        <v>1288.3</v>
+        <v>4890.75</v>
       </c>
       <c r="G190" t="n">
-        <v>1098492</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1300</v>
+        <v>4896.95</v>
       </c>
       <c r="D191" t="n">
-        <v>1318.5</v>
+        <v>4976.9</v>
       </c>
       <c r="E191" t="n">
-        <v>1257</v>
+        <v>4780.02</v>
       </c>
       <c r="F191" t="n">
-        <v>1316.2</v>
+        <v>4813</v>
       </c>
       <c r="G191" t="n">
-        <v>1172726</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1317.7</v>
+        <v>4790</v>
       </c>
       <c r="D192" t="n">
-        <v>1319.8</v>
+        <v>4968</v>
       </c>
       <c r="E192" t="n">
-        <v>1270.5</v>
+        <v>4780</v>
       </c>
       <c r="F192" t="n">
-        <v>1306</v>
+        <v>4939.2</v>
       </c>
       <c r="G192" t="n">
-        <v>832973</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1319.9</v>
+        <v>4958</v>
       </c>
       <c r="D193" t="n">
-        <v>1355.4</v>
+        <v>5085</v>
       </c>
       <c r="E193" t="n">
-        <v>1308</v>
+        <v>4888.8</v>
       </c>
       <c r="F193" t="n">
-        <v>1343.4</v>
+        <v>4903</v>
       </c>
       <c r="G193" t="n">
-        <v>1287698</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1379</v>
+        <v>4903</v>
       </c>
       <c r="D194" t="n">
-        <v>1468</v>
+        <v>4940</v>
       </c>
       <c r="E194" t="n">
-        <v>1361</v>
+        <v>4792.5</v>
       </c>
       <c r="F194" t="n">
-        <v>1377.8</v>
+        <v>4859.8</v>
       </c>
       <c r="G194" t="n">
-        <v>9950655</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1380.5</v>
+        <v>4866</v>
       </c>
       <c r="D195" t="n">
-        <v>1403.3</v>
+        <v>4907.9</v>
       </c>
       <c r="E195" t="n">
-        <v>1363</v>
+        <v>4753</v>
       </c>
       <c r="F195" t="n">
-        <v>1366.8</v>
+        <v>4837.4</v>
       </c>
       <c r="G195" t="n">
-        <v>1567542</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1380</v>
+        <v>4860</v>
       </c>
       <c r="D196" t="n">
-        <v>1397.5</v>
+        <v>5200</v>
       </c>
       <c r="E196" t="n">
-        <v>1351.6</v>
+        <v>4860</v>
       </c>
       <c r="F196" t="n">
-        <v>1360.6</v>
+        <v>5181</v>
       </c>
       <c r="G196" t="n">
-        <v>1098353</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1360.6</v>
+        <v>5200</v>
       </c>
       <c r="D197" t="n">
-        <v>1428</v>
+        <v>5269</v>
       </c>
       <c r="E197" t="n">
-        <v>1354.5</v>
+        <v>4991.3</v>
       </c>
       <c r="F197" t="n">
-        <v>1421.6</v>
+        <v>5007.2</v>
       </c>
       <c r="G197" t="n">
-        <v>2055261</v>
+        <v>1695255</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1428.14</v>
+        <v>5022</v>
       </c>
       <c r="D198" t="n">
-        <v>1451.52</v>
+        <v>5225</v>
       </c>
       <c r="E198" t="n">
-        <v>1417.55</v>
+        <v>5008.3</v>
       </c>
       <c r="F198" t="n">
-        <v>1432.63</v>
+        <v>5212.4</v>
       </c>
       <c r="G198" t="n">
-        <v>1243415</v>
+        <v>1438746</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1432.53</v>
+        <v>5110</v>
       </c>
       <c r="D199" t="n">
-        <v>1458.51</v>
+        <v>5396.4</v>
       </c>
       <c r="E199" t="n">
-        <v>1403.56</v>
+        <v>5092.8</v>
       </c>
       <c r="F199" t="n">
-        <v>1416.55</v>
+        <v>5354.5</v>
       </c>
       <c r="G199" t="n">
-        <v>1123973</v>
+        <v>2395703</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1412.46</v>
+        <v>5324.9</v>
       </c>
       <c r="D200" t="n">
-        <v>1432.53</v>
+        <v>5338</v>
       </c>
       <c r="E200" t="n">
-        <v>1406.06</v>
+        <v>5025</v>
       </c>
       <c r="F200" t="n">
-        <v>1423.24</v>
+        <v>5065</v>
       </c>
       <c r="G200" t="n">
-        <v>509551</v>
+        <v>1923210</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1432.63</v>
+        <v>5095.7</v>
       </c>
       <c r="D201" t="n">
-        <v>1520.44</v>
+        <v>5224.8</v>
       </c>
       <c r="E201" t="n">
-        <v>1426.04</v>
+        <v>5093</v>
       </c>
       <c r="F201" t="n">
-        <v>1514.85</v>
+        <v>5216.1</v>
       </c>
       <c r="G201" t="n">
-        <v>3863757</v>
+        <v>457693</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12677,25 +13151,25 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1514.85</v>
+        <v>1417</v>
       </c>
       <c r="D202" t="n">
-        <v>1541.42</v>
+        <v>1436</v>
       </c>
       <c r="E202" t="n">
-        <v>1485.38</v>
+        <v>1410.1</v>
       </c>
       <c r="F202" t="n">
-        <v>1493.27</v>
+        <v>1423.9</v>
       </c>
       <c r="G202" t="n">
-        <v>1508375</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12704,25 +13178,25 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1493.27</v>
+        <v>1428</v>
       </c>
       <c r="D203" t="n">
-        <v>1512.45</v>
+        <v>1428</v>
       </c>
       <c r="E203" t="n">
-        <v>1463.6</v>
+        <v>1351.5</v>
       </c>
       <c r="F203" t="n">
-        <v>1471.79</v>
+        <v>1359.1</v>
       </c>
       <c r="G203" t="n">
-        <v>749197</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12731,25 +13205,25 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1480.39</v>
+        <v>1349.8</v>
       </c>
       <c r="D204" t="n">
-        <v>1498.97</v>
+        <v>1357.8</v>
       </c>
       <c r="E204" t="n">
-        <v>1449.52</v>
+        <v>1330.1</v>
       </c>
       <c r="F204" t="n">
-        <v>1466.2</v>
+        <v>1340.8</v>
       </c>
       <c r="G204" t="n">
-        <v>742118</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12758,25 +13232,25 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1478.49</v>
+        <v>1340.8</v>
       </c>
       <c r="D205" t="n">
-        <v>1505.16</v>
+        <v>1387.7</v>
       </c>
       <c r="E205" t="n">
-        <v>1450.52</v>
+        <v>1316</v>
       </c>
       <c r="F205" t="n">
-        <v>1463.7</v>
+        <v>1374.4</v>
       </c>
       <c r="G205" t="n">
-        <v>811337</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12785,25 +13259,25 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1475.79</v>
+        <v>1372.9</v>
       </c>
       <c r="D206" t="n">
-        <v>1502.06</v>
+        <v>1390</v>
       </c>
       <c r="E206" t="n">
-        <v>1457.01</v>
+        <v>1355.1</v>
       </c>
       <c r="F206" t="n">
-        <v>1466.4</v>
+        <v>1363.5</v>
       </c>
       <c r="G206" t="n">
-        <v>972670</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12812,46 +13286,559 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1489.9</v>
+        <v>1363</v>
       </c>
       <c r="D207" t="n">
-        <v>1521</v>
+        <v>1392</v>
       </c>
       <c r="E207" t="n">
-        <v>1488.9</v>
+        <v>1355.1</v>
       </c>
       <c r="F207" t="n">
-        <v>1500.1</v>
+        <v>1380</v>
       </c>
       <c r="G207" t="n">
-        <v>2323890</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1288.3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1098492</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1318.5</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1257</v>
+      </c>
+      <c r="F209" t="n">
+        <v>1316.2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>1172726</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1317.7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G210" t="n">
+        <v>832973</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1308</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1287698</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1361</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1377.8</v>
+      </c>
+      <c r="G212" t="n">
+        <v>9950655</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1403.3</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1363</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1567542</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1397.5</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1351.6</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1098353</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1360.6</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1428</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1354.5</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1421.6</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2055261</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1428.14</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1451.52</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1417.55</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1243415</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1458.51</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1403.56</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1416.55</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1123973</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1412.46</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1406.06</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1423.24</v>
+      </c>
+      <c r="G218" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1520.44</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1426.04</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1541.42</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1485.38</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1512.45</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1463.6</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1471.79</v>
+      </c>
+      <c r="G221" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1480.39</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1498.97</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1449.52</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1466.2</v>
+      </c>
+      <c r="G222" t="n">
+        <v>742118</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1478.49</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1505.16</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1450.52</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="G223" t="n">
+        <v>811337</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1475.79</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1502.06</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1457.01</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1466.4</v>
+      </c>
+      <c r="G224" t="n">
+        <v>972670</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1489.9</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1488.9</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1500.1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2323890</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C208" t="n">
+      <c r="C226" t="n">
         <v>1507.9</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D226" t="n">
         <v>1514.6</v>
       </c>
-      <c r="E208" t="n">
-        <v>1491</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1504.4</v>
-      </c>
-      <c r="G208" t="n">
-        <v>182467</v>
+      <c r="E226" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="G226" t="n">
+        <v>901426</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1504.8</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1525.8</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1512.5</v>
+      </c>
+      <c r="G227" t="n">
+        <v>247380</v>
       </c>
     </row>
   </sheetData>
@@ -12865,7 +13852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13095,6 +14082,21 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 20 Aug 2026 04:08</t>
+          <t>Generated 21 Aug 2026 04:10</t>
         </is>
       </c>
     </row>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="F2" t="n">
         <v>4.66</v>
@@ -619,7 +619,7 @@
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="3">
@@ -629,25 +629,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>4.23</v>
+        <v>3.73</v>
       </c>
       <c r="D3" t="n">
-        <v>3.01</v>
+        <v>2.87</v>
       </c>
       <c r="E3" t="n">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="F3" t="n">
         <v>20.67</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.62</v>
+        <v>-3.9</v>
       </c>
       <c r="H3" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="4">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="D4" t="n">
-        <v>6.74</v>
+        <v>6.58</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>79.2</v>
       </c>
       <c r="F4" t="n">
         <v>26.91</v>
@@ -675,7 +675,7 @@
         <v>-6.17</v>
       </c>
       <c r="H4" t="n">
-        <v>8.029999999999999</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>11.73</v>
+        <v>11.22</v>
       </c>
       <c r="D5" t="n">
         <v>16.13</v>
@@ -703,7 +703,7 @@
         <v>-6.45</v>
       </c>
       <c r="H5" t="n">
-        <v>10.61</v>
+        <v>10.81</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,6 +3527,192 @@
         <v>1</v>
       </c>
       <c r="P46" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100</v>
+      </c>
+      <c r="F47" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>226.15</v>
+      </c>
+      <c r="I47" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="K47" t="n">
+        <v>245.51</v>
+      </c>
+      <c r="L47" t="n">
+        <v>264.87</v>
+      </c>
+      <c r="M47" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>99</v>
+      </c>
+      <c r="F48" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>576.65</v>
+      </c>
+      <c r="I48" t="n">
+        <v>533.86</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="K48" t="n">
+        <v>619.4400000000001</v>
+      </c>
+      <c r="L48" t="n">
+        <v>662.23</v>
+      </c>
+      <c r="M48" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>model=momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>99</v>
+      </c>
+      <c r="F49" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="K49" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L49" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="O49" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>model=momentum</t>
         </is>
@@ -3543,7 +3729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5016,6 +5202,105 @@
       </c>
       <c r="I46" t="n">
         <v>15.71</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>226.15</v>
+      </c>
+      <c r="E47" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="G47" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="H47" t="n">
+        <v>245.51</v>
+      </c>
+      <c r="I47" t="n">
+        <v>264.87</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>576.65</v>
+      </c>
+      <c r="E48" t="n">
+        <v>533.86</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G48" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="H48" t="n">
+        <v>619.4400000000001</v>
+      </c>
+      <c r="I48" t="n">
+        <v>662.23</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>14</v>
+      </c>
+      <c r="E49" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>
@@ -5029,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5132,7 +5417,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5152,7 +5437,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>228.5</v>
+        <v>226.15</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -5160,16 +5445,16 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.33</v>
+        <v>-1.38</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>208.57</v>
+        <v>206.79</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -5185,12 +5470,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5205,7 +5490,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1384.6</v>
+        <v>576.65</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -5213,16 +5498,16 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>5.88</v>
+        <v>0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.36</v>
+        <v>-2.68</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1240.6</v>
+        <v>533.86</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -5238,7 +5523,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5250,7 +5535,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5258,7 +5543,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14.05</v>
+        <v>14</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -5266,16 +5551,16 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -5291,7 +5576,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5311,26 +5596,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>226.53</v>
+        <v>223.9</v>
       </c>
       <c r="G5" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>3.47</v>
+        <v>2.64</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.12</v>
+        <v>-0.62</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>205.43</v>
+        <v>208.57</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -5346,12 +5631,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5366,26 +5651,26 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14.07</v>
+        <v>1390.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.14</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>1.07</v>
+        <v>5.43</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.35</v>
+        <v>-0.78</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>13.16</v>
+        <v>1240.6</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -5401,12 +5686,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5421,26 +5706,26 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>554.85</v>
+        <v>14.03</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>-0.21</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3.58</v>
+        <v>1.14</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.33</v>
+        <v>-0.71</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>521.95</v>
+        <v>13.22</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -5456,7 +5741,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5476,26 +5761,26 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>230.03</v>
+        <v>226.53</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.52</v>
+        <v>-1.16</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>3.47</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.23</v>
+        <v>-1.77</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>207.19</v>
+        <v>205.43</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -5511,7 +5796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5531,26 +5816,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14.12</v>
+        <v>14.07</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.35</v>
+        <v>-0.28</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.07</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.39</v>
+        <v>-1.35</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>12.95</v>
+        <v>13.16</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -5566,19 +5851,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5586,26 +5871,26 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1603</v>
+        <v>554.85</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.89</v>
+        <v>0.95</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>4.68</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.15</v>
+        <v>-0.33</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1505.54</v>
+        <v>521.95</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -5621,7 +5906,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5641,26 +5926,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>223.11</v>
+        <v>230.03</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.62</v>
+        <v>-1.52</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>5.06</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.36</v>
+        <v>-5.23</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>209.18</v>
+        <v>207.19</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -5676,12 +5961,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5696,26 +5981,26 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1616</v>
+        <v>14.12</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.66</v>
+        <v>-0.35</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.87</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.92</v>
+        <v>-4.39</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1508.29</v>
+        <v>12.95</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -5731,19 +6016,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5751,26 +6036,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14.11</v>
+        <v>1603</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.83</v>
+        <v>-3.89</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.39</v>
+        <v>-4.15</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>13.18</v>
+        <v>1505.54</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -5786,7 +6071,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5806,28 +6091,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>227.36</v>
+        <v>223.11</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.87</v>
+        <v>-1.62</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>1.36</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>5.06</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.18</v>
+        <v>-2.36</v>
       </c>
       <c r="N14" t="n">
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>209.53</v>
+        <v>209.18</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -5843,12 +6128,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5863,28 +6148,28 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>13.51</v>
+        <v>1616</v>
       </c>
       <c r="G15" t="n">
-        <v>4.44</v>
+        <v>-1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>-3.9</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>5.92</v>
+        <v>0.87</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.37</v>
+        <v>-4.92</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>13.02</v>
+        <v>1508.29</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -5900,19 +6185,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5920,28 +6205,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1583</v>
+        <v>14.11</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>-2.83</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.96</v>
+        <v>-0.78</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>3.49</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.94</v>
+        <v>-4.39</v>
       </c>
       <c r="N16" t="n">
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>1491.87</v>
+        <v>13.18</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -5957,7 +6242,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5977,28 +6262,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>221.52</v>
+        <v>227.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.64</v>
+        <v>-1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>-1.52</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>5.81</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.94</v>
+        <v>-4.18</v>
       </c>
       <c r="N17" t="n">
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>196.21</v>
+        <v>209.53</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -6014,7 +6299,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6034,34 +6319,34 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13.5</v>
+        <v>13.51</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="H18" t="n">
-        <v>4.22</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.96</v>
+        <v>-0.37</v>
       </c>
       <c r="N18" t="n">
         <v>7</v>
       </c>
       <c r="O18" t="n">
-        <v>12.72</v>
+        <v>13.02</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -6071,12 +6356,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -6091,31 +6376,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>547.7</v>
+        <v>1583</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.59</v>
+        <v>2.08</v>
       </c>
       <c r="H19" t="n">
-        <v>1.31</v>
+        <v>-1.96</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>5.29</v>
+        <v>3.49</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.97</v>
+        <v>-2.94</v>
       </c>
       <c r="N19" t="n">
         <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>531.64</v>
+        <v>1491.87</v>
       </c>
       <c r="P19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -6123,14 +6408,12 @@
       <c r="R19" t="b">
         <v>0</v>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6150,34 +6433,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>214.24</v>
+        <v>221.52</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>7.37</v>
+        <v>2.26</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>9.41</v>
+        <v>5.81</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="N20" t="n">
         <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>191.15</v>
+        <v>196.21</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -6187,12 +6470,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -6207,28 +6490,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4859.8</v>
+        <v>13.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.46</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>10.18</v>
+        <v>4.22</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>11.04</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2</v>
+        <v>-4.96</v>
       </c>
       <c r="N21" t="n">
         <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>4459.44</v>
+        <v>12.72</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -6244,12 +6527,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -6264,28 +6547,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1622</v>
+        <v>547.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.42</v>
+        <v>-0.59</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.17</v>
+        <v>1.31</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>3.08</v>
+        <v>6.04</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.27</v>
+        <v>-5.97</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>1559.39</v>
+        <v>531.64</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -6297,13 +6580,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6323,28 +6606,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>207.98</v>
+        <v>214.24</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>7.27</v>
+        <v>7.37</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>12.7</v>
+        <v>9.41</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.36</v>
+        <v>-2.33</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>183.84</v>
+        <v>191.15</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -6360,19 +6643,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -6380,58 +6663,56 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1630.1</v>
+        <v>4859.8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.86</v>
+        <v>10.18</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>2.57</v>
+        <v>14.8</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.74</v>
+        <v>-2.2</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1541.87</v>
+        <v>4459.44</v>
       </c>
       <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
         <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
       </c>
-      <c r="S24" t="n">
-        <v>9</v>
-      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -6439,44 +6720,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>381</v>
+        <v>1622</v>
       </c>
       <c r="G25" t="n">
-        <v>0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.31</v>
+        <v>-1.17</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>10.81</v>
+        <v>3.08</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.57</v>
+        <v>-5.27</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>359.23</v>
+        <v>1559.39</v>
       </c>
       <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
         <v>0</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6496,30 +6779,30 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>203.67</v>
+        <v>207.98</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="H26" t="n">
-        <v>11.63</v>
+        <v>7.27</v>
       </c>
       <c r="I26" t="n">
-        <v>12.19</v>
+        <v>8.74</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>15.09</v>
+        <v>12.7</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.31</v>
+        <v>-3.36</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>189.62</v>
+        <v>183.84</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -6535,7 +6818,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6555,30 +6838,30 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1620</v>
+        <v>1630.1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.62</v>
+        <v>0.12</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.28</v>
+        <v>-0.86</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.2</v>
+        <v>-4.74</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>3.21</v>
+        <v>2.57</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.15</v>
+        <v>-5.74</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>1537.22</v>
+        <v>1541.87</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -6590,13 +6873,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6619,13 +6902,13 @@
         <v>381</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H28" t="n">
-        <v>5.12</v>
+        <v>-1.31</v>
       </c>
       <c r="I28" t="n">
-        <v>1.84</v>
+        <v>2.76</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -6639,7 +6922,7 @@
         <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>357.53</v>
+        <v>359.23</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -6648,14 +6931,14 @@
         <v>1</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6675,30 +6958,30 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>212.23</v>
+        <v>203.67</v>
       </c>
       <c r="G29" t="n">
-        <v>-4.03</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>4.38</v>
+        <v>11.63</v>
       </c>
       <c r="I29" t="n">
-        <v>6.74</v>
+        <v>9.93</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>10.45</v>
+        <v>15.09</v>
       </c>
       <c r="M29" t="n">
-        <v>-5.29</v>
+        <v>-1.31</v>
       </c>
       <c r="N29" t="n">
         <v>12</v>
       </c>
       <c r="O29" t="n">
-        <v>190.08</v>
+        <v>189.62</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -6714,12 +6997,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -6734,51 +7017,53 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4890.75</v>
+        <v>1620</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.59</v>
+        <v>0.62</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.09</v>
+        <v>-2.28</v>
       </c>
       <c r="I30" t="n">
-        <v>3.56</v>
+        <v>-4.2</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>10.34</v>
+        <v>3.21</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.45</v>
+        <v>-5.15</v>
       </c>
       <c r="N30" t="n">
         <v>12</v>
       </c>
       <c r="O30" t="n">
-        <v>4486.28</v>
+        <v>1537.22</v>
       </c>
       <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
         <v>0</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6793,46 +7078,46 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1642</v>
+        <v>381</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.34</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.62</v>
+        <v>5.12</v>
       </c>
       <c r="I31" t="n">
-        <v>-6.17</v>
+        <v>1.21</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>10.81</v>
       </c>
       <c r="M31" t="n">
-        <v>-6.43</v>
+        <v>-1.57</v>
       </c>
       <c r="N31" t="n">
         <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>1534.19</v>
+        <v>357.53</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
       </c>
       <c r="Q31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6852,30 +7137,30 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>202.78</v>
+        <v>212.23</v>
       </c>
       <c r="G32" t="n">
-        <v>4.66</v>
+        <v>-4.03</v>
       </c>
       <c r="H32" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="I32" t="n">
-        <v>13.44</v>
+        <v>6.74</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>15.59</v>
+        <v>10.45</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.26</v>
+        <v>-5.29</v>
       </c>
       <c r="N32" t="n">
         <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>178.12</v>
+        <v>190.08</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -6891,7 +7176,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6903,7 +7188,7 @@
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -6911,30 +7196,30 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4759.23</v>
+        <v>4890.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.76</v>
+        <v>-1.59</v>
       </c>
       <c r="H33" t="n">
-        <v>2.11</v>
+        <v>-1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>12.51</v>
+        <v>3.56</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>13.39</v>
+        <v>14.07</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.55</v>
+        <v>-3.45</v>
       </c>
       <c r="N33" t="n">
         <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>4301.58</v>
+        <v>4486.28</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -6950,12 +7235,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -6970,36 +7255,36 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>377</v>
+        <v>1642</v>
       </c>
       <c r="G34" t="n">
-        <v>1.06</v>
+        <v>-1.34</v>
       </c>
       <c r="H34" t="n">
-        <v>2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="I34" t="n">
-        <v>2.92</v>
+        <v>-6.17</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>11.99</v>
+        <v>1.83</v>
       </c>
       <c r="M34" t="n">
-        <v>-2.61</v>
+        <v>-6.43</v>
       </c>
       <c r="N34" t="n">
         <v>13</v>
       </c>
       <c r="O34" t="n">
-        <v>351.82</v>
+        <v>1534.19</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
       </c>
       <c r="Q34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
@@ -7009,19 +7294,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -7029,30 +7314,30 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4583.14</v>
+        <v>202.78</v>
       </c>
       <c r="G35" t="n">
-        <v>3.84</v>
+        <v>4.66</v>
       </c>
       <c r="H35" t="n">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="I35" t="n">
-        <v>13.73</v>
+        <v>13.44</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>17.74</v>
+        <v>15.59</v>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-1.26</v>
       </c>
       <c r="N35" t="n">
         <v>14</v>
       </c>
       <c r="O35" t="n">
-        <v>4135.84</v>
+        <v>178.12</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -7061,26 +7346,26 @@
         <v>1</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -7088,60 +7373,58 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1647</v>
+        <v>4759.23</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.06</v>
+        <v>2.76</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.91</v>
+        <v>2.11</v>
       </c>
       <c r="I36" t="n">
-        <v>-3.52</v>
+        <v>12.51</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>17.22</v>
       </c>
       <c r="M36" t="n">
-        <v>-6.71</v>
+        <v>-3.55</v>
       </c>
       <c r="N36" t="n">
         <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>1536.8</v>
+        <v>4301.58</v>
       </c>
       <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
         <v>1</v>
       </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
       <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>13</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -7149,30 +7432,30 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1360.6</v>
+        <v>377</v>
       </c>
       <c r="G37" t="n">
-        <v>4.48</v>
+        <v>1.06</v>
       </c>
       <c r="H37" t="n">
-        <v>11.34</v>
+        <v>2.92</v>
       </c>
       <c r="I37" t="n">
-        <v>7.78</v>
+        <v>2.92</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>13.29</v>
+        <v>11.99</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="N37" t="n">
         <v>14</v>
       </c>
       <c r="O37" t="n">
-        <v>1251.99</v>
+        <v>351.82</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -7188,12 +7471,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7208,48 +7491,46 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1377.8</v>
+        <v>4583.14</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8</v>
+        <v>3.84</v>
       </c>
       <c r="H38" t="n">
-        <v>2.81</v>
+        <v>6.98</v>
       </c>
       <c r="I38" t="n">
-        <v>6.42</v>
-      </c>
-      <c r="J38" t="n">
-        <v>9.779999999999999</v>
-      </c>
+        <v>13.73</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>11.88</v>
+        <v>21.73</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O38" t="n">
-        <v>1318.08</v>
+        <v>4135.84</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
       </c>
       <c r="Q38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7269,32 +7550,30 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1659</v>
+        <v>1647</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.82</v>
+        <v>-0.06</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.35</v>
+        <v>-0.91</v>
       </c>
       <c r="I39" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-6.45</v>
-      </c>
+        <v>-3.52</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="M39" t="n">
-        <v>-7.38</v>
+        <v>-6.71</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O39" t="n">
-        <v>1555.52</v>
+        <v>1536.8</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -7306,25 +7585,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -7332,38 +7611,36 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1781.3</v>
+        <v>1360.6</v>
       </c>
       <c r="G40" t="n">
-        <v>1.96</v>
+        <v>4.48</v>
       </c>
       <c r="H40" t="n">
-        <v>2.73</v>
+        <v>11.34</v>
       </c>
       <c r="I40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.08</v>
-      </c>
+        <v>7.78</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>5.02</v>
+        <v>13.29</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O40" t="n">
-        <v>1697.2</v>
+        <v>1251.99</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -7373,12 +7650,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7393,52 +7670,60 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>193.56</v>
+        <v>1377.8</v>
       </c>
       <c r="G41" t="n">
-        <v>-4.58</v>
+        <v>-0.8</v>
       </c>
       <c r="H41" t="n">
-        <v>9.65</v>
+        <v>2.81</v>
       </c>
       <c r="I41" t="n">
-        <v>14.45</v>
+        <v>6.42</v>
       </c>
       <c r="J41" t="n">
-        <v>17.03</v>
+        <v>4.78</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>21.1</v>
+        <v>11.88</v>
       </c>
       <c r="M41" t="n">
-        <v>-6.46</v>
+        <v>-1.9</v>
       </c>
       <c r="N41" t="n">
         <v>17</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>1318.08</v>
+      </c>
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
       <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -7446,40 +7731,50 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4361.38</v>
+        <v>1659</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.87</v>
+        <v>-0.82</v>
       </c>
       <c r="H42" t="n">
-        <v>12.14</v>
+        <v>-2.35</v>
       </c>
       <c r="I42" t="n">
-        <v>10.91</v>
+        <v>-4.58</v>
       </c>
       <c r="J42" t="n">
-        <v>16.13</v>
+        <v>-6.45</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>23.73</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>-4.32</v>
+        <v>-7.38</v>
       </c>
       <c r="N42" t="n">
         <v>17</v>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>1555.52</v>
+      </c>
+      <c r="P42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7491,7 +7786,7 @@
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7502,49 +7797,57 @@
         <v>1781.3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H43" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="I43" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="J43" t="n">
-        <v>1.15</v>
+        <v>2.45</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>5.02</v>
       </c>
       <c r="M43" t="n">
-        <v>-1.52</v>
+        <v>-0.67</v>
       </c>
       <c r="N43" t="n">
         <v>17</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>1697.2</v>
+      </c>
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
       <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -7552,26 +7855,26 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1202</v>
+        <v>193.56</v>
       </c>
       <c r="G44" t="n">
-        <v>3.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H44" t="n">
-        <v>20.67</v>
+        <v>9.65</v>
       </c>
       <c r="I44" t="n">
-        <v>26.91</v>
+        <v>14.45</v>
       </c>
       <c r="J44" t="n">
-        <v>21.95</v>
+        <v>17.03</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>31.45</v>
+        <v>21.1</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.91</v>
+        <v>-6.46</v>
       </c>
       <c r="N44" t="n">
         <v>18</v>
@@ -7585,19 +7888,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -7605,26 +7908,26 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>188.39</v>
+        <v>4361.38</v>
       </c>
       <c r="G45" t="n">
-        <v>2.74</v>
+        <v>-3.87</v>
       </c>
       <c r="H45" t="n">
-        <v>7.64</v>
+        <v>12.14</v>
       </c>
       <c r="I45" t="n">
-        <v>13.72</v>
+        <v>10.91</v>
       </c>
       <c r="J45" t="n">
-        <v>22.1</v>
+        <v>16.13</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>24.42</v>
+        <v>27.92</v>
       </c>
       <c r="M45" t="n">
-        <v>-3.9</v>
+        <v>-4.32</v>
       </c>
       <c r="N45" t="n">
         <v>18</v>
@@ -7638,19 +7941,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -7658,26 +7961,26 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4395.7</v>
+        <v>1781.3</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>8.27</v>
+        <v>3.01</v>
       </c>
       <c r="I46" t="n">
-        <v>10.56</v>
+        <v>3.86</v>
       </c>
       <c r="J46" t="n">
-        <v>21.81</v>
+        <v>1.15</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>22.77</v>
+        <v>5.02</v>
       </c>
       <c r="M46" t="n">
-        <v>-5.07</v>
+        <v>-1.52</v>
       </c>
       <c r="N46" t="n">
         <v>18</v>
@@ -7687,6 +7990,165 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H47" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="I47" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="J47" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="N47" t="n">
+        <v>19</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>96</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="I48" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J48" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>19</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>92</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>4395.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="N49" t="n">
+        <v>19</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7699,7 +8161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8417,34 +8879,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1188.4</v>
+        <v>1556.9</v>
       </c>
       <c r="D27" t="n">
-        <v>1207.9</v>
+        <v>1559.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1158</v>
+        <v>1545</v>
       </c>
       <c r="F27" t="n">
-        <v>1201.8</v>
+        <v>1552.9</v>
       </c>
       <c r="G27" t="n">
-        <v>3482939</v>
+        <v>293529</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8453,25 +8915,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1225</v>
+        <v>1188.4</v>
       </c>
       <c r="D28" t="n">
-        <v>1318.9</v>
+        <v>1207.9</v>
       </c>
       <c r="E28" t="n">
-        <v>1225</v>
+        <v>1158</v>
       </c>
       <c r="F28" t="n">
-        <v>1296.4</v>
+        <v>1201.8</v>
       </c>
       <c r="G28" t="n">
-        <v>17106822</v>
+        <v>3482939</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8480,25 +8942,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1325</v>
+        <v>1225</v>
       </c>
       <c r="D29" t="n">
-        <v>1345</v>
+        <v>1318.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1251.5</v>
+        <v>1225</v>
       </c>
       <c r="F29" t="n">
-        <v>1267.1</v>
+        <v>1296.4</v>
       </c>
       <c r="G29" t="n">
-        <v>10436460</v>
+        <v>17106822</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8507,25 +8969,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1270</v>
+        <v>1325</v>
       </c>
       <c r="D30" t="n">
-        <v>1285</v>
+        <v>1345</v>
       </c>
       <c r="E30" t="n">
-        <v>1246.1</v>
+        <v>1251.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1282.2</v>
+        <v>1267.1</v>
       </c>
       <c r="G30" t="n">
-        <v>4135957</v>
+        <v>10436460</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8534,25 +8996,25 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="F31" t="n">
         <v>1282.2</v>
       </c>
-      <c r="D31" t="n">
-        <v>1333.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1272.6</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1296.7</v>
-      </c>
       <c r="G31" t="n">
-        <v>5275779</v>
+        <v>4135957</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8561,25 +9023,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1302.7</v>
+        <v>1282.2</v>
       </c>
       <c r="D32" t="n">
-        <v>1315.8</v>
+        <v>1333.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1257.1</v>
+        <v>1272.6</v>
       </c>
       <c r="F32" t="n">
-        <v>1288.4</v>
+        <v>1296.7</v>
       </c>
       <c r="G32" t="n">
-        <v>3844546</v>
+        <v>5275779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8588,25 +9050,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1290</v>
+        <v>1302.7</v>
       </c>
       <c r="D33" t="n">
-        <v>1312</v>
+        <v>1315.8</v>
       </c>
       <c r="E33" t="n">
-        <v>1262</v>
+        <v>1257.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1268.2</v>
+        <v>1288.4</v>
       </c>
       <c r="G33" t="n">
-        <v>2691508</v>
+        <v>3844546</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8615,25 +9077,25 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1312</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1262</v>
+      </c>
+      <c r="F34" t="n">
         <v>1268.2</v>
       </c>
-      <c r="D34" t="n">
-        <v>1271.5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1233.2</v>
-      </c>
       <c r="G34" t="n">
-        <v>2619436</v>
+        <v>2691508</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8642,25 +9104,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1224.1</v>
+        <v>1268.2</v>
       </c>
       <c r="D35" t="n">
-        <v>1224.7</v>
+        <v>1271.5</v>
       </c>
       <c r="E35" t="n">
-        <v>1188.1</v>
+        <v>1221.2</v>
       </c>
       <c r="F35" t="n">
-        <v>1208.7</v>
+        <v>1233.2</v>
       </c>
       <c r="G35" t="n">
-        <v>3613338</v>
+        <v>2619436</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8669,25 +9131,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1214.9</v>
+        <v>1224.1</v>
       </c>
       <c r="D36" t="n">
-        <v>1233.9</v>
+        <v>1224.7</v>
       </c>
       <c r="E36" t="n">
-        <v>1196.5</v>
+        <v>1188.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1214.9</v>
+        <v>1208.7</v>
       </c>
       <c r="G36" t="n">
-        <v>1911132</v>
+        <v>3613338</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8696,25 +9158,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1213</v>
+        <v>1214.9</v>
       </c>
       <c r="D37" t="n">
-        <v>1229</v>
+        <v>1233.9</v>
       </c>
       <c r="E37" t="n">
-        <v>1196.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1202</v>
+        <v>1214.9</v>
       </c>
       <c r="G37" t="n">
-        <v>2067763</v>
+        <v>1911132</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8723,25 +9185,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1207.2</v>
+        <v>1213</v>
       </c>
       <c r="D38" t="n">
-        <v>1252</v>
+        <v>1229</v>
       </c>
       <c r="E38" t="n">
-        <v>1191.1</v>
+        <v>1196.1</v>
       </c>
       <c r="F38" t="n">
-        <v>1246.1</v>
+        <v>1202</v>
       </c>
       <c r="G38" t="n">
-        <v>3306087</v>
+        <v>2067763</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8750,25 +9212,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1253</v>
+        <v>1207.2</v>
       </c>
       <c r="D39" t="n">
-        <v>1265.9</v>
+        <v>1252</v>
       </c>
       <c r="E39" t="n">
-        <v>1232.5</v>
+        <v>1191.1</v>
       </c>
       <c r="F39" t="n">
-        <v>1240.9</v>
+        <v>1246.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2463994</v>
+        <v>3306087</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8777,25 +9239,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D40" t="n">
-        <v>1274.6</v>
+        <v>1265.9</v>
       </c>
       <c r="E40" t="n">
-        <v>1232.1</v>
+        <v>1232.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1260.3</v>
+        <v>1240.9</v>
       </c>
       <c r="G40" t="n">
-        <v>3182495</v>
+        <v>2463994</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8804,25 +9266,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1269</v>
+        <v>1247</v>
       </c>
       <c r="D41" t="n">
-        <v>1289.9</v>
+        <v>1274.6</v>
       </c>
       <c r="E41" t="n">
-        <v>1242</v>
+        <v>1232.1</v>
       </c>
       <c r="F41" t="n">
-        <v>1272.7</v>
+        <v>1260.3</v>
       </c>
       <c r="G41" t="n">
-        <v>3918512</v>
+        <v>3182495</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8831,25 +9293,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1341.2</v>
+        <v>1269</v>
       </c>
       <c r="D42" t="n">
-        <v>1500</v>
+        <v>1289.9</v>
       </c>
       <c r="E42" t="n">
-        <v>1336.5</v>
+        <v>1242</v>
       </c>
       <c r="F42" t="n">
-        <v>1450.4</v>
+        <v>1272.7</v>
       </c>
       <c r="G42" t="n">
-        <v>23853424</v>
+        <v>3918512</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8858,25 +9320,25 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1465</v>
+        <v>1341.2</v>
       </c>
       <c r="D43" t="n">
-        <v>1479.5</v>
+        <v>1500</v>
       </c>
       <c r="E43" t="n">
-        <v>1405</v>
+        <v>1336.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1470.8</v>
+        <v>1450.4</v>
       </c>
       <c r="G43" t="n">
-        <v>6958528</v>
+        <v>23853424</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8885,25 +9347,25 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1479.5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F44" t="n">
         <v>1470.8</v>
       </c>
-      <c r="D44" t="n">
-        <v>1505</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1440</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1453.2</v>
-      </c>
       <c r="G44" t="n">
-        <v>4844393</v>
+        <v>6958528</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8912,25 +9374,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1450</v>
+        <v>1470.8</v>
       </c>
       <c r="D45" t="n">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E45" t="n">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="F45" t="n">
-        <v>1481.5</v>
+        <v>1453.2</v>
       </c>
       <c r="G45" t="n">
-        <v>4646531</v>
+        <v>4844393</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8939,25 +9401,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1488</v>
+        <v>1450</v>
       </c>
       <c r="D46" t="n">
-        <v>1520</v>
+        <v>1508</v>
       </c>
       <c r="E46" t="n">
-        <v>1457</v>
+        <v>1446</v>
       </c>
       <c r="F46" t="n">
-        <v>1466.2</v>
+        <v>1481.5</v>
       </c>
       <c r="G46" t="n">
-        <v>3972989</v>
+        <v>4646531</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8966,25 +9428,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1472.4</v>
+        <v>1488</v>
       </c>
       <c r="D47" t="n">
-        <v>1534.8</v>
+        <v>1520</v>
       </c>
       <c r="E47" t="n">
-        <v>1472</v>
+        <v>1457</v>
       </c>
       <c r="F47" t="n">
-        <v>1525.4</v>
+        <v>1466.2</v>
       </c>
       <c r="G47" t="n">
-        <v>4867021</v>
+        <v>3972989</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8993,25 +9455,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1531.7</v>
+        <v>1472.4</v>
       </c>
       <c r="D48" t="n">
-        <v>1580</v>
+        <v>1534.8</v>
       </c>
       <c r="E48" t="n">
-        <v>1511.1</v>
+        <v>1472</v>
       </c>
       <c r="F48" t="n">
-        <v>1569.4</v>
+        <v>1525.4</v>
       </c>
       <c r="G48" t="n">
-        <v>4521175</v>
+        <v>4867021</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9020,25 +9482,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1575</v>
+        <v>1531.7</v>
       </c>
       <c r="D49" t="n">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="E49" t="n">
-        <v>1500.1</v>
+        <v>1511.1</v>
       </c>
       <c r="F49" t="n">
-        <v>1526.5</v>
+        <v>1569.4</v>
       </c>
       <c r="G49" t="n">
-        <v>4013245</v>
+        <v>4521175</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9047,25 +9509,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1530</v>
+        <v>1575</v>
       </c>
       <c r="D50" t="n">
-        <v>1541</v>
+        <v>1575</v>
       </c>
       <c r="E50" t="n">
-        <v>1501.9</v>
+        <v>1500.1</v>
       </c>
       <c r="F50" t="n">
-        <v>1511.5</v>
+        <v>1526.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2250949</v>
+        <v>4013245</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9074,25 +9536,25 @@
         </is>
       </c>
       <c r="C51" t="n">
+        <v>1530</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1541</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1501.9</v>
+      </c>
+      <c r="F51" t="n">
         <v>1511.5</v>
       </c>
-      <c r="D51" t="n">
-        <v>1533</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1475</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1485.2</v>
-      </c>
       <c r="G51" t="n">
-        <v>2475472</v>
+        <v>2250949</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9101,25 +9563,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1484.7</v>
+        <v>1511.5</v>
       </c>
       <c r="D52" t="n">
-        <v>1504</v>
+        <v>1533</v>
       </c>
       <c r="E52" t="n">
-        <v>1455</v>
+        <v>1475</v>
       </c>
       <c r="F52" t="n">
-        <v>1465.8</v>
+        <v>1485.2</v>
       </c>
       <c r="G52" t="n">
-        <v>2760706</v>
+        <v>2475472</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9128,25 +9590,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1468.1</v>
+        <v>1484.7</v>
       </c>
       <c r="D53" t="n">
-        <v>1473.3</v>
+        <v>1504</v>
       </c>
       <c r="E53" t="n">
-        <v>1431</v>
+        <v>1455</v>
       </c>
       <c r="F53" t="n">
-        <v>1438.2</v>
+        <v>1465.8</v>
       </c>
       <c r="G53" t="n">
-        <v>1688332</v>
+        <v>2760706</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9155,79 +9617,79 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1445.5</v>
+        <v>1468.1</v>
       </c>
       <c r="D54" t="n">
-        <v>1467</v>
+        <v>1473.3</v>
       </c>
       <c r="E54" t="n">
-        <v>1442.2</v>
+        <v>1431</v>
       </c>
       <c r="F54" t="n">
-        <v>1442.2</v>
+        <v>1438.2</v>
       </c>
       <c r="G54" t="n">
-        <v>297401</v>
+        <v>1688332</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1235.9</v>
+        <v>1445.5</v>
       </c>
       <c r="D55" t="n">
-        <v>1285.8</v>
+        <v>1467</v>
       </c>
       <c r="E55" t="n">
-        <v>1220.3</v>
+        <v>1421.7</v>
       </c>
       <c r="F55" t="n">
-        <v>1275.4</v>
+        <v>1449.6</v>
       </c>
       <c r="G55" t="n">
-        <v>1468654</v>
+        <v>1720215</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1270</v>
+        <v>1457</v>
       </c>
       <c r="D56" t="n">
-        <v>1270</v>
+        <v>1471.3</v>
       </c>
       <c r="E56" t="n">
-        <v>1235</v>
+        <v>1448.7</v>
       </c>
       <c r="F56" t="n">
-        <v>1240.1</v>
+        <v>1450.9</v>
       </c>
       <c r="G56" t="n">
-        <v>782776</v>
+        <v>334842</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9236,25 +9698,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1249</v>
+        <v>1235.9</v>
       </c>
       <c r="D57" t="n">
-        <v>1449</v>
+        <v>1285.8</v>
       </c>
       <c r="E57" t="n">
-        <v>1237</v>
+        <v>1220.3</v>
       </c>
       <c r="F57" t="n">
-        <v>1426.1</v>
+        <v>1275.4</v>
       </c>
       <c r="G57" t="n">
-        <v>17236108</v>
+        <v>1468654</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9263,25 +9725,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1418</v>
+        <v>1270</v>
       </c>
       <c r="D58" t="n">
-        <v>1444</v>
+        <v>1270</v>
       </c>
       <c r="E58" t="n">
-        <v>1370.1</v>
+        <v>1235</v>
       </c>
       <c r="F58" t="n">
-        <v>1379.5</v>
+        <v>1240.1</v>
       </c>
       <c r="G58" t="n">
-        <v>2824270</v>
+        <v>782776</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9290,25 +9752,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1377.1</v>
+        <v>1249</v>
       </c>
       <c r="D59" t="n">
-        <v>1378.9</v>
+        <v>1449</v>
       </c>
       <c r="E59" t="n">
-        <v>1308</v>
+        <v>1237</v>
       </c>
       <c r="F59" t="n">
-        <v>1341.8</v>
+        <v>1426.1</v>
       </c>
       <c r="G59" t="n">
-        <v>1846258</v>
+        <v>17236108</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9317,25 +9779,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1341.8</v>
+        <v>1418</v>
       </c>
       <c r="D60" t="n">
-        <v>1368.8</v>
+        <v>1444</v>
       </c>
       <c r="E60" t="n">
-        <v>1311</v>
+        <v>1370.1</v>
       </c>
       <c r="F60" t="n">
-        <v>1321.9</v>
+        <v>1379.5</v>
       </c>
       <c r="G60" t="n">
-        <v>755166</v>
+        <v>2824270</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9344,25 +9806,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1332.1</v>
+        <v>1377.1</v>
       </c>
       <c r="D61" t="n">
-        <v>1397.3</v>
+        <v>1378.9</v>
       </c>
       <c r="E61" t="n">
-        <v>1309.1</v>
+        <v>1308</v>
       </c>
       <c r="F61" t="n">
-        <v>1382.4</v>
+        <v>1341.8</v>
       </c>
       <c r="G61" t="n">
-        <v>2149658</v>
+        <v>1846258</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9371,25 +9833,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1400</v>
+        <v>1341.8</v>
       </c>
       <c r="D62" t="n">
-        <v>1454.5</v>
+        <v>1368.8</v>
       </c>
       <c r="E62" t="n">
-        <v>1384.9</v>
+        <v>1311</v>
       </c>
       <c r="F62" t="n">
-        <v>1404</v>
+        <v>1321.9</v>
       </c>
       <c r="G62" t="n">
-        <v>3584947</v>
+        <v>755166</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9398,25 +9860,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1429</v>
+        <v>1332.1</v>
       </c>
       <c r="D63" t="n">
-        <v>1489.7</v>
+        <v>1397.3</v>
       </c>
       <c r="E63" t="n">
-        <v>1421.2</v>
+        <v>1309.1</v>
       </c>
       <c r="F63" t="n">
-        <v>1440.3</v>
+        <v>1382.4</v>
       </c>
       <c r="G63" t="n">
-        <v>5720727</v>
+        <v>2149658</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9425,106 +9887,106 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1457</v>
+        <v>1400</v>
       </c>
       <c r="D64" t="n">
-        <v>1466</v>
+        <v>1454.5</v>
       </c>
       <c r="E64" t="n">
-        <v>1379.6</v>
+        <v>1384.9</v>
       </c>
       <c r="F64" t="n">
-        <v>1384.6</v>
+        <v>1404</v>
       </c>
       <c r="G64" t="n">
-        <v>715693</v>
+        <v>3584947</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>211.95</v>
+        <v>1429</v>
       </c>
       <c r="D65" t="n">
-        <v>214.55</v>
+        <v>1489.7</v>
       </c>
       <c r="E65" t="n">
-        <v>206.1</v>
+        <v>1421.2</v>
       </c>
       <c r="F65" t="n">
-        <v>212.78</v>
+        <v>1440.3</v>
       </c>
       <c r="G65" t="n">
-        <v>12863408</v>
+        <v>5720727</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>214.3</v>
+        <v>1457</v>
       </c>
       <c r="D66" t="n">
-        <v>223.41</v>
+        <v>1466</v>
       </c>
       <c r="E66" t="n">
-        <v>214.3</v>
+        <v>1379.6</v>
       </c>
       <c r="F66" t="n">
-        <v>223.08</v>
+        <v>1390.5</v>
       </c>
       <c r="G66" t="n">
-        <v>32151413</v>
+        <v>2227820</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>226</v>
+        <v>1394.1</v>
       </c>
       <c r="D67" t="n">
-        <v>229.4</v>
+        <v>1408</v>
       </c>
       <c r="E67" t="n">
-        <v>221.18</v>
+        <v>1380</v>
       </c>
       <c r="F67" t="n">
-        <v>224.38</v>
+        <v>1400</v>
       </c>
       <c r="G67" t="n">
-        <v>14379534</v>
+        <v>307983</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9533,25 +9995,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>217.24</v>
+        <v>211.95</v>
       </c>
       <c r="D68" t="n">
-        <v>219.7</v>
+        <v>214.55</v>
       </c>
       <c r="E68" t="n">
-        <v>213.17</v>
+        <v>206.1</v>
       </c>
       <c r="F68" t="n">
-        <v>213.17</v>
+        <v>212.78</v>
       </c>
       <c r="G68" t="n">
-        <v>14642282</v>
+        <v>12863408</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9560,25 +10022,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>208.25</v>
+        <v>214.3</v>
       </c>
       <c r="D69" t="n">
-        <v>213.7</v>
+        <v>223.41</v>
       </c>
       <c r="E69" t="n">
-        <v>203.16</v>
+        <v>214.3</v>
       </c>
       <c r="F69" t="n">
-        <v>208.03</v>
+        <v>223.08</v>
       </c>
       <c r="G69" t="n">
-        <v>18348510</v>
+        <v>32151413</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9587,25 +10049,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D70" t="n">
-        <v>218.43</v>
+        <v>229.4</v>
       </c>
       <c r="E70" t="n">
-        <v>209</v>
+        <v>221.18</v>
       </c>
       <c r="F70" t="n">
-        <v>217.97</v>
+        <v>224.38</v>
       </c>
       <c r="G70" t="n">
-        <v>20144780</v>
+        <v>14379534</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9614,25 +10076,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>222</v>
+        <v>217.24</v>
       </c>
       <c r="D71" t="n">
-        <v>228</v>
+        <v>219.7</v>
       </c>
       <c r="E71" t="n">
-        <v>214.11</v>
+        <v>213.17</v>
       </c>
       <c r="F71" t="n">
-        <v>217.9</v>
+        <v>213.17</v>
       </c>
       <c r="G71" t="n">
-        <v>55935312</v>
+        <v>14642282</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9641,25 +10103,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>221.96</v>
+        <v>208.25</v>
       </c>
       <c r="D72" t="n">
-        <v>222.4</v>
+        <v>213.7</v>
       </c>
       <c r="E72" t="n">
-        <v>207.01</v>
+        <v>203.16</v>
       </c>
       <c r="F72" t="n">
-        <v>207.01</v>
+        <v>208.03</v>
       </c>
       <c r="G72" t="n">
-        <v>29190459</v>
+        <v>18348510</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9668,25 +10130,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D73" t="n">
-        <v>204.78</v>
+        <v>218.43</v>
       </c>
       <c r="E73" t="n">
-        <v>196.66</v>
+        <v>209</v>
       </c>
       <c r="F73" t="n">
-        <v>196.85</v>
+        <v>217.97</v>
       </c>
       <c r="G73" t="n">
-        <v>31552378</v>
+        <v>20144780</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9695,25 +10157,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D74" t="n">
-        <v>200.9</v>
+        <v>228</v>
       </c>
       <c r="E74" t="n">
-        <v>191.1</v>
+        <v>214.11</v>
       </c>
       <c r="F74" t="n">
-        <v>192.54</v>
+        <v>217.9</v>
       </c>
       <c r="G74" t="n">
-        <v>26152896</v>
+        <v>55935312</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9722,25 +10184,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>187</v>
+        <v>221.96</v>
       </c>
       <c r="D75" t="n">
-        <v>196.9</v>
+        <v>222.4</v>
       </c>
       <c r="E75" t="n">
-        <v>182.92</v>
+        <v>207.01</v>
       </c>
       <c r="F75" t="n">
-        <v>188.39</v>
+        <v>207.01</v>
       </c>
       <c r="G75" t="n">
-        <v>42541118</v>
+        <v>29190459</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9749,25 +10211,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D76" t="n">
-        <v>195.5</v>
+        <v>204.78</v>
       </c>
       <c r="E76" t="n">
-        <v>181.05</v>
+        <v>196.66</v>
       </c>
       <c r="F76" t="n">
-        <v>193.56</v>
+        <v>196.85</v>
       </c>
       <c r="G76" t="n">
-        <v>40104195</v>
+        <v>31552378</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9776,25 +10238,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D77" t="n">
-        <v>195.53</v>
+        <v>200.9</v>
       </c>
       <c r="E77" t="n">
-        <v>183.9</v>
+        <v>191.1</v>
       </c>
       <c r="F77" t="n">
-        <v>184.69</v>
+        <v>192.54</v>
       </c>
       <c r="G77" t="n">
-        <v>21043194</v>
+        <v>26152896</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9803,25 +10265,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>193.92</v>
+        <v>187</v>
       </c>
       <c r="D78" t="n">
-        <v>193.92</v>
+        <v>196.9</v>
       </c>
       <c r="E78" t="n">
-        <v>191.01</v>
+        <v>182.92</v>
       </c>
       <c r="F78" t="n">
-        <v>193.92</v>
+        <v>188.39</v>
       </c>
       <c r="G78" t="n">
-        <v>33053426</v>
+        <v>42541118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9830,25 +10292,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>196.95</v>
+        <v>189</v>
       </c>
       <c r="D79" t="n">
-        <v>203.61</v>
+        <v>195.5</v>
       </c>
       <c r="E79" t="n">
-        <v>195.7</v>
+        <v>181.05</v>
       </c>
       <c r="F79" t="n">
-        <v>202.52</v>
+        <v>193.56</v>
       </c>
       <c r="G79" t="n">
-        <v>39140552</v>
+        <v>40104195</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9857,25 +10319,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>202.4</v>
+        <v>193</v>
       </c>
       <c r="D80" t="n">
-        <v>207</v>
+        <v>195.53</v>
       </c>
       <c r="E80" t="n">
-        <v>200.22</v>
+        <v>183.9</v>
       </c>
       <c r="F80" t="n">
-        <v>202.78</v>
+        <v>184.69</v>
       </c>
       <c r="G80" t="n">
-        <v>19636718</v>
+        <v>21043194</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9884,25 +10346,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>205.8</v>
+        <v>193.92</v>
       </c>
       <c r="D81" t="n">
-        <v>212.91</v>
+        <v>193.92</v>
       </c>
       <c r="E81" t="n">
-        <v>205.03</v>
+        <v>191.01</v>
       </c>
       <c r="F81" t="n">
-        <v>212.23</v>
+        <v>193.92</v>
       </c>
       <c r="G81" t="n">
-        <v>37479685</v>
+        <v>33053426</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9911,25 +10373,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>212.4</v>
+        <v>196.95</v>
       </c>
       <c r="D82" t="n">
-        <v>213.45</v>
+        <v>203.61</v>
       </c>
       <c r="E82" t="n">
-        <v>203</v>
+        <v>195.7</v>
       </c>
       <c r="F82" t="n">
-        <v>203.67</v>
+        <v>202.52</v>
       </c>
       <c r="G82" t="n">
-        <v>19195935</v>
+        <v>39140552</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9938,25 +10400,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>203.98</v>
+        <v>202.4</v>
       </c>
       <c r="D83" t="n">
-        <v>211.52</v>
+        <v>207</v>
       </c>
       <c r="E83" t="n">
-        <v>201</v>
+        <v>200.22</v>
       </c>
       <c r="F83" t="n">
-        <v>207.98</v>
+        <v>202.78</v>
       </c>
       <c r="G83" t="n">
-        <v>19489977</v>
+        <v>19636718</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9965,25 +10427,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>209</v>
+        <v>205.8</v>
       </c>
       <c r="D84" t="n">
-        <v>216.6</v>
+        <v>212.91</v>
       </c>
       <c r="E84" t="n">
-        <v>207.83</v>
+        <v>205.03</v>
       </c>
       <c r="F84" t="n">
-        <v>212.97</v>
+        <v>212.23</v>
       </c>
       <c r="G84" t="n">
-        <v>19215795</v>
+        <v>37479685</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9992,25 +10454,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>214</v>
+        <v>212.4</v>
       </c>
       <c r="D85" t="n">
-        <v>215.8</v>
+        <v>213.45</v>
       </c>
       <c r="E85" t="n">
-        <v>209.25</v>
+        <v>203</v>
       </c>
       <c r="F85" t="n">
-        <v>214.24</v>
+        <v>203.67</v>
       </c>
       <c r="G85" t="n">
-        <v>15006611</v>
+        <v>19195935</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10019,25 +10481,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>215.4</v>
+        <v>203.98</v>
       </c>
       <c r="D86" t="n">
-        <v>223.61</v>
+        <v>211.52</v>
       </c>
       <c r="E86" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="F86" t="n">
-        <v>221.52</v>
+        <v>207.98</v>
       </c>
       <c r="G86" t="n">
-        <v>28062533</v>
+        <v>19489977</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10046,25 +10508,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D87" t="n">
-        <v>230.95</v>
+        <v>216.6</v>
       </c>
       <c r="E87" t="n">
-        <v>222.62</v>
+        <v>207.83</v>
       </c>
       <c r="F87" t="n">
-        <v>227.36</v>
+        <v>212.97</v>
       </c>
       <c r="G87" t="n">
-        <v>23585794</v>
+        <v>19215795</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10073,25 +10535,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D88" t="n">
-        <v>230.7</v>
+        <v>215.8</v>
       </c>
       <c r="E88" t="n">
-        <v>220.7</v>
+        <v>209.25</v>
       </c>
       <c r="F88" t="n">
-        <v>223.11</v>
+        <v>214.24</v>
       </c>
       <c r="G88" t="n">
-        <v>16693107</v>
+        <v>15006611</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10100,25 +10562,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>223.9</v>
+        <v>215.4</v>
       </c>
       <c r="D89" t="n">
-        <v>225.95</v>
+        <v>223.61</v>
       </c>
       <c r="E89" t="n">
-        <v>217.85</v>
+        <v>215</v>
       </c>
       <c r="F89" t="n">
-        <v>219.5</v>
+        <v>221.52</v>
       </c>
       <c r="G89" t="n">
-        <v>9863534</v>
+        <v>28062533</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10127,25 +10589,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>218.01</v>
+        <v>223</v>
       </c>
       <c r="D90" t="n">
-        <v>230.47</v>
+        <v>230.95</v>
       </c>
       <c r="E90" t="n">
-        <v>218.01</v>
+        <v>222.62</v>
       </c>
       <c r="F90" t="n">
-        <v>230.03</v>
+        <v>227.36</v>
       </c>
       <c r="G90" t="n">
-        <v>35739264</v>
+        <v>23585794</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10154,25 +10616,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D91" t="n">
-        <v>234.4</v>
+        <v>230.7</v>
       </c>
       <c r="E91" t="n">
-        <v>224</v>
+        <v>220.7</v>
       </c>
       <c r="F91" t="n">
-        <v>226.53</v>
+        <v>223.11</v>
       </c>
       <c r="G91" t="n">
-        <v>14962246</v>
+        <v>16693107</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10181,133 +10643,133 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>227.95</v>
+        <v>223.9</v>
       </c>
       <c r="D92" t="n">
-        <v>229.8</v>
+        <v>225.95</v>
       </c>
       <c r="E92" t="n">
-        <v>225.46</v>
+        <v>217.85</v>
       </c>
       <c r="F92" t="n">
-        <v>228.5</v>
+        <v>219.5</v>
       </c>
       <c r="G92" t="n">
-        <v>2643323</v>
+        <v>9863534</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>481.25</v>
+        <v>218.01</v>
       </c>
       <c r="D93" t="n">
-        <v>489.85</v>
+        <v>230.47</v>
       </c>
       <c r="E93" t="n">
-        <v>477.5</v>
+        <v>218.01</v>
       </c>
       <c r="F93" t="n">
-        <v>480.25</v>
+        <v>230.03</v>
       </c>
       <c r="G93" t="n">
-        <v>2347659</v>
+        <v>35739264</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>485.2</v>
+        <v>233</v>
       </c>
       <c r="D94" t="n">
-        <v>499</v>
+        <v>234.4</v>
       </c>
       <c r="E94" t="n">
-        <v>482.55</v>
+        <v>224</v>
       </c>
       <c r="F94" t="n">
-        <v>491.6</v>
+        <v>226.53</v>
       </c>
       <c r="G94" t="n">
-        <v>7339280</v>
+        <v>14962246</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>495</v>
+        <v>227.95</v>
       </c>
       <c r="D95" t="n">
-        <v>498.5</v>
+        <v>229.8</v>
       </c>
       <c r="E95" t="n">
-        <v>491</v>
+        <v>222.51</v>
       </c>
       <c r="F95" t="n">
-        <v>495.05</v>
+        <v>223.9</v>
       </c>
       <c r="G95" t="n">
-        <v>2755226</v>
+        <v>10056116</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>495.05</v>
+        <v>225</v>
       </c>
       <c r="D96" t="n">
-        <v>504.3</v>
+        <v>226.99</v>
       </c>
       <c r="E96" t="n">
-        <v>490.05</v>
+        <v>223.03</v>
       </c>
       <c r="F96" t="n">
-        <v>492.35</v>
+        <v>226.15</v>
       </c>
       <c r="G96" t="n">
-        <v>4448305</v>
+        <v>2283312</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10316,25 +10778,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>496.2</v>
+        <v>481.25</v>
       </c>
       <c r="D97" t="n">
-        <v>539.6</v>
+        <v>489.85</v>
       </c>
       <c r="E97" t="n">
-        <v>495.1</v>
+        <v>477.5</v>
       </c>
       <c r="F97" t="n">
-        <v>533.8</v>
+        <v>480.25</v>
       </c>
       <c r="G97" t="n">
-        <v>22701332</v>
+        <v>2347659</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10343,25 +10805,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>542.45</v>
+        <v>485.2</v>
       </c>
       <c r="D98" t="n">
-        <v>551</v>
+        <v>499</v>
       </c>
       <c r="E98" t="n">
-        <v>525.55</v>
+        <v>482.55</v>
       </c>
       <c r="F98" t="n">
-        <v>545.95</v>
+        <v>491.6</v>
       </c>
       <c r="G98" t="n">
-        <v>19838083</v>
+        <v>7339280</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10370,25 +10832,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>543.75</v>
+        <v>495</v>
       </c>
       <c r="D99" t="n">
-        <v>548</v>
+        <v>498.5</v>
       </c>
       <c r="E99" t="n">
-        <v>532.1</v>
+        <v>491</v>
       </c>
       <c r="F99" t="n">
-        <v>536.1</v>
+        <v>495.05</v>
       </c>
       <c r="G99" t="n">
-        <v>9431736</v>
+        <v>2755226</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10397,25 +10859,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>537.95</v>
+        <v>495.05</v>
       </c>
       <c r="D100" t="n">
-        <v>552</v>
+        <v>504.3</v>
       </c>
       <c r="E100" t="n">
-        <v>522</v>
+        <v>490.05</v>
       </c>
       <c r="F100" t="n">
-        <v>526.25</v>
+        <v>492.35</v>
       </c>
       <c r="G100" t="n">
-        <v>12427899</v>
+        <v>4448305</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10424,25 +10886,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>531</v>
+        <v>496.2</v>
       </c>
       <c r="D101" t="n">
-        <v>538.8</v>
+        <v>539.6</v>
       </c>
       <c r="E101" t="n">
-        <v>527.7</v>
+        <v>495.1</v>
       </c>
       <c r="F101" t="n">
-        <v>533.3</v>
+        <v>533.8</v>
       </c>
       <c r="G101" t="n">
-        <v>5547022</v>
+        <v>22701332</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10451,25 +10913,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>530.85</v>
+        <v>542.45</v>
       </c>
       <c r="D102" t="n">
-        <v>569.9</v>
+        <v>551</v>
       </c>
       <c r="E102" t="n">
-        <v>529.6</v>
+        <v>525.55</v>
       </c>
       <c r="F102" t="n">
-        <v>547.7</v>
+        <v>545.95</v>
       </c>
       <c r="G102" t="n">
-        <v>36903374</v>
+        <v>19838083</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10478,25 +10940,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>549</v>
+        <v>543.75</v>
       </c>
       <c r="D103" t="n">
-        <v>570.5</v>
+        <v>548</v>
       </c>
       <c r="E103" t="n">
-        <v>542</v>
+        <v>532.1</v>
       </c>
       <c r="F103" t="n">
-        <v>544.45</v>
+        <v>536.1</v>
       </c>
       <c r="G103" t="n">
-        <v>14649216</v>
+        <v>9431736</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10505,25 +10967,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>546.5</v>
+        <v>537.95</v>
       </c>
       <c r="D104" t="n">
-        <v>546.7</v>
+        <v>552</v>
       </c>
       <c r="E104" t="n">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="F104" t="n">
-        <v>529.05</v>
+        <v>526.25</v>
       </c>
       <c r="G104" t="n">
-        <v>8696054</v>
+        <v>12427899</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10532,25 +10994,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D105" t="n">
-        <v>574.9</v>
+        <v>538.8</v>
       </c>
       <c r="E105" t="n">
-        <v>534.1</v>
+        <v>527.7</v>
       </c>
       <c r="F105" t="n">
-        <v>572.65</v>
+        <v>533.3</v>
       </c>
       <c r="G105" t="n">
-        <v>29333771</v>
+        <v>5547022</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10559,25 +11021,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>568.6</v>
+        <v>530.85</v>
       </c>
       <c r="D106" t="n">
-        <v>576.7</v>
+        <v>569.9</v>
       </c>
       <c r="E106" t="n">
-        <v>555.55</v>
+        <v>529.6</v>
       </c>
       <c r="F106" t="n">
-        <v>566.35</v>
+        <v>547.7</v>
       </c>
       <c r="G106" t="n">
-        <v>15501582</v>
+        <v>36903374</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10586,25 +11048,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D107" t="n">
-        <v>569</v>
+        <v>570.5</v>
       </c>
       <c r="E107" t="n">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="F107" t="n">
-        <v>554.85</v>
+        <v>544.45</v>
       </c>
       <c r="G107" t="n">
-        <v>5929490</v>
+        <v>14649216</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10613,160 +11075,160 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>565</v>
+        <v>546.5</v>
       </c>
       <c r="D108" t="n">
-        <v>574.7</v>
+        <v>546.7</v>
       </c>
       <c r="E108" t="n">
-        <v>558.9</v>
+        <v>515</v>
       </c>
       <c r="F108" t="n">
-        <v>560.95</v>
+        <v>529.05</v>
       </c>
       <c r="G108" t="n">
-        <v>3461008</v>
+        <v>8696054</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>13.05</v>
+        <v>535</v>
       </c>
       <c r="D109" t="n">
-        <v>13.18</v>
+        <v>574.9</v>
       </c>
       <c r="E109" t="n">
-        <v>12.85</v>
+        <v>534.1</v>
       </c>
       <c r="F109" t="n">
-        <v>12.87</v>
+        <v>572.65</v>
       </c>
       <c r="G109" t="n">
-        <v>230386335</v>
+        <v>29333771</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>12.98</v>
+        <v>568.6</v>
       </c>
       <c r="D110" t="n">
-        <v>13.08</v>
+        <v>576.7</v>
       </c>
       <c r="E110" t="n">
-        <v>12.76</v>
+        <v>555.55</v>
       </c>
       <c r="F110" t="n">
-        <v>13.01</v>
+        <v>566.35</v>
       </c>
       <c r="G110" t="n">
-        <v>387269596</v>
+        <v>15501582</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13.01</v>
+        <v>560</v>
       </c>
       <c r="D111" t="n">
-        <v>13.11</v>
+        <v>569</v>
       </c>
       <c r="E111" t="n">
-        <v>12.82</v>
+        <v>553</v>
       </c>
       <c r="F111" t="n">
-        <v>12.86</v>
+        <v>554.85</v>
       </c>
       <c r="G111" t="n">
-        <v>235409728</v>
+        <v>5929490</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12.89</v>
+        <v>565</v>
       </c>
       <c r="D112" t="n">
-        <v>13.05</v>
+        <v>574.7</v>
       </c>
       <c r="E112" t="n">
-        <v>12.73</v>
+        <v>553.6</v>
       </c>
       <c r="F112" t="n">
-        <v>12.9</v>
+        <v>560.1</v>
       </c>
       <c r="G112" t="n">
-        <v>308781891</v>
+        <v>9758301</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12.91</v>
+        <v>562.95</v>
       </c>
       <c r="D113" t="n">
-        <v>13.04</v>
+        <v>580.8</v>
       </c>
       <c r="E113" t="n">
-        <v>12.77</v>
+        <v>561.2</v>
       </c>
       <c r="F113" t="n">
-        <v>12.8</v>
+        <v>576.65</v>
       </c>
       <c r="G113" t="n">
-        <v>204366752</v>
+        <v>4459665</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10775,25 +11237,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="D114" t="n">
-        <v>12.9</v>
+        <v>13.18</v>
       </c>
       <c r="E114" t="n">
-        <v>12.63</v>
+        <v>12.85</v>
       </c>
       <c r="F114" t="n">
-        <v>12.63</v>
+        <v>12.87</v>
       </c>
       <c r="G114" t="n">
-        <v>204537429</v>
+        <v>230386335</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10802,25 +11264,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12.64</v>
+        <v>12.98</v>
       </c>
       <c r="D115" t="n">
-        <v>12.88</v>
+        <v>13.08</v>
       </c>
       <c r="E115" t="n">
-        <v>12.6</v>
+        <v>12.76</v>
       </c>
       <c r="F115" t="n">
-        <v>12.73</v>
+        <v>13.01</v>
       </c>
       <c r="G115" t="n">
-        <v>205855564</v>
+        <v>387269596</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10829,25 +11291,25 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12.92</v>
+        <v>13.01</v>
       </c>
       <c r="D116" t="n">
-        <v>13.07</v>
+        <v>13.11</v>
       </c>
       <c r="E116" t="n">
-        <v>12.77</v>
+        <v>12.82</v>
       </c>
       <c r="F116" t="n">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="G116" t="n">
-        <v>413469644</v>
+        <v>235409728</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10856,25 +11318,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>13.14</v>
+        <v>12.89</v>
       </c>
       <c r="D117" t="n">
-        <v>13.3</v>
+        <v>13.05</v>
       </c>
       <c r="E117" t="n">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
       <c r="F117" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="G117" t="n">
-        <v>662095209</v>
+        <v>308781891</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10883,25 +11345,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12.93</v>
+        <v>12.91</v>
       </c>
       <c r="D118" t="n">
-        <v>13.69</v>
+        <v>13.04</v>
       </c>
       <c r="E118" t="n">
-        <v>12.83</v>
+        <v>12.77</v>
       </c>
       <c r="F118" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="G118" t="n">
-        <v>772547405</v>
+        <v>204366752</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10910,25 +11372,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>13.67</v>
+        <v>12.89</v>
       </c>
       <c r="D119" t="n">
-        <v>13.88</v>
+        <v>12.9</v>
       </c>
       <c r="E119" t="n">
-        <v>13.46</v>
+        <v>12.63</v>
       </c>
       <c r="F119" t="n">
-        <v>13.51</v>
+        <v>12.63</v>
       </c>
       <c r="G119" t="n">
-        <v>547253456</v>
+        <v>204537429</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10937,25 +11399,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>13.53</v>
+        <v>12.64</v>
       </c>
       <c r="D120" t="n">
-        <v>14.19</v>
+        <v>12.88</v>
       </c>
       <c r="E120" t="n">
-        <v>13.49</v>
+        <v>12.6</v>
       </c>
       <c r="F120" t="n">
-        <v>14.11</v>
+        <v>12.73</v>
       </c>
       <c r="G120" t="n">
-        <v>778908986</v>
+        <v>205855564</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10964,25 +11426,25 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>14.11</v>
+        <v>12.92</v>
       </c>
       <c r="D121" t="n">
-        <v>14.14</v>
+        <v>13.07</v>
       </c>
       <c r="E121" t="n">
-        <v>13.66</v>
+        <v>12.77</v>
       </c>
       <c r="F121" t="n">
-        <v>13.71</v>
+        <v>12.92</v>
       </c>
       <c r="G121" t="n">
-        <v>310430357</v>
+        <v>413469644</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10991,25 +11453,25 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>13.65</v>
+        <v>13.14</v>
       </c>
       <c r="D122" t="n">
-        <v>14.31</v>
+        <v>13.3</v>
       </c>
       <c r="E122" t="n">
-        <v>13.5</v>
+        <v>12.79</v>
       </c>
       <c r="F122" t="n">
-        <v>14.12</v>
+        <v>12.89</v>
       </c>
       <c r="G122" t="n">
-        <v>820797167</v>
+        <v>662095209</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11018,25 +11480,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14.12</v>
+        <v>12.93</v>
       </c>
       <c r="D123" t="n">
-        <v>14.22</v>
+        <v>13.69</v>
       </c>
       <c r="E123" t="n">
-        <v>13.88</v>
+        <v>12.83</v>
       </c>
       <c r="F123" t="n">
-        <v>14.07</v>
+        <v>13.5</v>
       </c>
       <c r="G123" t="n">
-        <v>320742876</v>
+        <v>772547405</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11045,187 +11507,187 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>14.14</v>
+        <v>13.67</v>
       </c>
       <c r="D124" t="n">
-        <v>14.19</v>
+        <v>13.88</v>
       </c>
       <c r="E124" t="n">
-        <v>14.05</v>
+        <v>13.46</v>
       </c>
       <c r="F124" t="n">
-        <v>14.05</v>
+        <v>13.51</v>
       </c>
       <c r="G124" t="n">
-        <v>58825145</v>
+        <v>547253456</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1554.3</v>
+        <v>13.53</v>
       </c>
       <c r="D125" t="n">
-        <v>1569</v>
+        <v>14.19</v>
       </c>
       <c r="E125" t="n">
-        <v>1551.3</v>
+        <v>13.49</v>
       </c>
       <c r="F125" t="n">
-        <v>1557.6</v>
+        <v>14.11</v>
       </c>
       <c r="G125" t="n">
-        <v>1001677</v>
+        <v>778908986</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1560.4</v>
+        <v>14.11</v>
       </c>
       <c r="D126" t="n">
-        <v>1561</v>
+        <v>14.14</v>
       </c>
       <c r="E126" t="n">
-        <v>1520.4</v>
+        <v>13.66</v>
       </c>
       <c r="F126" t="n">
-        <v>1529.8</v>
+        <v>13.71</v>
       </c>
       <c r="G126" t="n">
-        <v>1011017</v>
+        <v>310430357</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1534.9</v>
+        <v>13.65</v>
       </c>
       <c r="D127" t="n">
-        <v>1572.2</v>
+        <v>14.31</v>
       </c>
       <c r="E127" t="n">
-        <v>1527.2</v>
+        <v>13.5</v>
       </c>
       <c r="F127" t="n">
-        <v>1558.9</v>
+        <v>14.12</v>
       </c>
       <c r="G127" t="n">
-        <v>1235837</v>
+        <v>820797167</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1559.7</v>
+        <v>14.12</v>
       </c>
       <c r="D128" t="n">
-        <v>1600.1</v>
+        <v>14.22</v>
       </c>
       <c r="E128" t="n">
-        <v>1557</v>
+        <v>13.88</v>
       </c>
       <c r="F128" t="n">
-        <v>1593.2</v>
+        <v>14.07</v>
       </c>
       <c r="G128" t="n">
-        <v>1871739</v>
+        <v>320742876</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1591</v>
+        <v>14.14</v>
       </c>
       <c r="D129" t="n">
-        <v>1593.2</v>
+        <v>14.19</v>
       </c>
       <c r="E129" t="n">
-        <v>1566</v>
+        <v>13.93</v>
       </c>
       <c r="F129" t="n">
-        <v>1577.8</v>
+        <v>14.03</v>
       </c>
       <c r="G129" t="n">
-        <v>1183077</v>
+        <v>232109943</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1577.7</v>
+        <v>14.03</v>
       </c>
       <c r="D130" t="n">
-        <v>1586.1</v>
+        <v>14.09</v>
       </c>
       <c r="E130" t="n">
-        <v>1561.1</v>
+        <v>13.97</v>
       </c>
       <c r="F130" t="n">
-        <v>1568.3</v>
+        <v>14</v>
       </c>
       <c r="G130" t="n">
-        <v>1098268</v>
+        <v>36708312</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11234,25 +11696,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1560</v>
+        <v>1554.3</v>
       </c>
       <c r="D131" t="n">
-        <v>1610</v>
+        <v>1569</v>
       </c>
       <c r="E131" t="n">
-        <v>1554.9</v>
+        <v>1551.3</v>
       </c>
       <c r="F131" t="n">
-        <v>1601.2</v>
+        <v>1557.6</v>
       </c>
       <c r="G131" t="n">
-        <v>2647403</v>
+        <v>1001677</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11261,25 +11723,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1624.8</v>
+        <v>1560.4</v>
       </c>
       <c r="D132" t="n">
-        <v>1734.5</v>
+        <v>1561</v>
       </c>
       <c r="E132" t="n">
-        <v>1617.1</v>
+        <v>1520.4</v>
       </c>
       <c r="F132" t="n">
-        <v>1713.4</v>
+        <v>1529.8</v>
       </c>
       <c r="G132" t="n">
-        <v>7989771</v>
+        <v>1011017</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11288,25 +11750,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1713</v>
+        <v>1534.9</v>
       </c>
       <c r="D133" t="n">
-        <v>1762</v>
+        <v>1572.2</v>
       </c>
       <c r="E133" t="n">
-        <v>1707.7</v>
+        <v>1527.2</v>
       </c>
       <c r="F133" t="n">
-        <v>1758.9</v>
+        <v>1558.9</v>
       </c>
       <c r="G133" t="n">
-        <v>4407907</v>
+        <v>1235837</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11315,25 +11777,25 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1762</v>
+        <v>1559.7</v>
       </c>
       <c r="D134" t="n">
-        <v>1797.9</v>
+        <v>1600.1</v>
       </c>
       <c r="E134" t="n">
-        <v>1754.3</v>
+        <v>1557</v>
       </c>
       <c r="F134" t="n">
-        <v>1781.3</v>
+        <v>1593.2</v>
       </c>
       <c r="G134" t="n">
-        <v>3000811</v>
+        <v>1871739</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11342,25 +11804,25 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1785</v>
+        <v>1591</v>
       </c>
       <c r="D135" t="n">
-        <v>1798.9</v>
+        <v>1593.2</v>
       </c>
       <c r="E135" t="n">
-        <v>1773.3</v>
+        <v>1566</v>
       </c>
       <c r="F135" t="n">
-        <v>1781.3</v>
+        <v>1577.8</v>
       </c>
       <c r="G135" t="n">
-        <v>2402202</v>
+        <v>1183077</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11369,25 +11831,25 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1785</v>
+        <v>1577.7</v>
       </c>
       <c r="D136" t="n">
-        <v>1826.6</v>
+        <v>1586.1</v>
       </c>
       <c r="E136" t="n">
-        <v>1785</v>
+        <v>1561.1</v>
       </c>
       <c r="F136" t="n">
-        <v>1816.2</v>
+        <v>1568.3</v>
       </c>
       <c r="G136" t="n">
-        <v>2502579</v>
+        <v>1098268</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11396,25 +11858,25 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1821</v>
+        <v>1560</v>
       </c>
       <c r="D137" t="n">
-        <v>1838.3</v>
+        <v>1610</v>
       </c>
       <c r="E137" t="n">
-        <v>1789.1</v>
+        <v>1554.9</v>
       </c>
       <c r="F137" t="n">
-        <v>1811.4</v>
+        <v>1601.2</v>
       </c>
       <c r="G137" t="n">
-        <v>1919384</v>
+        <v>2647403</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11423,25 +11885,25 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1811</v>
+        <v>1624.8</v>
       </c>
       <c r="D138" t="n">
-        <v>1850</v>
+        <v>1734.5</v>
       </c>
       <c r="E138" t="n">
-        <v>1806.1</v>
+        <v>1617.1</v>
       </c>
       <c r="F138" t="n">
-        <v>1850</v>
+        <v>1713.4</v>
       </c>
       <c r="G138" t="n">
-        <v>1405192</v>
+        <v>7989771</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11450,25 +11912,25 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1854</v>
+        <v>1713</v>
       </c>
       <c r="D139" t="n">
-        <v>1856.6</v>
+        <v>1762</v>
       </c>
       <c r="E139" t="n">
-        <v>1834.5</v>
+        <v>1707.7</v>
       </c>
       <c r="F139" t="n">
-        <v>1835</v>
+        <v>1758.9</v>
       </c>
       <c r="G139" t="n">
-        <v>2090998</v>
+        <v>4407907</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11477,25 +11939,25 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1843</v>
+        <v>1762</v>
       </c>
       <c r="D140" t="n">
-        <v>1854.9</v>
+        <v>1797.9</v>
       </c>
       <c r="E140" t="n">
-        <v>1830</v>
+        <v>1754.3</v>
       </c>
       <c r="F140" t="n">
-        <v>1830</v>
+        <v>1781.3</v>
       </c>
       <c r="G140" t="n">
-        <v>2037418</v>
+        <v>3000811</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11504,25 +11966,25 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1838</v>
+        <v>1785</v>
       </c>
       <c r="D141" t="n">
-        <v>1856</v>
+        <v>1798.9</v>
       </c>
       <c r="E141" t="n">
-        <v>1833.2</v>
+        <v>1773.3</v>
       </c>
       <c r="F141" t="n">
-        <v>1844.3</v>
+        <v>1781.3</v>
       </c>
       <c r="G141" t="n">
-        <v>1553067</v>
+        <v>2402202</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11531,25 +11993,25 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1845</v>
+        <v>1785</v>
       </c>
       <c r="D142" t="n">
-        <v>1870.8</v>
+        <v>1826.6</v>
       </c>
       <c r="E142" t="n">
-        <v>1832.8</v>
+        <v>1785</v>
       </c>
       <c r="F142" t="n">
-        <v>1854</v>
+        <v>1816.2</v>
       </c>
       <c r="G142" t="n">
-        <v>1386592</v>
+        <v>2502579</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11558,25 +12020,25 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1851</v>
+        <v>1821</v>
       </c>
       <c r="D143" t="n">
-        <v>1859</v>
+        <v>1838.3</v>
       </c>
       <c r="E143" t="n">
-        <v>1833.1</v>
+        <v>1789.1</v>
       </c>
       <c r="F143" t="n">
-        <v>1858</v>
+        <v>1811.4</v>
       </c>
       <c r="G143" t="n">
-        <v>1514239</v>
+        <v>1919384</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11585,25 +12047,25 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1856.3</v>
+        <v>1811</v>
       </c>
       <c r="D144" t="n">
-        <v>1862.3</v>
+        <v>1850</v>
       </c>
       <c r="E144" t="n">
-        <v>1835</v>
+        <v>1806.1</v>
       </c>
       <c r="F144" t="n">
         <v>1850</v>
       </c>
       <c r="G144" t="n">
-        <v>1088545</v>
+        <v>1405192</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11612,25 +12074,25 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="D145" t="n">
-        <v>1851.7</v>
+        <v>1856.6</v>
       </c>
       <c r="E145" t="n">
-        <v>1820.6</v>
+        <v>1834.5</v>
       </c>
       <c r="F145" t="n">
-        <v>1851.7</v>
+        <v>1835</v>
       </c>
       <c r="G145" t="n">
-        <v>1345856</v>
+        <v>2090998</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11639,25 +12101,25 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1849.9</v>
+        <v>1843</v>
       </c>
       <c r="D146" t="n">
-        <v>1853.2</v>
+        <v>1854.9</v>
       </c>
       <c r="E146" t="n">
-        <v>1777.7</v>
+        <v>1830</v>
       </c>
       <c r="F146" t="n">
-        <v>1787.3</v>
+        <v>1830</v>
       </c>
       <c r="G146" t="n">
-        <v>1581352</v>
+        <v>2037418</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11666,25 +12128,25 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1770</v>
+        <v>1838</v>
       </c>
       <c r="D147" t="n">
-        <v>1824</v>
+        <v>1856</v>
       </c>
       <c r="E147" t="n">
-        <v>1769.4</v>
+        <v>1833.2</v>
       </c>
       <c r="F147" t="n">
-        <v>1809.7</v>
+        <v>1844.3</v>
       </c>
       <c r="G147" t="n">
-        <v>1631767</v>
+        <v>1553067</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11693,25 +12155,25 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1810</v>
+        <v>1845</v>
       </c>
       <c r="D148" t="n">
-        <v>1824.6</v>
+        <v>1870.8</v>
       </c>
       <c r="E148" t="n">
-        <v>1802.1</v>
+        <v>1832.8</v>
       </c>
       <c r="F148" t="n">
-        <v>1814</v>
+        <v>1854</v>
       </c>
       <c r="G148" t="n">
-        <v>1291914</v>
+        <v>1386592</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11720,25 +12182,25 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1814</v>
+        <v>1851</v>
       </c>
       <c r="D149" t="n">
-        <v>1818</v>
+        <v>1859</v>
       </c>
       <c r="E149" t="n">
-        <v>1789.9</v>
+        <v>1833.1</v>
       </c>
       <c r="F149" t="n">
-        <v>1801.8</v>
+        <v>1858</v>
       </c>
       <c r="G149" t="n">
-        <v>1426377</v>
+        <v>1514239</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11747,214 +12209,214 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1819</v>
+        <v>1856.3</v>
       </c>
       <c r="D150" t="n">
-        <v>1832</v>
+        <v>1862.3</v>
       </c>
       <c r="E150" t="n">
-        <v>1813.8</v>
+        <v>1835</v>
       </c>
       <c r="F150" t="n">
-        <v>1818.4</v>
+        <v>1850</v>
       </c>
       <c r="G150" t="n">
-        <v>293760</v>
+        <v>1088545</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>344</v>
+        <v>1850</v>
       </c>
       <c r="D151" t="n">
-        <v>346.3</v>
+        <v>1851.7</v>
       </c>
       <c r="E151" t="n">
-        <v>341.25</v>
+        <v>1820.6</v>
       </c>
       <c r="F151" t="n">
-        <v>342.9</v>
+        <v>1851.7</v>
       </c>
       <c r="G151" t="n">
-        <v>4465145</v>
+        <v>1345856</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>344.2</v>
+        <v>1849.9</v>
       </c>
       <c r="D152" t="n">
-        <v>347.75</v>
+        <v>1853.2</v>
       </c>
       <c r="E152" t="n">
-        <v>339.95</v>
+        <v>1777.7</v>
       </c>
       <c r="F152" t="n">
-        <v>342.4</v>
+        <v>1787.3</v>
       </c>
       <c r="G152" t="n">
-        <v>3803051</v>
+        <v>1581352</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>346</v>
+        <v>1770</v>
       </c>
       <c r="D153" t="n">
-        <v>351</v>
+        <v>1824</v>
       </c>
       <c r="E153" t="n">
-        <v>343.65</v>
+        <v>1769.4</v>
       </c>
       <c r="F153" t="n">
-        <v>346</v>
+        <v>1809.7</v>
       </c>
       <c r="G153" t="n">
-        <v>5175178</v>
+        <v>1631767</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>341.8</v>
+        <v>1810</v>
       </c>
       <c r="D154" t="n">
-        <v>344.9</v>
+        <v>1824.6</v>
       </c>
       <c r="E154" t="n">
-        <v>339.65</v>
+        <v>1802.1</v>
       </c>
       <c r="F154" t="n">
-        <v>343.9</v>
+        <v>1814</v>
       </c>
       <c r="G154" t="n">
-        <v>2253982</v>
+        <v>1291914</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>345.1</v>
+        <v>1814</v>
       </c>
       <c r="D155" t="n">
-        <v>346.05</v>
+        <v>1818</v>
       </c>
       <c r="E155" t="n">
-        <v>338.35</v>
+        <v>1789.9</v>
       </c>
       <c r="F155" t="n">
-        <v>339.35</v>
+        <v>1801.8</v>
       </c>
       <c r="G155" t="n">
-        <v>3868006</v>
+        <v>1426377</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>339.4</v>
+        <v>1819</v>
       </c>
       <c r="D156" t="n">
-        <v>340.2</v>
+        <v>1832</v>
       </c>
       <c r="E156" t="n">
-        <v>333</v>
+        <v>1813.8</v>
       </c>
       <c r="F156" t="n">
-        <v>334.55</v>
+        <v>1825</v>
       </c>
       <c r="G156" t="n">
-        <v>3721274</v>
+        <v>1315065</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>335</v>
+        <v>1825</v>
       </c>
       <c r="D157" t="n">
-        <v>346.1</v>
+        <v>1836.4</v>
       </c>
       <c r="E157" t="n">
-        <v>332</v>
+        <v>1816.3</v>
       </c>
       <c r="F157" t="n">
-        <v>344.7</v>
+        <v>1822.8</v>
       </c>
       <c r="G157" t="n">
-        <v>5431501</v>
+        <v>251339</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11963,25 +12425,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>345.5</v>
+        <v>344</v>
       </c>
       <c r="D158" t="n">
-        <v>349.65</v>
+        <v>346.3</v>
       </c>
       <c r="E158" t="n">
-        <v>342.6</v>
+        <v>341.25</v>
       </c>
       <c r="F158" t="n">
-        <v>347.65</v>
+        <v>342.9</v>
       </c>
       <c r="G158" t="n">
-        <v>6318472</v>
+        <v>4465145</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11990,25 +12452,25 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>352</v>
+        <v>344.2</v>
       </c>
       <c r="D159" t="n">
-        <v>355.75</v>
+        <v>347.75</v>
       </c>
       <c r="E159" t="n">
-        <v>347.65</v>
+        <v>339.95</v>
       </c>
       <c r="F159" t="n">
-        <v>350.05</v>
+        <v>342.4</v>
       </c>
       <c r="G159" t="n">
-        <v>7186013</v>
+        <v>3803051</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12017,25 +12479,25 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>357.95</v>
+        <v>346</v>
       </c>
       <c r="D160" t="n">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="E160" t="n">
-        <v>353.5</v>
+        <v>343.65</v>
       </c>
       <c r="F160" t="n">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="G160" t="n">
-        <v>12541474</v>
+        <v>5175178</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12044,25 +12506,25 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>373</v>
+        <v>341.8</v>
       </c>
       <c r="D161" t="n">
-        <v>382.45</v>
+        <v>344.9</v>
       </c>
       <c r="E161" t="n">
-        <v>367.15</v>
+        <v>339.65</v>
       </c>
       <c r="F161" t="n">
-        <v>377</v>
+        <v>343.9</v>
       </c>
       <c r="G161" t="n">
-        <v>15775994</v>
+        <v>2253982</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12071,25 +12533,25 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>381</v>
+        <v>345.1</v>
       </c>
       <c r="D162" t="n">
-        <v>383.9</v>
+        <v>346.05</v>
       </c>
       <c r="E162" t="n">
-        <v>375.15</v>
+        <v>338.35</v>
       </c>
       <c r="F162" t="n">
-        <v>381</v>
+        <v>339.35</v>
       </c>
       <c r="G162" t="n">
-        <v>8940938</v>
+        <v>3868006</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12098,25 +12560,25 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>385</v>
+        <v>339.4</v>
       </c>
       <c r="D163" t="n">
-        <v>385.05</v>
+        <v>340.2</v>
       </c>
       <c r="E163" t="n">
-        <v>376.5</v>
+        <v>333</v>
       </c>
       <c r="F163" t="n">
-        <v>381</v>
+        <v>334.55</v>
       </c>
       <c r="G163" t="n">
-        <v>6636333</v>
+        <v>3721274</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12125,25 +12587,25 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>382.5</v>
+        <v>335</v>
       </c>
       <c r="D164" t="n">
-        <v>382.85</v>
+        <v>346.1</v>
       </c>
       <c r="E164" t="n">
-        <v>377.15</v>
+        <v>332</v>
       </c>
       <c r="F164" t="n">
-        <v>381</v>
+        <v>344.7</v>
       </c>
       <c r="G164" t="n">
-        <v>4423953</v>
+        <v>5431501</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12152,25 +12614,25 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>381.7</v>
+        <v>345.5</v>
       </c>
       <c r="D165" t="n">
-        <v>387.7</v>
+        <v>349.65</v>
       </c>
       <c r="E165" t="n">
-        <v>381.1</v>
+        <v>342.6</v>
       </c>
       <c r="F165" t="n">
-        <v>382.7</v>
+        <v>347.65</v>
       </c>
       <c r="G165" t="n">
-        <v>5292453</v>
+        <v>6318472</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12179,25 +12641,25 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>387.15</v>
+        <v>352</v>
       </c>
       <c r="D166" t="n">
-        <v>393.7</v>
+        <v>355.75</v>
       </c>
       <c r="E166" t="n">
-        <v>384.5</v>
+        <v>347.65</v>
       </c>
       <c r="F166" t="n">
-        <v>388</v>
+        <v>350.05</v>
       </c>
       <c r="G166" t="n">
-        <v>8155315</v>
+        <v>7186013</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12206,25 +12668,25 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>398.5</v>
+        <v>357.95</v>
       </c>
       <c r="D167" t="n">
-        <v>422.2</v>
+        <v>369</v>
       </c>
       <c r="E167" t="n">
-        <v>398.5</v>
+        <v>353.5</v>
       </c>
       <c r="F167" t="n">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="G167" t="n">
-        <v>34388331</v>
+        <v>12541474</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12233,25 +12695,25 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>410.5</v>
+        <v>373</v>
       </c>
       <c r="D168" t="n">
-        <v>413.65</v>
+        <v>382.45</v>
       </c>
       <c r="E168" t="n">
-        <v>400</v>
+        <v>367.15</v>
       </c>
       <c r="F168" t="n">
-        <v>400.5</v>
+        <v>377</v>
       </c>
       <c r="G168" t="n">
-        <v>9738984</v>
+        <v>15775994</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12260,25 +12722,25 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>378.6</v>
+        <v>381</v>
       </c>
       <c r="D169" t="n">
-        <v>384.95</v>
+        <v>383.9</v>
       </c>
       <c r="E169" t="n">
-        <v>375</v>
+        <v>375.15</v>
       </c>
       <c r="F169" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="G169" t="n">
-        <v>14954594</v>
+        <v>8940938</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12287,25 +12749,25 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>377.9</v>
+        <v>385</v>
       </c>
       <c r="D170" t="n">
-        <v>391.5</v>
+        <v>385.05</v>
       </c>
       <c r="E170" t="n">
         <v>376.5</v>
       </c>
       <c r="F170" t="n">
-        <v>387.55</v>
+        <v>381</v>
       </c>
       <c r="G170" t="n">
-        <v>9724992</v>
+        <v>6636333</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12314,25 +12776,25 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>386.8</v>
+        <v>382.5</v>
       </c>
       <c r="D171" t="n">
-        <v>390.85</v>
+        <v>382.85</v>
       </c>
       <c r="E171" t="n">
-        <v>385.8</v>
+        <v>377.15</v>
       </c>
       <c r="F171" t="n">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G171" t="n">
-        <v>2824411</v>
+        <v>4423953</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12341,25 +12803,25 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>382</v>
+        <v>381.7</v>
       </c>
       <c r="D172" t="n">
-        <v>386.55</v>
+        <v>387.7</v>
       </c>
       <c r="E172" t="n">
-        <v>379</v>
+        <v>381.1</v>
       </c>
       <c r="F172" t="n">
-        <v>386.55</v>
+        <v>382.7</v>
       </c>
       <c r="G172" t="n">
-        <v>3939022</v>
+        <v>5292453</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12368,241 +12830,241 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>392</v>
+        <v>387.15</v>
       </c>
       <c r="D173" t="n">
-        <v>395.75</v>
+        <v>393.7</v>
       </c>
       <c r="E173" t="n">
-        <v>387.4</v>
+        <v>384.5</v>
       </c>
       <c r="F173" t="n">
         <v>388</v>
       </c>
       <c r="G173" t="n">
-        <v>1481893</v>
+        <v>8155315</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4389.8</v>
+        <v>398.5</v>
       </c>
       <c r="D174" t="n">
-        <v>4485</v>
+        <v>422.2</v>
       </c>
       <c r="E174" t="n">
-        <v>4361.9</v>
+        <v>398.5</v>
       </c>
       <c r="F174" t="n">
-        <v>4398.1</v>
+        <v>420</v>
       </c>
       <c r="G174" t="n">
-        <v>1347378</v>
+        <v>34388331</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>4422</v>
+        <v>410.5</v>
       </c>
       <c r="D175" t="n">
-        <v>4495</v>
+        <v>413.65</v>
       </c>
       <c r="E175" t="n">
-        <v>4358</v>
+        <v>400</v>
       </c>
       <c r="F175" t="n">
-        <v>4371.4</v>
+        <v>400.5</v>
       </c>
       <c r="G175" t="n">
-        <v>902264</v>
+        <v>9738984</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4387.7</v>
+        <v>378.6</v>
       </c>
       <c r="D176" t="n">
-        <v>4404</v>
+        <v>384.95</v>
       </c>
       <c r="E176" t="n">
-        <v>4281.9</v>
+        <v>375</v>
       </c>
       <c r="F176" t="n">
-        <v>4304.2</v>
+        <v>376</v>
       </c>
       <c r="G176" t="n">
-        <v>463349</v>
+        <v>14954594</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4285</v>
+        <v>377.9</v>
       </c>
       <c r="D177" t="n">
-        <v>4317</v>
+        <v>391.5</v>
       </c>
       <c r="E177" t="n">
-        <v>4220</v>
+        <v>376.5</v>
       </c>
       <c r="F177" t="n">
-        <v>4244.3</v>
+        <v>387.55</v>
       </c>
       <c r="G177" t="n">
-        <v>398348</v>
+        <v>9724992</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4211</v>
+        <v>386.8</v>
       </c>
       <c r="D178" t="n">
-        <v>4220</v>
+        <v>390.85</v>
       </c>
       <c r="E178" t="n">
-        <v>4129.3</v>
+        <v>385.8</v>
       </c>
       <c r="F178" t="n">
-        <v>4178.1</v>
+        <v>388</v>
       </c>
       <c r="G178" t="n">
-        <v>470046</v>
+        <v>2824411</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>4190</v>
+        <v>382</v>
       </c>
       <c r="D179" t="n">
-        <v>4324.4</v>
+        <v>386.55</v>
       </c>
       <c r="E179" t="n">
-        <v>4190</v>
+        <v>379</v>
       </c>
       <c r="F179" t="n">
-        <v>4257.3</v>
+        <v>386.55</v>
       </c>
       <c r="G179" t="n">
-        <v>633457</v>
+        <v>3939022</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4290</v>
+        <v>392</v>
       </c>
       <c r="D180" t="n">
-        <v>4383</v>
+        <v>395.75</v>
       </c>
       <c r="E180" t="n">
-        <v>4266</v>
+        <v>385.1</v>
       </c>
       <c r="F180" t="n">
-        <v>4288.7</v>
+        <v>385.6</v>
       </c>
       <c r="G180" t="n">
-        <v>835107</v>
+        <v>5349753</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4299</v>
+        <v>388</v>
       </c>
       <c r="D181" t="n">
-        <v>4340</v>
+        <v>392.5</v>
       </c>
       <c r="E181" t="n">
-        <v>4216</v>
+        <v>384.6</v>
       </c>
       <c r="F181" t="n">
-        <v>4243.8</v>
+        <v>391.5</v>
       </c>
       <c r="G181" t="n">
-        <v>422024</v>
+        <v>1014755</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12611,25 +13073,25 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>4201.9</v>
+        <v>4389.8</v>
       </c>
       <c r="D182" t="n">
-        <v>4222</v>
+        <v>4485</v>
       </c>
       <c r="E182" t="n">
-        <v>4115</v>
+        <v>4361.9</v>
       </c>
       <c r="F182" t="n">
-        <v>4156</v>
+        <v>4398.1</v>
       </c>
       <c r="G182" t="n">
-        <v>378694</v>
+        <v>1347378</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12638,25 +13100,25 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>4181.8</v>
+        <v>4422</v>
       </c>
       <c r="D183" t="n">
-        <v>4385</v>
+        <v>4495</v>
       </c>
       <c r="E183" t="n">
-        <v>4129.4</v>
+        <v>4358</v>
       </c>
       <c r="F183" t="n">
-        <v>4362.2</v>
+        <v>4371.4</v>
       </c>
       <c r="G183" t="n">
-        <v>992864</v>
+        <v>902264</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12665,25 +13127,25 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>4380</v>
+        <v>4387.7</v>
       </c>
       <c r="D184" t="n">
-        <v>4478.3</v>
+        <v>4404</v>
       </c>
       <c r="E184" t="n">
-        <v>4280.1</v>
+        <v>4281.9</v>
       </c>
       <c r="F184" t="n">
-        <v>4395.7</v>
+        <v>4304.2</v>
       </c>
       <c r="G184" t="n">
-        <v>960643</v>
+        <v>463349</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12692,25 +13154,25 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>4497.2</v>
+        <v>4285</v>
       </c>
       <c r="D185" t="n">
-        <v>4541.17</v>
+        <v>4317</v>
       </c>
       <c r="E185" t="n">
-        <v>4319.31</v>
+        <v>4220</v>
       </c>
       <c r="F185" t="n">
-        <v>4361.38</v>
+        <v>4244.3</v>
       </c>
       <c r="G185" t="n">
-        <v>1616021</v>
+        <v>398348</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12719,25 +13181,25 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>4338</v>
+        <v>4211</v>
       </c>
       <c r="D186" t="n">
-        <v>4339.1</v>
+        <v>4220</v>
       </c>
       <c r="E186" t="n">
-        <v>4172.9</v>
+        <v>4129.3</v>
       </c>
       <c r="F186" t="n">
-        <v>4192.59</v>
+        <v>4178.1</v>
       </c>
       <c r="G186" t="n">
-        <v>648341</v>
+        <v>470046</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12746,25 +13208,25 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4297.32</v>
+        <v>4190</v>
       </c>
       <c r="D187" t="n">
-        <v>4595.14</v>
+        <v>4324.4</v>
       </c>
       <c r="E187" t="n">
-        <v>4249.35</v>
+        <v>4190</v>
       </c>
       <c r="F187" t="n">
-        <v>4521.18</v>
+        <v>4257.3</v>
       </c>
       <c r="G187" t="n">
-        <v>4510774</v>
+        <v>633457</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12773,25 +13235,25 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4557.56</v>
+        <v>4290</v>
       </c>
       <c r="D188" t="n">
-        <v>4737.05</v>
+        <v>4383</v>
       </c>
       <c r="E188" t="n">
-        <v>4537.17</v>
+        <v>4266</v>
       </c>
       <c r="F188" t="n">
-        <v>4583.14</v>
+        <v>4288.7</v>
       </c>
       <c r="G188" t="n">
-        <v>2334958</v>
+        <v>835107</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12800,25 +13262,25 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4606.13</v>
+        <v>4299</v>
       </c>
       <c r="D189" t="n">
-        <v>4777.02</v>
+        <v>4340</v>
       </c>
       <c r="E189" t="n">
-        <v>4590.24</v>
+        <v>4216</v>
       </c>
       <c r="F189" t="n">
-        <v>4759.23</v>
+        <v>4243.8</v>
       </c>
       <c r="G189" t="n">
-        <v>1899271</v>
+        <v>422024</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12827,25 +13289,25 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>4817.7</v>
+        <v>4201.9</v>
       </c>
       <c r="D190" t="n">
-        <v>4929.93</v>
+        <v>4222</v>
       </c>
       <c r="E190" t="n">
-        <v>4722.06</v>
+        <v>4115</v>
       </c>
       <c r="F190" t="n">
-        <v>4890.75</v>
+        <v>4156</v>
       </c>
       <c r="G190" t="n">
-        <v>1924204</v>
+        <v>378694</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12854,25 +13316,25 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>4896.95</v>
+        <v>4181.8</v>
       </c>
       <c r="D191" t="n">
-        <v>4976.9</v>
+        <v>4385</v>
       </c>
       <c r="E191" t="n">
-        <v>4780.02</v>
+        <v>4129.4</v>
       </c>
       <c r="F191" t="n">
-        <v>4813</v>
+        <v>4362.2</v>
       </c>
       <c r="G191" t="n">
-        <v>1117424</v>
+        <v>992864</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12881,25 +13343,25 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>4790</v>
+        <v>4380</v>
       </c>
       <c r="D192" t="n">
-        <v>4968</v>
+        <v>4478.3</v>
       </c>
       <c r="E192" t="n">
-        <v>4780</v>
+        <v>4280.1</v>
       </c>
       <c r="F192" t="n">
-        <v>4939.2</v>
+        <v>4395.7</v>
       </c>
       <c r="G192" t="n">
-        <v>1296942</v>
+        <v>960643</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12908,25 +13370,25 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>4958</v>
+        <v>4497.2</v>
       </c>
       <c r="D193" t="n">
-        <v>5085</v>
+        <v>4541.17</v>
       </c>
       <c r="E193" t="n">
-        <v>4888.8</v>
+        <v>4319.31</v>
       </c>
       <c r="F193" t="n">
-        <v>4903</v>
+        <v>4361.38</v>
       </c>
       <c r="G193" t="n">
-        <v>1210476</v>
+        <v>1616021</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12935,25 +13397,25 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>4903</v>
+        <v>4338</v>
       </c>
       <c r="D194" t="n">
-        <v>4940</v>
+        <v>4339.1</v>
       </c>
       <c r="E194" t="n">
-        <v>4792.5</v>
+        <v>4172.9</v>
       </c>
       <c r="F194" t="n">
-        <v>4859.8</v>
+        <v>4192.59</v>
       </c>
       <c r="G194" t="n">
-        <v>682980</v>
+        <v>648341</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12962,25 +13424,25 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>4866</v>
+        <v>4297.32</v>
       </c>
       <c r="D195" t="n">
-        <v>4907.9</v>
+        <v>4595.14</v>
       </c>
       <c r="E195" t="n">
-        <v>4753</v>
+        <v>4249.35</v>
       </c>
       <c r="F195" t="n">
-        <v>4837.4</v>
+        <v>4521.18</v>
       </c>
       <c r="G195" t="n">
-        <v>613049</v>
+        <v>4510774</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12989,25 +13451,25 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>4860</v>
+        <v>4557.56</v>
       </c>
       <c r="D196" t="n">
-        <v>5200</v>
+        <v>4737.05</v>
       </c>
       <c r="E196" t="n">
-        <v>4860</v>
+        <v>4537.17</v>
       </c>
       <c r="F196" t="n">
-        <v>5181</v>
+        <v>4583.14</v>
       </c>
       <c r="G196" t="n">
-        <v>3457670</v>
+        <v>2334958</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13016,25 +13478,25 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5200</v>
+        <v>4606.13</v>
       </c>
       <c r="D197" t="n">
-        <v>5269</v>
+        <v>4777.02</v>
       </c>
       <c r="E197" t="n">
-        <v>4991.3</v>
+        <v>4590.24</v>
       </c>
       <c r="F197" t="n">
-        <v>5007.2</v>
+        <v>4759.23</v>
       </c>
       <c r="G197" t="n">
-        <v>1695255</v>
+        <v>1899271</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13043,25 +13505,25 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5022</v>
+        <v>4817.7</v>
       </c>
       <c r="D198" t="n">
-        <v>5225</v>
+        <v>4929.93</v>
       </c>
       <c r="E198" t="n">
-        <v>5008.3</v>
+        <v>4722.06</v>
       </c>
       <c r="F198" t="n">
-        <v>5212.4</v>
+        <v>4890.75</v>
       </c>
       <c r="G198" t="n">
-        <v>1438746</v>
+        <v>1924204</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13070,25 +13532,25 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5110</v>
+        <v>4896.95</v>
       </c>
       <c r="D199" t="n">
-        <v>5396.4</v>
+        <v>4976.9</v>
       </c>
       <c r="E199" t="n">
-        <v>5092.8</v>
+        <v>4780.02</v>
       </c>
       <c r="F199" t="n">
-        <v>5354.5</v>
+        <v>4813</v>
       </c>
       <c r="G199" t="n">
-        <v>2395703</v>
+        <v>1117424</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13097,25 +13559,25 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5324.9</v>
+        <v>4790</v>
       </c>
       <c r="D200" t="n">
-        <v>5338</v>
+        <v>4968</v>
       </c>
       <c r="E200" t="n">
-        <v>5025</v>
+        <v>4780</v>
       </c>
       <c r="F200" t="n">
-        <v>5065</v>
+        <v>4939.2</v>
       </c>
       <c r="G200" t="n">
-        <v>1923210</v>
+        <v>1296942</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13124,268 +13586,268 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5095.7</v>
+        <v>4958</v>
       </c>
       <c r="D201" t="n">
-        <v>5224.8</v>
+        <v>5085</v>
       </c>
       <c r="E201" t="n">
-        <v>5093</v>
+        <v>4888.8</v>
       </c>
       <c r="F201" t="n">
-        <v>5216.1</v>
+        <v>4903</v>
       </c>
       <c r="G201" t="n">
-        <v>457693</v>
+        <v>1210476</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1417</v>
+        <v>4903</v>
       </c>
       <c r="D202" t="n">
-        <v>1436</v>
+        <v>4940</v>
       </c>
       <c r="E202" t="n">
-        <v>1410.1</v>
+        <v>4792.5</v>
       </c>
       <c r="F202" t="n">
-        <v>1423.9</v>
+        <v>4859.8</v>
       </c>
       <c r="G202" t="n">
-        <v>623969</v>
+        <v>682980</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1428</v>
+        <v>4866</v>
       </c>
       <c r="D203" t="n">
-        <v>1428</v>
+        <v>4907.9</v>
       </c>
       <c r="E203" t="n">
-        <v>1351.5</v>
+        <v>4753</v>
       </c>
       <c r="F203" t="n">
-        <v>1359.1</v>
+        <v>4837.4</v>
       </c>
       <c r="G203" t="n">
-        <v>808190</v>
+        <v>613049</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1349.8</v>
+        <v>4860</v>
       </c>
       <c r="D204" t="n">
-        <v>1357.8</v>
+        <v>5200</v>
       </c>
       <c r="E204" t="n">
-        <v>1330.1</v>
+        <v>4860</v>
       </c>
       <c r="F204" t="n">
-        <v>1340.8</v>
+        <v>5181</v>
       </c>
       <c r="G204" t="n">
-        <v>345535</v>
+        <v>3457670</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1340.8</v>
+        <v>5200</v>
       </c>
       <c r="D205" t="n">
-        <v>1387.7</v>
+        <v>5269</v>
       </c>
       <c r="E205" t="n">
-        <v>1316</v>
+        <v>4991.3</v>
       </c>
       <c r="F205" t="n">
-        <v>1374.4</v>
+        <v>5007.2</v>
       </c>
       <c r="G205" t="n">
-        <v>974660</v>
+        <v>1695255</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1372.9</v>
+        <v>5022</v>
       </c>
       <c r="D206" t="n">
-        <v>1390</v>
+        <v>5225</v>
       </c>
       <c r="E206" t="n">
-        <v>1355.1</v>
+        <v>5008.3</v>
       </c>
       <c r="F206" t="n">
-        <v>1363.5</v>
+        <v>5212.4</v>
       </c>
       <c r="G206" t="n">
-        <v>479123</v>
+        <v>1438746</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1363</v>
+        <v>5110</v>
       </c>
       <c r="D207" t="n">
-        <v>1392</v>
+        <v>5396.4</v>
       </c>
       <c r="E207" t="n">
-        <v>1355.1</v>
+        <v>5092.8</v>
       </c>
       <c r="F207" t="n">
-        <v>1380</v>
+        <v>5354.5</v>
       </c>
       <c r="G207" t="n">
-        <v>616767</v>
+        <v>2395703</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1360</v>
+        <v>5324.9</v>
       </c>
       <c r="D208" t="n">
-        <v>1368</v>
+        <v>5338</v>
       </c>
       <c r="E208" t="n">
-        <v>1272.1</v>
+        <v>5025</v>
       </c>
       <c r="F208" t="n">
-        <v>1288.3</v>
+        <v>5065</v>
       </c>
       <c r="G208" t="n">
-        <v>1098492</v>
+        <v>1923210</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1300</v>
+        <v>5095.7</v>
       </c>
       <c r="D209" t="n">
-        <v>1318.5</v>
+        <v>5449.9</v>
       </c>
       <c r="E209" t="n">
-        <v>1257</v>
+        <v>5093</v>
       </c>
       <c r="F209" t="n">
-        <v>1316.2</v>
+        <v>5419.8</v>
       </c>
       <c r="G209" t="n">
-        <v>1172726</v>
+        <v>4457308</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1317.7</v>
+        <v>5400</v>
       </c>
       <c r="D210" t="n">
-        <v>1319.8</v>
+        <v>5579</v>
       </c>
       <c r="E210" t="n">
-        <v>1270.5</v>
+        <v>5360</v>
       </c>
       <c r="F210" t="n">
-        <v>1306</v>
+        <v>5556.8</v>
       </c>
       <c r="G210" t="n">
-        <v>832973</v>
+        <v>1086319</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13394,25 +13856,25 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1319.9</v>
+        <v>1417</v>
       </c>
       <c r="D211" t="n">
-        <v>1355.4</v>
+        <v>1436</v>
       </c>
       <c r="E211" t="n">
-        <v>1308</v>
+        <v>1410.1</v>
       </c>
       <c r="F211" t="n">
-        <v>1343.4</v>
+        <v>1423.9</v>
       </c>
       <c r="G211" t="n">
-        <v>1287698</v>
+        <v>623969</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13421,25 +13883,25 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1379</v>
+        <v>1428</v>
       </c>
       <c r="D212" t="n">
-        <v>1468</v>
+        <v>1428</v>
       </c>
       <c r="E212" t="n">
-        <v>1361</v>
+        <v>1351.5</v>
       </c>
       <c r="F212" t="n">
-        <v>1377.8</v>
+        <v>1359.1</v>
       </c>
       <c r="G212" t="n">
-        <v>9950655</v>
+        <v>808190</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13448,25 +13910,25 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1380.5</v>
+        <v>1349.8</v>
       </c>
       <c r="D213" t="n">
-        <v>1403.3</v>
+        <v>1357.8</v>
       </c>
       <c r="E213" t="n">
-        <v>1363</v>
+        <v>1330.1</v>
       </c>
       <c r="F213" t="n">
-        <v>1366.8</v>
+        <v>1340.8</v>
       </c>
       <c r="G213" t="n">
-        <v>1567542</v>
+        <v>345535</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13475,25 +13937,25 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1380</v>
+        <v>1340.8</v>
       </c>
       <c r="D214" t="n">
-        <v>1397.5</v>
+        <v>1387.7</v>
       </c>
       <c r="E214" t="n">
-        <v>1351.6</v>
+        <v>1316</v>
       </c>
       <c r="F214" t="n">
-        <v>1360.6</v>
+        <v>1374.4</v>
       </c>
       <c r="G214" t="n">
-        <v>1098353</v>
+        <v>974660</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13502,25 +13964,25 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1360.6</v>
+        <v>1372.9</v>
       </c>
       <c r="D215" t="n">
-        <v>1428</v>
+        <v>1390</v>
       </c>
       <c r="E215" t="n">
-        <v>1354.5</v>
+        <v>1355.1</v>
       </c>
       <c r="F215" t="n">
-        <v>1421.6</v>
+        <v>1363.5</v>
       </c>
       <c r="G215" t="n">
-        <v>2055261</v>
+        <v>479123</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13529,25 +13991,25 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1428.14</v>
+        <v>1363</v>
       </c>
       <c r="D216" t="n">
-        <v>1451.52</v>
+        <v>1392</v>
       </c>
       <c r="E216" t="n">
-        <v>1417.55</v>
+        <v>1355.1</v>
       </c>
       <c r="F216" t="n">
-        <v>1432.63</v>
+        <v>1380</v>
       </c>
       <c r="G216" t="n">
-        <v>1243415</v>
+        <v>616767</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13556,25 +14018,25 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1432.53</v>
+        <v>1360</v>
       </c>
       <c r="D217" t="n">
-        <v>1458.51</v>
+        <v>1368</v>
       </c>
       <c r="E217" t="n">
-        <v>1403.56</v>
+        <v>1272.1</v>
       </c>
       <c r="F217" t="n">
-        <v>1416.55</v>
+        <v>1288.3</v>
       </c>
       <c r="G217" t="n">
-        <v>1123973</v>
+        <v>1098492</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13583,25 +14045,25 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1412.46</v>
+        <v>1300</v>
       </c>
       <c r="D218" t="n">
-        <v>1432.53</v>
+        <v>1318.5</v>
       </c>
       <c r="E218" t="n">
-        <v>1406.06</v>
+        <v>1257</v>
       </c>
       <c r="F218" t="n">
-        <v>1423.24</v>
+        <v>1316.2</v>
       </c>
       <c r="G218" t="n">
-        <v>509551</v>
+        <v>1172726</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13610,25 +14072,25 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1432.63</v>
+        <v>1317.7</v>
       </c>
       <c r="D219" t="n">
-        <v>1520.44</v>
+        <v>1319.8</v>
       </c>
       <c r="E219" t="n">
-        <v>1426.04</v>
+        <v>1270.5</v>
       </c>
       <c r="F219" t="n">
-        <v>1514.85</v>
+        <v>1306</v>
       </c>
       <c r="G219" t="n">
-        <v>3863757</v>
+        <v>832973</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13637,25 +14099,25 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>1514.85</v>
+        <v>1319.9</v>
       </c>
       <c r="D220" t="n">
-        <v>1541.42</v>
+        <v>1355.4</v>
       </c>
       <c r="E220" t="n">
-        <v>1485.38</v>
+        <v>1308</v>
       </c>
       <c r="F220" t="n">
-        <v>1493.27</v>
+        <v>1343.4</v>
       </c>
       <c r="G220" t="n">
-        <v>1508375</v>
+        <v>1287698</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13664,25 +14126,25 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1493.27</v>
+        <v>1379</v>
       </c>
       <c r="D221" t="n">
-        <v>1512.45</v>
+        <v>1468</v>
       </c>
       <c r="E221" t="n">
-        <v>1463.6</v>
+        <v>1361</v>
       </c>
       <c r="F221" t="n">
-        <v>1471.79</v>
+        <v>1377.8</v>
       </c>
       <c r="G221" t="n">
-        <v>749197</v>
+        <v>9950655</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13691,25 +14153,25 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1480.39</v>
+        <v>1380.5</v>
       </c>
       <c r="D222" t="n">
-        <v>1498.97</v>
+        <v>1403.3</v>
       </c>
       <c r="E222" t="n">
-        <v>1449.52</v>
+        <v>1363</v>
       </c>
       <c r="F222" t="n">
-        <v>1466.2</v>
+        <v>1366.8</v>
       </c>
       <c r="G222" t="n">
-        <v>742118</v>
+        <v>1567542</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13718,25 +14180,25 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1478.49</v>
+        <v>1380</v>
       </c>
       <c r="D223" t="n">
-        <v>1505.16</v>
+        <v>1397.5</v>
       </c>
       <c r="E223" t="n">
-        <v>1450.52</v>
+        <v>1351.6</v>
       </c>
       <c r="F223" t="n">
-        <v>1463.7</v>
+        <v>1360.6</v>
       </c>
       <c r="G223" t="n">
-        <v>811337</v>
+        <v>1098353</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13745,25 +14207,25 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1475.79</v>
+        <v>1360.6</v>
       </c>
       <c r="D224" t="n">
-        <v>1502.06</v>
+        <v>1428</v>
       </c>
       <c r="E224" t="n">
-        <v>1457.01</v>
+        <v>1354.5</v>
       </c>
       <c r="F224" t="n">
-        <v>1466.4</v>
+        <v>1421.6</v>
       </c>
       <c r="G224" t="n">
-        <v>972670</v>
+        <v>2055261</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13772,25 +14234,25 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1489.9</v>
+        <v>1428.14</v>
       </c>
       <c r="D225" t="n">
-        <v>1521</v>
+        <v>1451.52</v>
       </c>
       <c r="E225" t="n">
-        <v>1488.9</v>
+        <v>1417.55</v>
       </c>
       <c r="F225" t="n">
-        <v>1500.1</v>
+        <v>1432.63</v>
       </c>
       <c r="G225" t="n">
-        <v>2323890</v>
+        <v>1243415</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -13799,46 +14261,316 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1507.9</v>
+        <v>1432.53</v>
       </c>
       <c r="D226" t="n">
-        <v>1514.6</v>
+        <v>1458.51</v>
       </c>
       <c r="E226" t="n">
-        <v>1475</v>
+        <v>1403.56</v>
       </c>
       <c r="F226" t="n">
-        <v>1494.8</v>
+        <v>1416.55</v>
       </c>
       <c r="G226" t="n">
-        <v>901426</v>
+        <v>1123973</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1412.46</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1432.53</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1406.06</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1423.24</v>
+      </c>
+      <c r="G227" t="n">
+        <v>509551</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1432.63</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1520.44</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1426.04</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3863757</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1514.85</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1541.42</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1485.38</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1508375</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1493.27</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1512.45</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1463.6</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1471.79</v>
+      </c>
+      <c r="G230" t="n">
+        <v>749197</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1480.39</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1498.97</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1449.52</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1466.2</v>
+      </c>
+      <c r="G231" t="n">
+        <v>742118</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1478.49</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1505.16</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1450.52</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="G232" t="n">
+        <v>811337</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1475.79</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1502.06</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1457.01</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1466.4</v>
+      </c>
+      <c r="G233" t="n">
+        <v>972670</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1489.9</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1488.9</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1500.1</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2323890</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1507.9</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1514.6</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1494.8</v>
+      </c>
+      <c r="G235" t="n">
+        <v>901426</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>SYRMA</t>
         </is>
       </c>
-      <c r="C227" t="n">
+      <c r="C236" t="n">
         <v>1504.8</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D236" t="n">
         <v>1525.8</v>
       </c>
-      <c r="E227" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F227" t="n">
-        <v>1512.5</v>
-      </c>
-      <c r="G227" t="n">
-        <v>247380</v>
+      <c r="E236" t="n">
+        <v>1415.7</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1443.7</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1342162</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SYRMA</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1449</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1430.1</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="G237" t="n">
+        <v>146570</v>
       </c>
     </row>
   </sheetData>
@@ -13852,7 +14584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14097,6 +14829,21 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>risk_off</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/daily_tracker.xlsx
+++ b/reports/daily_tracker.xlsx
@@ -524,7 +524,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generated 10 Sep 2026 08:20</t>
+          <t>Generated 10 Sep 2026 21:03</t>
         </is>
       </c>
     </row>
@@ -613,13 +613,13 @@
         <v>49.4</v>
       </c>
       <c r="F2" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="G2" t="n">
         <v>-4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -8869,20 +8869,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2607</v>
+        <v>2608.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>6.82</v>
+        <v>6.76</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8</v>
+        <v>-0.86</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
@@ -8927,7 +8927,7 @@
         <v>2599.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -24100,10 +24100,10 @@
         <v>2586.1</v>
       </c>
       <c r="F396" t="n">
-        <v>2607</v>
+        <v>2608.5</v>
       </c>
       <c r="G396" t="n">
-        <v>585329</v>
+        <v>759849</v>
       </c>
     </row>
     <row r="397">
